--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H75" headerRowCount="1">
-  <autoFilter ref="A1:H75"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H76" headerRowCount="1">
+  <autoFilter ref="A1:H76"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -1269,7 +1269,9 @@
       <c r="G12" s="8" t="n">
         <v>900</v>
       </c>
-      <c r="H12" s="2" t="n"/>
+      <c r="H12" s="8" t="n">
+        <v>2150</v>
+      </c>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -2264,7 +2266,9 @@
         <v>59.99</v>
       </c>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
+      <c r="G9" s="8" t="n">
+        <v>2150</v>
+      </c>
       <c r="H9" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A9,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A9,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3471,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6333,6 +6337,44 @@
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Compucenter (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G76" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
         <is>
           <t>ver</t>
         </is>
@@ -6414,10 +6456,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId75"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId76"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Historial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H76" headerRowCount="1">
-  <autoFilter ref="A1:H76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H82" headerRowCount="1">
+  <autoFilter ref="A1:H82"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -982,12 +982,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -996,20 +996,18 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>329</v>
+        <v>114.99</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>283.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="H8" s="8" t="n">
-        <v>5664</v>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="H8" s="2" t="n"/>
       <c r="I8" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1019,7 +1017,7 @@
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L8" s="11">
         <f>IF(D8="","",MIN(MAX(Supuestos!$B$5,CEILING((K8*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D8*Supuestos!$B$9))</f>
@@ -1049,12 +1047,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1063,18 +1061,20 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>114.99</v>
+        <v>329</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>283.99</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H9" s="2" t="n"/>
+        <v>4800</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1084,7 +1084,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1311,12 +1311,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1325,18 +1325,18 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>259.78</v>
+        <v>485</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>149.99</v>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="8" t="n">
-        <v>2300</v>
-      </c>
+        <v>399.99</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1346,7 +1346,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L13" s="11">
         <f>IF(D13="","",MIN(MAX(Supuestos!$B$5,CEILING((K13*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D13*Supuestos!$B$9))</f>
@@ -1376,7 +1376,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1390,16 +1390,18 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>138.9</v>
+        <v>259.78</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>135</v>
+        <v>149.99</v>
       </c>
       <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="H14" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1409,7 +1411,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1439,7 +1441,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1452,10 +1454,14 @@
           <t>ver en eBay</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
+      <c r="D15" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F15" s="7" t="n">
-        <v>305</v>
+        <v>135</v>
       </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="2" t="n"/>
@@ -1498,7 +1504,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1511,14 +1517,10 @@
           <t>ver en eBay</t>
         </is>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>144.25</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="7" t="n">
-        <v>122.99</v>
+        <v>305</v>
       </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
@@ -1561,7 +1563,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1575,13 +1577,13 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>150</v>
+        <v>144.25</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>119.95</v>
+        <v>122.99</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1594,7 +1596,7 @@
         <v/>
       </c>
       <c r="K17" s="8" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="L17" s="11">
         <f>IF(D17="","",MIN(MAX(Supuestos!$B$5,CEILING((K17*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D17*Supuestos!$B$9))</f>
@@ -1624,12 +1626,12 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1638,13 +1640,13 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>485</v>
+        <v>150</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>399.99</v>
+        <v>119.95</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
@@ -1657,7 +1659,7 @@
         <v/>
       </c>
       <c r="K18" s="8" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="L18" s="11">
         <f>IF(D18="","",MIN(MAX(Supuestos!$B$5,CEILING((K18*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D18*Supuestos!$B$9))</f>
@@ -1995,7 +1997,9 @@
         <v>454.99</v>
       </c>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
+      <c r="G4" s="8" t="n">
+        <v>6140</v>
+      </c>
       <c r="H4" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A4,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A4,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2051,7 +2055,7 @@
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="8" t="n">
-        <v>5664</v>
+        <v>4760</v>
       </c>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
@@ -2597,7 +2601,9 @@
       <c r="E15" s="7" t="n">
         <v>399.99</v>
       </c>
-      <c r="F15" s="2" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>4500</v>
+      </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A15,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A15,Dólar!$A:$A,0))),"")</f>
@@ -3475,7 +3481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6375,6 +6381,234 @@
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Tienda Supermall (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>6140</v>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (garantía 6 meses)</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Tienda Supermall (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>4760</v>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>ver</t>
         </is>
@@ -6457,10 +6691,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId76"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId82"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H82" headerRowCount="1">
-  <autoFilter ref="A1:H82"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H83" headerRowCount="1">
+  <autoFilter ref="A1:H83"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -3481,7 +3481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6609,6 +6609,44 @@
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>6700</v>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>ver</t>
         </is>
@@ -6697,10 +6735,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId82"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId82"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId83"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H83" headerRowCount="1">
-  <autoFilter ref="A1:H83"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H99" headerRowCount="1">
+  <autoFilter ref="A1:H99"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -785,12 +785,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -799,18 +799,18 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>209.99</v>
+        <v>144.25</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>179.99</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>3550</v>
-      </c>
-      <c r="H5" s="2" t="n"/>
+        <v>122.99</v>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="I5" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="K5" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L5" s="11">
         <f>IF(D5="","",MIN(MAX(Supuestos!$B$5,CEILING((K5*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D5*Supuestos!$B$9))</f>
@@ -850,12 +850,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -864,17 +864,19 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>244.87</v>
+        <v>209.99</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>209.99</v>
-      </c>
-      <c r="G6" s="2" t="n"/>
+        <v>179.99</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>3550</v>
+      </c>
       <c r="H6" s="8" t="n">
-        <v>3950</v>
+        <v>4060</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -885,7 +887,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -915,7 +917,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -929,19 +931,17 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>164.49</v>
+        <v>244.87</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>136.99</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>2700</v>
-      </c>
+        <v>209.99</v>
+      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="8" t="n">
-        <v>2537</v>
+        <v>3950</v>
       </c>
       <c r="I7" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -952,7 +952,7 @@
         <v/>
       </c>
       <c r="K7" s="8" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="L7" s="11">
         <f>IF(D7="","",MIN(MAX(Supuestos!$B$5,CEILING((K7*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D7*Supuestos!$B$9))</f>
@@ -982,12 +982,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -996,18 +996,18 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>114.99</v>
+        <v>150</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H8" s="2" t="n"/>
+        <v>119.95</v>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="8" t="n">
+        <v>2460</v>
+      </c>
       <c r="I8" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1017,7 +1017,7 @@
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="L8" s="11">
         <f>IF(D8="","",MIN(MAX(Supuestos!$B$5,CEILING((K8*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D8*Supuestos!$B$9))</f>
@@ -1047,7 +1047,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>329</v>
+        <v>164.49</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>283.99</v>
+        <v>136.99</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>4800</v>
+        <v>2700</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>4760</v>
+        <v>2520</v>
       </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1084,7 +1084,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1114,12 +1114,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1128,18 +1128,20 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>425</v>
+        <v>114.99</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>10.99</v>
+        <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>399.9</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H10" s="2" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1149,7 +1151,7 @@
         <v/>
       </c>
       <c r="K10" s="8" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="L10" s="11">
         <f>IF(D10="","",MIN(MAX(Supuestos!$B$5,CEILING((K10*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D10*Supuestos!$B$9))</f>
@@ -1179,7 +1181,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1193,17 +1195,19 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>499.99</v>
+        <v>329</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="G11" s="2" t="n"/>
+        <v>283.99</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="H11" s="8" t="n">
-        <v>5580</v>
+        <v>4760</v>
       </c>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1244,7 +1248,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1258,20 +1262,18 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>75</v>
+        <v>425</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>10.99</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>59.99</v>
+        <v>399.9</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>2150</v>
-      </c>
+        <v>6200</v>
+      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1281,7 +1283,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="L12" s="11">
         <f>IF(D12="","",MIN(MAX(Supuestos!$B$5,CEILING((K12*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D12*Supuestos!$B$9))</f>
@@ -1311,12 +1313,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1325,18 +1327,18 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>485</v>
+        <v>499.99</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H13" s="2" t="n"/>
+        <v>454.99</v>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="8" t="n">
+        <v>5580</v>
+      </c>
       <c r="I13" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1346,7 +1348,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L13" s="11">
         <f>IF(D13="","",MIN(MAX(Supuestos!$B$5,CEILING((K13*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D13*Supuestos!$B$9))</f>
@@ -1376,12 +1378,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1390,17 +1392,19 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>259.78</v>
+        <v>75</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>149.99</v>
-      </c>
-      <c r="G14" s="2" t="n"/>
+        <v>59.99</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>900</v>
+      </c>
       <c r="H14" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1411,7 +1415,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1441,12 +1445,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1455,15 +1459,17 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>138.9</v>
+        <v>485</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>135</v>
-      </c>
-      <c r="G15" s="2" t="n"/>
+        <v>399.99</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>4500</v>
+      </c>
       <c r="H15" s="2" t="n"/>
       <c r="I15" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1474,7 +1480,7 @@
         <v/>
       </c>
       <c r="K15" s="8" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="L15" s="11">
         <f>IF(D15="","",MIN(MAX(Supuestos!$B$5,CEILING((K15*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D15*Supuestos!$B$9))</f>
@@ -1504,7 +1510,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1517,13 +1523,19 @@
           <t>ver en eBay</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="D16" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F16" s="7" t="n">
-        <v>305</v>
+        <v>149.99</v>
       </c>
       <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="n"/>
+      <c r="H16" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="I16" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1533,7 +1545,7 @@
         <v/>
       </c>
       <c r="K16" s="8" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="L16" s="11">
         <f>IF(D16="","",MIN(MAX(Supuestos!$B$5,CEILING((K16*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D16*Supuestos!$B$9))</f>
@@ -1563,7 +1575,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1577,13 +1589,13 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>144.25</v>
+        <v>138.9</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>122.99</v>
+        <v>135</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1626,7 +1638,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1639,14 +1651,10 @@
           <t>ver en eBay</t>
         </is>
       </c>
-      <c r="D18" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>0</v>
-      </c>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="7" t="n">
-        <v>119.95</v>
+        <v>305</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
@@ -1659,7 +1667,7 @@
         <v/>
       </c>
       <c r="K18" s="8" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="L18" s="11">
         <f>IF(D18="","",MIN(MAX(Supuestos!$B$5,CEILING((K18*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D18*Supuestos!$B$9))</f>
@@ -1887,7 +1895,9 @@
         <v>179.99</v>
       </c>
       <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
+      <c r="G2" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H2" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A2,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A2,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -1942,7 +1952,9 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2162,7 +2174,9 @@
         <v>122.99</v>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H7" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2328,7 +2342,7 @@
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="8" t="n">
-        <v>2537</v>
+        <v>2520</v>
       </c>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
@@ -2439,7 +2453,9 @@
         <v>119.95</v>
       </c>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="8" t="n">
+        <v>2460</v>
+      </c>
       <c r="H12" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A12,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A12,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2492,7 +2508,9 @@
         <v>209.99</v>
       </c>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
+      <c r="G13" s="8" t="n">
+        <v>4290</v>
+      </c>
       <c r="H13" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A13,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A13,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3481,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6647,6 +6665,614 @@
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>4290</v>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>5660</v>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>5860</v>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>1860</v>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>2152</v>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>4560</v>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
         <is>
           <t>ver</t>
         </is>
@@ -6736,10 +7362,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId81"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId83"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId99"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H99" headerRowCount="1">
-  <autoFilter ref="A1:H99"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H102" headerRowCount="1">
+  <autoFilter ref="A1:H102"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -3499,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7273,6 +7273,120 @@
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
         <is>
           <t>ver</t>
         </is>
@@ -7378,10 +7492,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId99"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId102"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -785,12 +785,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>144.25</v>
+        <v>209.99</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>122.99</v>
+        <v>179.99</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
-        <v>2860</v>
+        <v>4060</v>
       </c>
       <c r="I5" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="K5" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L5" s="11">
         <f>IF(D5="","",MIN(MAX(Supuestos!$B$5,CEILING((K5*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D5*Supuestos!$B$9))</f>
@@ -850,12 +850,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -864,19 +864,17 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>209.99</v>
+        <v>144.25</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>179.99</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>3550</v>
-      </c>
+        <v>122.99</v>
+      </c>
+      <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
-        <v>4060</v>
+        <v>2860</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -887,7 +885,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -1069,9 +1067,7 @@
       <c r="F9" s="7" t="n">
         <v>136.99</v>
       </c>
-      <c r="G9" s="8" t="n">
-        <v>2700</v>
-      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="8" t="n">
         <v>2520</v>
       </c>
@@ -2670,9 +2666,7 @@
       </c>
       <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="n"/>
-      <c r="F16" s="8" t="n">
-        <v>3550</v>
-      </c>
+      <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A16,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A16,Dólar!$A:$A,0))),"")</f>
@@ -2682,11 +2676,7 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A16,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>ver anuncio</t>
-        </is>
-      </c>
+      <c r="J16" s="2" t="n"/>
       <c r="K16" s="5" t="n"/>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2970,9 +2960,7 @@
       </c>
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
-      <c r="F22" s="8" t="n">
-        <v>2700</v>
-      </c>
+      <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A22,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A22,Dólar!$A:$A,0))),"")</f>
@@ -2982,11 +2970,7 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A22,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>ver anuncio</t>
-        </is>
-      </c>
+      <c r="J22" s="2" t="n"/>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
@@ -3190,19 +3174,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId24"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5901,7 +5883,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>no indicado (anuncio dice i5 14400; confirmar si es F)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -6243,7 +6225,7 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>no indicado (SanDisk 2TB; no dice si es NVMe o SATA)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O25" headerRowCount="1">
-  <autoFilter ref="A1:O25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O39" headerRowCount="1">
+  <autoFilter ref="A1:O39"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H102" headerRowCount="1">
-  <autoFilter ref="A1:H102"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H128" headerRowCount="1">
+  <autoFilter ref="A1:H128"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -633,7 +633,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>¿Qué conviene traer? · 12/10/2026</t>
+          <t>¿Qué conviene traer? · 13/10/2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -785,12 +785,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>209.99</v>
+        <v>143.24</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>179.99</v>
+        <v>122.99</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
-        <v>4060</v>
+        <v>2860</v>
       </c>
       <c r="I5" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="K5" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L5" s="11">
         <f>IF(D5="","",MIN(MAX(Supuestos!$B$5,CEILING((K5*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D5*Supuestos!$B$9))</f>
@@ -850,12 +850,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -864,17 +864,17 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>144.25</v>
+        <v>209.99</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>122.99</v>
+        <v>170</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
-        <v>2860</v>
+        <v>4060</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -885,7 +885,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="8" t="n">
@@ -1065,7 +1065,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="8" t="n">
@@ -1374,7 +1374,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1388,20 +1388,18 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>75</v>
+        <v>485</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>59.99</v>
+        <v>383.99</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>2150</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="H14" s="2" t="n"/>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1411,7 +1409,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1441,7 +1439,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1455,18 +1453,20 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>485</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>399.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H15" s="2" t="n"/>
+        <v>900</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>2150</v>
+      </c>
       <c r="I15" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="K15" s="8" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="L15" s="11">
         <f>IF(D15="","",MIN(MAX(Supuestos!$B$5,CEILING((K15*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D15*Supuestos!$B$9))</f>
@@ -1650,7 +1650,7 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1888,12 +1888,10 @@
         <v>209.99</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>179.99</v>
+        <v>170</v>
       </c>
       <c r="F2" s="2" t="n"/>
-      <c r="G2" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A2,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A2,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -1908,7 +1906,7 @@
         </is>
       </c>
       <c r="K2" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L2" s="16">
         <f>IF(OR($K2="",D2=""),"",IF(COUNTIFS($B:$B,$B2,$A:$A,$K2,D:D,"&gt;=0")=0,"",D2-SUMIFS(D:D,$B:$B,$B2,$A:$A,$K2)))</f>
@@ -1929,7 +1927,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1948,9 +1946,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -1965,7 +1961,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L3" s="16">
         <f>IF(OR($K3="",D3=""),"",IF(COUNTIFS($B:$B,$B3,$A:$A,$K3,D:D,"&gt;=0")=0,"",D3-SUMIFS(D:D,$B:$B,$B3,$A:$A,$K3)))</f>
@@ -1986,7 +1982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -2005,9 +2001,7 @@
         <v>454.99</v>
       </c>
       <c r="F4" s="2" t="n"/>
-      <c r="G4" s="8" t="n">
-        <v>6140</v>
-      </c>
+      <c r="G4" s="2" t="n"/>
       <c r="H4" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A4,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A4,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2022,7 +2016,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L4" s="16">
         <f>IF(OR($K4="",D4=""),"",IF(COUNTIFS($B:$B,$B4,$A:$A,$K4,D:D,"&gt;=0")=0,"",D4-SUMIFS(D:D,$B:$B,$B4,$A:$A,$K4)))</f>
@@ -2043,7 +2037,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -2062,9 +2056,7 @@
         <v>283.99</v>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="8" t="n">
-        <v>4760</v>
-      </c>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2079,7 +2071,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L5" s="16">
         <f>IF(OR($K5="",D5=""),"",IF(COUNTIFS($B:$B,$B5,$A:$A,$K5,D:D,"&gt;=0")=0,"",D5-SUMIFS(D:D,$B:$B,$B5,$A:$A,$K5)))</f>
@@ -2100,7 +2092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2114,7 +2106,7 @@
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
@@ -2131,7 +2123,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K6" s="5" t="n"/>
+      <c r="K6" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
         <v/>
@@ -2151,7 +2145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2164,15 +2158,13 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>144.25</v>
+        <v>143.24</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>122.99</v>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="8" t="n">
-        <v>2860</v>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2187,7 +2179,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L7" s="16">
         <f>IF(OR($K7="",D7=""),"",IF(COUNTIFS($B:$B,$B7,$A:$A,$K7,D:D,"&gt;=0")=0,"",D7-SUMIFS(D:D,$B:$B,$B7,$A:$A,$K7)))</f>
@@ -2208,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -2241,7 +2233,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n"/>
+      <c r="K8" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L8" s="16">
         <f>IF(OR($K8="",D8=""),"",IF(COUNTIFS($B:$B,$B8,$A:$A,$K8,D:D,"&gt;=0")=0,"",D8-SUMIFS(D:D,$B:$B,$B8,$A:$A,$K8)))</f>
         <v/>
@@ -2261,7 +2255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2274,15 +2268,13 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>75</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>59.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="8" t="n">
-        <v>2150</v>
-      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A9,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A9,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2297,7 +2289,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L9" s="16">
         <f>IF(OR($K9="",D9=""),"",IF(COUNTIFS($B:$B,$B9,$A:$A,$K9,D:D,"&gt;=0")=0,"",D9-SUMIFS(D:D,$B:$B,$B9,$A:$A,$K9)))</f>
@@ -2318,7 +2310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2334,12 +2326,10 @@
         <v>164.49</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="8" t="n">
-        <v>2520</v>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2354,7 +2344,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L10" s="16">
         <f>IF(OR($K10="",D10=""),"",IF(COUNTIFS($B:$B,$B10,$A:$A,$K10,D:D,"&gt;=0")=0,"",D10-SUMIFS(D:D,$B:$B,$B10,$A:$A,$K10)))</f>
@@ -2375,7 +2365,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2387,9 +2377,7 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>259.78</v>
-      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="7" t="n">
         <v>149.99</v>
       </c>
@@ -2409,7 +2397,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L11" s="16">
         <f>IF(OR($K11="",D11=""),"",IF(COUNTIFS($B:$B,$B11,$A:$A,$K11,D:D,"&gt;=0")=0,"",D11-SUMIFS(D:D,$B:$B,$B11,$A:$A,$K11)))</f>
@@ -2430,7 +2418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2446,12 +2434,10 @@
         <v>150</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A12,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A12,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2465,7 +2451,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K12" s="5" t="n"/>
+      <c r="K12" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L12" s="16">
         <f>IF(OR($K12="",D12=""),"",IF(COUNTIFS($B:$B,$B12,$A:$A,$K12,D:D,"&gt;=0")=0,"",D12-SUMIFS(D:D,$B:$B,$B12,$A:$A,$K12)))</f>
         <v/>
@@ -2485,7 +2473,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2498,15 +2486,13 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>209.99</v>
       </c>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G13" s="2" t="n"/>
       <c r="H13" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A13,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A13,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2521,7 +2507,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L13" s="16">
         <f>IF(OR($K13="",D13=""),"",IF(COUNTIFS($B:$B,$B13,$A:$A,$K13,D:D,"&gt;=0")=0,"",D13-SUMIFS(D:D,$B:$B,$B13,$A:$A,$K13)))</f>
@@ -2542,7 +2528,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2576,7 +2562,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L14" s="16">
         <f>IF(OR($K14="",D14=""),"",IF(COUNTIFS($B:$B,$B14,$A:$A,$K14,D:D,"&gt;=0")=0,"",D14-SUMIFS(D:D,$B:$B,$B14,$A:$A,$K14)))</f>
@@ -2597,7 +2583,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -2613,11 +2599,9 @@
         <v>493</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>4500</v>
-      </c>
+        <v>383.99</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A15,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A15,Dólar!$A:$A,0))),"")</f>
@@ -2632,7 +2616,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K15" s="5" t="n"/>
+      <c r="K15" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L15" s="16">
         <f>IF(OR($K15="",D15=""),"",IF(COUNTIFS($B:$B,$B15,$A:$A,$K15,D:D,"&gt;=0")=0,"",D15-SUMIFS(D:D,$B:$B,$B15,$A:$A,$K15)))</f>
         <v/>
@@ -2652,7 +2638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -2664,10 +2650,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
+      <c r="D16" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>179.99</v>
+      </c>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
+      <c r="G16" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H16" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A16,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A16,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2676,8 +2668,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A16,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="5" t="n"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K16" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
         <v/>
@@ -2697,7 +2695,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -2709,12 +2707,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G17" s="2" t="n"/>
+      <c r="D17" s="7" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H17" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2728,7 +2730,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K17" s="5" t="n"/>
+      <c r="K17" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L17" s="16">
         <f>IF(OR($K17="",D17=""),"",IF(COUNTIFS($B:$B,$B17,$A:$A,$K17,D:D,"&gt;=0")=0,"",D17-SUMIFS(D:D,$B:$B,$B17,$A:$A,$K17)))</f>
         <v/>
@@ -2748,7 +2752,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -2760,11 +2764,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="D18" s="7" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>454.99</v>
+      </c>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="8" t="n">
-        <v>5580</v>
+        <v>6140</v>
       </c>
       <c r="H18" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A18,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A18,Dólar!$A:$A,0))),"")</f>
@@ -2779,7 +2787,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K18" s="5" t="n"/>
+      <c r="K18" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L18" s="16">
         <f>IF(OR($K18="",D18=""),"",IF(COUNTIFS($B:$B,$B18,$A:$A,$K18,D:D,"&gt;=0")=0,"",D18-SUMIFS(D:D,$B:$B,$B18,$A:$A,$K18)))</f>
         <v/>
@@ -2799,7 +2809,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2811,12 +2821,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G19" s="2" t="n"/>
+      <c r="D19" s="7" t="n">
+        <v>329</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="H19" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2830,7 +2844,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K19" s="5" t="n"/>
+      <c r="K19" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L19" s="16">
         <f>IF(OR($K19="",D19=""),"",IF(COUNTIFS($B:$B,$B19,$A:$A,$K19,D:D,"&gt;=0")=0,"",D19-SUMIFS(D:D,$B:$B,$B19,$A:$A,$K19)))</f>
         <v/>
@@ -2850,11 +2866,11 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2863,7 +2879,9 @@
         </is>
       </c>
       <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
+      <c r="E20" s="7" t="n">
+        <v>305</v>
+      </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="9">
@@ -2874,7 +2892,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A20,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="16">
         <f>IF(OR($K20="",D20=""),"",IF(COUNTIFS($B:$B,$B20,$A:$A,$K20,D:D,"&gt;=0")=0,"",D20-SUMIFS(D:D,$B:$B,$B20,$A:$A,$K20)))</f>
@@ -2895,24 +2917,28 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="G21" s="2" t="n"/>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H21" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2926,7 +2952,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K21" s="5" t="n"/>
+      <c r="K21" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L21" s="16">
         <f>IF(OR($K21="",D21=""),"",IF(COUNTIFS($B:$B,$B21,$A:$A,$K21,D:D,"&gt;=0")=0,"",D21-SUMIFS(D:D,$B:$B,$B21,$A:$A,$K21)))</f>
         <v/>
@@ -2946,11 +2974,11 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2958,8 +2986,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
+      <c r="D22" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="9">
@@ -2970,7 +3002,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A22,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J22" s="2" t="n"/>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
@@ -2991,23 +3027,27 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>59.99</v>
+      </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="H23" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A23,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A23,Dólar!$A:$A,0))),"")</f>
@@ -3022,7 +3062,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K23" s="5" t="n"/>
+      <c r="K23" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L23" s="16">
         <f>IF(OR($K23="",D23=""),"",IF(COUNTIFS($B:$B,$B23,$A:$A,$K23,D:D,"&gt;=0")=0,"",D23-SUMIFS(D:D,$B:$B,$B23,$A:$A,$K23)))</f>
         <v/>
@@ -3042,11 +3084,11 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -3054,11 +3096,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
+      <c r="D24" s="7" t="n">
+        <v>164.49</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>136.99</v>
+      </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="8" t="n">
-        <v>3950</v>
+        <v>2520</v>
       </c>
       <c r="H24" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))),"")</f>
@@ -3073,7 +3119,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K24" s="5" t="n"/>
+      <c r="K24" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L24" s="16">
         <f>IF(OR($K24="",D24=""),"",IF(COUNTIFS($B:$B,$B24,$A:$A,$K24,D:D,"&gt;=0")=0,"",D24-SUMIFS(D:D,$B:$B,$B24,$A:$A,$K24)))</f>
         <v/>
@@ -3093,23 +3141,25 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="8" t="n">
-        <v>6200</v>
-      </c>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
       <c r="H25" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A25,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A25,Dólar!$A:$A,0))),"")</f>
@@ -3124,7 +3174,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K25" s="5" t="n"/>
+      <c r="K25" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L25" s="16">
         <f>IF(OR($K25="",D25=""),"",IF(COUNTIFS($B:$B,$B25,$A:$A,$K25,D:D,"&gt;=0")=0,"",D25-SUMIFS(D:D,$B:$B,$B25,$A:$A,$K25)))</f>
         <v/>
@@ -3142,8 +3194,722 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="F26" s="2" t="n"/>
+      <c r="G26" s="8" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H26" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A26,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A26,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I26" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A26,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="16">
+        <f>IF(OR($K26="",D26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,D:D,"&gt;=0")=0,"",D26-SUMIFS(D:D,$B:$B,$B26,$A:$A,$K26)))</f>
+        <v/>
+      </c>
+      <c r="M26" s="16">
+        <f>IF(OR($K26="",E26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,E:E,"&gt;=0")=0,"",E26-SUMIFS(E:E,$B:$B,$B26,$A:$A,$K26)))</f>
+        <v/>
+      </c>
+      <c r="N26" s="16">
+        <f>IF(OR($K26="",F26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,F:F,"&gt;=0")=0,"",F26-SUMIFS(F:F,$B:$B,$B26,$A:$A,$K26)))</f>
+        <v/>
+      </c>
+      <c r="O26" s="16">
+        <f>IF(OR($K26="",G26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,G:G,"&gt;=0")=0,"",G26-SUMIFS(G:G,$B:$B,$B26,$A:$A,$K26)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H27" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A27,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A27,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I27" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A27,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K27" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L27" s="16">
+        <f>IF(OR($K27="",D27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,D:D,"&gt;=0")=0,"",D27-SUMIFS(D:D,$B:$B,$B27,$A:$A,$K27)))</f>
+        <v/>
+      </c>
+      <c r="M27" s="16">
+        <f>IF(OR($K27="",E27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,E:E,"&gt;=0")=0,"",E27-SUMIFS(E:E,$B:$B,$B27,$A:$A,$K27)))</f>
+        <v/>
+      </c>
+      <c r="N27" s="16">
+        <f>IF(OR($K27="",F27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,F:F,"&gt;=0")=0,"",F27-SUMIFS(F:F,$B:$B,$B27,$A:$A,$K27)))</f>
+        <v/>
+      </c>
+      <c r="O27" s="16">
+        <f>IF(OR($K27="",G27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,G:G,"&gt;=0")=0,"",G27-SUMIFS(G:G,$B:$B,$B27,$A:$A,$K27)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A28,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A28,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I28" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A28,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K28" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L28" s="16">
+        <f>IF(OR($K28="",D28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,D:D,"&gt;=0")=0,"",D28-SUMIFS(D:D,$B:$B,$B28,$A:$A,$K28)))</f>
+        <v/>
+      </c>
+      <c r="M28" s="16">
+        <f>IF(OR($K28="",E28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,E:E,"&gt;=0")=0,"",E28-SUMIFS(E:E,$B:$B,$B28,$A:$A,$K28)))</f>
+        <v/>
+      </c>
+      <c r="N28" s="16">
+        <f>IF(OR($K28="",F28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,F:F,"&gt;=0")=0,"",F28-SUMIFS(F:F,$B:$B,$B28,$A:$A,$K28)))</f>
+        <v/>
+      </c>
+      <c r="O28" s="16">
+        <f>IF(OR($K28="",G28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,G:G,"&gt;=0")=0,"",G28-SUMIFS(G:G,$B:$B,$B28,$A:$A,$K28)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A29,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A29,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I29" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A29,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="16">
+        <f>IF(OR($K29="",D29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,D:D,"&gt;=0")=0,"",D29-SUMIFS(D:D,$B:$B,$B29,$A:$A,$K29)))</f>
+        <v/>
+      </c>
+      <c r="M29" s="16">
+        <f>IF(OR($K29="",E29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,E:E,"&gt;=0")=0,"",E29-SUMIFS(E:E,$B:$B,$B29,$A:$A,$K29)))</f>
+        <v/>
+      </c>
+      <c r="N29" s="16">
+        <f>IF(OR($K29="",F29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,F:F,"&gt;=0")=0,"",F29-SUMIFS(F:F,$B:$B,$B29,$A:$A,$K29)))</f>
+        <v/>
+      </c>
+      <c r="O29" s="16">
+        <f>IF(OR($K29="",G29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,G:G,"&gt;=0")=0,"",G29-SUMIFS(G:G,$B:$B,$B29,$A:$A,$K29)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A30,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A30,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I30" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A30,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="16">
+        <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
+        <v/>
+      </c>
+      <c r="M30" s="16">
+        <f>IF(OR($K30="",E30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,E:E,"&gt;=0")=0,"",E30-SUMIFS(E:E,$B:$B,$B30,$A:$A,$K30)))</f>
+        <v/>
+      </c>
+      <c r="N30" s="16">
+        <f>IF(OR($K30="",F30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,F:F,"&gt;=0")=0,"",F30-SUMIFS(F:F,$B:$B,$B30,$A:$A,$K30)))</f>
+        <v/>
+      </c>
+      <c r="O30" s="16">
+        <f>IF(OR($K30="",G30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,G:G,"&gt;=0")=0,"",G30-SUMIFS(G:G,$B:$B,$B30,$A:$A,$K30)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I31" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A31,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="16">
+        <f>IF(OR($K31="",D31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,D:D,"&gt;=0")=0,"",D31-SUMIFS(D:D,$B:$B,$B31,$A:$A,$K31)))</f>
+        <v/>
+      </c>
+      <c r="M31" s="16">
+        <f>IF(OR($K31="",E31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,E:E,"&gt;=0")=0,"",E31-SUMIFS(E:E,$B:$B,$B31,$A:$A,$K31)))</f>
+        <v/>
+      </c>
+      <c r="N31" s="16">
+        <f>IF(OR($K31="",F31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,F:F,"&gt;=0")=0,"",F31-SUMIFS(F:F,$B:$B,$B31,$A:$A,$K31)))</f>
+        <v/>
+      </c>
+      <c r="O31" s="16">
+        <f>IF(OR($K31="",G31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,G:G,"&gt;=0")=0,"",G31-SUMIFS(G:G,$B:$B,$B31,$A:$A,$K31)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="H32" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A32,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A32,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A32,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="16">
+        <f>IF(OR($K32="",D32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,D:D,"&gt;=0")=0,"",D32-SUMIFS(D:D,$B:$B,$B32,$A:$A,$K32)))</f>
+        <v/>
+      </c>
+      <c r="M32" s="16">
+        <f>IF(OR($K32="",E32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,E:E,"&gt;=0")=0,"",E32-SUMIFS(E:E,$B:$B,$B32,$A:$A,$K32)))</f>
+        <v/>
+      </c>
+      <c r="N32" s="16">
+        <f>IF(OR($K32="",F32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,F:F,"&gt;=0")=0,"",F32-SUMIFS(F:F,$B:$B,$B32,$A:$A,$K32)))</f>
+        <v/>
+      </c>
+      <c r="O32" s="16">
+        <f>IF(OR($K32="",G32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,G:G,"&gt;=0")=0,"",G32-SUMIFS(G:G,$B:$B,$B32,$A:$A,$K32)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A33,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="16">
+        <f>IF(OR($K33="",D33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,D:D,"&gt;=0")=0,"",D33-SUMIFS(D:D,$B:$B,$B33,$A:$A,$K33)))</f>
+        <v/>
+      </c>
+      <c r="M33" s="16">
+        <f>IF(OR($K33="",E33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,E:E,"&gt;=0")=0,"",E33-SUMIFS(E:E,$B:$B,$B33,$A:$A,$K33)))</f>
+        <v/>
+      </c>
+      <c r="N33" s="16">
+        <f>IF(OR($K33="",F33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,F:F,"&gt;=0")=0,"",F33-SUMIFS(F:F,$B:$B,$B33,$A:$A,$K33)))</f>
+        <v/>
+      </c>
+      <c r="O33" s="16">
+        <f>IF(OR($K33="",G33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,G:G,"&gt;=0")=0,"",G33-SUMIFS(G:G,$B:$B,$B33,$A:$A,$K33)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A34,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A34,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A34,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="16">
+        <f>IF(OR($K34="",D34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,D:D,"&gt;=0")=0,"",D34-SUMIFS(D:D,$B:$B,$B34,$A:$A,$K34)))</f>
+        <v/>
+      </c>
+      <c r="M34" s="16">
+        <f>IF(OR($K34="",E34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,E:E,"&gt;=0")=0,"",E34-SUMIFS(E:E,$B:$B,$B34,$A:$A,$K34)))</f>
+        <v/>
+      </c>
+      <c r="N34" s="16">
+        <f>IF(OR($K34="",F34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,F:F,"&gt;=0")=0,"",F34-SUMIFS(F:F,$B:$B,$B34,$A:$A,$K34)))</f>
+        <v/>
+      </c>
+      <c r="O34" s="16">
+        <f>IF(OR($K34="",G34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,G:G,"&gt;=0")=0,"",G34-SUMIFS(G:G,$B:$B,$B34,$A:$A,$K34)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A35,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="16">
+        <f>IF(OR($K35="",D35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,D:D,"&gt;=0")=0,"",D35-SUMIFS(D:D,$B:$B,$B35,$A:$A,$K35)))</f>
+        <v/>
+      </c>
+      <c r="M35" s="16">
+        <f>IF(OR($K35="",E35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,E:E,"&gt;=0")=0,"",E35-SUMIFS(E:E,$B:$B,$B35,$A:$A,$K35)))</f>
+        <v/>
+      </c>
+      <c r="N35" s="16">
+        <f>IF(OR($K35="",F35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,F:F,"&gt;=0")=0,"",F35-SUMIFS(F:F,$B:$B,$B35,$A:$A,$K35)))</f>
+        <v/>
+      </c>
+      <c r="O35" s="16">
+        <f>IF(OR($K35="",G35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,G:G,"&gt;=0")=0,"",G35-SUMIFS(G:G,$B:$B,$B35,$A:$A,$K35)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A36,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A36,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A36,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="16">
+        <f>IF(OR($K36="",D36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,D:D,"&gt;=0")=0,"",D36-SUMIFS(D:D,$B:$B,$B36,$A:$A,$K36)))</f>
+        <v/>
+      </c>
+      <c r="M36" s="16">
+        <f>IF(OR($K36="",E36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,E:E,"&gt;=0")=0,"",E36-SUMIFS(E:E,$B:$B,$B36,$A:$A,$K36)))</f>
+        <v/>
+      </c>
+      <c r="N36" s="16">
+        <f>IF(OR($K36="",F36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,F:F,"&gt;=0")=0,"",F36-SUMIFS(F:F,$B:$B,$B36,$A:$A,$K36)))</f>
+        <v/>
+      </c>
+      <c r="O36" s="16">
+        <f>IF(OR($K36="",G36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,G:G,"&gt;=0")=0,"",G36-SUMIFS(G:G,$B:$B,$B36,$A:$A,$K36)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H37" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A37,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A37,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A37,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="16">
+        <f>IF(OR($K37="",D37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,D:D,"&gt;=0")=0,"",D37-SUMIFS(D:D,$B:$B,$B37,$A:$A,$K37)))</f>
+        <v/>
+      </c>
+      <c r="M37" s="16">
+        <f>IF(OR($K37="",E37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,E:E,"&gt;=0")=0,"",E37-SUMIFS(E:E,$B:$B,$B37,$A:$A,$K37)))</f>
+        <v/>
+      </c>
+      <c r="N37" s="16">
+        <f>IF(OR($K37="",F37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,F:F,"&gt;=0")=0,"",F37-SUMIFS(F:F,$B:$B,$B37,$A:$A,$K37)))</f>
+        <v/>
+      </c>
+      <c r="O37" s="16">
+        <f>IF(OR($K37="",G37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,G:G,"&gt;=0")=0,"",G37-SUMIFS(G:G,$B:$B,$B37,$A:$A,$K37)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H38" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A38,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="16">
+        <f>IF(OR($K38="",D38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,D:D,"&gt;=0")=0,"",D38-SUMIFS(D:D,$B:$B,$B38,$A:$A,$K38)))</f>
+        <v/>
+      </c>
+      <c r="M38" s="16">
+        <f>IF(OR($K38="",E38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,E:E,"&gt;=0")=0,"",E38-SUMIFS(E:E,$B:$B,$B38,$A:$A,$K38)))</f>
+        <v/>
+      </c>
+      <c r="N38" s="16">
+        <f>IF(OR($K38="",F38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,F:F,"&gt;=0")=0,"",F38-SUMIFS(F:F,$B:$B,$B38,$A:$A,$K38)))</f>
+        <v/>
+      </c>
+      <c r="O38" s="16">
+        <f>IF(OR($K38="",G38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,G:G,"&gt;=0")=0,"",G38-SUMIFS(G:G,$B:$B,$B38,$A:$A,$K38)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A39,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A39,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A39,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="16">
+        <f>IF(OR($K39="",D39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,D:D,"&gt;=0")=0,"",D39-SUMIFS(D:D,$B:$B,$B39,$A:$A,$K39)))</f>
+        <v/>
+      </c>
+      <c r="M39" s="16">
+        <f>IF(OR($K39="",E39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,E:E,"&gt;=0")=0,"",E39-SUMIFS(E:E,$B:$B,$B39,$A:$A,$K39)))</f>
+        <v/>
+      </c>
+      <c r="N39" s="16">
+        <f>IF(OR($K39="",F39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,F:F,"&gt;=0")=0,"",F39-SUMIFS(F:F,$B:$B,$B39,$A:$A,$K39)))</f>
+        <v/>
+      </c>
+      <c r="O39" s="16">
+        <f>IF(OR($K39="",G39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,G:G,"&gt;=0")=0,"",G39-SUMIFS(G:G,$B:$B,$B39,$A:$A,$K39)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M25">
+  <conditionalFormatting sqref="L2:M39">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -3151,7 +3917,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O25">
+  <conditionalFormatting sqref="N2:O39">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3174,17 +3940,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId36"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3349,7 +4129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3470,6 +4250,32 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B5" s="19" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="E5" s="10">
+        <f>IF(COUNT(C5:D5)=2,AVERAGE(C5:D5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>11.87</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>BCB oficial 11.73; paralelo dolarbolivia.net 13/10 (compra 11.85 / venta 11.88); usado = promedio del paralelo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3481,7 +4287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5552,34 +6358,34 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
-        <v>5580</v>
+        <v>138.9</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; (New) AMD Ryzen 5 5600 Vermeer Zen3 6-Core 12-Thread AM4 CPU</t>
         </is>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -5590,34 +6396,34 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E56" s="11" t="n">
-        <v>2300</v>
+        <v>143.24</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor silaxon 99.6%; AMD Ryzen 5 7600 3.80GHz 6 Core 12 Thread AM5 100-000001015</t>
         </is>
       </c>
       <c r="H56" s="6" t="inlineStr">
@@ -5628,34 +6434,34 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
-        <v>3950</v>
+        <v>329</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor aaawavecom 99.8%; AMD Ryzen 7 7800X3D Processor Zen 4 8-Core 4.2GHz AM5 CPU (N</t>
         </is>
       </c>
       <c r="H57" s="6" t="inlineStr">
@@ -5666,34 +6472,34 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E58" s="11" t="n">
-        <v>4800</v>
+        <v>499.99</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay API; vendedor saguarowholesalesupply 100.0%; AMD Ryzen 9 9950X Desktop Processor AM5 New Sealed; envío no indicado</t>
         </is>
       </c>
       <c r="H58" s="6" t="inlineStr">
@@ -5704,34 +6510,34 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>5190</v>
+        <v>150</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor algonz1137 100.0%; INTEL CPU Core i5-12400F / 6/12 / 2.5GHz / 6xxChipset / BX80; envío no indicado</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -5742,34 +6548,34 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E60" s="11" t="n">
-        <v>5390</v>
+        <v>164.49</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t xml:space="preserve">eBay API; vendedor newegg 99.6%; Intel Core i5-14400F - Core i5 14th Gen Raptor Lake 10-Core </t>
         </is>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -5780,34 +6586,34 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>2000</v>
+        <v>234.99</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor good_neighbor_mercantile 99.4%; Intel Core Ultra 7 265K CPU Desktop Processor LGA 1851 20-Co</t>
         </is>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -5818,34 +6624,34 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E62" s="11" t="n">
-        <v>2650</v>
+        <v>493</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t xml:space="preserve">eBay API; vendedor blessshoppingshangrila 100.0%; New Corsair VENGEANCE 32GB (2x16GB) Memory DDR5-5600MHz RAM </t>
         </is>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -5856,34 +6662,34 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>2700</v>
+        <v>435.99</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>eBay API; vendedor wojiapanpan_4 100.0%; Corsair Vengeance RGB RS 32GB 2x16GB DDR5 6000 CL38 AMD EXPO</t>
         </is>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -5894,34 +6700,34 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E64" s="11" t="n">
-        <v>6200</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t>eBay API; vendedor klolot3 100.0%; TeamGroup Vulcan Z 16GB (2x8GB) DDR4 3200 Desktop Gaming RAM; envío no indicado</t>
         </is>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -5932,34 +6738,34 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>540</v>
+        <v>114.99</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>eBay API; vendedor gadgetworld03 99.0%; Derlar DN-850Q 1TB M.2 NVME PCIe 4.0 SSD - New</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -5970,34 +6776,34 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E66" s="11" t="n">
-        <v>900</v>
+        <v>209.99</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>eBay API; vendedor ram_technologies 100.0%; RAM Tech 2TB NVMe SSD Gen4 M.2 2280 | 5000MB/s Read 4500MB/s</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -6008,34 +6814,34 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>1500</v>
+        <v>135</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>eBay API; vendedor btlsln 100.0%; AMD Ryzen 5 5600 Desktop Processor (6 Cores, Socket AM4); envío no indicado</t>
         </is>
       </c>
       <c r="H67" s="6" t="inlineStr">
@@ -6046,34 +6852,34 @@
     </row>
     <row r="68">
       <c r="A68" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E68" s="11" t="n">
-        <v>1500</v>
+        <v>299.99</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>eBay API; vendedor paymore_fontana 99.3%; AMD Ryzen 7 5700X3D 3.00GHz 8 Core 100-000001503 16 Thread A</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
@@ -6084,34 +6890,34 @@
     </row>
     <row r="69">
       <c r="A69" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
-        <v>1850</v>
+        <v>122.99</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>eBay API; vendedor paymore_cumberland 98.6%; AMD Ryzen 5 7600 3.80GHz 6 Core 100-000001015 12 Thread AM5</t>
         </is>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -6122,34 +6928,34 @@
     </row>
     <row r="70">
       <c r="A70" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E70" s="11" t="n">
-        <v>2000</v>
+        <v>283.99</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>eBay API; vendedor paymore_pooler 99.7%; AMD Ryzen 7 7800X3D 4.20GHz 8 Core 100-000000910 16 Thread A</t>
         </is>
       </c>
       <c r="H70" s="6" t="inlineStr">
@@ -6160,34 +6966,34 @@
     </row>
     <row r="71">
       <c r="A71" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
-        <v>1800</v>
+        <v>454.99</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>eBay API; vendedor goodios_direct 99.6%; **  AMD Ryzen 9 9950X Processor - USED  **</t>
         </is>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -6198,34 +7004,34 @@
     </row>
     <row r="72">
       <c r="A72" s="15" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E72" s="11" t="n">
-        <v>3550</v>
+        <v>99</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>eBay API; vendedor sale_of_the_day 100.0%; Intel Core i5-12400F; envío no indicado</t>
         </is>
       </c>
       <c r="H72" s="6" t="inlineStr">
@@ -6236,34 +7042,34 @@
     </row>
     <row r="73">
       <c r="A73" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>5664</v>
+        <v>149.99</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>eBay API; vendedor techrec-recycling 99.6%; Intel Core i5-13400 2.50GHz 10-Core LGA1700 20MB Desktop Pro</t>
         </is>
       </c>
       <c r="H73" s="6" t="inlineStr">
@@ -6274,11 +7080,11 @@
     </row>
     <row r="74">
       <c r="A74" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -6288,20 +7094,20 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E74" s="11" t="n">
-        <v>2537</v>
+        <v>134</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>eBay API; vendedor htam86 99.7%; Intel Core i5-14400F 10-Core 16-Thread 4.7GHz LGA 1700 CPU S</t>
         </is>
       </c>
       <c r="H74" s="6" t="inlineStr">
@@ -6312,34 +7118,34 @@
     </row>
     <row r="75">
       <c r="A75" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>3127</v>
+        <v>209.99</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t xml:space="preserve">eBay API; vendedor paymore_bustleton 99.4%; Intel Core Ultra 7 265K 3.90GHz 20 Core SRQCW 20 Thread LGA </t>
         </is>
       </c>
       <c r="H75" s="6" t="inlineStr">
@@ -6350,34 +7156,34 @@
     </row>
     <row r="76">
       <c r="A76" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E76" s="11" t="n">
-        <v>2150</v>
+        <v>383.99</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t>eBay API; vendedor sly-systems 99.7%; Corsair Vengeance RGB Pro 32GB (2x16GB) RAM DDR5 5600MHz</t>
         </is>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -6388,34 +7194,34 @@
     </row>
     <row r="77">
       <c r="A77" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E77" s="11" t="n">
-        <v>6140</v>
+        <v>399.9</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t>eBay API; vendedor thaigamer 100.0%; Corsair Vengeance RGB DDR5 32GB (2x16GB) 6000MHz DIMM RGB CM; envío no indicado</t>
         </is>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -6426,34 +7232,34 @@
     </row>
     <row r="78">
       <c r="A78" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E78" s="11" t="n">
-        <v>4760</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>eBay API; vendedor corefoundry 100.0%; ADATA XPG Spectrix D41 16GB (2x8GB) DDR4 3200MHz CL16 Deskto; envío no indicado</t>
         </is>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -6464,34 +7270,34 @@
     </row>
     <row r="79">
       <c r="A79" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E79" s="11" t="n">
-        <v>6800</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor anotherdudestreasures 98.9%; SK hynix PC611 1TB NVMe PCIe Gen3 x4 M.2 2280 Internal SSD H</t>
         </is>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -6502,34 +7308,34 @@
     </row>
     <row r="80">
       <c r="A80" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E80" s="11" t="n">
-        <v>2100</v>
+        <v>170</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>eBay API; vendedor bunyip1992 100.0%; Inland 2TB Gen 3 NVME SSD Used Good</t>
         </is>
       </c>
       <c r="H80" s="6" t="inlineStr">
@@ -6540,7 +7346,7 @@
     </row>
     <row r="81">
       <c r="A81" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
@@ -6549,16 +7355,16 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>1800</v>
+        <v>5580</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
@@ -6567,7 +7373,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -6578,25 +7384,25 @@
     </row>
     <row r="82">
       <c r="A82" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>4500</v>
+        <v>2300</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -6605,7 +7411,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
@@ -6616,7 +7422,7 @@
     </row>
     <row r="83">
       <c r="A83" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
@@ -6625,16 +7431,16 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
-        <v>6700</v>
+        <v>3950</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
@@ -6643,7 +7449,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -6654,25 +7460,25 @@
     </row>
     <row r="84">
       <c r="A84" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E84" s="11" t="n">
-        <v>2520</v>
+        <v>4800</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -6681,7 +7487,7 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -6692,25 +7498,25 @@
     </row>
     <row r="85">
       <c r="A85" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
-        <v>4290</v>
+        <v>5190</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
@@ -6719,7 +7525,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -6730,25 +7536,25 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E86" s="11" t="n">
-        <v>2860</v>
+        <v>5390</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
@@ -6757,7 +7563,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
@@ -6768,25 +7574,25 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2460</v>
+        <v>2000</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
@@ -6795,7 +7601,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
@@ -6806,25 +7612,25 @@
     </row>
     <row r="88">
       <c r="A88" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E88" s="11" t="n">
-        <v>5360</v>
+        <v>2650</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -6833,7 +7639,7 @@
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
@@ -6844,25 +7650,25 @@
     </row>
     <row r="89">
       <c r="A89" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
-        <v>1710</v>
+        <v>2700</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
@@ -6871,7 +7677,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
@@ -6882,25 +7688,25 @@
     </row>
     <row r="90">
       <c r="A90" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E90" s="11" t="n">
-        <v>2310</v>
+        <v>6200</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -6909,7 +7715,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
@@ -6920,11 +7726,11 @@
     </row>
     <row r="91">
       <c r="A91" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -6934,11 +7740,11 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
-        <v>2160</v>
+        <v>540</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
@@ -6947,7 +7753,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -6958,25 +7764,25 @@
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E92" s="11" t="n">
-        <v>5360</v>
+        <v>900</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
@@ -6985,7 +7791,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
@@ -6996,25 +7802,25 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
-        <v>5660</v>
+        <v>1500</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
@@ -7023,7 +7829,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
@@ -7034,25 +7840,25 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E94" s="11" t="n">
-        <v>5860</v>
+        <v>1500</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
@@ -7061,7 +7867,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -7072,11 +7878,11 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -7086,11 +7892,11 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
@@ -7099,7 +7905,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
@@ -7110,11 +7916,11 @@
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -7124,11 +7930,11 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E96" s="11" t="n">
-        <v>2060</v>
+        <v>2000</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
@@ -7137,7 +7943,7 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
@@ -7148,11 +7954,11 @@
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -7162,11 +7968,11 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
-        <v>2152</v>
+        <v>1800</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
@@ -7175,7 +7981,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
@@ -7186,11 +7992,11 @@
     </row>
     <row r="98">
       <c r="A98" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -7200,11 +8006,11 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E98" s="11" t="n">
-        <v>4060</v>
+        <v>3550</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
@@ -7213,7 +8019,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
@@ -7233,16 +8039,16 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
-        <v>4560</v>
+        <v>5664</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
@@ -7251,7 +8057,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
@@ -7271,16 +8077,16 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E100" s="11" t="n">
-        <v>5500</v>
+        <v>2537</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
@@ -7289,7 +8095,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
@@ -7309,16 +8115,16 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
-        <v>2500</v>
+        <v>3127</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
@@ -7327,7 +8133,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
@@ -7347,28 +8153,1016 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Compucenter (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>2150</v>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Tienda Supermall (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>6140</v>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (garantía 6 meses)</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Tienda Supermall (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>4760</v>
+      </c>
+      <c r="F104" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G104" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H104" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>6800</v>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="inlineStr">
+        <is>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F106" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G107" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F108" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G108" s="5" t="inlineStr">
+        <is>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+        </is>
+      </c>
+      <c r="H108" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>6700</v>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G109" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H109" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F110" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G110" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H110" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
           <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
-      <c r="D102" s="5" t="inlineStr">
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>4290</v>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G111" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+        </is>
+      </c>
+      <c r="H111" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F112" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G112" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H112" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H113" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H115" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H116" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>5660</v>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H119" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>5860</v>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>1860</v>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H121" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>2152</v>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>4560</v>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H125" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
         <is>
           <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
-      <c r="E102" s="11" t="n">
+      <c r="E126" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H127" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="n">
         <v>5200</v>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
         </is>
       </c>
-      <c r="H102" s="6" t="inlineStr">
+      <c r="H128" s="6" t="inlineStr">
         <is>
           <t>ver</t>
         </is>
@@ -7477,10 +9271,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId127"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId102"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId128"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H128" headerRowCount="1">
-  <autoFilter ref="A1:H128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H131" headerRowCount="1">
+  <autoFilter ref="A1:H131"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -1045,12 +1045,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1059,17 +1059,19 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>164.49</v>
+        <v>114.99</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>134</v>
-      </c>
-      <c r="G9" s="2" t="n"/>
+        <v>99.98999999999999</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>1800</v>
+      </c>
       <c r="H9" s="8" t="n">
-        <v>2520</v>
+        <v>1860</v>
       </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1080,7 +1082,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1110,12 +1112,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1124,19 +1126,19 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>114.99</v>
+        <v>329</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>283.99</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1860</v>
+        <v>4760</v>
       </c>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1147,7 +1149,7 @@
         <v/>
       </c>
       <c r="K10" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L10" s="11">
         <f>IF(D10="","",MIN(MAX(Supuestos!$B$5,CEILING((K10*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D10*Supuestos!$B$9))</f>
@@ -1177,7 +1179,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1191,19 +1193,17 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>329</v>
+        <v>164.49</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>4800</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G11" s="2" t="n"/>
       <c r="H11" s="8" t="n">
-        <v>4760</v>
+        <v>2460</v>
       </c>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1214,7 +1214,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="L11" s="11">
         <f>IF(D11="","",MIN(MAX(Supuestos!$B$5,CEILING((K11*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D11*Supuestos!$B$9))</f>
@@ -2056,7 +2056,9 @@
         <v>283.99</v>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="8" t="n">
+        <v>5500</v>
+      </c>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2329,7 +2331,9 @@
         <v>134</v>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="8" t="n">
+        <v>2460</v>
+      </c>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4287,7 +4291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9167,6 +9171,108 @@
           <t>ver</t>
         </is>
       </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Historial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -240,7 +240,7 @@
   <commentList>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
-        <t>Aduana sin confirmar con los couriers: probar aquí, por ejemplo 0,1 = 10 %.</t>
+        <t>Los dos couriers ya incluyen la aduana (Santi, 13/10): queda en 0. Probar aquí solo si algún envío la cobra aparte, por ejemplo 0,1 = 10 %.</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
@@ -4071,7 +4071,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Aduana boliviana (sin confirmar)</t>
+          <t>Aduana boliviana extra (incluida en los couriers)</t>
         </is>
       </c>
       <c r="B10" s="22" t="n">

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H131" headerRowCount="1">
-  <autoFilter ref="A1:H131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H133" headerRowCount="1">
+  <autoFilter ref="A1:H133"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -2055,7 +2055,9 @@
       <c r="E5" s="7" t="n">
         <v>283.99</v>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="G5" s="8" t="n">
         <v>5500</v>
       </c>
@@ -4291,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9273,6 +9275,78 @@
         </is>
       </c>
       <c r="H131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>6840</v>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9403,10 +9477,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId128"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId128"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId129"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H133" headerRowCount="1">
-  <autoFilter ref="A1:H133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H134" headerRowCount="1">
+  <autoFilter ref="A1:H134"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -2059,7 +2059,7 @@
         <v>4800</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5500</v>
+        <v>5350</v>
       </c>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
@@ -4293,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9347,6 +9347,40 @@
           <t>ver</t>
         </is>
       </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>5350</v>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Historial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O39" headerRowCount="1">
-  <autoFilter ref="A1:O39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O53" headerRowCount="1">
+  <autoFilter ref="A1:O53"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H134" headerRowCount="1">
-  <autoFilter ref="A1:H134"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H160" headerRowCount="1">
+  <autoFilter ref="A1:H160"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -633,7 +633,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>¿Qué conviene traer? · 13/10/2026</t>
+          <t>¿Qué conviene traer? · 14/10/2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -799,13 +799,13 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>143.24</v>
+        <v>142.24</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>122.99</v>
+        <v>121.99</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>170</v>
+        <v>164.99</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>209.99</v>
+        <v>229</v>
       </c>
       <c r="G7" s="2" t="n"/>
       <c r="H7" s="8" t="n">
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>99</v>
+        <v>120.99</v>
       </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="8" t="n">
@@ -1045,12 +1045,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1059,19 +1059,19 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>114.99</v>
+        <v>329</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>275.99</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>1800</v>
+        <v>4800</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1860</v>
+        <v>4760</v>
       </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1082,7 +1082,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1112,7 +1112,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1126,19 +1126,17 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>329</v>
+        <v>164.49</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>4800</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="8" t="n">
-        <v>4760</v>
+        <v>2460</v>
       </c>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1149,7 +1147,7 @@
         <v/>
       </c>
       <c r="K10" s="8" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="L10" s="11">
         <f>IF(D10="","",MIN(MAX(Supuestos!$B$5,CEILING((K10*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D10*Supuestos!$B$9))</f>
@@ -1179,12 +1177,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1193,18 +1191,18 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>164.49</v>
+        <v>425</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0</v>
+        <v>10.99</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>134</v>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="8" t="n">
-        <v>2460</v>
-      </c>
+        <v>399.9</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1214,7 +1212,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="L11" s="11">
         <f>IF(D11="","",MIN(MAX(Supuestos!$B$5,CEILING((K11*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D11*Supuestos!$B$9))</f>
@@ -1244,12 +1242,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1258,18 +1256,20 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>425</v>
+        <v>117.99</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>10.99</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>399.9</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H12" s="2" t="n"/>
+        <v>1800</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="L12" s="11">
         <f>IF(D12="","",MIN(MAX(Supuestos!$B$5,CEILING((K12*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D12*Supuestos!$B$9))</f>
@@ -1374,7 +1374,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1388,18 +1388,20 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>485</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>383.99</v>
+        <v>65</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H14" s="2" t="n"/>
+        <v>900</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>2150</v>
+      </c>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1409,7 +1411,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1439,7 +1441,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1453,20 +1455,18 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>429.97</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>379.99</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>2150</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="K15" s="8" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="L15" s="11">
         <f>IF(D15="","",MIN(MAX(Supuestos!$B$5,CEILING((K15*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D15*Supuestos!$B$9))</f>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1650,7 +1650,7 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="7" t="n">
-        <v>299.99</v>
+        <v>295</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>209.99</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>170</v>
+        <v>164.99</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="K2" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L2" s="16">
         <f>IF(OR($K2="",D2=""),"",IF(COUNTIFS($B:$B,$B2,$A:$A,$K2,D:D,"&gt;=0")=0,"",D2-SUMIFS(D:D,$B:$B,$B2,$A:$A,$K2)))</f>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>114.99</v>
+        <v>117.99</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L3" s="16">
         <f>IF(OR($K3="",D3=""),"",IF(COUNTIFS($B:$B,$B3,$A:$A,$K3,D:D,"&gt;=0")=0,"",D3-SUMIFS(D:D,$B:$B,$B3,$A:$A,$K3)))</f>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L4" s="16">
         <f>IF(OR($K4="",D4=""),"",IF(COUNTIFS($B:$B,$B4,$A:$A,$K4,D:D,"&gt;=0")=0,"",D4-SUMIFS(D:D,$B:$B,$B4,$A:$A,$K4)))</f>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -2053,14 +2053,10 @@
         <v>329</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>5350</v>
-      </c>
+        <v>275.99</v>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2075,7 +2071,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L5" s="16">
         <f>IF(OR($K5="",D5=""),"",IF(COUNTIFS($B:$B,$B5,$A:$A,$K5,D:D,"&gt;=0")=0,"",D5-SUMIFS(D:D,$B:$B,$B5,$A:$A,$K5)))</f>
@@ -2096,7 +2092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2110,7 +2106,7 @@
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="7" t="n">
-        <v>299.99</v>
+        <v>295</v>
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
@@ -2128,7 +2124,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
@@ -2149,7 +2145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2162,10 +2158,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>143.24</v>
+        <v>142.24</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>122.99</v>
+        <v>121.99</v>
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
@@ -2183,7 +2179,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L7" s="16">
         <f>IF(OR($K7="",D7=""),"",IF(COUNTIFS($B:$B,$B7,$A:$A,$K7,D:D,"&gt;=0")=0,"",D7-SUMIFS(D:D,$B:$B,$B7,$A:$A,$K7)))</f>
@@ -2204,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -2220,7 +2216,7 @@
         <v>138.9</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
@@ -2238,7 +2234,7 @@
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L8" s="16">
         <f>IF(OR($K8="",D8=""),"",IF(COUNTIFS($B:$B,$B8,$A:$A,$K8,D:D,"&gt;=0")=0,"",D8-SUMIFS(D:D,$B:$B,$B8,$A:$A,$K8)))</f>
@@ -2259,7 +2255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2272,10 +2268,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>65</v>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
@@ -2293,7 +2289,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L9" s="16">
         <f>IF(OR($K9="",D9=""),"",IF(COUNTIFS($B:$B,$B9,$A:$A,$K9,D:D,"&gt;=0")=0,"",D9-SUMIFS(D:D,$B:$B,$B9,$A:$A,$K9)))</f>
@@ -2314,7 +2310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2333,9 +2329,7 @@
         <v>134</v>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2350,7 +2344,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L10" s="16">
         <f>IF(OR($K10="",D10=""),"",IF(COUNTIFS($B:$B,$B10,$A:$A,$K10,D:D,"&gt;=0")=0,"",D10-SUMIFS(D:D,$B:$B,$B10,$A:$A,$K10)))</f>
@@ -2371,7 +2365,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2403,7 +2397,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L11" s="16">
         <f>IF(OR($K11="",D11=""),"",IF(COUNTIFS($B:$B,$B11,$A:$A,$K11,D:D,"&gt;=0")=0,"",D11-SUMIFS(D:D,$B:$B,$B11,$A:$A,$K11)))</f>
@@ -2424,7 +2418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2440,7 +2434,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>99</v>
+        <v>120.99</v>
       </c>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
@@ -2458,7 +2452,7 @@
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L12" s="16">
         <f>IF(OR($K12="",D12=""),"",IF(COUNTIFS($B:$B,$B12,$A:$A,$K12,D:D,"&gt;=0")=0,"",D12-SUMIFS(D:D,$B:$B,$B12,$A:$A,$K12)))</f>
@@ -2479,7 +2473,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2495,7 +2489,7 @@
         <v>234.99</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>209.99</v>
+        <v>229</v>
       </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
@@ -2513,7 +2507,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L13" s="16">
         <f>IF(OR($K13="",D13=""),"",IF(COUNTIFS($B:$B,$B13,$A:$A,$K13,D:D,"&gt;=0")=0,"",D13-SUMIFS(D:D,$B:$B,$B13,$A:$A,$K13)))</f>
@@ -2534,7 +2528,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2568,7 +2562,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L14" s="16">
         <f>IF(OR($K14="",D14=""),"",IF(COUNTIFS($B:$B,$B14,$A:$A,$K14,D:D,"&gt;=0")=0,"",D14-SUMIFS(D:D,$B:$B,$B14,$A:$A,$K14)))</f>
@@ -2589,7 +2583,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -2602,10 +2596,10 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>493</v>
+        <v>429.97</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>383.99</v>
+        <v>379.99</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
@@ -2623,7 +2617,7 @@
         </is>
       </c>
       <c r="K15" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L15" s="16">
         <f>IF(OR($K15="",D15=""),"",IF(COUNTIFS($B:$B,$B15,$A:$A,$K15,D:D,"&gt;=0")=0,"",D15-SUMIFS(D:D,$B:$B,$B15,$A:$A,$K15)))</f>
@@ -2644,7 +2638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -2660,12 +2654,10 @@
         <v>209.99</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>179.99</v>
+        <v>170</v>
       </c>
       <c r="F16" s="2" t="n"/>
-      <c r="G16" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G16" s="2" t="n"/>
       <c r="H16" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A16,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A16,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2680,7 +2672,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2701,7 +2693,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -2720,9 +2712,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2737,7 +2727,7 @@
         </is>
       </c>
       <c r="K17" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L17" s="16">
         <f>IF(OR($K17="",D17=""),"",IF(COUNTIFS($B:$B,$B17,$A:$A,$K17,D:D,"&gt;=0")=0,"",D17-SUMIFS(D:D,$B:$B,$B17,$A:$A,$K17)))</f>
@@ -2758,7 +2748,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -2777,9 +2767,7 @@
         <v>454.99</v>
       </c>
       <c r="F18" s="2" t="n"/>
-      <c r="G18" s="8" t="n">
-        <v>6140</v>
-      </c>
+      <c r="G18" s="2" t="n"/>
       <c r="H18" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A18,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A18,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2794,7 +2782,7 @@
         </is>
       </c>
       <c r="K18" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L18" s="16">
         <f>IF(OR($K18="",D18=""),"",IF(COUNTIFS($B:$B,$B18,$A:$A,$K18,D:D,"&gt;=0")=0,"",D18-SUMIFS(D:D,$B:$B,$B18,$A:$A,$K18)))</f>
@@ -2815,7 +2803,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2833,9 +2821,11 @@
       <c r="E19" s="7" t="n">
         <v>283.99</v>
       </c>
-      <c r="F19" s="2" t="n"/>
+      <c r="F19" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="G19" s="8" t="n">
-        <v>4760</v>
+        <v>5350</v>
       </c>
       <c r="H19" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))),"")</f>
@@ -2851,7 +2841,7 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L19" s="16">
         <f>IF(OR($K19="",D19=""),"",IF(COUNTIFS($B:$B,$B19,$A:$A,$K19,D:D,"&gt;=0")=0,"",D19-SUMIFS(D:D,$B:$B,$B19,$A:$A,$K19)))</f>
@@ -2872,7 +2862,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2886,7 +2876,7 @@
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -2903,7 +2893,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K20" s="5" t="n"/>
+      <c r="K20" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L20" s="16">
         <f>IF(OR($K20="",D20=""),"",IF(COUNTIFS($B:$B,$B20,$A:$A,$K20,D:D,"&gt;=0")=0,"",D20-SUMIFS(D:D,$B:$B,$B20,$A:$A,$K20)))</f>
         <v/>
@@ -2923,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -2936,15 +2928,13 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>144.25</v>
+        <v>143.24</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>122.99</v>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="8" t="n">
-        <v>2860</v>
-      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2959,7 +2949,7 @@
         </is>
       </c>
       <c r="K21" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L21" s="16">
         <f>IF(OR($K21="",D21=""),"",IF(COUNTIFS($B:$B,$B21,$A:$A,$K21,D:D,"&gt;=0")=0,"",D21-SUMIFS(D:D,$B:$B,$B21,$A:$A,$K21)))</f>
@@ -2980,7 +2970,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3013,7 +3003,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K22" s="5" t="n"/>
+      <c r="K22" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
         <v/>
@@ -3033,7 +3025,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -3046,15 +3038,13 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>75</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>59.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F23" s="2" t="n"/>
-      <c r="G23" s="8" t="n">
-        <v>2150</v>
-      </c>
+      <c r="G23" s="2" t="n"/>
       <c r="H23" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A23,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A23,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3069,7 +3059,7 @@
         </is>
       </c>
       <c r="K23" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L23" s="16">
         <f>IF(OR($K23="",D23=""),"",IF(COUNTIFS($B:$B,$B23,$A:$A,$K23,D:D,"&gt;=0")=0,"",D23-SUMIFS(D:D,$B:$B,$B23,$A:$A,$K23)))</f>
@@ -3090,7 +3080,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -3106,11 +3096,11 @@
         <v>164.49</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="8" t="n">
-        <v>2520</v>
+        <v>2460</v>
       </c>
       <c r="H24" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))),"")</f>
@@ -3126,7 +3116,7 @@
         </is>
       </c>
       <c r="K24" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L24" s="16">
         <f>IF(OR($K24="",D24=""),"",IF(COUNTIFS($B:$B,$B24,$A:$A,$K24,D:D,"&gt;=0")=0,"",D24-SUMIFS(D:D,$B:$B,$B24,$A:$A,$K24)))</f>
@@ -3147,7 +3137,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -3159,9 +3149,7 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D25" s="7" t="n">
-        <v>259.78</v>
-      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="7" t="n">
         <v>149.99</v>
       </c>
@@ -3181,7 +3169,7 @@
         </is>
       </c>
       <c r="K25" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L25" s="16">
         <f>IF(OR($K25="",D25=""),"",IF(COUNTIFS($B:$B,$B25,$A:$A,$K25,D:D,"&gt;=0")=0,"",D25-SUMIFS(D:D,$B:$B,$B25,$A:$A,$K25)))</f>
@@ -3202,7 +3190,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3218,12 +3206,10 @@
         <v>150</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G26" s="2" t="n"/>
       <c r="H26" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A26,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A26,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3237,7 +3223,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K26" s="5" t="n"/>
+      <c r="K26" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L26" s="16">
         <f>IF(OR($K26="",D26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,D:D,"&gt;=0")=0,"",D26-SUMIFS(D:D,$B:$B,$B26,$A:$A,$K26)))</f>
         <v/>
@@ -3257,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3270,15 +3258,13 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>209.99</v>
       </c>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G27" s="2" t="n"/>
       <c r="H27" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A27,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A27,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3293,7 +3279,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L27" s="16">
         <f>IF(OR($K27="",D27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,D:D,"&gt;=0")=0,"",D27-SUMIFS(D:D,$B:$B,$B27,$A:$A,$K27)))</f>
@@ -3314,7 +3300,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -3348,7 +3334,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L28" s="16">
         <f>IF(OR($K28="",D28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,D:D,"&gt;=0")=0,"",D28-SUMIFS(D:D,$B:$B,$B28,$A:$A,$K28)))</f>
@@ -3369,7 +3355,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -3385,11 +3371,9 @@
         <v>493</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>4500</v>
-      </c>
+        <v>383.99</v>
+      </c>
+      <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A29,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A29,Dólar!$A:$A,0))),"")</f>
@@ -3404,7 +3388,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n"/>
+      <c r="K29" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L29" s="16">
         <f>IF(OR($K29="",D29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,D:D,"&gt;=0")=0,"",D29-SUMIFS(D:D,$B:$B,$B29,$A:$A,$K29)))</f>
         <v/>
@@ -3424,7 +3410,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3436,10 +3422,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
+      <c r="D30" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>179.99</v>
+      </c>
       <c r="F30" s="2" t="n"/>
-      <c r="G30" s="2" t="n"/>
+      <c r="G30" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H30" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A30,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A30,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3448,8 +3440,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A30,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="5" t="n"/>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K30" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L30" s="16">
         <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
         <v/>
@@ -3469,7 +3467,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3481,12 +3479,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G31" s="2" t="n"/>
+      <c r="D31" s="7" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H31" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3500,7 +3502,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K31" s="5" t="n"/>
+      <c r="K31" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L31" s="16">
         <f>IF(OR($K31="",D31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,D:D,"&gt;=0")=0,"",D31-SUMIFS(D:D,$B:$B,$B31,$A:$A,$K31)))</f>
         <v/>
@@ -3520,7 +3524,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3532,11 +3536,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
+      <c r="D32" s="7" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>454.99</v>
+      </c>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="8" t="n">
-        <v>5580</v>
+        <v>6140</v>
       </c>
       <c r="H32" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A32,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A32,Dólar!$A:$A,0))),"")</f>
@@ -3551,7 +3559,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K32" s="5" t="n"/>
+      <c r="K32" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L32" s="16">
         <f>IF(OR($K32="",D32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,D:D,"&gt;=0")=0,"",D32-SUMIFS(D:D,$B:$B,$B32,$A:$A,$K32)))</f>
         <v/>
@@ -3571,7 +3581,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3583,12 +3593,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-      <c r="F33" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G33" s="2" t="n"/>
+      <c r="D33" s="7" t="n">
+        <v>329</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="H33" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3602,7 +3616,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K33" s="5" t="n"/>
+      <c r="K33" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L33" s="16">
         <f>IF(OR($K33="",D33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,D:D,"&gt;=0")=0,"",D33-SUMIFS(D:D,$B:$B,$B33,$A:$A,$K33)))</f>
         <v/>
@@ -3622,11 +3638,11 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3635,7 +3651,9 @@
         </is>
       </c>
       <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
+      <c r="E34" s="7" t="n">
+        <v>305</v>
+      </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="9">
@@ -3646,7 +3664,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A34,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J34" s="2" t="n"/>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K34" s="5" t="n"/>
       <c r="L34" s="16">
         <f>IF(OR($K34="",D34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,D:D,"&gt;=0")=0,"",D34-SUMIFS(D:D,$B:$B,$B34,$A:$A,$K34)))</f>
@@ -3667,24 +3689,28 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-      <c r="F35" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="G35" s="2" t="n"/>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H35" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3698,7 +3724,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K35" s="5" t="n"/>
+      <c r="K35" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L35" s="16">
         <f>IF(OR($K35="",D35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,D:D,"&gt;=0")=0,"",D35-SUMIFS(D:D,$B:$B,$B35,$A:$A,$K35)))</f>
         <v/>
@@ -3718,11 +3746,11 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -3730,8 +3758,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
+      <c r="D36" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="9">
@@ -3742,7 +3774,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A36,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J36" s="2" t="n"/>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K36" s="5" t="n"/>
       <c r="L36" s="16">
         <f>IF(OR($K36="",D36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,D:D,"&gt;=0")=0,"",D36-SUMIFS(D:D,$B:$B,$B36,$A:$A,$K36)))</f>
@@ -3763,23 +3799,27 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>59.99</v>
+      </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="H37" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A37,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A37,Dólar!$A:$A,0))),"")</f>
@@ -3794,7 +3834,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K37" s="5" t="n"/>
+      <c r="K37" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L37" s="16">
         <f>IF(OR($K37="",D37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,D:D,"&gt;=0")=0,"",D37-SUMIFS(D:D,$B:$B,$B37,$A:$A,$K37)))</f>
         <v/>
@@ -3814,11 +3856,11 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -3826,11 +3868,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
+      <c r="D38" s="7" t="n">
+        <v>164.49</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>136.99</v>
+      </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="8" t="n">
-        <v>3950</v>
+        <v>2520</v>
       </c>
       <c r="H38" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))),"")</f>
@@ -3845,7 +3891,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K38" s="5" t="n"/>
+      <c r="K38" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L38" s="16">
         <f>IF(OR($K38="",D38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,D:D,"&gt;=0")=0,"",D38-SUMIFS(D:D,$B:$B,$B38,$A:$A,$K38)))</f>
         <v/>
@@ -3865,23 +3913,25 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="8" t="n">
-        <v>6200</v>
-      </c>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A39,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A39,Dólar!$A:$A,0))),"")</f>
@@ -3896,7 +3946,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K39" s="5" t="n"/>
+      <c r="K39" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L39" s="16">
         <f>IF(OR($K39="",D39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,D:D,"&gt;=0")=0,"",D39-SUMIFS(D:D,$B:$B,$B39,$A:$A,$K39)))</f>
         <v/>
@@ -3914,8 +3966,722 @@
         <v/>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="8" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H40" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A40,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A40,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A40,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="16">
+        <f>IF(OR($K40="",D40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,D:D,"&gt;=0")=0,"",D40-SUMIFS(D:D,$B:$B,$B40,$A:$A,$K40)))</f>
+        <v/>
+      </c>
+      <c r="M40" s="16">
+        <f>IF(OR($K40="",E40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,E:E,"&gt;=0")=0,"",E40-SUMIFS(E:E,$B:$B,$B40,$A:$A,$K40)))</f>
+        <v/>
+      </c>
+      <c r="N40" s="16">
+        <f>IF(OR($K40="",F40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,F:F,"&gt;=0")=0,"",F40-SUMIFS(F:F,$B:$B,$B40,$A:$A,$K40)))</f>
+        <v/>
+      </c>
+      <c r="O40" s="16">
+        <f>IF(OR($K40="",G40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,G:G,"&gt;=0")=0,"",G40-SUMIFS(G:G,$B:$B,$B40,$A:$A,$K40)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H41" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A41,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A41,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A41,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K41" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L41" s="16">
+        <f>IF(OR($K41="",D41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,D:D,"&gt;=0")=0,"",D41-SUMIFS(D:D,$B:$B,$B41,$A:$A,$K41)))</f>
+        <v/>
+      </c>
+      <c r="M41" s="16">
+        <f>IF(OR($K41="",E41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,E:E,"&gt;=0")=0,"",E41-SUMIFS(E:E,$B:$B,$B41,$A:$A,$K41)))</f>
+        <v/>
+      </c>
+      <c r="N41" s="16">
+        <f>IF(OR($K41="",F41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,F:F,"&gt;=0")=0,"",F41-SUMIFS(F:F,$B:$B,$B41,$A:$A,$K41)))</f>
+        <v/>
+      </c>
+      <c r="O41" s="16">
+        <f>IF(OR($K41="",G41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,G:G,"&gt;=0")=0,"",G41-SUMIFS(G:G,$B:$B,$B41,$A:$A,$K41)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A42,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A42,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A42,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K42" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L42" s="16">
+        <f>IF(OR($K42="",D42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,D:D,"&gt;=0")=0,"",D42-SUMIFS(D:D,$B:$B,$B42,$A:$A,$K42)))</f>
+        <v/>
+      </c>
+      <c r="M42" s="16">
+        <f>IF(OR($K42="",E42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,E:E,"&gt;=0")=0,"",E42-SUMIFS(E:E,$B:$B,$B42,$A:$A,$K42)))</f>
+        <v/>
+      </c>
+      <c r="N42" s="16">
+        <f>IF(OR($K42="",F42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,F:F,"&gt;=0")=0,"",F42-SUMIFS(F:F,$B:$B,$B42,$A:$A,$K42)))</f>
+        <v/>
+      </c>
+      <c r="O42" s="16">
+        <f>IF(OR($K42="",G42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,G:G,"&gt;=0")=0,"",G42-SUMIFS(G:G,$B:$B,$B42,$A:$A,$K42)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A43,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A43,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A43,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="16">
+        <f>IF(OR($K43="",D43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,D:D,"&gt;=0")=0,"",D43-SUMIFS(D:D,$B:$B,$B43,$A:$A,$K43)))</f>
+        <v/>
+      </c>
+      <c r="M43" s="16">
+        <f>IF(OR($K43="",E43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,E:E,"&gt;=0")=0,"",E43-SUMIFS(E:E,$B:$B,$B43,$A:$A,$K43)))</f>
+        <v/>
+      </c>
+      <c r="N43" s="16">
+        <f>IF(OR($K43="",F43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,F:F,"&gt;=0")=0,"",F43-SUMIFS(F:F,$B:$B,$B43,$A:$A,$K43)))</f>
+        <v/>
+      </c>
+      <c r="O43" s="16">
+        <f>IF(OR($K43="",G43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,G:G,"&gt;=0")=0,"",G43-SUMIFS(G:G,$B:$B,$B43,$A:$A,$K43)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A44,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A44,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A44,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="16">
+        <f>IF(OR($K44="",D44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,D:D,"&gt;=0")=0,"",D44-SUMIFS(D:D,$B:$B,$B44,$A:$A,$K44)))</f>
+        <v/>
+      </c>
+      <c r="M44" s="16">
+        <f>IF(OR($K44="",E44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,E:E,"&gt;=0")=0,"",E44-SUMIFS(E:E,$B:$B,$B44,$A:$A,$K44)))</f>
+        <v/>
+      </c>
+      <c r="N44" s="16">
+        <f>IF(OR($K44="",F44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,F:F,"&gt;=0")=0,"",F44-SUMIFS(F:F,$B:$B,$B44,$A:$A,$K44)))</f>
+        <v/>
+      </c>
+      <c r="O44" s="16">
+        <f>IF(OR($K44="",G44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,G:G,"&gt;=0")=0,"",G44-SUMIFS(G:G,$B:$B,$B44,$A:$A,$K44)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A45,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="16">
+        <f>IF(OR($K45="",D45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,D:D,"&gt;=0")=0,"",D45-SUMIFS(D:D,$B:$B,$B45,$A:$A,$K45)))</f>
+        <v/>
+      </c>
+      <c r="M45" s="16">
+        <f>IF(OR($K45="",E45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,E:E,"&gt;=0")=0,"",E45-SUMIFS(E:E,$B:$B,$B45,$A:$A,$K45)))</f>
+        <v/>
+      </c>
+      <c r="N45" s="16">
+        <f>IF(OR($K45="",F45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,F:F,"&gt;=0")=0,"",F45-SUMIFS(F:F,$B:$B,$B45,$A:$A,$K45)))</f>
+        <v/>
+      </c>
+      <c r="O45" s="16">
+        <f>IF(OR($K45="",G45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,G:G,"&gt;=0")=0,"",G45-SUMIFS(G:G,$B:$B,$B45,$A:$A,$K45)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="H46" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A46,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A46,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A46,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="16">
+        <f>IF(OR($K46="",D46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,D:D,"&gt;=0")=0,"",D46-SUMIFS(D:D,$B:$B,$B46,$A:$A,$K46)))</f>
+        <v/>
+      </c>
+      <c r="M46" s="16">
+        <f>IF(OR($K46="",E46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,E:E,"&gt;=0")=0,"",E46-SUMIFS(E:E,$B:$B,$B46,$A:$A,$K46)))</f>
+        <v/>
+      </c>
+      <c r="N46" s="16">
+        <f>IF(OR($K46="",F46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,F:F,"&gt;=0")=0,"",F46-SUMIFS(F:F,$B:$B,$B46,$A:$A,$K46)))</f>
+        <v/>
+      </c>
+      <c r="O46" s="16">
+        <f>IF(OR($K46="",G46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,G:G,"&gt;=0")=0,"",G46-SUMIFS(G:G,$B:$B,$B46,$A:$A,$K46)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A47,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="16">
+        <f>IF(OR($K47="",D47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,D:D,"&gt;=0")=0,"",D47-SUMIFS(D:D,$B:$B,$B47,$A:$A,$K47)))</f>
+        <v/>
+      </c>
+      <c r="M47" s="16">
+        <f>IF(OR($K47="",E47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,E:E,"&gt;=0")=0,"",E47-SUMIFS(E:E,$B:$B,$B47,$A:$A,$K47)))</f>
+        <v/>
+      </c>
+      <c r="N47" s="16">
+        <f>IF(OR($K47="",F47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,F:F,"&gt;=0")=0,"",F47-SUMIFS(F:F,$B:$B,$B47,$A:$A,$K47)))</f>
+        <v/>
+      </c>
+      <c r="O47" s="16">
+        <f>IF(OR($K47="",G47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,G:G,"&gt;=0")=0,"",G47-SUMIFS(G:G,$B:$B,$B47,$A:$A,$K47)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A48,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A48,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A48,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="16">
+        <f>IF(OR($K48="",D48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,D:D,"&gt;=0")=0,"",D48-SUMIFS(D:D,$B:$B,$B48,$A:$A,$K48)))</f>
+        <v/>
+      </c>
+      <c r="M48" s="16">
+        <f>IF(OR($K48="",E48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,E:E,"&gt;=0")=0,"",E48-SUMIFS(E:E,$B:$B,$B48,$A:$A,$K48)))</f>
+        <v/>
+      </c>
+      <c r="N48" s="16">
+        <f>IF(OR($K48="",F48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,F:F,"&gt;=0")=0,"",F48-SUMIFS(F:F,$B:$B,$B48,$A:$A,$K48)))</f>
+        <v/>
+      </c>
+      <c r="O48" s="16">
+        <f>IF(OR($K48="",G48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,G:G,"&gt;=0")=0,"",G48-SUMIFS(G:G,$B:$B,$B48,$A:$A,$K48)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A49,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="16">
+        <f>IF(OR($K49="",D49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,D:D,"&gt;=0")=0,"",D49-SUMIFS(D:D,$B:$B,$B49,$A:$A,$K49)))</f>
+        <v/>
+      </c>
+      <c r="M49" s="16">
+        <f>IF(OR($K49="",E49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,E:E,"&gt;=0")=0,"",E49-SUMIFS(E:E,$B:$B,$B49,$A:$A,$K49)))</f>
+        <v/>
+      </c>
+      <c r="N49" s="16">
+        <f>IF(OR($K49="",F49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,F:F,"&gt;=0")=0,"",F49-SUMIFS(F:F,$B:$B,$B49,$A:$A,$K49)))</f>
+        <v/>
+      </c>
+      <c r="O49" s="16">
+        <f>IF(OR($K49="",G49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,G:G,"&gt;=0")=0,"",G49-SUMIFS(G:G,$B:$B,$B49,$A:$A,$K49)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A50,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A50,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A50,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="16">
+        <f>IF(OR($K50="",D50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,D:D,"&gt;=0")=0,"",D50-SUMIFS(D:D,$B:$B,$B50,$A:$A,$K50)))</f>
+        <v/>
+      </c>
+      <c r="M50" s="16">
+        <f>IF(OR($K50="",E50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,E:E,"&gt;=0")=0,"",E50-SUMIFS(E:E,$B:$B,$B50,$A:$A,$K50)))</f>
+        <v/>
+      </c>
+      <c r="N50" s="16">
+        <f>IF(OR($K50="",F50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,F:F,"&gt;=0")=0,"",F50-SUMIFS(F:F,$B:$B,$B50,$A:$A,$K50)))</f>
+        <v/>
+      </c>
+      <c r="O50" s="16">
+        <f>IF(OR($K50="",G50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,G:G,"&gt;=0")=0,"",G50-SUMIFS(G:G,$B:$B,$B50,$A:$A,$K50)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H51" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A51,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A51,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A51,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="16">
+        <f>IF(OR($K51="",D51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,D:D,"&gt;=0")=0,"",D51-SUMIFS(D:D,$B:$B,$B51,$A:$A,$K51)))</f>
+        <v/>
+      </c>
+      <c r="M51" s="16">
+        <f>IF(OR($K51="",E51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,E:E,"&gt;=0")=0,"",E51-SUMIFS(E:E,$B:$B,$B51,$A:$A,$K51)))</f>
+        <v/>
+      </c>
+      <c r="N51" s="16">
+        <f>IF(OR($K51="",F51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,F:F,"&gt;=0")=0,"",F51-SUMIFS(F:F,$B:$B,$B51,$A:$A,$K51)))</f>
+        <v/>
+      </c>
+      <c r="O51" s="16">
+        <f>IF(OR($K51="",G51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,G:G,"&gt;=0")=0,"",G51-SUMIFS(G:G,$B:$B,$B51,$A:$A,$K51)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n"/>
+      <c r="G52" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H52" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A52,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="16">
+        <f>IF(OR($K52="",D52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,D:D,"&gt;=0")=0,"",D52-SUMIFS(D:D,$B:$B,$B52,$A:$A,$K52)))</f>
+        <v/>
+      </c>
+      <c r="M52" s="16">
+        <f>IF(OR($K52="",E52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,E:E,"&gt;=0")=0,"",E52-SUMIFS(E:E,$B:$B,$B52,$A:$A,$K52)))</f>
+        <v/>
+      </c>
+      <c r="N52" s="16">
+        <f>IF(OR($K52="",F52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,F:F,"&gt;=0")=0,"",F52-SUMIFS(F:F,$B:$B,$B52,$A:$A,$K52)))</f>
+        <v/>
+      </c>
+      <c r="O52" s="16">
+        <f>IF(OR($K52="",G52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,G:G,"&gt;=0")=0,"",G52-SUMIFS(G:G,$B:$B,$B52,$A:$A,$K52)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A53,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A53,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I53" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A53,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="16">
+        <f>IF(OR($K53="",D53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,D:D,"&gt;=0")=0,"",D53-SUMIFS(D:D,$B:$B,$B53,$A:$A,$K53)))</f>
+        <v/>
+      </c>
+      <c r="M53" s="16">
+        <f>IF(OR($K53="",E53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,E:E,"&gt;=0")=0,"",E53-SUMIFS(E:E,$B:$B,$B53,$A:$A,$K53)))</f>
+        <v/>
+      </c>
+      <c r="N53" s="16">
+        <f>IF(OR($K53="",F53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,F:F,"&gt;=0")=0,"",F53-SUMIFS(F:F,$B:$B,$B53,$A:$A,$K53)))</f>
+        <v/>
+      </c>
+      <c r="O53" s="16">
+        <f>IF(OR($K53="",G53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,G:G,"&gt;=0")=0,"",G53-SUMIFS(G:G,$B:$B,$B53,$A:$A,$K53)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M39">
+  <conditionalFormatting sqref="L2:M53">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -3923,7 +4689,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O39">
+  <conditionalFormatting sqref="N2:O53">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -3960,17 +4726,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId36"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4135,7 +4915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4282,6 +5062,32 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="E6" s="10">
+        <f>IF(COUNT(C6:D6)=2,AVERAGE(C6:D6),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>BCB oficial 11.70; paralelo dolarbolivia.net 14/10 (compra 11.84 / venta 11.88; la página es inconsistente entre compra y venta); usado = promedio del paralelo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4293,7 +5099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7352,34 +8158,34 @@
     </row>
     <row r="81">
       <c r="A81" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E81" s="11" t="n">
-        <v>5580</v>
+        <v>138.9</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; (New) AMD Ryzen 5 5600 Vermeer Zen3 6-Core 12-Thread AM4 CPU</t>
         </is>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -7390,34 +8196,34 @@
     </row>
     <row r="82">
       <c r="A82" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>2300</v>
+        <v>142.24</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor silaxon 99.6%; AMD Ryzen 5 7600 3.80GHz 6 Core 12 Thread AM5 100-000001015</t>
         </is>
       </c>
       <c r="H82" s="6" t="inlineStr">
@@ -7428,34 +8234,34 @@
     </row>
     <row r="83">
       <c r="A83" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E83" s="11" t="n">
-        <v>3950</v>
+        <v>329</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; AMD Ryzen 7 7800X3D 100-00000910 - Ryzen 7 7000 Series Proce</t>
         </is>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -7466,34 +8272,34 @@
     </row>
     <row r="84">
       <c r="A84" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E84" s="11" t="n">
-        <v>4800</v>
+        <v>499.99</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay API; vendedor saguarowholesalesupply 100.0%; AMD Ryzen 9 9950X Desktop Processor AM5 New Sealed; envío no indicado</t>
         </is>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -7504,34 +8310,34 @@
     </row>
     <row r="85">
       <c r="A85" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E85" s="11" t="n">
-        <v>5190</v>
+        <v>150</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor algonz1137 100.0%; INTEL CPU Core i5-12400F / 6/12 / 2.5GHz / 6xxChipset / BX80; envío no indicado</t>
         </is>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -7542,34 +8348,34 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E86" s="11" t="n">
-        <v>5390</v>
+        <v>164.49</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t xml:space="preserve">eBay API; vendedor newegg 99.6%; Intel Core i5-14400F - Core i5 14th Gen Raptor Lake 10-Core </t>
         </is>
       </c>
       <c r="H86" s="6" t="inlineStr">
@@ -7580,34 +8386,34 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
-        <v>2000</v>
+        <v>234.99</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor good_neighbor_mercantile 99.4%; Intel Core Ultra 7 265K CPU Desktop Processor LGA 1851 20-Co</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr">
@@ -7618,34 +8424,34 @@
     </row>
     <row r="88">
       <c r="A88" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E88" s="11" t="n">
-        <v>2650</v>
+        <v>429.97</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor uventure 99.7%; NEW 32GB (2x16GB) Corsair Vengeance DDR5 PC5-5600 Desktop RA</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr">
@@ -7656,34 +8462,34 @@
     </row>
     <row r="89">
       <c r="A89" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
-        <v>2700</v>
+        <v>435.99</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>eBay API; vendedor wojiapanpan_4 100.0%; Corsair Vengeance RGB RS 32GB 2x16GB DDR5 6000 CL38 AMD EXPO</t>
         </is>
       </c>
       <c r="H89" s="6" t="inlineStr">
@@ -7694,34 +8500,34 @@
     </row>
     <row r="90">
       <c r="A90" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E90" s="11" t="n">
-        <v>6200</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t>eBay API; vendedor californiadrapes 99.9%; Timetec Pinnacle Konduit 16GB (2x8GB) DDR4 3200MHz CL16 Desk</t>
         </is>
       </c>
       <c r="H90" s="6" t="inlineStr">
@@ -7732,34 +8538,34 @@
     </row>
     <row r="91">
       <c r="A91" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
-        <v>540</v>
+        <v>117.99</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>eBay API; vendedor netac-official-it 99.5%; Netac 1TB Internal SSD Solid State Drive M.2 2280 PCIe3.0 NV</t>
         </is>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -7770,34 +8576,34 @@
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E92" s="11" t="n">
-        <v>900</v>
+        <v>209.99</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>eBay API; vendedor ram_technologies 100.0%; RAM Tech 2TB NVMe SSD Gen4 M.2 2280 | 5000MB/s Read 4500MB/s</t>
         </is>
       </c>
       <c r="H92" s="6" t="inlineStr">
@@ -7808,34 +8614,34 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
-        <v>1500</v>
+        <v>129.99</v>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>eBay API; vendedor paymore_castleton 99.7%; AMD Ryzen 5 5600 3.50GHz 6 Core 100-000000927 12 Thread AM4</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr">
@@ -7846,34 +8652,34 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E94" s="11" t="n">
-        <v>1500</v>
+        <v>295</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>eBay API; vendedor antonidelacru-7 98.0%; AMD Ryzen 7 5700X3D 8-Core Socket AM4 3.0GHz CPU 96MB L3 Cac; envío no indicado</t>
         </is>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -7884,34 +8690,34 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
-        <v>1850</v>
+        <v>121.99</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>eBay API; vendedor paymore_university_square 98.6%; AMD Ryzen 5 7600 3.80GHz 6 Core 100-000001015 12 Thread AM5</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr">
@@ -7922,34 +8728,34 @@
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E96" s="11" t="n">
-        <v>2000</v>
+        <v>275.99</v>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>eBay API; vendedor paymore_university_square 98.6%; AMD Ryzen 7 7800X3D 4.20GHz 8 Core 100-000000910 16 Thread A</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr">
@@ -7960,34 +8766,34 @@
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
-        <v>1800</v>
+        <v>454.99</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>eBay API; vendedor goodios_direct 99.6%; **  AMD Ryzen 9 9950X Processor - USED  **</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr">
@@ -7998,34 +8804,34 @@
     </row>
     <row r="98">
       <c r="A98" s="15" t="n">
-        <v>46306</v>
+        <v>46309</v>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E98" s="11" t="n">
-        <v>3550</v>
+        <v>120.99</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>eBay API; vendedor vendingollc_1 100.0%; Intel Core i5-12400F 6-Core 2.5GHz SRL4W 65W LGA1700 Desktop</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
@@ -8036,34 +8842,34 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
-        <v>5664</v>
+        <v>149.99</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>eBay API; vendedor techrec-recycling 99.6%; Intel Core i5-13400 2.50GHz 10-Core LGA1700 20MB Desktop Pro</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
@@ -8074,11 +8880,11 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -8088,20 +8894,20 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E100" s="11" t="n">
-        <v>2537</v>
+        <v>134</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>eBay API; vendedor htam86 99.7%; Intel Core i5-14400F 10-Core 16-Thread 4.7GHz LGA 1700 CPU S</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
@@ -8112,34 +8918,34 @@
     </row>
     <row r="101">
       <c r="A101" s="15" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
-        <v>3127</v>
+        <v>229</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t>eBay API; vendedor archyinva 99.7%; Intel Core Ultra 7 265K 3.90GHz 20 Core Processor LGA 1851 S</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
@@ -8150,34 +8956,34 @@
     </row>
     <row r="102">
       <c r="A102" s="15" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E102" s="11" t="n">
-        <v>2150</v>
+        <v>379.99</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t>eBay API; vendedor nn-red 100.0%; Corsair Vengeance RGB Pro 32GB (2x16GB) RAM DDR5 5600MHz CMH; envío no indicado</t>
         </is>
       </c>
       <c r="H102" s="6" t="inlineStr">
@@ -8188,34 +8994,34 @@
     </row>
     <row r="103">
       <c r="A103" s="15" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
-        <v>6140</v>
+        <v>399.9</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t>eBay API; vendedor thaigamer 100.0%; Corsair Vengeance RGB DDR5 32GB (2x16GB) 6000MHz DIMM RGB CM; envío no indicado</t>
         </is>
       </c>
       <c r="H103" s="6" t="inlineStr">
@@ -8226,34 +9032,34 @@
     </row>
     <row r="104">
       <c r="A104" s="15" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E104" s="11" t="n">
-        <v>4760</v>
+        <v>65</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>eBay API; vendedor wasatch_pilot 100.0%; Crucial Ballistix 16GB (2x8GB) DDR4-3200 CL16 Red Desktop RA; envío no indicado</t>
         </is>
       </c>
       <c r="H104" s="6" t="inlineStr">
@@ -8264,34 +9070,34 @@
     </row>
     <row r="105">
       <c r="A105" s="15" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
-        <v>6800</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor mmm-electronics 100.0%; Solidigm P41 Plus 1TB NVMe M.2 2280 PCIe 4.0 SSD SSDPFKNU010; envío no indicado</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
@@ -8302,34 +9108,34 @@
     </row>
     <row r="106">
       <c r="A106" s="15" t="n">
-        <v>46307</v>
+        <v>46309</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E106" s="11" t="n">
-        <v>2100</v>
+        <v>164.99</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>eBay API; vendedor nixs-surplus 100.0%; WD Black SN750 2TB NVMe PCIe3.0 M.2 2280 Internal SSD WDBRPG</t>
         </is>
       </c>
       <c r="H106" s="6" t="inlineStr">
@@ -8340,7 +9146,7 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
@@ -8349,16 +9155,16 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
-        <v>1800</v>
+        <v>5580</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
@@ -8367,7 +9173,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
@@ -8378,25 +9184,25 @@
     </row>
     <row r="108">
       <c r="A108" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E108" s="11" t="n">
-        <v>4500</v>
+        <v>2300</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
@@ -8405,7 +9211,7 @@
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
@@ -8416,7 +9222,7 @@
     </row>
     <row r="109">
       <c r="A109" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
@@ -8425,16 +9231,16 @@
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
-        <v>6700</v>
+        <v>3950</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
@@ -8443,7 +9249,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
@@ -8454,25 +9260,25 @@
     </row>
     <row r="110">
       <c r="A110" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E110" s="11" t="n">
-        <v>2520</v>
+        <v>4800</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
@@ -8481,7 +9287,7 @@
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
@@ -8492,25 +9298,25 @@
     </row>
     <row r="111">
       <c r="A111" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
-        <v>4290</v>
+        <v>5190</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
@@ -8519,7 +9325,7 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
@@ -8530,25 +9336,25 @@
     </row>
     <row r="112">
       <c r="A112" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E112" s="11" t="n">
-        <v>2860</v>
+        <v>5390</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
@@ -8557,7 +9363,7 @@
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
@@ -8568,25 +9374,25 @@
     </row>
     <row r="113">
       <c r="A113" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
-        <v>2460</v>
+        <v>2000</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
@@ -8595,7 +9401,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
@@ -8606,25 +9412,25 @@
     </row>
     <row r="114">
       <c r="A114" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E114" s="11" t="n">
-        <v>5360</v>
+        <v>2650</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
@@ -8633,7 +9439,7 @@
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
@@ -8644,25 +9450,25 @@
     </row>
     <row r="115">
       <c r="A115" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
-        <v>1710</v>
+        <v>2700</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
@@ -8671,7 +9477,7 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
@@ -8682,25 +9488,25 @@
     </row>
     <row r="116">
       <c r="A116" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E116" s="11" t="n">
-        <v>2310</v>
+        <v>6200</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
@@ -8709,7 +9515,7 @@
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -8720,11 +9526,11 @@
     </row>
     <row r="117">
       <c r="A117" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
@@ -8734,11 +9540,11 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
-        <v>2160</v>
+        <v>540</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
@@ -8747,7 +9553,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
@@ -8758,25 +9564,25 @@
     </row>
     <row r="118">
       <c r="A118" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E118" s="11" t="n">
-        <v>5360</v>
+        <v>900</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
@@ -8785,7 +9591,7 @@
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
@@ -8796,25 +9602,25 @@
     </row>
     <row r="119">
       <c r="A119" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
-        <v>5660</v>
+        <v>1500</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
@@ -8823,7 +9629,7 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
@@ -8834,25 +9640,25 @@
     </row>
     <row r="120">
       <c r="A120" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E120" s="11" t="n">
-        <v>5860</v>
+        <v>1500</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
@@ -8861,7 +9667,7 @@
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
@@ -8872,11 +9678,11 @@
     </row>
     <row r="121">
       <c r="A121" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
@@ -8886,11 +9692,11 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
@@ -8899,7 +9705,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
@@ -8910,11 +9716,11 @@
     </row>
     <row r="122">
       <c r="A122" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -8924,11 +9730,11 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E122" s="11" t="n">
-        <v>2060</v>
+        <v>2000</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
@@ -8937,7 +9743,7 @@
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
@@ -8948,11 +9754,11 @@
     </row>
     <row r="123">
       <c r="A123" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
@@ -8962,11 +9768,11 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
-        <v>2152</v>
+        <v>1800</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
@@ -8975,7 +9781,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
@@ -8986,11 +9792,11 @@
     </row>
     <row r="124">
       <c r="A124" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -9000,11 +9806,11 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E124" s="11" t="n">
-        <v>4060</v>
+        <v>3550</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
@@ -9013,7 +9819,7 @@
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
@@ -9033,16 +9839,16 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
-        <v>4560</v>
+        <v>5664</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
@@ -9051,7 +9857,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
@@ -9071,16 +9877,16 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E126" s="11" t="n">
-        <v>5500</v>
+        <v>2537</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
@@ -9089,7 +9895,7 @@
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
@@ -9109,16 +9915,16 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
-        <v>2500</v>
+        <v>3127</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
@@ -9127,7 +9933,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
@@ -9147,16 +9953,16 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Compucenter (WhatsApp)</t>
         </is>
       </c>
       <c r="E128" s="11" t="n">
-        <v>5200</v>
+        <v>2150</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
@@ -9165,7 +9971,7 @@
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -9176,7 +9982,7 @@
     </row>
     <row r="129">
       <c r="A129" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
@@ -9185,16 +9991,16 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
-        <v>5500</v>
+        <v>6140</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
@@ -9203,14 +10009,18 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="n"/>
+          <t>nuevo OEM (garantía 6 meses)</t>
+        </is>
+      </c>
+      <c r="H129" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
@@ -9219,16 +10029,16 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E130" s="11" t="n">
-        <v>2460</v>
+        <v>4760</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
@@ -9237,14 +10047,18 @@
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="n"/>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
@@ -9253,16 +10067,16 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
-        <v>2500</v>
+        <v>6800</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
@@ -9271,14 +10085,18 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="n"/>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
@@ -9287,16 +10105,16 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E132" s="11" t="n">
-        <v>6840</v>
+        <v>2100</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
@@ -9305,32 +10123,36 @@
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="n"/>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
@@ -9339,7 +10161,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -9350,37 +10172,1009 @@
     </row>
     <row r="134">
       <c r="A134" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="n">
+        <v>6700</v>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G135" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="n">
+        <v>2520</v>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G136" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v>4290</v>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G137" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G138" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G139" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G140" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E141" s="11" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G141" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v>5660</v>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>5860</v>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v>1860</v>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E148" s="11" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F148" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H148" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>2152</v>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G149" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H149" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H150" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C151" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E151" s="11" t="n">
+        <v>4560</v>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H151" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C152" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E152" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F152" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H152" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G153" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H153" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E154" s="11" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H154" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="15" t="n">
         <v>46308</v>
       </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="B155" s="5" t="inlineStr">
         <is>
           <t>Tienda</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr">
+      <c r="C155" s="5" t="inlineStr">
         <is>
           <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
-      <c r="D134" s="5" t="inlineStr">
+      <c r="D155" s="5" t="inlineStr">
         <is>
           <t>OverCity (WhatsApp)</t>
         </is>
       </c>
-      <c r="E134" s="11" t="n">
+      <c r="E155" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G155" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C156" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E156" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F156" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G156" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C157" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E157" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G157" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C158" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E158" s="11" t="n">
+        <v>6840</v>
+      </c>
+      <c r="F158" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C159" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+        </is>
+      </c>
+      <c r="E159" s="11" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+        </is>
+      </c>
+      <c r="H159" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E160" s="11" t="n">
         <v>5350</v>
       </c>
-      <c r="F134" s="5" t="inlineStr">
+      <c r="F160" s="5" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
       </c>
-      <c r="G134" s="5" t="inlineStr">
+      <c r="G160" s="5" t="inlineStr">
         <is>
           <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
         </is>
       </c>
-      <c r="H134" s="2" t="n"/>
+      <c r="H160" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9511,11 +11305,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId125"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId154"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId129"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId155"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historial" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hoy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Historial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Supuestos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Dólar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Movimientos" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H160" headerRowCount="1">
-  <autoFilter ref="A1:H160"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H163" headerRowCount="1">
+  <autoFilter ref="A1:H163"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -5099,7 +5099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11175,6 +11175,116 @@
         </is>
       </c>
       <c r="H160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="n">
+        <v>7400</v>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H161" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (web)</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="n">
+        <v>2953</v>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i9-14900K</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Crazy Store (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="n">
+        <v>6013</v>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11332,10 +11442,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId156"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId155"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId157"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O53" headerRowCount="1">
-  <autoFilter ref="A1:O53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O67" headerRowCount="1">
+  <autoFilter ref="A1:O67"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H163" headerRowCount="1">
-  <autoFilter ref="A1:H163"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H189" headerRowCount="1">
+  <autoFilter ref="A1:H189"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -633,7 +633,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>¿Qué conviene traer? · 14/10/2026</t>
+          <t>¿Qué conviene traer? · 15/10/2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>121.99</v>
+        <v>120</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>164.99</v>
+        <v>175</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>120.99</v>
+        <v>114.99</v>
       </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="8" t="n">
@@ -1059,13 +1059,13 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>275.99</v>
+        <v>279.99</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>4800</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>134</v>
+        <v>134.99</v>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="8" t="n">
@@ -1197,7 +1197,7 @@
         <v>10.99</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>399.9</v>
+        <v>394.99</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>6200</v>
@@ -1256,13 +1256,13 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>117.99</v>
+        <v>128.99</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>1800</v>
@@ -1309,12 +1309,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1323,18 +1323,18 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>499.99</v>
+        <v>429.97</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="8" t="n">
-        <v>5580</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1344,7 +1344,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="L13" s="11">
         <f>IF(D13="","",MIN(MAX(Supuestos!$B$5,CEILING((K13*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D13*Supuestos!$B$9))</f>
@@ -1388,13 +1388,13 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>72.98999999999999</v>
+        <v>75</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>65</v>
+        <v>73.95</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>900</v>
@@ -1441,12 +1441,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1455,18 +1455,18 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>429.97</v>
+        <v>259.78</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>379.99</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H15" s="2" t="n"/>
+        <v>149.99</v>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="I15" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="K15" s="8" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="L15" s="11">
         <f>IF(D15="","",MIN(MAX(Supuestos!$B$5,CEILING((K15*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D15*Supuestos!$B$9))</f>
@@ -1506,7 +1506,7 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1520,17 +1520,17 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>259.78</v>
+        <v>689.34</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>149.99</v>
+        <v>375</v>
       </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="8" t="n">
-        <v>2300</v>
+        <v>5580</v>
       </c>
       <c r="I16" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1541,7 +1541,7 @@
         <v/>
       </c>
       <c r="K16" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L16" s="11">
         <f>IF(D16="","",MIN(MAX(Supuestos!$B$5,CEILING((K16*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D16*Supuestos!$B$9))</f>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>129.99</v>
+        <v>135</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>209.99</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>164.99</v>
+        <v>175</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="K2" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L2" s="16">
         <f>IF(OR($K2="",D2=""),"",IF(COUNTIFS($B:$B,$B2,$A:$A,$K2,D:D,"&gt;=0")=0,"",D2-SUMIFS(D:D,$B:$B,$B2,$A:$A,$K2)))</f>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>117.99</v>
+        <v>128.99</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L3" s="16">
         <f>IF(OR($K3="",D3=""),"",IF(COUNTIFS($B:$B,$B3,$A:$A,$K3,D:D,"&gt;=0")=0,"",D3-SUMIFS(D:D,$B:$B,$B3,$A:$A,$K3)))</f>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>499.99</v>
+        <v>689.34</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>454.99</v>
+        <v>375</v>
       </c>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L4" s="16">
         <f>IF(OR($K4="",D4=""),"",IF(COUNTIFS($B:$B,$B4,$A:$A,$K4,D:D,"&gt;=0")=0,"",D4-SUMIFS(D:D,$B:$B,$B4,$A:$A,$K4)))</f>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -2050,10 +2050,10 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>275.99</v>
+        <v>279.99</v>
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L5" s="16">
         <f>IF(OR($K5="",D5=""),"",IF(COUNTIFS($B:$B,$B5,$A:$A,$K5,D:D,"&gt;=0")=0,"",D5-SUMIFS(D:D,$B:$B,$B5,$A:$A,$K5)))</f>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>142.24</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>121.99</v>
+        <v>120</v>
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L7" s="16">
         <f>IF(OR($K7="",D7=""),"",IF(COUNTIFS($B:$B,$B7,$A:$A,$K7,D:D,"&gt;=0")=0,"",D7-SUMIFS(D:D,$B:$B,$B7,$A:$A,$K7)))</f>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>138.9</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>129.99</v>
+        <v>135</v>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L8" s="16">
         <f>IF(OR($K8="",D8=""),"",IF(COUNTIFS($B:$B,$B8,$A:$A,$K8,D:D,"&gt;=0")=0,"",D8-SUMIFS(D:D,$B:$B,$B8,$A:$A,$K8)))</f>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>72.98999999999999</v>
+        <v>75</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>65</v>
+        <v>73.95</v>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L9" s="16">
         <f>IF(OR($K9="",D9=""),"",IF(COUNTIFS($B:$B,$B9,$A:$A,$K9,D:D,"&gt;=0")=0,"",D9-SUMIFS(D:D,$B:$B,$B9,$A:$A,$K9)))</f>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>164.49</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>134</v>
+        <v>134.99</v>
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L10" s="16">
         <f>IF(OR($K10="",D10=""),"",IF(COUNTIFS($B:$B,$B10,$A:$A,$K10,D:D,"&gt;=0")=0,"",D10-SUMIFS(D:D,$B:$B,$B10,$A:$A,$K10)))</f>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L11" s="16">
         <f>IF(OR($K11="",D11=""),"",IF(COUNTIFS($B:$B,$B11,$A:$A,$K11,D:D,"&gt;=0")=0,"",D11-SUMIFS(D:D,$B:$B,$B11,$A:$A,$K11)))</f>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>120.99</v>
+        <v>114.99</v>
       </c>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L12" s="16">
         <f>IF(OR($K12="",D12=""),"",IF(COUNTIFS($B:$B,$B12,$A:$A,$K12,D:D,"&gt;=0")=0,"",D12-SUMIFS(D:D,$B:$B,$B12,$A:$A,$K12)))</f>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L13" s="16">
         <f>IF(OR($K13="",D13=""),"",IF(COUNTIFS($B:$B,$B13,$A:$A,$K13,D:D,"&gt;=0")=0,"",D13-SUMIFS(D:D,$B:$B,$B13,$A:$A,$K13)))</f>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>435.99</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>399.9</v>
+        <v>394.99</v>
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L14" s="16">
         <f>IF(OR($K14="",D14=""),"",IF(COUNTIFS($B:$B,$B14,$A:$A,$K14,D:D,"&gt;=0")=0,"",D14-SUMIFS(D:D,$B:$B,$B14,$A:$A,$K14)))</f>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>429.97</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="K15" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L15" s="16">
         <f>IF(OR($K15="",D15=""),"",IF(COUNTIFS($B:$B,$B15,$A:$A,$K15,D:D,"&gt;=0")=0,"",D15-SUMIFS(D:D,$B:$B,$B15,$A:$A,$K15)))</f>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>209.99</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>170</v>
+        <v>164.99</v>
       </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>114.99</v>
+        <v>117.99</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="K17" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L17" s="16">
         <f>IF(OR($K17="",D17=""),"",IF(COUNTIFS($B:$B,$B17,$A:$A,$K17,D:D,"&gt;=0")=0,"",D17-SUMIFS(D:D,$B:$B,$B17,$A:$A,$K17)))</f>
@@ -2748,7 +2748,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="K18" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L18" s="16">
         <f>IF(OR($K18="",D18=""),"",IF(COUNTIFS($B:$B,$B18,$A:$A,$K18,D:D,"&gt;=0")=0,"",D18-SUMIFS(D:D,$B:$B,$B18,$A:$A,$K18)))</f>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2819,14 +2819,10 @@
         <v>329</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>5350</v>
-      </c>
+        <v>275.99</v>
+      </c>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
       <c r="H19" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2841,7 +2837,7 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L19" s="16">
         <f>IF(OR($K19="",D19=""),"",IF(COUNTIFS($B:$B,$B19,$A:$A,$K19,D:D,"&gt;=0")=0,"",D19-SUMIFS(D:D,$B:$B,$B19,$A:$A,$K19)))</f>
@@ -2862,7 +2858,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2876,7 +2872,7 @@
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>299.99</v>
+        <v>295</v>
       </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -2894,7 +2890,7 @@
         </is>
       </c>
       <c r="K20" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L20" s="16">
         <f>IF(OR($K20="",D20=""),"",IF(COUNTIFS($B:$B,$B20,$A:$A,$K20,D:D,"&gt;=0")=0,"",D20-SUMIFS(D:D,$B:$B,$B20,$A:$A,$K20)))</f>
@@ -2915,7 +2911,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -2928,10 +2924,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>143.24</v>
+        <v>142.24</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>122.99</v>
+        <v>121.99</v>
       </c>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
@@ -2949,7 +2945,7 @@
         </is>
       </c>
       <c r="K21" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L21" s="16">
         <f>IF(OR($K21="",D21=""),"",IF(COUNTIFS($B:$B,$B21,$A:$A,$K21,D:D,"&gt;=0")=0,"",D21-SUMIFS(D:D,$B:$B,$B21,$A:$A,$K21)))</f>
@@ -2970,7 +2966,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -2986,7 +2982,7 @@
         <v>138.9</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
@@ -3004,7 +3000,7 @@
         </is>
       </c>
       <c r="K22" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
@@ -3025,7 +3021,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -3038,10 +3034,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>65</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -3059,7 +3055,7 @@
         </is>
       </c>
       <c r="K23" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L23" s="16">
         <f>IF(OR($K23="",D23=""),"",IF(COUNTIFS($B:$B,$B23,$A:$A,$K23,D:D,"&gt;=0")=0,"",D23-SUMIFS(D:D,$B:$B,$B23,$A:$A,$K23)))</f>
@@ -3080,7 +3076,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -3099,9 +3095,7 @@
         <v>134</v>
       </c>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G24" s="2" t="n"/>
       <c r="H24" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3116,7 +3110,7 @@
         </is>
       </c>
       <c r="K24" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L24" s="16">
         <f>IF(OR($K24="",D24=""),"",IF(COUNTIFS($B:$B,$B24,$A:$A,$K24,D:D,"&gt;=0")=0,"",D24-SUMIFS(D:D,$B:$B,$B24,$A:$A,$K24)))</f>
@@ -3137,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -3169,7 +3163,7 @@
         </is>
       </c>
       <c r="K25" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L25" s="16">
         <f>IF(OR($K25="",D25=""),"",IF(COUNTIFS($B:$B,$B25,$A:$A,$K25,D:D,"&gt;=0")=0,"",D25-SUMIFS(D:D,$B:$B,$B25,$A:$A,$K25)))</f>
@@ -3190,7 +3184,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3206,7 +3200,7 @@
         <v>150</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>99</v>
+        <v>120.99</v>
       </c>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
@@ -3224,7 +3218,7 @@
         </is>
       </c>
       <c r="K26" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L26" s="16">
         <f>IF(OR($K26="",D26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,D:D,"&gt;=0")=0,"",D26-SUMIFS(D:D,$B:$B,$B26,$A:$A,$K26)))</f>
@@ -3245,7 +3239,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3261,7 +3255,7 @@
         <v>234.99</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>209.99</v>
+        <v>229</v>
       </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
@@ -3279,7 +3273,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L27" s="16">
         <f>IF(OR($K27="",D27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,D:D,"&gt;=0")=0,"",D27-SUMIFS(D:D,$B:$B,$B27,$A:$A,$K27)))</f>
@@ -3300,7 +3294,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -3334,7 +3328,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L28" s="16">
         <f>IF(OR($K28="",D28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,D:D,"&gt;=0")=0,"",D28-SUMIFS(D:D,$B:$B,$B28,$A:$A,$K28)))</f>
@@ -3355,7 +3349,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -3368,10 +3362,10 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>493</v>
+        <v>429.97</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>383.99</v>
+        <v>379.99</v>
       </c>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
@@ -3389,7 +3383,7 @@
         </is>
       </c>
       <c r="K29" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L29" s="16">
         <f>IF(OR($K29="",D29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,D:D,"&gt;=0")=0,"",D29-SUMIFS(D:D,$B:$B,$B29,$A:$A,$K29)))</f>
@@ -3410,7 +3404,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3426,12 +3420,10 @@
         <v>209.99</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>179.99</v>
+        <v>170</v>
       </c>
       <c r="F30" s="2" t="n"/>
-      <c r="G30" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G30" s="2" t="n"/>
       <c r="H30" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A30,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A30,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3446,7 +3438,7 @@
         </is>
       </c>
       <c r="K30" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L30" s="16">
         <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
@@ -3467,7 +3459,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3486,9 +3478,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F31" s="2" t="n"/>
-      <c r="G31" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G31" s="2" t="n"/>
       <c r="H31" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3503,7 +3493,7 @@
         </is>
       </c>
       <c r="K31" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L31" s="16">
         <f>IF(OR($K31="",D31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,D:D,"&gt;=0")=0,"",D31-SUMIFS(D:D,$B:$B,$B31,$A:$A,$K31)))</f>
@@ -3524,7 +3514,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3543,9 +3533,7 @@
         <v>454.99</v>
       </c>
       <c r="F32" s="2" t="n"/>
-      <c r="G32" s="8" t="n">
-        <v>6140</v>
-      </c>
+      <c r="G32" s="2" t="n"/>
       <c r="H32" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A32,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A32,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3560,7 +3548,7 @@
         </is>
       </c>
       <c r="K32" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L32" s="16">
         <f>IF(OR($K32="",D32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,D:D,"&gt;=0")=0,"",D32-SUMIFS(D:D,$B:$B,$B32,$A:$A,$K32)))</f>
@@ -3581,7 +3569,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3599,9 +3587,11 @@
       <c r="E33" s="7" t="n">
         <v>283.99</v>
       </c>
-      <c r="F33" s="2" t="n"/>
+      <c r="F33" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="G33" s="8" t="n">
-        <v>4760</v>
+        <v>5350</v>
       </c>
       <c r="H33" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))),"")</f>
@@ -3617,7 +3607,7 @@
         </is>
       </c>
       <c r="K33" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L33" s="16">
         <f>IF(OR($K33="",D33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,D:D,"&gt;=0")=0,"",D33-SUMIFS(D:D,$B:$B,$B33,$A:$A,$K33)))</f>
@@ -3638,7 +3628,7 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -3652,7 +3642,7 @@
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
@@ -3669,7 +3659,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K34" s="5" t="n"/>
+      <c r="K34" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L34" s="16">
         <f>IF(OR($K34="",D34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,D:D,"&gt;=0")=0,"",D34-SUMIFS(D:D,$B:$B,$B34,$A:$A,$K34)))</f>
         <v/>
@@ -3689,7 +3681,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3702,15 +3694,13 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>144.25</v>
+        <v>143.24</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>122.99</v>
       </c>
       <c r="F35" s="2" t="n"/>
-      <c r="G35" s="8" t="n">
-        <v>2860</v>
-      </c>
+      <c r="G35" s="2" t="n"/>
       <c r="H35" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3725,7 +3715,7 @@
         </is>
       </c>
       <c r="K35" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L35" s="16">
         <f>IF(OR($K35="",D35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,D:D,"&gt;=0")=0,"",D35-SUMIFS(D:D,$B:$B,$B35,$A:$A,$K35)))</f>
@@ -3746,7 +3736,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -3779,7 +3769,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K36" s="5" t="n"/>
+      <c r="K36" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L36" s="16">
         <f>IF(OR($K36="",D36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,D:D,"&gt;=0")=0,"",D36-SUMIFS(D:D,$B:$B,$B36,$A:$A,$K36)))</f>
         <v/>
@@ -3799,7 +3791,7 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -3812,15 +3804,13 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>75</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>59.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F37" s="2" t="n"/>
-      <c r="G37" s="8" t="n">
-        <v>2150</v>
-      </c>
+      <c r="G37" s="2" t="n"/>
       <c r="H37" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A37,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A37,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3835,7 +3825,7 @@
         </is>
       </c>
       <c r="K37" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L37" s="16">
         <f>IF(OR($K37="",D37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,D:D,"&gt;=0")=0,"",D37-SUMIFS(D:D,$B:$B,$B37,$A:$A,$K37)))</f>
@@ -3856,7 +3846,7 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3872,11 +3862,11 @@
         <v>164.49</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="8" t="n">
-        <v>2520</v>
+        <v>2460</v>
       </c>
       <c r="H38" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))),"")</f>
@@ -3892,7 +3882,7 @@
         </is>
       </c>
       <c r="K38" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L38" s="16">
         <f>IF(OR($K38="",D38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,D:D,"&gt;=0")=0,"",D38-SUMIFS(D:D,$B:$B,$B38,$A:$A,$K38)))</f>
@@ -3913,7 +3903,7 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3925,9 +3915,7 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D39" s="7" t="n">
-        <v>259.78</v>
-      </c>
+      <c r="D39" s="2" t="n"/>
       <c r="E39" s="7" t="n">
         <v>149.99</v>
       </c>
@@ -3947,7 +3935,7 @@
         </is>
       </c>
       <c r="K39" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L39" s="16">
         <f>IF(OR($K39="",D39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,D:D,"&gt;=0")=0,"",D39-SUMIFS(D:D,$B:$B,$B39,$A:$A,$K39)))</f>
@@ -3968,7 +3956,7 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3984,12 +3972,10 @@
         <v>150</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="F40" s="2" t="n"/>
-      <c r="G40" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G40" s="2" t="n"/>
       <c r="H40" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A40,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A40,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4003,7 +3989,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K40" s="5" t="n"/>
+      <c r="K40" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L40" s="16">
         <f>IF(OR($K40="",D40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,D:D,"&gt;=0")=0,"",D40-SUMIFS(D:D,$B:$B,$B40,$A:$A,$K40)))</f>
         <v/>
@@ -4023,7 +4011,7 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -4036,15 +4024,13 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>209.99</v>
       </c>
       <c r="F41" s="2" t="n"/>
-      <c r="G41" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G41" s="2" t="n"/>
       <c r="H41" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A41,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A41,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4059,7 +4045,7 @@
         </is>
       </c>
       <c r="K41" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L41" s="16">
         <f>IF(OR($K41="",D41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,D:D,"&gt;=0")=0,"",D41-SUMIFS(D:D,$B:$B,$B41,$A:$A,$K41)))</f>
@@ -4080,7 +4066,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4114,7 +4100,7 @@
         </is>
       </c>
       <c r="K42" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L42" s="16">
         <f>IF(OR($K42="",D42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,D:D,"&gt;=0")=0,"",D42-SUMIFS(D:D,$B:$B,$B42,$A:$A,$K42)))</f>
@@ -4135,7 +4121,7 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4151,11 +4137,9 @@
         <v>493</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F43" s="8" t="n">
-        <v>4500</v>
-      </c>
+        <v>383.99</v>
+      </c>
+      <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
       <c r="H43" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A43,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A43,Dólar!$A:$A,0))),"")</f>
@@ -4170,7 +4154,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K43" s="5" t="n"/>
+      <c r="K43" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L43" s="16">
         <f>IF(OR($K43="",D43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,D:D,"&gt;=0")=0,"",D43-SUMIFS(D:D,$B:$B,$B43,$A:$A,$K43)))</f>
         <v/>
@@ -4190,7 +4176,7 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4202,10 +4188,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
+      <c r="D44" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>179.99</v>
+      </c>
       <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
+      <c r="G44" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H44" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A44,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A44,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4214,8 +4206,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A44,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="5" t="n"/>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K44" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L44" s="16">
         <f>IF(OR($K44="",D44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,D:D,"&gt;=0")=0,"",D44-SUMIFS(D:D,$B:$B,$B44,$A:$A,$K44)))</f>
         <v/>
@@ -4235,7 +4233,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
@@ -4247,12 +4245,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G45" s="2" t="n"/>
+      <c r="D45" s="7" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F45" s="2" t="n"/>
+      <c r="G45" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H45" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4266,7 +4268,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K45" s="5" t="n"/>
+      <c r="K45" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L45" s="16">
         <f>IF(OR($K45="",D45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,D:D,"&gt;=0")=0,"",D45-SUMIFS(D:D,$B:$B,$B45,$A:$A,$K45)))</f>
         <v/>
@@ -4286,7 +4290,7 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -4298,11 +4302,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
+      <c r="D46" s="7" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>454.99</v>
+      </c>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="8" t="n">
-        <v>5580</v>
+        <v>6140</v>
       </c>
       <c r="H46" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A46,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A46,Dólar!$A:$A,0))),"")</f>
@@ -4317,7 +4325,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K46" s="5" t="n"/>
+      <c r="K46" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L46" s="16">
         <f>IF(OR($K46="",D46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,D:D,"&gt;=0")=0,"",D46-SUMIFS(D:D,$B:$B,$B46,$A:$A,$K46)))</f>
         <v/>
@@ -4337,7 +4347,7 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
@@ -4349,12 +4359,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="n"/>
-      <c r="F47" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G47" s="2" t="n"/>
+      <c r="D47" s="7" t="n">
+        <v>329</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="H47" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4368,7 +4382,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K47" s="5" t="n"/>
+      <c r="K47" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L47" s="16">
         <f>IF(OR($K47="",D47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,D:D,"&gt;=0")=0,"",D47-SUMIFS(D:D,$B:$B,$B47,$A:$A,$K47)))</f>
         <v/>
@@ -4388,11 +4404,11 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4401,7 +4417,9 @@
         </is>
       </c>
       <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
+      <c r="E48" s="7" t="n">
+        <v>305</v>
+      </c>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="9">
@@ -4412,7 +4430,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A48,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J48" s="2" t="n"/>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K48" s="5" t="n"/>
       <c r="L48" s="16">
         <f>IF(OR($K48="",D48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,D:D,"&gt;=0")=0,"",D48-SUMIFS(D:D,$B:$B,$B48,$A:$A,$K48)))</f>
@@ -4433,24 +4455,28 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="G49" s="2" t="n"/>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="F49" s="2" t="n"/>
+      <c r="G49" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H49" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4464,7 +4490,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K49" s="5" t="n"/>
+      <c r="K49" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L49" s="16">
         <f>IF(OR($K49="",D49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,D:D,"&gt;=0")=0,"",D49-SUMIFS(D:D,$B:$B,$B49,$A:$A,$K49)))</f>
         <v/>
@@ -4484,11 +4512,11 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -4496,8 +4524,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
+      <c r="D50" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="9">
@@ -4508,7 +4540,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A50,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J50" s="2" t="n"/>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K50" s="5" t="n"/>
       <c r="L50" s="16">
         <f>IF(OR($K50="",D50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,D:D,"&gt;=0")=0,"",D50-SUMIFS(D:D,$B:$B,$B50,$A:$A,$K50)))</f>
@@ -4529,23 +4565,27 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <v>59.99</v>
+      </c>
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="H51" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A51,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A51,Dólar!$A:$A,0))),"")</f>
@@ -4560,7 +4600,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K51" s="5" t="n"/>
+      <c r="K51" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L51" s="16">
         <f>IF(OR($K51="",D51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,D:D,"&gt;=0")=0,"",D51-SUMIFS(D:D,$B:$B,$B51,$A:$A,$K51)))</f>
         <v/>
@@ -4580,11 +4622,11 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -4592,11 +4634,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
+      <c r="D52" s="7" t="n">
+        <v>164.49</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>136.99</v>
+      </c>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="8" t="n">
-        <v>3950</v>
+        <v>2520</v>
       </c>
       <c r="H52" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))),"")</f>
@@ -4611,7 +4657,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K52" s="5" t="n"/>
+      <c r="K52" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L52" s="16">
         <f>IF(OR($K52="",D52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,D:D,"&gt;=0")=0,"",D52-SUMIFS(D:D,$B:$B,$B52,$A:$A,$K52)))</f>
         <v/>
@@ -4631,23 +4679,25 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="8" t="n">
-        <v>6200</v>
-      </c>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A53,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A53,Dólar!$A:$A,0))),"")</f>
@@ -4662,7 +4712,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K53" s="5" t="n"/>
+      <c r="K53" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L53" s="16">
         <f>IF(OR($K53="",D53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,D:D,"&gt;=0")=0,"",D53-SUMIFS(D:D,$B:$B,$B53,$A:$A,$K53)))</f>
         <v/>
@@ -4680,8 +4732,722 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="F54" s="2" t="n"/>
+      <c r="G54" s="8" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H54" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A54,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A54,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I54" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A54,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="16">
+        <f>IF(OR($K54="",D54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,D:D,"&gt;=0")=0,"",D54-SUMIFS(D:D,$B:$B,$B54,$A:$A,$K54)))</f>
+        <v/>
+      </c>
+      <c r="M54" s="16">
+        <f>IF(OR($K54="",E54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,E:E,"&gt;=0")=0,"",E54-SUMIFS(E:E,$B:$B,$B54,$A:$A,$K54)))</f>
+        <v/>
+      </c>
+      <c r="N54" s="16">
+        <f>IF(OR($K54="",F54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,F:F,"&gt;=0")=0,"",F54-SUMIFS(F:F,$B:$B,$B54,$A:$A,$K54)))</f>
+        <v/>
+      </c>
+      <c r="O54" s="16">
+        <f>IF(OR($K54="",G54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,G:G,"&gt;=0")=0,"",G54-SUMIFS(G:G,$B:$B,$B54,$A:$A,$K54)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="F55" s="2" t="n"/>
+      <c r="G55" s="8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H55" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A55,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A55,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I55" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A55,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K55" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L55" s="16">
+        <f>IF(OR($K55="",D55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,D:D,"&gt;=0")=0,"",D55-SUMIFS(D:D,$B:$B,$B55,$A:$A,$K55)))</f>
+        <v/>
+      </c>
+      <c r="M55" s="16">
+        <f>IF(OR($K55="",E55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,E:E,"&gt;=0")=0,"",E55-SUMIFS(E:E,$B:$B,$B55,$A:$A,$K55)))</f>
+        <v/>
+      </c>
+      <c r="N55" s="16">
+        <f>IF(OR($K55="",F55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,F:F,"&gt;=0")=0,"",F55-SUMIFS(F:F,$B:$B,$B55,$A:$A,$K55)))</f>
+        <v/>
+      </c>
+      <c r="O55" s="16">
+        <f>IF(OR($K55="",G55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,G:G,"&gt;=0")=0,"",G55-SUMIFS(G:G,$B:$B,$B55,$A:$A,$K55)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="F56" s="2" t="n"/>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A56,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A56,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I56" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A56,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K56" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L56" s="16">
+        <f>IF(OR($K56="",D56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,D:D,"&gt;=0")=0,"",D56-SUMIFS(D:D,$B:$B,$B56,$A:$A,$K56)))</f>
+        <v/>
+      </c>
+      <c r="M56" s="16">
+        <f>IF(OR($K56="",E56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,E:E,"&gt;=0")=0,"",E56-SUMIFS(E:E,$B:$B,$B56,$A:$A,$K56)))</f>
+        <v/>
+      </c>
+      <c r="N56" s="16">
+        <f>IF(OR($K56="",F56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,F:F,"&gt;=0")=0,"",F56-SUMIFS(F:F,$B:$B,$B56,$A:$A,$K56)))</f>
+        <v/>
+      </c>
+      <c r="O56" s="16">
+        <f>IF(OR($K56="",G56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,G:G,"&gt;=0")=0,"",G56-SUMIFS(G:G,$B:$B,$B56,$A:$A,$K56)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A57,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A57,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I57" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A57,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="16">
+        <f>IF(OR($K57="",D57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,D:D,"&gt;=0")=0,"",D57-SUMIFS(D:D,$B:$B,$B57,$A:$A,$K57)))</f>
+        <v/>
+      </c>
+      <c r="M57" s="16">
+        <f>IF(OR($K57="",E57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,E:E,"&gt;=0")=0,"",E57-SUMIFS(E:E,$B:$B,$B57,$A:$A,$K57)))</f>
+        <v/>
+      </c>
+      <c r="N57" s="16">
+        <f>IF(OR($K57="",F57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,F:F,"&gt;=0")=0,"",F57-SUMIFS(F:F,$B:$B,$B57,$A:$A,$K57)))</f>
+        <v/>
+      </c>
+      <c r="O57" s="16">
+        <f>IF(OR($K57="",G57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,G:G,"&gt;=0")=0,"",G57-SUMIFS(G:G,$B:$B,$B57,$A:$A,$K57)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n"/>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A58,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A58,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I58" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A58,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="16">
+        <f>IF(OR($K58="",D58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,D:D,"&gt;=0")=0,"",D58-SUMIFS(D:D,$B:$B,$B58,$A:$A,$K58)))</f>
+        <v/>
+      </c>
+      <c r="M58" s="16">
+        <f>IF(OR($K58="",E58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,E:E,"&gt;=0")=0,"",E58-SUMIFS(E:E,$B:$B,$B58,$A:$A,$K58)))</f>
+        <v/>
+      </c>
+      <c r="N58" s="16">
+        <f>IF(OR($K58="",F58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,F:F,"&gt;=0")=0,"",F58-SUMIFS(F:F,$B:$B,$B58,$A:$A,$K58)))</f>
+        <v/>
+      </c>
+      <c r="O58" s="16">
+        <f>IF(OR($K58="",G58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,G:G,"&gt;=0")=0,"",G58-SUMIFS(G:G,$B:$B,$B58,$A:$A,$K58)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I59" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A59,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="16">
+        <f>IF(OR($K59="",D59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,D:D,"&gt;=0")=0,"",D59-SUMIFS(D:D,$B:$B,$B59,$A:$A,$K59)))</f>
+        <v/>
+      </c>
+      <c r="M59" s="16">
+        <f>IF(OR($K59="",E59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,E:E,"&gt;=0")=0,"",E59-SUMIFS(E:E,$B:$B,$B59,$A:$A,$K59)))</f>
+        <v/>
+      </c>
+      <c r="N59" s="16">
+        <f>IF(OR($K59="",F59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,F:F,"&gt;=0")=0,"",F59-SUMIFS(F:F,$B:$B,$B59,$A:$A,$K59)))</f>
+        <v/>
+      </c>
+      <c r="O59" s="16">
+        <f>IF(OR($K59="",G59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,G:G,"&gt;=0")=0,"",G59-SUMIFS(G:G,$B:$B,$B59,$A:$A,$K59)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="H60" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A60,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A60,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I60" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A60,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="16">
+        <f>IF(OR($K60="",D60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,D:D,"&gt;=0")=0,"",D60-SUMIFS(D:D,$B:$B,$B60,$A:$A,$K60)))</f>
+        <v/>
+      </c>
+      <c r="M60" s="16">
+        <f>IF(OR($K60="",E60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,E:E,"&gt;=0")=0,"",E60-SUMIFS(E:E,$B:$B,$B60,$A:$A,$K60)))</f>
+        <v/>
+      </c>
+      <c r="N60" s="16">
+        <f>IF(OR($K60="",F60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,F:F,"&gt;=0")=0,"",F60-SUMIFS(F:F,$B:$B,$B60,$A:$A,$K60)))</f>
+        <v/>
+      </c>
+      <c r="O60" s="16">
+        <f>IF(OR($K60="",G60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,G:G,"&gt;=0")=0,"",G60-SUMIFS(G:G,$B:$B,$B60,$A:$A,$K60)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I61" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A61,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="16">
+        <f>IF(OR($K61="",D61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,D:D,"&gt;=0")=0,"",D61-SUMIFS(D:D,$B:$B,$B61,$A:$A,$K61)))</f>
+        <v/>
+      </c>
+      <c r="M61" s="16">
+        <f>IF(OR($K61="",E61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,E:E,"&gt;=0")=0,"",E61-SUMIFS(E:E,$B:$B,$B61,$A:$A,$K61)))</f>
+        <v/>
+      </c>
+      <c r="N61" s="16">
+        <f>IF(OR($K61="",F61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,F:F,"&gt;=0")=0,"",F61-SUMIFS(F:F,$B:$B,$B61,$A:$A,$K61)))</f>
+        <v/>
+      </c>
+      <c r="O61" s="16">
+        <f>IF(OR($K61="",G61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,G:G,"&gt;=0")=0,"",G61-SUMIFS(G:G,$B:$B,$B61,$A:$A,$K61)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n"/>
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A62,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A62,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I62" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A62,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J62" s="2" t="n"/>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="16">
+        <f>IF(OR($K62="",D62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,D:D,"&gt;=0")=0,"",D62-SUMIFS(D:D,$B:$B,$B62,$A:$A,$K62)))</f>
+        <v/>
+      </c>
+      <c r="M62" s="16">
+        <f>IF(OR($K62="",E62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,E:E,"&gt;=0")=0,"",E62-SUMIFS(E:E,$B:$B,$B62,$A:$A,$K62)))</f>
+        <v/>
+      </c>
+      <c r="N62" s="16">
+        <f>IF(OR($K62="",F62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,F:F,"&gt;=0")=0,"",F62-SUMIFS(F:F,$B:$B,$B62,$A:$A,$K62)))</f>
+        <v/>
+      </c>
+      <c r="O62" s="16">
+        <f>IF(OR($K62="",G62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,G:G,"&gt;=0")=0,"",G62-SUMIFS(G:G,$B:$B,$B62,$A:$A,$K62)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I63" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A63,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="16">
+        <f>IF(OR($K63="",D63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,D:D,"&gt;=0")=0,"",D63-SUMIFS(D:D,$B:$B,$B63,$A:$A,$K63)))</f>
+        <v/>
+      </c>
+      <c r="M63" s="16">
+        <f>IF(OR($K63="",E63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,E:E,"&gt;=0")=0,"",E63-SUMIFS(E:E,$B:$B,$B63,$A:$A,$K63)))</f>
+        <v/>
+      </c>
+      <c r="N63" s="16">
+        <f>IF(OR($K63="",F63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,F:F,"&gt;=0")=0,"",F63-SUMIFS(F:F,$B:$B,$B63,$A:$A,$K63)))</f>
+        <v/>
+      </c>
+      <c r="O63" s="16">
+        <f>IF(OR($K63="",G63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,G:G,"&gt;=0")=0,"",G63-SUMIFS(G:G,$B:$B,$B63,$A:$A,$K63)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A64,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A64,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I64" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A64,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="16">
+        <f>IF(OR($K64="",D64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,D:D,"&gt;=0")=0,"",D64-SUMIFS(D:D,$B:$B,$B64,$A:$A,$K64)))</f>
+        <v/>
+      </c>
+      <c r="M64" s="16">
+        <f>IF(OR($K64="",E64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,E:E,"&gt;=0")=0,"",E64-SUMIFS(E:E,$B:$B,$B64,$A:$A,$K64)))</f>
+        <v/>
+      </c>
+      <c r="N64" s="16">
+        <f>IF(OR($K64="",F64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,F:F,"&gt;=0")=0,"",F64-SUMIFS(F:F,$B:$B,$B64,$A:$A,$K64)))</f>
+        <v/>
+      </c>
+      <c r="O64" s="16">
+        <f>IF(OR($K64="",G64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,G:G,"&gt;=0")=0,"",G64-SUMIFS(G:G,$B:$B,$B64,$A:$A,$K64)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H65" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A65,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A65,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I65" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A65,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="16">
+        <f>IF(OR($K65="",D65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,D:D,"&gt;=0")=0,"",D65-SUMIFS(D:D,$B:$B,$B65,$A:$A,$K65)))</f>
+        <v/>
+      </c>
+      <c r="M65" s="16">
+        <f>IF(OR($K65="",E65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,E:E,"&gt;=0")=0,"",E65-SUMIFS(E:E,$B:$B,$B65,$A:$A,$K65)))</f>
+        <v/>
+      </c>
+      <c r="N65" s="16">
+        <f>IF(OR($K65="",F65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,F:F,"&gt;=0")=0,"",F65-SUMIFS(F:F,$B:$B,$B65,$A:$A,$K65)))</f>
+        <v/>
+      </c>
+      <c r="O65" s="16">
+        <f>IF(OR($K65="",G65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,G:G,"&gt;=0")=0,"",G65-SUMIFS(G:G,$B:$B,$B65,$A:$A,$K65)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n"/>
+      <c r="G66" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H66" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A66,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="16">
+        <f>IF(OR($K66="",D66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,D:D,"&gt;=0")=0,"",D66-SUMIFS(D:D,$B:$B,$B66,$A:$A,$K66)))</f>
+        <v/>
+      </c>
+      <c r="M66" s="16">
+        <f>IF(OR($K66="",E66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,E:E,"&gt;=0")=0,"",E66-SUMIFS(E:E,$B:$B,$B66,$A:$A,$K66)))</f>
+        <v/>
+      </c>
+      <c r="N66" s="16">
+        <f>IF(OR($K66="",F66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,F:F,"&gt;=0")=0,"",F66-SUMIFS(F:F,$B:$B,$B66,$A:$A,$K66)))</f>
+        <v/>
+      </c>
+      <c r="O66" s="16">
+        <f>IF(OR($K66="",G66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,G:G,"&gt;=0")=0,"",G66-SUMIFS(G:G,$B:$B,$B66,$A:$A,$K66)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A67,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A67,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A67,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="16">
+        <f>IF(OR($K67="",D67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,D:D,"&gt;=0")=0,"",D67-SUMIFS(D:D,$B:$B,$B67,$A:$A,$K67)))</f>
+        <v/>
+      </c>
+      <c r="M67" s="16">
+        <f>IF(OR($K67="",E67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,E:E,"&gt;=0")=0,"",E67-SUMIFS(E:E,$B:$B,$B67,$A:$A,$K67)))</f>
+        <v/>
+      </c>
+      <c r="N67" s="16">
+        <f>IF(OR($K67="",F67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,F:F,"&gt;=0")=0,"",F67-SUMIFS(F:F,$B:$B,$B67,$A:$A,$K67)))</f>
+        <v/>
+      </c>
+      <c r="O67" s="16">
+        <f>IF(OR($K67="",G67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,G:G,"&gt;=0")=0,"",G67-SUMIFS(G:G,$B:$B,$B67,$A:$A,$K67)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M53">
+  <conditionalFormatting sqref="L2:M67">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -4689,7 +5455,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O53">
+  <conditionalFormatting sqref="N2:O67">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -4740,17 +5506,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId63"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId50"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId64"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4915,7 +5695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5088,6 +5868,32 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="E7" s="10">
+        <f>IF(COUNT(C7:D7)=2,AVERAGE(C7:D7),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>BCB oficial 11.70; paralelo dolarbolivia.net 15/10 (compra 11.86 / venta 11.83; la página es inconsistente entre compra y venta); usado = promedio del paralelo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5099,7 +5905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9146,34 +9952,34 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
-        <v>5580</v>
+        <v>138.9</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; (New) AMD Ryzen 5 5600 Vermeer Zen3 6-Core 12-Thread AM4 CPU</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
@@ -9184,34 +9990,34 @@
     </row>
     <row r="108">
       <c r="A108" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E108" s="11" t="n">
-        <v>2300</v>
+        <v>142.24</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor silaxon 99.6%; AMD Ryzen 5 7600 3.80GHz 6 Core 12 Thread AM5 100-000001015</t>
         </is>
       </c>
       <c r="H108" s="6" t="inlineStr">
@@ -9222,34 +10028,34 @@
     </row>
     <row r="109">
       <c r="A109" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
-        <v>3950</v>
+        <v>320</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor am-834577 100.0%; AMD Ryzen 7 7800X3D 8-Core, 16-Thread Desktop Processor, Bra</t>
         </is>
       </c>
       <c r="H109" s="6" t="inlineStr">
@@ -9260,34 +10066,34 @@
     </row>
     <row r="110">
       <c r="A110" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E110" s="11" t="n">
-        <v>4800</v>
+        <v>689.34</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay API; vendedor tech-r-us-store 99.9%; AMD 100-100001277WOF Ryzen 9 9950X CPU 16 Cores 32 Threads u; envío no indicado</t>
         </is>
       </c>
       <c r="H110" s="6" t="inlineStr">
@@ -9298,34 +10104,34 @@
     </row>
     <row r="111">
       <c r="A111" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
-        <v>5190</v>
+        <v>150</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor algonz1137 100.0%; INTEL CPU Core i5-12400F / 6/12 / 2.5GHz / 6xxChipset / BX80; envío no indicado</t>
         </is>
       </c>
       <c r="H111" s="6" t="inlineStr">
@@ -9336,34 +10142,34 @@
     </row>
     <row r="112">
       <c r="A112" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E112" s="11" t="n">
-        <v>5390</v>
+        <v>164.49</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t xml:space="preserve">eBay API; vendedor newegg 99.6%; Intel Core i5-14400F - Core i5 14th Gen Raptor Lake 10-Core </t>
         </is>
       </c>
       <c r="H112" s="6" t="inlineStr">
@@ -9374,34 +10180,34 @@
     </row>
     <row r="113">
       <c r="A113" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
-        <v>2000</v>
+        <v>234.99</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor good_neighbor_mercantile 99.4%; Intel Core Ultra 7 265K CPU Desktop Processor LGA 1851 20-Co</t>
         </is>
       </c>
       <c r="H113" s="6" t="inlineStr">
@@ -9412,34 +10218,34 @@
     </row>
     <row r="114">
       <c r="A114" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E114" s="11" t="n">
-        <v>2650</v>
+        <v>429.97</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor uventure 99.7%; NEW 32GB (2x16GB) Corsair Vengeance DDR5 PC5-5600 Desktop RA</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
@@ -9450,34 +10256,34 @@
     </row>
     <row r="115">
       <c r="A115" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
-        <v>2700</v>
+        <v>435.99</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>eBay API; vendedor wojiapanpan_4 100.0%; Corsair Vengeance RGB RS 32GB 2x16GB DDR5 6000 CL38 AMD EXPO</t>
         </is>
       </c>
       <c r="H115" s="6" t="inlineStr">
@@ -9488,34 +10294,34 @@
     </row>
     <row r="116">
       <c r="A116" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E116" s="11" t="n">
-        <v>6200</v>
+        <v>75</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t>eBay API; vendedor juniorarredondo 100.0%; Silicon Power Gaming Turbine 16GB (2x8GB) DDR4-3200 PC4-2560</t>
         </is>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -9526,34 +10332,34 @@
     </row>
     <row r="117">
       <c r="A117" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
-        <v>540</v>
+        <v>128.99</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>eBay API; vendedor netac-official-store 99.9%; Netac M.2 2280 1TB PCIe3.0 NVMe 1.4 3D NAND Internal Solid S</t>
         </is>
       </c>
       <c r="H117" s="6" t="inlineStr">
@@ -9564,34 +10370,34 @@
     </row>
     <row r="118">
       <c r="A118" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E118" s="11" t="n">
-        <v>900</v>
+        <v>209.99</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>eBay API; vendedor ram_technologies 100.0%; RAM Tech 2TB NVMe SSD Gen4 M.2 2280 | 5000MB/s Read 4500MB/s</t>
         </is>
       </c>
       <c r="H118" s="6" t="inlineStr">
@@ -9602,34 +10408,34 @@
     </row>
     <row r="119">
       <c r="A119" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
-        <v>1500</v>
+        <v>135</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>eBay API; vendedor btlsln 100.0%; AMD Ryzen 5 5600 Desktop Processor (6 Cores, Socket AM4); envío no indicado</t>
         </is>
       </c>
       <c r="H119" s="6" t="inlineStr">
@@ -9640,34 +10446,34 @@
     </row>
     <row r="120">
       <c r="A120" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E120" s="11" t="n">
-        <v>1500</v>
+        <v>295</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>eBay API; vendedor antonidelacru-7 98.0%; AMD Ryzen 7 5700X3D 8-Core Socket AM4 3.0GHz CPU 96MB L3 Cac; envío no indicado</t>
         </is>
       </c>
       <c r="H120" s="6" t="inlineStr">
@@ -9678,34 +10484,34 @@
     </row>
     <row r="121">
       <c r="A121" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
-        <v>1850</v>
+        <v>120</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>eBay API; vendedor shenidss9ckq 99.0%; AMD Ryzen 5 7600 3.80GHz 6 Core 100-000001015 12 Thread AM5</t>
         </is>
       </c>
       <c r="H121" s="6" t="inlineStr">
@@ -9716,34 +10522,34 @@
     </row>
     <row r="122">
       <c r="A122" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E122" s="11" t="n">
-        <v>2000</v>
+        <v>279.99</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>eBay API; vendedor paymore_summerlin 99.2%; AMD Ryzen 7 7800X3D 4.20GHz 8 Core 100-000000910 16 Thread A</t>
         </is>
       </c>
       <c r="H122" s="6" t="inlineStr">
@@ -9754,34 +10560,34 @@
     </row>
     <row r="123">
       <c r="A123" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
-        <v>1800</v>
+        <v>375</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>eBay API; vendedor jbfum_346 100.0%; AMD Ryzen 9 9950X - Granite Ridge (Zen 5) 16-Core 4.3 GHz AM; envío no indicado</t>
         </is>
       </c>
       <c r="H123" s="6" t="inlineStr">
@@ -9792,34 +10598,34 @@
     </row>
     <row r="124">
       <c r="A124" s="15" t="n">
-        <v>46306</v>
+        <v>46310</v>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E124" s="11" t="n">
-        <v>3550</v>
+        <v>114.99</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>eBay API; vendedor cc_us_jfuaoe 100.0%; Intel Core i5-12400F 12th Gen CPU LGA 1700 2.50GHz 10-Core 1; envío no indicado</t>
         </is>
       </c>
       <c r="H124" s="6" t="inlineStr">
@@ -9830,34 +10636,34 @@
     </row>
     <row r="125">
       <c r="A125" s="15" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
-        <v>5664</v>
+        <v>149.99</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>eBay API; vendedor techrec-recycling 99.6%; Intel Core i5-13400 2.50GHz 10-Core LGA1700 20MB Desktop Pro</t>
         </is>
       </c>
       <c r="H125" s="6" t="inlineStr">
@@ -9868,11 +10674,11 @@
     </row>
     <row r="126">
       <c r="A126" s="15" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
@@ -9882,20 +10688,20 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E126" s="11" t="n">
-        <v>2537</v>
+        <v>134.99</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>eBay API; vendedor wiifixitllc 99.0%; Intel Core i5-14400F 2.50GHz 10 Core  16 Thread LGA 1700</t>
         </is>
       </c>
       <c r="H126" s="6" t="inlineStr">
@@ -9906,34 +10712,34 @@
     </row>
     <row r="127">
       <c r="A127" s="15" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
-        <v>3127</v>
+        <v>229</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t>eBay API; vendedor archyinva 99.7%; Intel Core Ultra 7 265K 3.90GHz 20 Core Processor LGA 1851 S</t>
         </is>
       </c>
       <c r="H127" s="6" t="inlineStr">
@@ -9944,34 +10750,34 @@
     </row>
     <row r="128">
       <c r="A128" s="15" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E128" s="11" t="n">
-        <v>2150</v>
+        <v>375</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t>eBay API; vendedor rmbsr26 100.0%; CORSAIR - VENGEANCE 32GB (2x16GB) DDR5 5600MHz [CMK32GX5M2B5</t>
         </is>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -9982,34 +10788,34 @@
     </row>
     <row r="129">
       <c r="A129" s="15" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
-        <v>6140</v>
+        <v>394.99</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t>eBay API; vendedor briansdirectdeals 100.0%; Corsair Vengeance RGB DDR5 32GB (2x16GB) RAM 6000MHz CMH32GX; envío no indicado</t>
         </is>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -10020,34 +10826,34 @@
     </row>
     <row r="130">
       <c r="A130" s="15" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E130" s="11" t="n">
-        <v>4760</v>
+        <v>73.95</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>eBay API; vendedor lmunaco91 98.5%; G.SKILL RipJaws V DDR4-3200 16GB (2x8GB) DIMM Desktop RAM; envío no indicado</t>
         </is>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -10058,34 +10864,34 @@
     </row>
     <row r="131">
       <c r="A131" s="15" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
-        <v>6800</v>
+        <v>80</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor oldmacguy 100.0%; Samsung MZ-VL21T0A 1TB M.2 2280 PCIe NVMe SSD (MZVL21T0HCLR-; envío no indicado</t>
         </is>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -10096,34 +10902,34 @@
     </row>
     <row r="132">
       <c r="A132" s="15" t="n">
-        <v>46307</v>
+        <v>46310</v>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E132" s="11" t="n">
-        <v>2100</v>
+        <v>175</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>eBay API; vendedor papasmurfjr 100.0%; Western Digital SN530 2TB NVMe   screen shots for Disk Healt; envío no indicado</t>
         </is>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -10134,7 +10940,7 @@
     </row>
     <row r="133">
       <c r="A133" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
@@ -10143,16 +10949,16 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
-        <v>1800</v>
+        <v>5580</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
@@ -10161,7 +10967,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -10172,25 +10978,25 @@
     </row>
     <row r="134">
       <c r="A134" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E134" s="11" t="n">
-        <v>4500</v>
+        <v>2300</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
@@ -10199,7 +11005,7 @@
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -10210,7 +11016,7 @@
     </row>
     <row r="135">
       <c r="A135" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
@@ -10219,16 +11025,16 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
-        <v>6700</v>
+        <v>3950</v>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
@@ -10237,7 +11043,7 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -10248,25 +11054,25 @@
     </row>
     <row r="136">
       <c r="A136" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E136" s="11" t="n">
-        <v>2520</v>
+        <v>4800</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
@@ -10275,7 +11081,7 @@
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
@@ -10286,25 +11092,25 @@
     </row>
     <row r="137">
       <c r="A137" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
-        <v>4290</v>
+        <v>5190</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
@@ -10313,7 +11119,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
@@ -10324,25 +11130,25 @@
     </row>
     <row r="138">
       <c r="A138" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E138" s="11" t="n">
-        <v>2860</v>
+        <v>5390</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
@@ -10351,7 +11157,7 @@
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -10362,25 +11168,25 @@
     </row>
     <row r="139">
       <c r="A139" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
-        <v>2460</v>
+        <v>2000</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
@@ -10389,7 +11195,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -10400,25 +11206,25 @@
     </row>
     <row r="140">
       <c r="A140" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E140" s="11" t="n">
-        <v>5360</v>
+        <v>2650</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
@@ -10427,7 +11233,7 @@
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -10438,25 +11244,25 @@
     </row>
     <row r="141">
       <c r="A141" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
-        <v>1710</v>
+        <v>2700</v>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
@@ -10465,7 +11271,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -10476,25 +11282,25 @@
     </row>
     <row r="142">
       <c r="A142" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E142" s="11" t="n">
-        <v>2310</v>
+        <v>6200</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
@@ -10503,7 +11309,7 @@
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -10514,11 +11320,11 @@
     </row>
     <row r="143">
       <c r="A143" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
@@ -10528,11 +11334,11 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
-        <v>2160</v>
+        <v>540</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
@@ -10541,7 +11347,7 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
@@ -10552,25 +11358,25 @@
     </row>
     <row r="144">
       <c r="A144" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E144" s="11" t="n">
-        <v>5360</v>
+        <v>900</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
@@ -10579,7 +11385,7 @@
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H144" s="6" t="inlineStr">
@@ -10590,25 +11396,25 @@
     </row>
     <row r="145">
       <c r="A145" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
-        <v>5660</v>
+        <v>1500</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
@@ -10617,7 +11423,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
@@ -10628,25 +11434,25 @@
     </row>
     <row r="146">
       <c r="A146" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E146" s="11" t="n">
-        <v>5860</v>
+        <v>1500</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
@@ -10655,7 +11461,7 @@
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H146" s="6" t="inlineStr">
@@ -10666,11 +11472,11 @@
     </row>
     <row r="147">
       <c r="A147" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
@@ -10680,11 +11486,11 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
@@ -10693,7 +11499,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
@@ -10704,11 +11510,11 @@
     </row>
     <row r="148">
       <c r="A148" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
@@ -10718,11 +11524,11 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E148" s="11" t="n">
-        <v>2060</v>
+        <v>2000</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
@@ -10731,7 +11537,7 @@
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H148" s="6" t="inlineStr">
@@ -10742,11 +11548,11 @@
     </row>
     <row r="149">
       <c r="A149" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
@@ -10756,11 +11562,11 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
-        <v>2152</v>
+        <v>1800</v>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
@@ -10769,7 +11575,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
@@ -10780,11 +11586,11 @@
     </row>
     <row r="150">
       <c r="A150" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
@@ -10794,11 +11600,11 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E150" s="11" t="n">
-        <v>4060</v>
+        <v>3550</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
@@ -10807,7 +11613,7 @@
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H150" s="6" t="inlineStr">
@@ -10827,16 +11633,16 @@
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
-        <v>4560</v>
+        <v>5664</v>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
@@ -10845,7 +11651,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
@@ -10865,16 +11671,16 @@
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E152" s="11" t="n">
-        <v>5500</v>
+        <v>2537</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
@@ -10883,7 +11689,7 @@
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
@@ -10903,16 +11709,16 @@
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
-        <v>2500</v>
+        <v>3127</v>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
@@ -10921,7 +11727,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
@@ -10941,16 +11747,16 @@
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Compucenter (WhatsApp)</t>
         </is>
       </c>
       <c r="E154" s="11" t="n">
-        <v>5200</v>
+        <v>2150</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
@@ -10959,7 +11765,7 @@
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
         </is>
       </c>
       <c r="H154" s="6" t="inlineStr">
@@ -10970,7 +11776,7 @@
     </row>
     <row r="155">
       <c r="A155" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
@@ -10979,16 +11785,16 @@
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
-        <v>5500</v>
+        <v>6140</v>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
@@ -10997,14 +11803,18 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="n"/>
+          <t>nuevo OEM (garantía 6 meses)</t>
+        </is>
+      </c>
+      <c r="H155" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
@@ -11013,16 +11823,16 @@
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E156" s="11" t="n">
-        <v>2460</v>
+        <v>4760</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
@@ -11031,14 +11841,18 @@
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H156" s="2" t="n"/>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H156" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
@@ -11047,16 +11861,16 @@
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
-        <v>2500</v>
+        <v>6800</v>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
@@ -11065,14 +11879,18 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H157" s="2" t="n"/>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
@@ -11081,16 +11899,16 @@
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E158" s="11" t="n">
-        <v>6840</v>
+        <v>2100</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
@@ -11099,32 +11917,36 @@
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="n"/>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H158" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
@@ -11133,7 +11955,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
@@ -11144,25 +11966,25 @@
     </row>
     <row r="160">
       <c r="A160" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E160" s="11" t="n">
-        <v>5350</v>
+        <v>4500</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
@@ -11171,32 +11993,36 @@
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="n"/>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+        </is>
+      </c>
+      <c r="H160" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
-        <v>7400</v>
+        <v>6700</v>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
@@ -11205,7 +12031,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
@@ -11216,7 +12042,7 @@
     </row>
     <row r="162">
       <c r="A162" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
@@ -11230,11 +12056,11 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (web)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E162" s="11" t="n">
-        <v>2953</v>
+        <v>2520</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
@@ -11243,7 +12069,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+          <t>disponible (web)</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
@@ -11254,37 +12080,1005 @@
     </row>
     <row r="163">
       <c r="A163" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="n">
+        <v>4290</v>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+        </is>
+      </c>
+      <c r="H163" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="n">
+        <v>2860</v>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="n">
+        <v>1710</v>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="n">
+        <v>2310</v>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="n">
+        <v>2160</v>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="n">
+        <v>5360</v>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>5660</v>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C172" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E172" s="11" t="n">
+        <v>5860</v>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G172" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C173" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="n">
+        <v>1860</v>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G173" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>2060</v>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G174" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C175" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E175" s="11" t="n">
+        <v>2152</v>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G175" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E176" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G176" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E177" s="11" t="n">
+        <v>4560</v>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G177" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C178" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E178" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G178" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H178" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C179" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E179" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G179" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H179" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G180" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H180" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E181" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G182" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E183" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G183" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="n">
+        <v>6840</v>
+      </c>
+      <c r="F184" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G184" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G185" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+        </is>
+      </c>
+      <c r="H185" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E186" s="11" t="n">
+        <v>5350</v>
+      </c>
+      <c r="F186" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G186" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="15" t="n">
         <v>46309</v>
       </c>
-      <c r="B163" s="5" t="inlineStr">
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="n">
+        <v>7400</v>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G187" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H187" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
         <is>
           <t>Tienda</t>
         </is>
       </c>
-      <c r="C163" s="5" t="inlineStr">
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (web)</t>
+        </is>
+      </c>
+      <c r="E188" s="11" t="n">
+        <v>2953</v>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G188" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H188" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
         <is>
           <t>Intel Core i9-14900K</t>
         </is>
       </c>
-      <c r="D163" s="5" t="inlineStr">
+      <c r="D189" s="5" t="inlineStr">
         <is>
           <t>Crazy Store (WhatsApp)</t>
         </is>
       </c>
-      <c r="E163" s="11" t="n">
+      <c r="E189" s="11" t="n">
         <v>6013</v>
       </c>
-      <c r="F163" s="5" t="inlineStr">
+      <c r="F189" s="5" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
       </c>
-      <c r="G163" s="5" t="inlineStr">
+      <c r="G189" s="5" t="inlineStr">
         <is>
           <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
         </is>
       </c>
-      <c r="H163" s="2" t="n"/>
+      <c r="H189" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11441,13 +13235,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId182"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId157"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId183"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H189" headerRowCount="1">
-  <autoFilter ref="A1:H189"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H196" headerRowCount="1">
+  <autoFilter ref="A1:H196"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -785,12 +785,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>142.24</v>
+        <v>209.99</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
-        <v>2860</v>
+        <v>4060</v>
       </c>
       <c r="I5" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="K5" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L5" s="11">
         <f>IF(D5="","",MIN(MAX(Supuestos!$B$5,CEILING((K5*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D5*Supuestos!$B$9))</f>
@@ -850,12 +850,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -864,17 +864,17 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>209.99</v>
+        <v>142.24</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
-        <v>4060</v>
+        <v>2800</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -885,7 +885,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -980,7 +980,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -994,17 +994,19 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>114.99</v>
-      </c>
-      <c r="G8" s="2" t="n"/>
+        <v>279.99</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="H8" s="8" t="n">
-        <v>2460</v>
+        <v>4760</v>
       </c>
       <c r="I8" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1015,7 +1017,7 @@
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="L8" s="11">
         <f>IF(D8="","",MIN(MAX(Supuestos!$B$5,CEILING((K8*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D8*Supuestos!$B$9))</f>
@@ -1045,7 +1047,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1059,19 +1061,17 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>320</v>
+        <v>164.49</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>279.99</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>4800</v>
-      </c>
+        <v>134.99</v>
+      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="8" t="n">
-        <v>4760</v>
+        <v>2460</v>
       </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1082,7 +1082,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1112,7 +1112,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1126,17 +1126,17 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>164.49</v>
+        <v>150</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>134.99</v>
+        <v>114.99</v>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="8" t="n">
-        <v>2460</v>
+        <v>2260</v>
       </c>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -2056,7 +2056,9 @@
         <v>279.99</v>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="8" t="n">
+        <v>5890</v>
+      </c>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2164,7 +2166,9 @@
         <v>120</v>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H7" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2329,7 +2333,9 @@
         <v>134.99</v>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="8" t="n">
+        <v>2750</v>
+      </c>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2437,7 +2443,9 @@
         <v>114.99</v>
       </c>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
+      <c r="G12" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="H12" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A12,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A12,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5905,7 +5913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H189"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13079,6 +13087,244 @@
         </is>
       </c>
       <c r="H189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B190" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C190" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E190" s="11" t="n">
+        <v>5890</v>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G190" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
+        </is>
+      </c>
+      <c r="H190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G191" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
+        </is>
+      </c>
+      <c r="H191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B192" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+        </is>
+      </c>
+      <c r="D192" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E192" s="11" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G192" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B193" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>PC Factor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="n">
+        <v>3792</v>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B194" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B195" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G195" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B196" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H196" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H196" headerRowCount="1">
-  <autoFilter ref="A1:H196"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H198" headerRowCount="1">
+  <autoFilter ref="A1:H198"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -5913,7 +5913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H196"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13325,6 +13325,74 @@
         </is>
       </c>
       <c r="H196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B197" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7700X</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="inlineStr">
+        <is>
+          <t>sin confirmar si es sellado (se preguntó)</t>
+        </is>
+      </c>
+      <c r="H197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B198" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E198" s="11" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H198" headerRowCount="1">
-  <autoFilter ref="A1:H198"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H202" headerRowCount="1">
+  <autoFilter ref="A1:H202"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -1268,7 +1268,7 @@
         <v>1800</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1860</v>
+        <v>1754</v>
       </c>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1946,7 +1946,9 @@
         <v>80</v>
       </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
+      <c r="G3" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5913,7 +5915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13393,6 +13395,142 @@
         </is>
       </c>
       <c r="H198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B199" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
+        </is>
+      </c>
+      <c r="H199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B200" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C200" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E200" s="11" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F200" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G200" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B201" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E201" s="11" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E202" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H202" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O67" headerRowCount="1">
-  <autoFilter ref="A1:O67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O81" headerRowCount="1">
+  <autoFilter ref="A1:O81"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H202" headerRowCount="1">
-  <autoFilter ref="A1:H202"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H228" headerRowCount="1">
+  <autoFilter ref="A1:H228"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -633,7 +633,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>¿Qué conviene traer? · 15/10/2026</t>
+          <t>¿Qué conviene traer? · 16/10/2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>175</v>
+        <v>161.99</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>142.24</v>
+        <v>141.24</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
@@ -1047,12 +1047,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1061,17 +1061,19 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>164.49</v>
+        <v>110</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>134.99</v>
-      </c>
-      <c r="G9" s="2" t="n"/>
+        <v>80</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>1800</v>
+      </c>
       <c r="H9" s="8" t="n">
-        <v>2460</v>
+        <v>1754</v>
       </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1082,7 +1084,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1112,7 +1114,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1126,17 +1128,17 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>150</v>
+        <v>164.49</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>114.99</v>
+        <v>139.99</v>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="8" t="n">
-        <v>2260</v>
+        <v>2460</v>
       </c>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1177,12 +1179,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1191,18 +1193,18 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>425</v>
+        <v>150</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>10.99</v>
+        <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>394.99</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H11" s="2" t="n"/>
+        <v>120.99</v>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1212,7 +1214,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="L11" s="11">
         <f>IF(D11="","",MIN(MAX(Supuestos!$B$5,CEILING((K11*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D11*Supuestos!$B$9))</f>
@@ -1242,12 +1244,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1256,20 +1258,18 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>128.99</v>
+        <v>474.49</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>80</v>
+        <v>389.99</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1754</v>
-      </c>
+        <v>6200</v>
+      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="L12" s="11">
         <f>IF(D12="","",MIN(MAX(Supuestos!$B$5,CEILING((K12*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D12*Supuestos!$B$9))</f>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>4500</v>
@@ -1374,12 +1374,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1388,19 +1388,17 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>75</v>
+        <v>549.99</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>73.95</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>900</v>
-      </c>
+        <v>454.99</v>
+      </c>
+      <c r="G14" s="2" t="n"/>
       <c r="H14" s="8" t="n">
-        <v>2150</v>
+        <v>5580</v>
       </c>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1411,7 +1409,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1506,12 +1504,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1520,17 +1518,19 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>689.34</v>
+        <v>108.97</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0</v>
+        <v>9.99</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>375</v>
-      </c>
-      <c r="G16" s="2" t="n"/>
+        <v>73.95</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>900</v>
+      </c>
       <c r="H16" s="8" t="n">
-        <v>5580</v>
+        <v>2150</v>
       </c>
       <c r="I16" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1541,7 +1541,7 @@
         <v/>
       </c>
       <c r="K16" s="8" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="L16" s="11">
         <f>IF(D16="","",MIN(MAX(Supuestos!$B$5,CEILING((K16*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D16*Supuestos!$B$9))</f>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1650,7 +1650,7 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="7" t="n">
-        <v>295</v>
+        <v>298.01</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O67"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>209.99</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>175</v>
+        <v>161.99</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="K2" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L2" s="16">
         <f>IF(OR($K2="",D2=""),"",IF(COUNTIFS($B:$B,$B2,$A:$A,$K2,D:D,"&gt;=0")=0,"",D2-SUMIFS(D:D,$B:$B,$B2,$A:$A,$K2)))</f>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1940,15 +1940,13 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>128.99</v>
+        <v>110</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>80</v>
       </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="8" t="n">
-        <v>1754</v>
-      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -1963,7 +1961,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L3" s="16">
         <f>IF(OR($K3="",D3=""),"",IF(COUNTIFS($B:$B,$B3,$A:$A,$K3,D:D,"&gt;=0")=0,"",D3-SUMIFS(D:D,$B:$B,$B3,$A:$A,$K3)))</f>
@@ -1984,7 +1982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -1997,10 +1995,10 @@
         </is>
       </c>
       <c r="D4" s="7" t="n">
-        <v>689.34</v>
+        <v>549.99</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>375</v>
+        <v>454.99</v>
       </c>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="n"/>
@@ -2018,7 +2016,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L4" s="16">
         <f>IF(OR($K4="",D4=""),"",IF(COUNTIFS($B:$B,$B4,$A:$A,$K4,D:D,"&gt;=0")=0,"",D4-SUMIFS(D:D,$B:$B,$B4,$A:$A,$K4)))</f>
@@ -2039,7 +2037,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -2058,9 +2056,7 @@
         <v>279.99</v>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="8" t="n">
-        <v>5890</v>
-      </c>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2075,7 +2071,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L5" s="16">
         <f>IF(OR($K5="",D5=""),"",IF(COUNTIFS($B:$B,$B5,$A:$A,$K5,D:D,"&gt;=0")=0,"",D5-SUMIFS(D:D,$B:$B,$B5,$A:$A,$K5)))</f>
@@ -2096,7 +2092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2110,7 +2106,7 @@
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="7" t="n">
-        <v>295</v>
+        <v>298.01</v>
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
@@ -2128,7 +2124,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
@@ -2149,7 +2145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2162,15 +2158,13 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>142.24</v>
+        <v>141.24</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="8" t="n">
-        <v>2800</v>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2185,7 +2179,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L7" s="16">
         <f>IF(OR($K7="",D7=""),"",IF(COUNTIFS($B:$B,$B7,$A:$A,$K7,D:D,"&gt;=0")=0,"",D7-SUMIFS(D:D,$B:$B,$B7,$A:$A,$K7)))</f>
@@ -2206,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -2222,7 +2216,7 @@
         <v>138.9</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
@@ -2240,7 +2234,7 @@
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L8" s="16">
         <f>IF(OR($K8="",D8=""),"",IF(COUNTIFS($B:$B,$B8,$A:$A,$K8,D:D,"&gt;=0")=0,"",D8-SUMIFS(D:D,$B:$B,$B8,$A:$A,$K8)))</f>
@@ -2261,7 +2255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2274,7 +2268,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>75</v>
+        <v>118.96</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>73.95</v>
@@ -2295,7 +2289,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L9" s="16">
         <f>IF(OR($K9="",D9=""),"",IF(COUNTIFS($B:$B,$B9,$A:$A,$K9,D:D,"&gt;=0")=0,"",D9-SUMIFS(D:D,$B:$B,$B9,$A:$A,$K9)))</f>
@@ -2316,7 +2310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2332,12 +2326,10 @@
         <v>164.49</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>134.99</v>
+        <v>139.99</v>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="8" t="n">
-        <v>2750</v>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2352,7 +2344,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L10" s="16">
         <f>IF(OR($K10="",D10=""),"",IF(COUNTIFS($B:$B,$B10,$A:$A,$K10,D:D,"&gt;=0")=0,"",D10-SUMIFS(D:D,$B:$B,$B10,$A:$A,$K10)))</f>
@@ -2373,7 +2365,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2405,7 +2397,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L11" s="16">
         <f>IF(OR($K11="",D11=""),"",IF(COUNTIFS($B:$B,$B11,$A:$A,$K11,D:D,"&gt;=0")=0,"",D11-SUMIFS(D:D,$B:$B,$B11,$A:$A,$K11)))</f>
@@ -2426,7 +2418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2442,12 +2434,10 @@
         <v>150</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>114.99</v>
+        <v>120.99</v>
       </c>
       <c r="F12" s="2" t="n"/>
-      <c r="G12" s="8" t="n">
-        <v>2260</v>
-      </c>
+      <c r="G12" s="2" t="n"/>
       <c r="H12" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A12,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A12,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2462,7 +2452,7 @@
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L12" s="16">
         <f>IF(OR($K12="",D12=""),"",IF(COUNTIFS($B:$B,$B12,$A:$A,$K12,D:D,"&gt;=0")=0,"",D12-SUMIFS(D:D,$B:$B,$B12,$A:$A,$K12)))</f>
@@ -2483,7 +2473,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2517,7 +2507,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L13" s="16">
         <f>IF(OR($K13="",D13=""),"",IF(COUNTIFS($B:$B,$B13,$A:$A,$K13,D:D,"&gt;=0")=0,"",D13-SUMIFS(D:D,$B:$B,$B13,$A:$A,$K13)))</f>
@@ -2538,7 +2528,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2551,10 +2541,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>435.99</v>
+        <v>474.49</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>394.99</v>
+        <v>389.99</v>
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
@@ -2572,7 +2562,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L14" s="16">
         <f>IF(OR($K14="",D14=""),"",IF(COUNTIFS($B:$B,$B14,$A:$A,$K14,D:D,"&gt;=0")=0,"",D14-SUMIFS(D:D,$B:$B,$B14,$A:$A,$K14)))</f>
@@ -2593,7 +2583,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -2609,7 +2599,7 @@
         <v>429.97</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
@@ -2627,7 +2617,7 @@
         </is>
       </c>
       <c r="K15" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L15" s="16">
         <f>IF(OR($K15="",D15=""),"",IF(COUNTIFS($B:$B,$B15,$A:$A,$K15,D:D,"&gt;=0")=0,"",D15-SUMIFS(D:D,$B:$B,$B15,$A:$A,$K15)))</f>
@@ -2648,7 +2638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -2664,7 +2654,7 @@
         <v>209.99</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>164.99</v>
+        <v>175</v>
       </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
@@ -2682,7 +2672,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2703,7 +2693,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -2716,13 +2706,15 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>117.99</v>
+        <v>128.99</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
+      <c r="G17" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="H17" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2737,7 +2729,7 @@
         </is>
       </c>
       <c r="K17" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L17" s="16">
         <f>IF(OR($K17="",D17=""),"",IF(COUNTIFS($B:$B,$B17,$A:$A,$K17,D:D,"&gt;=0")=0,"",D17-SUMIFS(D:D,$B:$B,$B17,$A:$A,$K17)))</f>
@@ -2758,7 +2750,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -2771,10 +2763,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>499.99</v>
+        <v>689.34</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>454.99</v>
+        <v>375</v>
       </c>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
@@ -2792,7 +2784,7 @@
         </is>
       </c>
       <c r="K18" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L18" s="16">
         <f>IF(OR($K18="",D18=""),"",IF(COUNTIFS($B:$B,$B18,$A:$A,$K18,D:D,"&gt;=0")=0,"",D18-SUMIFS(D:D,$B:$B,$B18,$A:$A,$K18)))</f>
@@ -2813,7 +2805,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2826,13 +2818,15 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>275.99</v>
+        <v>279.99</v>
       </c>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
+      <c r="G19" s="8" t="n">
+        <v>5890</v>
+      </c>
       <c r="H19" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2847,7 +2841,7 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L19" s="16">
         <f>IF(OR($K19="",D19=""),"",IF(COUNTIFS($B:$B,$B19,$A:$A,$K19,D:D,"&gt;=0")=0,"",D19-SUMIFS(D:D,$B:$B,$B19,$A:$A,$K19)))</f>
@@ -2868,7 +2862,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2900,7 +2894,7 @@
         </is>
       </c>
       <c r="K20" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L20" s="16">
         <f>IF(OR($K20="",D20=""),"",IF(COUNTIFS($B:$B,$B20,$A:$A,$K20,D:D,"&gt;=0")=0,"",D20-SUMIFS(D:D,$B:$B,$B20,$A:$A,$K20)))</f>
@@ -2921,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -2937,10 +2931,12 @@
         <v>142.24</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>121.99</v>
+        <v>120</v>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="G21" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H21" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2955,7 +2951,7 @@
         </is>
       </c>
       <c r="K21" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L21" s="16">
         <f>IF(OR($K21="",D21=""),"",IF(COUNTIFS($B:$B,$B21,$A:$A,$K21,D:D,"&gt;=0")=0,"",D21-SUMIFS(D:D,$B:$B,$B21,$A:$A,$K21)))</f>
@@ -2976,7 +2972,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -2992,7 +2988,7 @@
         <v>138.9</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>129.99</v>
+        <v>135</v>
       </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
@@ -3010,7 +3006,7 @@
         </is>
       </c>
       <c r="K22" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
@@ -3031,7 +3027,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -3044,10 +3040,10 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>72.98999999999999</v>
+        <v>75</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>65</v>
+        <v>73.95</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -3065,7 +3061,7 @@
         </is>
       </c>
       <c r="K23" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L23" s="16">
         <f>IF(OR($K23="",D23=""),"",IF(COUNTIFS($B:$B,$B23,$A:$A,$K23,D:D,"&gt;=0")=0,"",D23-SUMIFS(D:D,$B:$B,$B23,$A:$A,$K23)))</f>
@@ -3086,7 +3082,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -3102,10 +3098,12 @@
         <v>164.49</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>134</v>
+        <v>134.99</v>
       </c>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
+      <c r="G24" s="8" t="n">
+        <v>2750</v>
+      </c>
       <c r="H24" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3120,7 +3118,7 @@
         </is>
       </c>
       <c r="K24" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L24" s="16">
         <f>IF(OR($K24="",D24=""),"",IF(COUNTIFS($B:$B,$B24,$A:$A,$K24,D:D,"&gt;=0")=0,"",D24-SUMIFS(D:D,$B:$B,$B24,$A:$A,$K24)))</f>
@@ -3141,7 +3139,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -3173,7 +3171,7 @@
         </is>
       </c>
       <c r="K25" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L25" s="16">
         <f>IF(OR($K25="",D25=""),"",IF(COUNTIFS($B:$B,$B25,$A:$A,$K25,D:D,"&gt;=0")=0,"",D25-SUMIFS(D:D,$B:$B,$B25,$A:$A,$K25)))</f>
@@ -3194,7 +3192,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3210,10 +3208,12 @@
         <v>150</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>120.99</v>
+        <v>114.99</v>
       </c>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
+      <c r="G26" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="H26" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A26,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A26,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="K26" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L26" s="16">
         <f>IF(OR($K26="",D26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,D:D,"&gt;=0")=0,"",D26-SUMIFS(D:D,$B:$B,$B26,$A:$A,$K26)))</f>
@@ -3249,7 +3249,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L27" s="16">
         <f>IF(OR($K27="",D27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,D:D,"&gt;=0")=0,"",D27-SUMIFS(D:D,$B:$B,$B27,$A:$A,$K27)))</f>
@@ -3304,7 +3304,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>435.99</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>399.9</v>
+        <v>394.99</v>
       </c>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L28" s="16">
         <f>IF(OR($K28="",D28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,D:D,"&gt;=0")=0,"",D28-SUMIFS(D:D,$B:$B,$B28,$A:$A,$K28)))</f>
@@ -3359,7 +3359,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>429.97</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="K29" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L29" s="16">
         <f>IF(OR($K29="",D29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,D:D,"&gt;=0")=0,"",D29-SUMIFS(D:D,$B:$B,$B29,$A:$A,$K29)))</f>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         <v>209.99</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>170</v>
+        <v>164.99</v>
       </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="K30" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L30" s="16">
         <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>114.99</v>
+        <v>117.99</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="K31" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L31" s="16">
         <f>IF(OR($K31="",D31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,D:D,"&gt;=0")=0,"",D31-SUMIFS(D:D,$B:$B,$B31,$A:$A,$K31)))</f>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="K32" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L32" s="16">
         <f>IF(OR($K32="",D32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,D:D,"&gt;=0")=0,"",D32-SUMIFS(D:D,$B:$B,$B32,$A:$A,$K32)))</f>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3595,14 +3595,10 @@
         <v>329</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="F33" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G33" s="8" t="n">
-        <v>5350</v>
-      </c>
+        <v>275.99</v>
+      </c>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
       <c r="H33" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3617,7 +3613,7 @@
         </is>
       </c>
       <c r="K33" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L33" s="16">
         <f>IF(OR($K33="",D33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,D:D,"&gt;=0")=0,"",D33-SUMIFS(D:D,$B:$B,$B33,$A:$A,$K33)))</f>
@@ -3638,7 +3634,7 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -3652,7 +3648,7 @@
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>299.99</v>
+        <v>295</v>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
@@ -3670,7 +3666,7 @@
         </is>
       </c>
       <c r="K34" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L34" s="16">
         <f>IF(OR($K34="",D34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,D:D,"&gt;=0")=0,"",D34-SUMIFS(D:D,$B:$B,$B34,$A:$A,$K34)))</f>
@@ -3691,7 +3687,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3704,10 +3700,10 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>143.24</v>
+        <v>142.24</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>122.99</v>
+        <v>121.99</v>
       </c>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
@@ -3725,7 +3721,7 @@
         </is>
       </c>
       <c r="K35" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L35" s="16">
         <f>IF(OR($K35="",D35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,D:D,"&gt;=0")=0,"",D35-SUMIFS(D:D,$B:$B,$B35,$A:$A,$K35)))</f>
@@ -3746,7 +3742,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -3762,7 +3758,7 @@
         <v>138.9</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
@@ -3780,7 +3776,7 @@
         </is>
       </c>
       <c r="K36" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L36" s="16">
         <f>IF(OR($K36="",D36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,D:D,"&gt;=0")=0,"",D36-SUMIFS(D:D,$B:$B,$B36,$A:$A,$K36)))</f>
@@ -3801,7 +3797,7 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -3814,10 +3810,10 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>65</v>
       </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
@@ -3835,7 +3831,7 @@
         </is>
       </c>
       <c r="K37" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L37" s="16">
         <f>IF(OR($K37="",D37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,D:D,"&gt;=0")=0,"",D37-SUMIFS(D:D,$B:$B,$B37,$A:$A,$K37)))</f>
@@ -3856,7 +3852,7 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3875,9 +3871,7 @@
         <v>134</v>
       </c>
       <c r="F38" s="2" t="n"/>
-      <c r="G38" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G38" s="2" t="n"/>
       <c r="H38" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3892,7 +3886,7 @@
         </is>
       </c>
       <c r="K38" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L38" s="16">
         <f>IF(OR($K38="",D38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,D:D,"&gt;=0")=0,"",D38-SUMIFS(D:D,$B:$B,$B38,$A:$A,$K38)))</f>
@@ -3913,7 +3907,7 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3945,7 +3939,7 @@
         </is>
       </c>
       <c r="K39" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L39" s="16">
         <f>IF(OR($K39="",D39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,D:D,"&gt;=0")=0,"",D39-SUMIFS(D:D,$B:$B,$B39,$A:$A,$K39)))</f>
@@ -3966,7 +3960,7 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3982,7 +3976,7 @@
         <v>150</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>99</v>
+        <v>120.99</v>
       </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
@@ -4000,7 +3994,7 @@
         </is>
       </c>
       <c r="K40" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L40" s="16">
         <f>IF(OR($K40="",D40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,D:D,"&gt;=0")=0,"",D40-SUMIFS(D:D,$B:$B,$B40,$A:$A,$K40)))</f>
@@ -4021,7 +4015,7 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -4037,7 +4031,7 @@
         <v>234.99</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>209.99</v>
+        <v>229</v>
       </c>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
@@ -4055,7 +4049,7 @@
         </is>
       </c>
       <c r="K41" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L41" s="16">
         <f>IF(OR($K41="",D41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,D:D,"&gt;=0")=0,"",D41-SUMIFS(D:D,$B:$B,$B41,$A:$A,$K41)))</f>
@@ -4076,7 +4070,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4110,7 +4104,7 @@
         </is>
       </c>
       <c r="K42" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L42" s="16">
         <f>IF(OR($K42="",D42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,D:D,"&gt;=0")=0,"",D42-SUMIFS(D:D,$B:$B,$B42,$A:$A,$K42)))</f>
@@ -4131,7 +4125,7 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4144,10 +4138,10 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>493</v>
+        <v>429.97</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>383.99</v>
+        <v>379.99</v>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
@@ -4165,7 +4159,7 @@
         </is>
       </c>
       <c r="K43" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L43" s="16">
         <f>IF(OR($K43="",D43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,D:D,"&gt;=0")=0,"",D43-SUMIFS(D:D,$B:$B,$B43,$A:$A,$K43)))</f>
@@ -4186,7 +4180,7 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4202,12 +4196,10 @@
         <v>209.99</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>179.99</v>
+        <v>170</v>
       </c>
       <c r="F44" s="2" t="n"/>
-      <c r="G44" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G44" s="2" t="n"/>
       <c r="H44" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A44,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A44,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4222,7 +4214,7 @@
         </is>
       </c>
       <c r="K44" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L44" s="16">
         <f>IF(OR($K44="",D44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,D:D,"&gt;=0")=0,"",D44-SUMIFS(D:D,$B:$B,$B44,$A:$A,$K44)))</f>
@@ -4243,7 +4235,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
@@ -4262,9 +4254,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F45" s="2" t="n"/>
-      <c r="G45" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G45" s="2" t="n"/>
       <c r="H45" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4279,7 +4269,7 @@
         </is>
       </c>
       <c r="K45" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L45" s="16">
         <f>IF(OR($K45="",D45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,D:D,"&gt;=0")=0,"",D45-SUMIFS(D:D,$B:$B,$B45,$A:$A,$K45)))</f>
@@ -4300,7 +4290,7 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -4319,9 +4309,7 @@
         <v>454.99</v>
       </c>
       <c r="F46" s="2" t="n"/>
-      <c r="G46" s="8" t="n">
-        <v>6140</v>
-      </c>
+      <c r="G46" s="2" t="n"/>
       <c r="H46" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A46,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A46,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4336,7 +4324,7 @@
         </is>
       </c>
       <c r="K46" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L46" s="16">
         <f>IF(OR($K46="",D46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,D:D,"&gt;=0")=0,"",D46-SUMIFS(D:D,$B:$B,$B46,$A:$A,$K46)))</f>
@@ -4357,7 +4345,7 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
@@ -4375,9 +4363,11 @@
       <c r="E47" s="7" t="n">
         <v>283.99</v>
       </c>
-      <c r="F47" s="2" t="n"/>
+      <c r="F47" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="G47" s="8" t="n">
-        <v>4760</v>
+        <v>5350</v>
       </c>
       <c r="H47" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))),"")</f>
@@ -4393,7 +4383,7 @@
         </is>
       </c>
       <c r="K47" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L47" s="16">
         <f>IF(OR($K47="",D47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,D:D,"&gt;=0")=0,"",D47-SUMIFS(D:D,$B:$B,$B47,$A:$A,$K47)))</f>
@@ -4414,7 +4404,7 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
@@ -4428,7 +4418,7 @@
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
@@ -4445,7 +4435,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K48" s="5" t="n"/>
+      <c r="K48" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L48" s="16">
         <f>IF(OR($K48="",D48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,D:D,"&gt;=0")=0,"",D48-SUMIFS(D:D,$B:$B,$B48,$A:$A,$K48)))</f>
         <v/>
@@ -4465,7 +4457,7 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
@@ -4478,15 +4470,13 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>144.25</v>
+        <v>143.24</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>122.99</v>
       </c>
       <c r="F49" s="2" t="n"/>
-      <c r="G49" s="8" t="n">
-        <v>2860</v>
-      </c>
+      <c r="G49" s="2" t="n"/>
       <c r="H49" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4501,7 +4491,7 @@
         </is>
       </c>
       <c r="K49" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L49" s="16">
         <f>IF(OR($K49="",D49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,D:D,"&gt;=0")=0,"",D49-SUMIFS(D:D,$B:$B,$B49,$A:$A,$K49)))</f>
@@ -4522,7 +4512,7 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
@@ -4555,7 +4545,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K50" s="5" t="n"/>
+      <c r="K50" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L50" s="16">
         <f>IF(OR($K50="",D50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,D:D,"&gt;=0")=0,"",D50-SUMIFS(D:D,$B:$B,$B50,$A:$A,$K50)))</f>
         <v/>
@@ -4575,7 +4567,7 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
@@ -4588,15 +4580,13 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>75</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>59.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F51" s="2" t="n"/>
-      <c r="G51" s="8" t="n">
-        <v>2150</v>
-      </c>
+      <c r="G51" s="2" t="n"/>
       <c r="H51" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A51,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A51,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4611,7 +4601,7 @@
         </is>
       </c>
       <c r="K51" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L51" s="16">
         <f>IF(OR($K51="",D51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,D:D,"&gt;=0")=0,"",D51-SUMIFS(D:D,$B:$B,$B51,$A:$A,$K51)))</f>
@@ -4632,7 +4622,7 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -4648,11 +4638,11 @@
         <v>164.49</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="8" t="n">
-        <v>2520</v>
+        <v>2460</v>
       </c>
       <c r="H52" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))),"")</f>
@@ -4668,7 +4658,7 @@
         </is>
       </c>
       <c r="K52" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L52" s="16">
         <f>IF(OR($K52="",D52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,D:D,"&gt;=0")=0,"",D52-SUMIFS(D:D,$B:$B,$B52,$A:$A,$K52)))</f>
@@ -4689,7 +4679,7 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
@@ -4701,9 +4691,7 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D53" s="7" t="n">
-        <v>259.78</v>
-      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" s="7" t="n">
         <v>149.99</v>
       </c>
@@ -4723,7 +4711,7 @@
         </is>
       </c>
       <c r="K53" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L53" s="16">
         <f>IF(OR($K53="",D53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,D:D,"&gt;=0")=0,"",D53-SUMIFS(D:D,$B:$B,$B53,$A:$A,$K53)))</f>
@@ -4744,7 +4732,7 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
@@ -4760,12 +4748,10 @@
         <v>150</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="F54" s="2" t="n"/>
-      <c r="G54" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G54" s="2" t="n"/>
       <c r="H54" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A54,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A54,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4779,7 +4765,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K54" s="5" t="n"/>
+      <c r="K54" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L54" s="16">
         <f>IF(OR($K54="",D54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,D:D,"&gt;=0")=0,"",D54-SUMIFS(D:D,$B:$B,$B54,$A:$A,$K54)))</f>
         <v/>
@@ -4799,7 +4787,7 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
@@ -4812,15 +4800,13 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>209.99</v>
       </c>
       <c r="F55" s="2" t="n"/>
-      <c r="G55" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G55" s="2" t="n"/>
       <c r="H55" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A55,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A55,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4835,7 +4821,7 @@
         </is>
       </c>
       <c r="K55" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L55" s="16">
         <f>IF(OR($K55="",D55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,D:D,"&gt;=0")=0,"",D55-SUMIFS(D:D,$B:$B,$B55,$A:$A,$K55)))</f>
@@ -4856,7 +4842,7 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
@@ -4890,7 +4876,7 @@
         </is>
       </c>
       <c r="K56" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L56" s="16">
         <f>IF(OR($K56="",D56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,D:D,"&gt;=0")=0,"",D56-SUMIFS(D:D,$B:$B,$B56,$A:$A,$K56)))</f>
@@ -4911,7 +4897,7 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
@@ -4927,11 +4913,9 @@
         <v>493</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F57" s="8" t="n">
-        <v>4500</v>
-      </c>
+        <v>383.99</v>
+      </c>
+      <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
       <c r="H57" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A57,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A57,Dólar!$A:$A,0))),"")</f>
@@ -4946,7 +4930,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K57" s="5" t="n"/>
+      <c r="K57" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L57" s="16">
         <f>IF(OR($K57="",D57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,D:D,"&gt;=0")=0,"",D57-SUMIFS(D:D,$B:$B,$B57,$A:$A,$K57)))</f>
         <v/>
@@ -4966,7 +4952,7 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
@@ -4978,10 +4964,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
+      <c r="D58" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>179.99</v>
+      </c>
       <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
+      <c r="G58" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H58" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A58,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A58,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4990,8 +4982,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A58,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="5" t="n"/>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K58" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L58" s="16">
         <f>IF(OR($K58="",D58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,D:D,"&gt;=0")=0,"",D58-SUMIFS(D:D,$B:$B,$B58,$A:$A,$K58)))</f>
         <v/>
@@ -5011,7 +5009,7 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
@@ -5023,12 +5021,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="n"/>
-      <c r="F59" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G59" s="2" t="n"/>
+      <c r="D59" s="7" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F59" s="2" t="n"/>
+      <c r="G59" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H59" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5042,7 +5044,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K59" s="5" t="n"/>
+      <c r="K59" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L59" s="16">
         <f>IF(OR($K59="",D59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,D:D,"&gt;=0")=0,"",D59-SUMIFS(D:D,$B:$B,$B59,$A:$A,$K59)))</f>
         <v/>
@@ -5062,7 +5066,7 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
@@ -5074,11 +5078,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
+      <c r="D60" s="7" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>454.99</v>
+      </c>
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="8" t="n">
-        <v>5580</v>
+        <v>6140</v>
       </c>
       <c r="H60" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A60,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A60,Dólar!$A:$A,0))),"")</f>
@@ -5093,7 +5101,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K60" s="5" t="n"/>
+      <c r="K60" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L60" s="16">
         <f>IF(OR($K60="",D60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,D:D,"&gt;=0")=0,"",D60-SUMIFS(D:D,$B:$B,$B60,$A:$A,$K60)))</f>
         <v/>
@@ -5113,7 +5123,7 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
@@ -5125,12 +5135,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D61" s="2" t="n"/>
-      <c r="E61" s="2" t="n"/>
-      <c r="F61" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G61" s="2" t="n"/>
+      <c r="D61" s="7" t="n">
+        <v>329</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="H61" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5144,7 +5158,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K61" s="5" t="n"/>
+      <c r="K61" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L61" s="16">
         <f>IF(OR($K61="",D61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,D:D,"&gt;=0")=0,"",D61-SUMIFS(D:D,$B:$B,$B61,$A:$A,$K61)))</f>
         <v/>
@@ -5164,11 +5180,11 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5177,7 +5193,9 @@
         </is>
       </c>
       <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
+      <c r="E62" s="7" t="n">
+        <v>305</v>
+      </c>
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="9">
@@ -5188,7 +5206,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A62,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J62" s="2" t="n"/>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K62" s="5" t="n"/>
       <c r="L62" s="16">
         <f>IF(OR($K62="",D62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,D:D,"&gt;=0")=0,"",D62-SUMIFS(D:D,$B:$B,$B62,$A:$A,$K62)))</f>
@@ -5209,24 +5231,28 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="G63" s="2" t="n"/>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="F63" s="2" t="n"/>
+      <c r="G63" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H63" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5240,7 +5266,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K63" s="5" t="n"/>
+      <c r="K63" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L63" s="16">
         <f>IF(OR($K63="",D63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,D:D,"&gt;=0")=0,"",D63-SUMIFS(D:D,$B:$B,$B63,$A:$A,$K63)))</f>
         <v/>
@@ -5260,11 +5288,11 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -5272,8 +5300,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
+      <c r="D64" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="n"/>
       <c r="H64" s="9">
@@ -5284,7 +5316,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A64,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J64" s="2" t="n"/>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K64" s="5" t="n"/>
       <c r="L64" s="16">
         <f>IF(OR($K64="",D64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,D:D,"&gt;=0")=0,"",D64-SUMIFS(D:D,$B:$B,$B64,$A:$A,$K64)))</f>
@@ -5305,23 +5341,27 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>59.99</v>
+      </c>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="H65" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A65,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A65,Dólar!$A:$A,0))),"")</f>
@@ -5336,7 +5376,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K65" s="5" t="n"/>
+      <c r="K65" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L65" s="16">
         <f>IF(OR($K65="",D65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,D:D,"&gt;=0")=0,"",D65-SUMIFS(D:D,$B:$B,$B65,$A:$A,$K65)))</f>
         <v/>
@@ -5356,11 +5398,11 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -5368,11 +5410,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
+      <c r="D66" s="7" t="n">
+        <v>164.49</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>136.99</v>
+      </c>
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="8" t="n">
-        <v>3950</v>
+        <v>2520</v>
       </c>
       <c r="H66" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))),"")</f>
@@ -5387,7 +5433,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K66" s="5" t="n"/>
+      <c r="K66" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L66" s="16">
         <f>IF(OR($K66="",D66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,D:D,"&gt;=0")=0,"",D66-SUMIFS(D:D,$B:$B,$B66,$A:$A,$K66)))</f>
         <v/>
@@ -5407,23 +5455,25 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="n"/>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="8" t="n">
-        <v>6200</v>
-      </c>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="F67" s="2" t="n"/>
       <c r="G67" s="2" t="n"/>
       <c r="H67" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A67,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A67,Dólar!$A:$A,0))),"")</f>
@@ -5438,7 +5488,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K67" s="5" t="n"/>
+      <c r="K67" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L67" s="16">
         <f>IF(OR($K67="",D67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,D:D,"&gt;=0")=0,"",D67-SUMIFS(D:D,$B:$B,$B67,$A:$A,$K67)))</f>
         <v/>
@@ -5456,8 +5508,722 @@
         <v/>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="F68" s="2" t="n"/>
+      <c r="G68" s="8" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H68" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A68,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A68,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A68,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="16">
+        <f>IF(OR($K68="",D68=""),"",IF(COUNTIFS($B:$B,$B68,$A:$A,$K68,D:D,"&gt;=0")=0,"",D68-SUMIFS(D:D,$B:$B,$B68,$A:$A,$K68)))</f>
+        <v/>
+      </c>
+      <c r="M68" s="16">
+        <f>IF(OR($K68="",E68=""),"",IF(COUNTIFS($B:$B,$B68,$A:$A,$K68,E:E,"&gt;=0")=0,"",E68-SUMIFS(E:E,$B:$B,$B68,$A:$A,$K68)))</f>
+        <v/>
+      </c>
+      <c r="N68" s="16">
+        <f>IF(OR($K68="",F68=""),"",IF(COUNTIFS($B:$B,$B68,$A:$A,$K68,F:F,"&gt;=0")=0,"",F68-SUMIFS(F:F,$B:$B,$B68,$A:$A,$K68)))</f>
+        <v/>
+      </c>
+      <c r="O68" s="16">
+        <f>IF(OR($K68="",G68=""),"",IF(COUNTIFS($B:$B,$B68,$A:$A,$K68,G:G,"&gt;=0")=0,"",G68-SUMIFS(G:G,$B:$B,$B68,$A:$A,$K68)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H69" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A69,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A69,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A69,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K69" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L69" s="16">
+        <f>IF(OR($K69="",D69=""),"",IF(COUNTIFS($B:$B,$B69,$A:$A,$K69,D:D,"&gt;=0")=0,"",D69-SUMIFS(D:D,$B:$B,$B69,$A:$A,$K69)))</f>
+        <v/>
+      </c>
+      <c r="M69" s="16">
+        <f>IF(OR($K69="",E69=""),"",IF(COUNTIFS($B:$B,$B69,$A:$A,$K69,E:E,"&gt;=0")=0,"",E69-SUMIFS(E:E,$B:$B,$B69,$A:$A,$K69)))</f>
+        <v/>
+      </c>
+      <c r="N69" s="16">
+        <f>IF(OR($K69="",F69=""),"",IF(COUNTIFS($B:$B,$B69,$A:$A,$K69,F:F,"&gt;=0")=0,"",F69-SUMIFS(F:F,$B:$B,$B69,$A:$A,$K69)))</f>
+        <v/>
+      </c>
+      <c r="O69" s="16">
+        <f>IF(OR($K69="",G69=""),"",IF(COUNTIFS($B:$B,$B69,$A:$A,$K69,G:G,"&gt;=0")=0,"",G69-SUMIFS(G:G,$B:$B,$B69,$A:$A,$K69)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="F70" s="2" t="n"/>
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A70,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A70,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A70,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K70" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L70" s="16">
+        <f>IF(OR($K70="",D70=""),"",IF(COUNTIFS($B:$B,$B70,$A:$A,$K70,D:D,"&gt;=0")=0,"",D70-SUMIFS(D:D,$B:$B,$B70,$A:$A,$K70)))</f>
+        <v/>
+      </c>
+      <c r="M70" s="16">
+        <f>IF(OR($K70="",E70=""),"",IF(COUNTIFS($B:$B,$B70,$A:$A,$K70,E:E,"&gt;=0")=0,"",E70-SUMIFS(E:E,$B:$B,$B70,$A:$A,$K70)))</f>
+        <v/>
+      </c>
+      <c r="N70" s="16">
+        <f>IF(OR($K70="",F70=""),"",IF(COUNTIFS($B:$B,$B70,$A:$A,$K70,F:F,"&gt;=0")=0,"",F70-SUMIFS(F:F,$B:$B,$B70,$A:$A,$K70)))</f>
+        <v/>
+      </c>
+      <c r="O70" s="16">
+        <f>IF(OR($K70="",G70=""),"",IF(COUNTIFS($B:$B,$B70,$A:$A,$K70,G:G,"&gt;=0")=0,"",G70-SUMIFS(G:G,$B:$B,$B70,$A:$A,$K70)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A71,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A71,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A71,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="16">
+        <f>IF(OR($K71="",D71=""),"",IF(COUNTIFS($B:$B,$B71,$A:$A,$K71,D:D,"&gt;=0")=0,"",D71-SUMIFS(D:D,$B:$B,$B71,$A:$A,$K71)))</f>
+        <v/>
+      </c>
+      <c r="M71" s="16">
+        <f>IF(OR($K71="",E71=""),"",IF(COUNTIFS($B:$B,$B71,$A:$A,$K71,E:E,"&gt;=0")=0,"",E71-SUMIFS(E:E,$B:$B,$B71,$A:$A,$K71)))</f>
+        <v/>
+      </c>
+      <c r="N71" s="16">
+        <f>IF(OR($K71="",F71=""),"",IF(COUNTIFS($B:$B,$B71,$A:$A,$K71,F:F,"&gt;=0")=0,"",F71-SUMIFS(F:F,$B:$B,$B71,$A:$A,$K71)))</f>
+        <v/>
+      </c>
+      <c r="O71" s="16">
+        <f>IF(OR($K71="",G71=""),"",IF(COUNTIFS($B:$B,$B71,$A:$A,$K71,G:G,"&gt;=0")=0,"",G71-SUMIFS(G:G,$B:$B,$B71,$A:$A,$K71)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A72,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A72,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I72" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A72,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="16">
+        <f>IF(OR($K72="",D72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,D:D,"&gt;=0")=0,"",D72-SUMIFS(D:D,$B:$B,$B72,$A:$A,$K72)))</f>
+        <v/>
+      </c>
+      <c r="M72" s="16">
+        <f>IF(OR($K72="",E72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,E:E,"&gt;=0")=0,"",E72-SUMIFS(E:E,$B:$B,$B72,$A:$A,$K72)))</f>
+        <v/>
+      </c>
+      <c r="N72" s="16">
+        <f>IF(OR($K72="",F72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,F:F,"&gt;=0")=0,"",F72-SUMIFS(F:F,$B:$B,$B72,$A:$A,$K72)))</f>
+        <v/>
+      </c>
+      <c r="O72" s="16">
+        <f>IF(OR($K72="",G72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,G:G,"&gt;=0")=0,"",G72-SUMIFS(G:G,$B:$B,$B72,$A:$A,$K72)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A73,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="16">
+        <f>IF(OR($K73="",D73=""),"",IF(COUNTIFS($B:$B,$B73,$A:$A,$K73,D:D,"&gt;=0")=0,"",D73-SUMIFS(D:D,$B:$B,$B73,$A:$A,$K73)))</f>
+        <v/>
+      </c>
+      <c r="M73" s="16">
+        <f>IF(OR($K73="",E73=""),"",IF(COUNTIFS($B:$B,$B73,$A:$A,$K73,E:E,"&gt;=0")=0,"",E73-SUMIFS(E:E,$B:$B,$B73,$A:$A,$K73)))</f>
+        <v/>
+      </c>
+      <c r="N73" s="16">
+        <f>IF(OR($K73="",F73=""),"",IF(COUNTIFS($B:$B,$B73,$A:$A,$K73,F:F,"&gt;=0")=0,"",F73-SUMIFS(F:F,$B:$B,$B73,$A:$A,$K73)))</f>
+        <v/>
+      </c>
+      <c r="O73" s="16">
+        <f>IF(OR($K73="",G73=""),"",IF(COUNTIFS($B:$B,$B73,$A:$A,$K73,G:G,"&gt;=0")=0,"",G73-SUMIFS(G:G,$B:$B,$B73,$A:$A,$K73)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="H74" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A74,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A74,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A74,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="16">
+        <f>IF(OR($K74="",D74=""),"",IF(COUNTIFS($B:$B,$B74,$A:$A,$K74,D:D,"&gt;=0")=0,"",D74-SUMIFS(D:D,$B:$B,$B74,$A:$A,$K74)))</f>
+        <v/>
+      </c>
+      <c r="M74" s="16">
+        <f>IF(OR($K74="",E74=""),"",IF(COUNTIFS($B:$B,$B74,$A:$A,$K74,E:E,"&gt;=0")=0,"",E74-SUMIFS(E:E,$B:$B,$B74,$A:$A,$K74)))</f>
+        <v/>
+      </c>
+      <c r="N74" s="16">
+        <f>IF(OR($K74="",F74=""),"",IF(COUNTIFS($B:$B,$B74,$A:$A,$K74,F:F,"&gt;=0")=0,"",F74-SUMIFS(F:F,$B:$B,$B74,$A:$A,$K74)))</f>
+        <v/>
+      </c>
+      <c r="O74" s="16">
+        <f>IF(OR($K74="",G74=""),"",IF(COUNTIFS($B:$B,$B74,$A:$A,$K74,G:G,"&gt;=0")=0,"",G74-SUMIFS(G:G,$B:$B,$B74,$A:$A,$K74)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I75" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A75,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n"/>
+      <c r="L75" s="16">
+        <f>IF(OR($K75="",D75=""),"",IF(COUNTIFS($B:$B,$B75,$A:$A,$K75,D:D,"&gt;=0")=0,"",D75-SUMIFS(D:D,$B:$B,$B75,$A:$A,$K75)))</f>
+        <v/>
+      </c>
+      <c r="M75" s="16">
+        <f>IF(OR($K75="",E75=""),"",IF(COUNTIFS($B:$B,$B75,$A:$A,$K75,E:E,"&gt;=0")=0,"",E75-SUMIFS(E:E,$B:$B,$B75,$A:$A,$K75)))</f>
+        <v/>
+      </c>
+      <c r="N75" s="16">
+        <f>IF(OR($K75="",F75=""),"",IF(COUNTIFS($B:$B,$B75,$A:$A,$K75,F:F,"&gt;=0")=0,"",F75-SUMIFS(F:F,$B:$B,$B75,$A:$A,$K75)))</f>
+        <v/>
+      </c>
+      <c r="O75" s="16">
+        <f>IF(OR($K75="",G75=""),"",IF(COUNTIFS($B:$B,$B75,$A:$A,$K75,G:G,"&gt;=0")=0,"",G75-SUMIFS(G:G,$B:$B,$B75,$A:$A,$K75)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A76,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A76,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I76" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A76,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J76" s="2" t="n"/>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="16">
+        <f>IF(OR($K76="",D76=""),"",IF(COUNTIFS($B:$B,$B76,$A:$A,$K76,D:D,"&gt;=0")=0,"",D76-SUMIFS(D:D,$B:$B,$B76,$A:$A,$K76)))</f>
+        <v/>
+      </c>
+      <c r="M76" s="16">
+        <f>IF(OR($K76="",E76=""),"",IF(COUNTIFS($B:$B,$B76,$A:$A,$K76,E:E,"&gt;=0")=0,"",E76-SUMIFS(E:E,$B:$B,$B76,$A:$A,$K76)))</f>
+        <v/>
+      </c>
+      <c r="N76" s="16">
+        <f>IF(OR($K76="",F76=""),"",IF(COUNTIFS($B:$B,$B76,$A:$A,$K76,F:F,"&gt;=0")=0,"",F76-SUMIFS(F:F,$B:$B,$B76,$A:$A,$K76)))</f>
+        <v/>
+      </c>
+      <c r="O76" s="16">
+        <f>IF(OR($K76="",G76=""),"",IF(COUNTIFS($B:$B,$B76,$A:$A,$K76,G:G,"&gt;=0")=0,"",G76-SUMIFS(G:G,$B:$B,$B76,$A:$A,$K76)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A77,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="16">
+        <f>IF(OR($K77="",D77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,D:D,"&gt;=0")=0,"",D77-SUMIFS(D:D,$B:$B,$B77,$A:$A,$K77)))</f>
+        <v/>
+      </c>
+      <c r="M77" s="16">
+        <f>IF(OR($K77="",E77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,E:E,"&gt;=0")=0,"",E77-SUMIFS(E:E,$B:$B,$B77,$A:$A,$K77)))</f>
+        <v/>
+      </c>
+      <c r="N77" s="16">
+        <f>IF(OR($K77="",F77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,F:F,"&gt;=0")=0,"",F77-SUMIFS(F:F,$B:$B,$B77,$A:$A,$K77)))</f>
+        <v/>
+      </c>
+      <c r="O77" s="16">
+        <f>IF(OR($K77="",G77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,G:G,"&gt;=0")=0,"",G77-SUMIFS(G:G,$B:$B,$B77,$A:$A,$K77)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A78,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A78,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I78" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A78,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J78" s="2" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="16">
+        <f>IF(OR($K78="",D78=""),"",IF(COUNTIFS($B:$B,$B78,$A:$A,$K78,D:D,"&gt;=0")=0,"",D78-SUMIFS(D:D,$B:$B,$B78,$A:$A,$K78)))</f>
+        <v/>
+      </c>
+      <c r="M78" s="16">
+        <f>IF(OR($K78="",E78=""),"",IF(COUNTIFS($B:$B,$B78,$A:$A,$K78,E:E,"&gt;=0")=0,"",E78-SUMIFS(E:E,$B:$B,$B78,$A:$A,$K78)))</f>
+        <v/>
+      </c>
+      <c r="N78" s="16">
+        <f>IF(OR($K78="",F78=""),"",IF(COUNTIFS($B:$B,$B78,$A:$A,$K78,F:F,"&gt;=0")=0,"",F78-SUMIFS(F:F,$B:$B,$B78,$A:$A,$K78)))</f>
+        <v/>
+      </c>
+      <c r="O78" s="16">
+        <f>IF(OR($K78="",G78=""),"",IF(COUNTIFS($B:$B,$B78,$A:$A,$K78,G:G,"&gt;=0")=0,"",G78-SUMIFS(G:G,$B:$B,$B78,$A:$A,$K78)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n"/>
+      <c r="G79" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H79" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A79,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A79,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I79" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A79,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="16">
+        <f>IF(OR($K79="",D79=""),"",IF(COUNTIFS($B:$B,$B79,$A:$A,$K79,D:D,"&gt;=0")=0,"",D79-SUMIFS(D:D,$B:$B,$B79,$A:$A,$K79)))</f>
+        <v/>
+      </c>
+      <c r="M79" s="16">
+        <f>IF(OR($K79="",E79=""),"",IF(COUNTIFS($B:$B,$B79,$A:$A,$K79,E:E,"&gt;=0")=0,"",E79-SUMIFS(E:E,$B:$B,$B79,$A:$A,$K79)))</f>
+        <v/>
+      </c>
+      <c r="N79" s="16">
+        <f>IF(OR($K79="",F79=""),"",IF(COUNTIFS($B:$B,$B79,$A:$A,$K79,F:F,"&gt;=0")=0,"",F79-SUMIFS(F:F,$B:$B,$B79,$A:$A,$K79)))</f>
+        <v/>
+      </c>
+      <c r="O79" s="16">
+        <f>IF(OR($K79="",G79=""),"",IF(COUNTIFS($B:$B,$B79,$A:$A,$K79,G:G,"&gt;=0")=0,"",G79-SUMIFS(G:G,$B:$B,$B79,$A:$A,$K79)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H80" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I80" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A80,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n"/>
+      <c r="L80" s="16">
+        <f>IF(OR($K80="",D80=""),"",IF(COUNTIFS($B:$B,$B80,$A:$A,$K80,D:D,"&gt;=0")=0,"",D80-SUMIFS(D:D,$B:$B,$B80,$A:$A,$K80)))</f>
+        <v/>
+      </c>
+      <c r="M80" s="16">
+        <f>IF(OR($K80="",E80=""),"",IF(COUNTIFS($B:$B,$B80,$A:$A,$K80,E:E,"&gt;=0")=0,"",E80-SUMIFS(E:E,$B:$B,$B80,$A:$A,$K80)))</f>
+        <v/>
+      </c>
+      <c r="N80" s="16">
+        <f>IF(OR($K80="",F80=""),"",IF(COUNTIFS($B:$B,$B80,$A:$A,$K80,F:F,"&gt;=0")=0,"",F80-SUMIFS(F:F,$B:$B,$B80,$A:$A,$K80)))</f>
+        <v/>
+      </c>
+      <c r="O80" s="16">
+        <f>IF(OR($K80="",G80=""),"",IF(COUNTIFS($B:$B,$B80,$A:$A,$K80,G:G,"&gt;=0")=0,"",G80-SUMIFS(G:G,$B:$B,$B80,$A:$A,$K80)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A81,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A81,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I81" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A81,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="16">
+        <f>IF(OR($K81="",D81=""),"",IF(COUNTIFS($B:$B,$B81,$A:$A,$K81,D:D,"&gt;=0")=0,"",D81-SUMIFS(D:D,$B:$B,$B81,$A:$A,$K81)))</f>
+        <v/>
+      </c>
+      <c r="M81" s="16">
+        <f>IF(OR($K81="",E81=""),"",IF(COUNTIFS($B:$B,$B81,$A:$A,$K81,E:E,"&gt;=0")=0,"",E81-SUMIFS(E:E,$B:$B,$B81,$A:$A,$K81)))</f>
+        <v/>
+      </c>
+      <c r="N81" s="16">
+        <f>IF(OR($K81="",F81=""),"",IF(COUNTIFS($B:$B,$B81,$A:$A,$K81,F:F,"&gt;=0")=0,"",F81-SUMIFS(F:F,$B:$B,$B81,$A:$A,$K81)))</f>
+        <v/>
+      </c>
+      <c r="O81" s="16">
+        <f>IF(OR($K81="",G81=""),"",IF(COUNTIFS($B:$B,$B81,$A:$A,$K81,G:G,"&gt;=0")=0,"",G81-SUMIFS(G:G,$B:$B,$B81,$A:$A,$K81)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M67">
+  <conditionalFormatting sqref="L2:M81">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -5465,7 +6231,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O67">
+  <conditionalFormatting sqref="N2:O81">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5530,17 +6296,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId64"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId78"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5705,7 +6485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5904,6 +6684,32 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D8" s="19" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="E8" s="10">
+        <f>IF(COUNT(C8:D8)=2,AVERAGE(C8:D8),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>BCB oficial 11.68; paralelo dolarbolivia.net 16/10 (compra 11.83 / venta 11.79; la página es inconsistente entre compra y venta); usado = promedio del paralelo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5915,7 +6721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H202"/>
+  <dimension ref="A1:H228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10950,34 +11756,34 @@
     </row>
     <row r="133">
       <c r="A133" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
-        <v>5580</v>
+        <v>138.9</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; (New) AMD Ryzen 5 5600 Vermeer Zen3 6-Core 12-Thread AM4 CPU</t>
         </is>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -10988,34 +11794,34 @@
     </row>
     <row r="134">
       <c r="A134" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E134" s="11" t="n">
-        <v>2300</v>
+        <v>141.24</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor silaxon 99.6%; AMD Ryzen 5 7600 3.80GHz 6 Core 12 Thread AM5 100-000001015</t>
         </is>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -11026,34 +11832,34 @@
     </row>
     <row r="135">
       <c r="A135" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
-        <v>3950</v>
+        <v>320</v>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor am-834577 100.0%; AMD Ryzen 7 7800X3D 8-Core, 16-Thread Desktop Processor, Bra</t>
         </is>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -11064,34 +11870,34 @@
     </row>
     <row r="136">
       <c r="A136" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E136" s="11" t="n">
-        <v>4800</v>
+        <v>549.99</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay API; vendedor newegg 99.6%; AMD Ryzen 9 9950X - Ryzen 9 9000 Series Granite Ridge (Zen 5</t>
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
@@ -11102,34 +11908,34 @@
     </row>
     <row r="137">
       <c r="A137" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
-        <v>5190</v>
+        <v>150</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor algonz1137 100.0%; INTEL CPU Core i5-12400F / 6/12 / 2.5GHz / 6xxChipset / BX80; envío no indicado</t>
         </is>
       </c>
       <c r="H137" s="6" t="inlineStr">
@@ -11140,34 +11946,34 @@
     </row>
     <row r="138">
       <c r="A138" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E138" s="11" t="n">
-        <v>5390</v>
+        <v>164.49</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t xml:space="preserve">eBay API; vendedor newegg 99.6%; Intel Core i5-14400F - Core i5 14th Gen Raptor Lake 10-Core </t>
         </is>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -11178,34 +11984,34 @@
     </row>
     <row r="139">
       <c r="A139" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
-        <v>2000</v>
+        <v>234.99</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor good_neighbor_mercantile 99.4%; Intel Core Ultra 7 265K CPU Desktop Processor LGA 1851 20-Co</t>
         </is>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -11216,34 +12022,34 @@
     </row>
     <row r="140">
       <c r="A140" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E140" s="11" t="n">
-        <v>2650</v>
+        <v>429.97</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor uventure 99.7%; NEW 32GB (2x16GB) Corsair Vengeance DDR5 PC5-5600 Desktop RA</t>
         </is>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -11254,34 +12060,34 @@
     </row>
     <row r="141">
       <c r="A141" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
-        <v>2700</v>
+        <v>474.49</v>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>eBay API; vendedor hbk41096 100.0%; CORSAIR Vengence RGB DDR5 RAM 32GB (2x16GB) 6000MHz C36 UDIM; envío no indicado</t>
         </is>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -11292,34 +12098,34 @@
     </row>
     <row r="142">
       <c r="A142" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E142" s="11" t="n">
-        <v>6200</v>
+        <v>118.96</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t xml:space="preserve">eBay API; vendedor bike_fix 99.0%; T-Force Vulcan Z DDR4 RAM 16GB (2x8GB) 3200MHz CL16 Desktop </t>
         </is>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -11330,34 +12136,34 @@
     </row>
     <row r="143">
       <c r="A143" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
-        <v>540</v>
+        <v>110</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>eBay API; vendedor techguy0891 99.7%; Derlar DN-850Q 1TB M.2 NVMe PCIe 4.0 SSD - New</t>
         </is>
       </c>
       <c r="H143" s="6" t="inlineStr">
@@ -11368,34 +12174,34 @@
     </row>
     <row r="144">
       <c r="A144" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E144" s="11" t="n">
-        <v>900</v>
+        <v>209.99</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>eBay API; vendedor ram_technologies 100.0%; RAM Tech 2TB NVMe SSD Gen4 M.2 2280 | 5000MB/s Read 4500MB/s</t>
         </is>
       </c>
       <c r="H144" s="6" t="inlineStr">
@@ -11406,34 +12212,34 @@
     </row>
     <row r="145">
       <c r="A145" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
-        <v>1500</v>
+        <v>129.99</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>eBay API; vendedor paymore_sugar_land 99.4%; AMD Ryzen 5 5600 3.50GHz 6 Core 100-000000927 12 Thread AM4</t>
         </is>
       </c>
       <c r="H145" s="6" t="inlineStr">
@@ -11444,34 +12250,34 @@
     </row>
     <row r="146">
       <c r="A146" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E146" s="11" t="n">
-        <v>1500</v>
+        <v>298.01</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>eBay API; vendedor cyborcat 100.0%; AMD Ryzen 7 5700X3D 8-Core 16-Thread AM4 CPU Processor - Wor</t>
         </is>
       </c>
       <c r="H146" s="6" t="inlineStr">
@@ -11482,34 +12288,34 @@
     </row>
     <row r="147">
       <c r="A147" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
-        <v>1850</v>
+        <v>120</v>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>eBay API; vendedor shenidss9ckq 99.0%; AMD Ryzen 5 7600 3.80GHz 6 Core 100-000001015 12 Thread AM5</t>
         </is>
       </c>
       <c r="H147" s="6" t="inlineStr">
@@ -11520,34 +12326,34 @@
     </row>
     <row r="148">
       <c r="A148" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E148" s="11" t="n">
-        <v>2000</v>
+        <v>279.99</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>eBay API; vendedor paymore_buford 99.5%; AMD Ryzen 7 7800X3D 4.20GHz 8 Core 100-000000910 16 Thread A</t>
         </is>
       </c>
       <c r="H148" s="6" t="inlineStr">
@@ -11558,34 +12364,34 @@
     </row>
     <row r="149">
       <c r="A149" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
-        <v>1800</v>
+        <v>454.99</v>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>eBay API; vendedor goodios_direct 99.6%; **  AMD Ryzen 9 9950X Processor - USED  **</t>
         </is>
       </c>
       <c r="H149" s="6" t="inlineStr">
@@ -11596,34 +12402,34 @@
     </row>
     <row r="150">
       <c r="A150" s="15" t="n">
-        <v>46306</v>
+        <v>46311</v>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E150" s="11" t="n">
-        <v>3550</v>
+        <v>120.99</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>eBay API; vendedor vendingollc_1 100.0%; Intel Core i5-12400F 6-Core 2.5GHz SRL4W 65W LGA1700 Desktop</t>
         </is>
       </c>
       <c r="H150" s="6" t="inlineStr">
@@ -11634,34 +12440,34 @@
     </row>
     <row r="151">
       <c r="A151" s="15" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
-        <v>5664</v>
+        <v>149.99</v>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>eBay API; vendedor techrec-recycling 99.6%; Intel Core i5-13400 2.50GHz 10-Core LGA1700 20MB Desktop Pro</t>
         </is>
       </c>
       <c r="H151" s="6" t="inlineStr">
@@ -11672,11 +12478,11 @@
     </row>
     <row r="152">
       <c r="A152" s="15" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
@@ -11686,20 +12492,20 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E152" s="11" t="n">
-        <v>2537</v>
+        <v>139.99</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>eBay API; vendedor paymore_cary 99.7%; Intel Core i5-14400F 2.50GHz 10 Core SRN47 16 Thread LGA 170</t>
         </is>
       </c>
       <c r="H152" s="6" t="inlineStr">
@@ -11710,34 +12516,34 @@
     </row>
     <row r="153">
       <c r="A153" s="15" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
-        <v>3127</v>
+        <v>229</v>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t>eBay API; vendedor archyinva 99.7%; Intel Core Ultra 7 265K 3.90GHz 20 Core Processor LGA 1851 S</t>
         </is>
       </c>
       <c r="H153" s="6" t="inlineStr">
@@ -11748,34 +12554,34 @@
     </row>
     <row r="154">
       <c r="A154" s="15" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E154" s="11" t="n">
-        <v>2150</v>
+        <v>379.99</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t>eBay API; vendedor nn-red 100.0%; Corsair Vengeance RGB Pro 32GB (2x16GB) RAM DDR5 5600MHz CMH; envío no indicado</t>
         </is>
       </c>
       <c r="H154" s="6" t="inlineStr">
@@ -11786,34 +12592,34 @@
     </row>
     <row r="155">
       <c r="A155" s="15" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
-        <v>6140</v>
+        <v>389.99</v>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t>eBay API; vendedor briansdirectdeals 100.0%; Corsair Vengeance RGB DDR5 32GB (2x16GB) RAM 6000MHz CMH32GX; envío no indicado</t>
         </is>
       </c>
       <c r="H155" s="6" t="inlineStr">
@@ -11824,34 +12630,34 @@
     </row>
     <row r="156">
       <c r="A156" s="15" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E156" s="11" t="n">
-        <v>4760</v>
+        <v>73.95</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>eBay API; vendedor lmunaco91 98.5%; G.SKILL RipJaws V DDR4-3200 16GB (2x8GB) DIMM Desktop RAM; envío no indicado</t>
         </is>
       </c>
       <c r="H156" s="6" t="inlineStr">
@@ -11862,34 +12668,34 @@
     </row>
     <row r="157">
       <c r="A157" s="15" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
-        <v>6800</v>
+        <v>80</v>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor oldmacguy 100.0%; Samsung MZ-VL21T0A 1TB M.2 2280 PCIe NVMe SSD (MZVL21T0HCLR-; envío no indicado</t>
         </is>
       </c>
       <c r="H157" s="6" t="inlineStr">
@@ -11900,34 +12706,34 @@
     </row>
     <row r="158">
       <c r="A158" s="15" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E158" s="11" t="n">
-        <v>2100</v>
+        <v>161.99</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t xml:space="preserve">eBay API; vendedor intek22 100.0%; Kioxia WG4HZNV2T000200 2TB Exceria Plus G3 NVMe Solid State </t>
         </is>
       </c>
       <c r="H158" s="6" t="inlineStr">
@@ -11938,7 +12744,7 @@
     </row>
     <row r="159">
       <c r="A159" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
@@ -11947,16 +12753,16 @@
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
-        <v>1800</v>
+        <v>5580</v>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
@@ -11965,7 +12771,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
@@ -11976,25 +12782,25 @@
     </row>
     <row r="160">
       <c r="A160" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E160" s="11" t="n">
-        <v>4500</v>
+        <v>2300</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
@@ -12003,7 +12809,7 @@
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H160" s="6" t="inlineStr">
@@ -12014,7 +12820,7 @@
     </row>
     <row r="161">
       <c r="A161" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
@@ -12023,16 +12829,16 @@
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
-        <v>6700</v>
+        <v>3950</v>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
@@ -12041,7 +12847,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
@@ -12052,25 +12858,25 @@
     </row>
     <row r="162">
       <c r="A162" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E162" s="11" t="n">
-        <v>2520</v>
+        <v>4800</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
@@ -12079,7 +12885,7 @@
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
@@ -12090,25 +12896,25 @@
     </row>
     <row r="163">
       <c r="A163" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
-        <v>4290</v>
+        <v>5190</v>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
@@ -12117,7 +12923,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H163" s="6" t="inlineStr">
@@ -12128,25 +12934,25 @@
     </row>
     <row r="164">
       <c r="A164" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E164" s="11" t="n">
-        <v>2860</v>
+        <v>5390</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
@@ -12155,7 +12961,7 @@
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H164" s="6" t="inlineStr">
@@ -12166,25 +12972,25 @@
     </row>
     <row r="165">
       <c r="A165" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
-        <v>2460</v>
+        <v>2000</v>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
@@ -12193,7 +12999,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H165" s="6" t="inlineStr">
@@ -12204,25 +13010,25 @@
     </row>
     <row r="166">
       <c r="A166" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E166" s="11" t="n">
-        <v>5360</v>
+        <v>2650</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
@@ -12231,7 +13037,7 @@
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
@@ -12242,25 +13048,25 @@
     </row>
     <row r="167">
       <c r="A167" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
-        <v>1710</v>
+        <v>2700</v>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
@@ -12269,7 +13075,7 @@
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
@@ -12280,25 +13086,25 @@
     </row>
     <row r="168">
       <c r="A168" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E168" s="11" t="n">
-        <v>2310</v>
+        <v>6200</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
@@ -12307,7 +13113,7 @@
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
@@ -12318,11 +13124,11 @@
     </row>
     <row r="169">
       <c r="A169" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
@@ -12332,11 +13138,11 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
-        <v>2160</v>
+        <v>540</v>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
@@ -12345,7 +13151,7 @@
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H169" s="6" t="inlineStr">
@@ -12356,25 +13162,25 @@
     </row>
     <row r="170">
       <c r="A170" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E170" s="11" t="n">
-        <v>5360</v>
+        <v>900</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
@@ -12383,7 +13189,7 @@
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H170" s="6" t="inlineStr">
@@ -12394,25 +13200,25 @@
     </row>
     <row r="171">
       <c r="A171" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
-        <v>5660</v>
+        <v>1500</v>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
@@ -12421,7 +13227,7 @@
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H171" s="6" t="inlineStr">
@@ -12432,25 +13238,25 @@
     </row>
     <row r="172">
       <c r="A172" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E172" s="11" t="n">
-        <v>5860</v>
+        <v>1500</v>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
@@ -12459,7 +13265,7 @@
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H172" s="6" t="inlineStr">
@@ -12470,11 +13276,11 @@
     </row>
     <row r="173">
       <c r="A173" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
@@ -12484,11 +13290,11 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
@@ -12497,7 +13303,7 @@
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H173" s="6" t="inlineStr">
@@ -12508,11 +13314,11 @@
     </row>
     <row r="174">
       <c r="A174" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
@@ -12522,11 +13328,11 @@
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2060</v>
+        <v>2000</v>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
@@ -12535,7 +13341,7 @@
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H174" s="6" t="inlineStr">
@@ -12546,11 +13352,11 @@
     </row>
     <row r="175">
       <c r="A175" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
@@ -12560,11 +13366,11 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E175" s="11" t="n">
-        <v>2152</v>
+        <v>1800</v>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
@@ -12573,7 +13379,7 @@
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
@@ -12584,11 +13390,11 @@
     </row>
     <row r="176">
       <c r="A176" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
@@ -12598,11 +13404,11 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E176" s="11" t="n">
-        <v>4060</v>
+        <v>3550</v>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
@@ -12611,7 +13417,7 @@
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H176" s="6" t="inlineStr">
@@ -12631,16 +13437,16 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E177" s="11" t="n">
-        <v>4560</v>
+        <v>5664</v>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
@@ -12649,7 +13455,7 @@
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H177" s="6" t="inlineStr">
@@ -12669,16 +13475,16 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E178" s="11" t="n">
-        <v>5500</v>
+        <v>2537</v>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
@@ -12687,7 +13493,7 @@
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H178" s="6" t="inlineStr">
@@ -12707,16 +13513,16 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E179" s="11" t="n">
-        <v>2500</v>
+        <v>3127</v>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
@@ -12725,7 +13531,7 @@
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H179" s="6" t="inlineStr">
@@ -12745,16 +13551,16 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Compucenter (WhatsApp)</t>
         </is>
       </c>
       <c r="E180" s="11" t="n">
-        <v>5200</v>
+        <v>2150</v>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
@@ -12763,7 +13569,7 @@
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
@@ -12774,7 +13580,7 @@
     </row>
     <row r="181">
       <c r="A181" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
@@ -12783,16 +13589,16 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E181" s="11" t="n">
-        <v>5500</v>
+        <v>6140</v>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
@@ -12801,14 +13607,18 @@
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
-        </is>
-      </c>
-      <c r="H181" s="2" t="n"/>
+          <t>nuevo OEM (garantía 6 meses)</t>
+        </is>
+      </c>
+      <c r="H181" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
@@ -12817,16 +13627,16 @@
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E182" s="11" t="n">
-        <v>2460</v>
+        <v>4760</v>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
@@ -12835,14 +13645,18 @@
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H182" s="2" t="n"/>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H182" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
@@ -12851,16 +13665,16 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
-        <v>2500</v>
+        <v>6800</v>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
@@ -12869,14 +13683,18 @@
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H183" s="2" t="n"/>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H183" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
@@ -12885,16 +13703,16 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E184" s="11" t="n">
-        <v>6840</v>
+        <v>2100</v>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
@@ -12903,32 +13721,36 @@
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
-        </is>
-      </c>
-      <c r="H184" s="2" t="n"/>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H184" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
@@ -12937,7 +13759,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
@@ -12948,25 +13770,25 @@
     </row>
     <row r="186">
       <c r="A186" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E186" s="11" t="n">
-        <v>5350</v>
+        <v>4500</v>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
@@ -12975,32 +13797,36 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
-        </is>
-      </c>
-      <c r="H186" s="2" t="n"/>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+        </is>
+      </c>
+      <c r="H186" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
-        <v>7400</v>
+        <v>6700</v>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
@@ -13009,7 +13835,7 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
@@ -13020,7 +13846,7 @@
     </row>
     <row r="188">
       <c r="A188" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
@@ -13034,11 +13860,11 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (web)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E188" s="11" t="n">
-        <v>2953</v>
+        <v>2520</v>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
@@ -13047,7 +13873,7 @@
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+          <t>disponible (web)</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
@@ -13058,7 +13884,7 @@
     </row>
     <row r="189">
       <c r="A189" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
@@ -13067,16 +13893,16 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900K</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Crazy Store (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
-        <v>6013</v>
+        <v>4290</v>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
@@ -13085,14 +13911,18 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H189" s="2" t="n"/>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+        </is>
+      </c>
+      <c r="H189" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
@@ -13101,16 +13931,16 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E190" s="11" t="n">
-        <v>5890</v>
+        <v>2860</v>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
@@ -13119,14 +13949,18 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
-        </is>
-      </c>
-      <c r="H190" s="2" t="n"/>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H190" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
@@ -13135,16 +13969,16 @@
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E191" s="11" t="n">
-        <v>3080</v>
+        <v>2460</v>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
@@ -13153,14 +13987,18 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
-        </is>
-      </c>
-      <c r="H191" s="2" t="n"/>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H191" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
@@ -13169,16 +14007,16 @@
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E192" s="11" t="n">
-        <v>3650</v>
+        <v>5360</v>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
@@ -13187,14 +14025,18 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H192" s="2" t="n"/>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H192" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
@@ -13203,16 +14045,16 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>PC Factor (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
-        <v>3792</v>
+        <v>1710</v>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
@@ -13221,14 +14063,18 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H193" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H193" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
@@ -13237,16 +14083,16 @@
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E194" s="11" t="n">
-        <v>2800</v>
+        <v>2310</v>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
@@ -13255,14 +14101,18 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="H194" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H194" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
@@ -13271,16 +14121,16 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
-        <v>2260</v>
+        <v>2160</v>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
@@ -13289,14 +14139,18 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H195" s="2" t="n"/>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H195" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
@@ -13305,16 +14159,16 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E196" s="11" t="n">
-        <v>2750</v>
+        <v>5360</v>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
@@ -13323,14 +14177,18 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H196" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H196" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
@@ -13339,16 +14197,16 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7700X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
-        <v>3480</v>
+        <v>5660</v>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
@@ -13357,14 +14215,18 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>sin confirmar si es sellado (se preguntó)</t>
-        </is>
-      </c>
-      <c r="H197" s="2" t="n"/>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H197" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
@@ -13373,16 +14235,16 @@
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E198" s="11" t="n">
-        <v>2900</v>
+        <v>5860</v>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
@@ -13391,14 +14253,18 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
-        </is>
-      </c>
-      <c r="H198" s="2" t="n"/>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H198" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
@@ -13412,11 +14278,11 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
-        <v>1754</v>
+        <v>1860</v>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
@@ -13425,14 +14291,18 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
-        </is>
-      </c>
-      <c r="H199" s="2" t="n"/>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H199" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
@@ -13441,16 +14311,16 @@
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E200" s="11" t="n">
-        <v>2785</v>
+        <v>2060</v>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
@@ -13459,14 +14329,18 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H200" s="2" t="n"/>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H200" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
@@ -13475,16 +14349,16 @@
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
-        <v>1778</v>
+        <v>2152</v>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
@@ -13493,44 +14367,964 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H201" s="2" t="n"/>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H201" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D202" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E202" s="11" t="n">
+        <v>4060</v>
+      </c>
+      <c r="F202" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="inlineStr">
+        <is>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H202" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico · Supermall (web)</t>
+        </is>
+      </c>
+      <c r="E203" s="11" t="n">
+        <v>4560</v>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H203" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C204" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D204" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E204" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F204" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G204" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H204" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E205" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G205" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H205" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B206" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C206" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D206" s="5" t="inlineStr">
+        <is>
+          <t>Viadata Computadoras (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E206" s="11" t="n">
+        <v>5200</v>
+      </c>
+      <c r="F206" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G206" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H206" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E207" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G207" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B208" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C208" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D208" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E208" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F208" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G208" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C209" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E209" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G209" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D210" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E210" s="11" t="n">
+        <v>6840</v>
+      </c>
+      <c r="F210" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G210" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+        </is>
+      </c>
+      <c r="E211" s="11" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G211" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+        </is>
+      </c>
+      <c r="H211" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C212" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="n">
+        <v>5350</v>
+      </c>
+      <c r="F212" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G212" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B213" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="n">
+        <v>7400</v>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G213" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H213" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B214" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C214" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D214" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (web)</t>
+        </is>
+      </c>
+      <c r="E214" s="11" t="n">
+        <v>2953</v>
+      </c>
+      <c r="F214" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G214" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H214" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i9-14900K</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>Crazy Store (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E215" s="11" t="n">
+        <v>6013</v>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G215" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="15" t="n">
         <v>46310</v>
       </c>
-      <c r="B202" s="5" t="inlineStr">
+      <c r="B216" s="5" t="inlineStr">
         <is>
           <t>Tienda</t>
         </is>
       </c>
-      <c r="C202" s="5" t="inlineStr">
+      <c r="C216" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E216" s="11" t="n">
+        <v>5890</v>
+      </c>
+      <c r="F216" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G216" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B217" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C217" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E217" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G217" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E218" s="11" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F218" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G218" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C219" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>PC Factor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E219" s="11" t="n">
+        <v>3792</v>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G219" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B220" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C220" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D220" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E220" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F220" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G220" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B221" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E221" s="11" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G221" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C222" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E222" s="11" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F222" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G222" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B223" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7700X</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E223" s="11" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G223" s="5" t="inlineStr">
+        <is>
+          <t>sin confirmar si es sellado (se preguntó)</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B224" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C224" s="5" t="inlineStr">
+        <is>
+          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+        </is>
+      </c>
+      <c r="D224" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E224" s="11" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F224" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G224" s="5" t="inlineStr">
+        <is>
+          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B225" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E225" s="11" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G225" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E226" s="11" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F226" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G226" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B227" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C227" s="5" t="inlineStr">
         <is>
           <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
-      <c r="D202" s="5" t="inlineStr">
+      <c r="D227" s="5" t="inlineStr">
         <is>
           <t>Shopping PC (catálogo PDF)</t>
         </is>
       </c>
-      <c r="E202" s="11" t="n">
+      <c r="E227" s="11" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B228" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D228" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E228" s="11" t="n">
         <v>1600</v>
       </c>
-      <c r="F202" s="5" t="inlineStr">
+      <c r="F228" s="5" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
       </c>
-      <c r="G202" s="5" t="inlineStr">
+      <c r="G228" s="5" t="inlineStr">
         <is>
           <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
         </is>
       </c>
-      <c r="H202" s="2" t="n"/>
+      <c r="H228" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -13713,13 +15507,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId177"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId208"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId183"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId209"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H228" headerRowCount="1">
-  <autoFilter ref="A1:H228"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H233" headerRowCount="1">
+  <autoFilter ref="A1:H233"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -1070,7 +1070,7 @@
         <v>80</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>1800</v>
+        <v>1730</v>
       </c>
       <c r="H9" s="8" t="n">
         <v>1754</v>
@@ -1114,7 +1114,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1128,17 +1128,17 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>164.49</v>
+        <v>150</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>139.99</v>
+        <v>120.99</v>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="8" t="n">
-        <v>2460</v>
+        <v>2260</v>
       </c>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1179,7 +1179,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1193,17 +1193,17 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>150</v>
+        <v>164.49</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>120.99</v>
+        <v>139.99</v>
       </c>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="8" t="n">
-        <v>2260</v>
+        <v>2384</v>
       </c>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1945,7 +1945,9 @@
       <c r="E3" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F3" s="2" t="n"/>
+      <c r="F3" s="8" t="n">
+        <v>1730</v>
+      </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
@@ -2056,7 +2058,9 @@
         <v>279.99</v>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
+      <c r="G5" s="8" t="n">
+        <v>5664</v>
+      </c>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2329,7 +2333,9 @@
         <v>139.99</v>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="2" t="n"/>
+      <c r="G10" s="8" t="n">
+        <v>2384</v>
+      </c>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6721,7 +6727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H228"/>
+  <dimension ref="A1:H233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15325,6 +15331,192 @@
         </is>
       </c>
       <c r="H228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E229" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E230" s="11" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F230" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+        </is>
+      </c>
+      <c r="H230" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C231" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E231" s="11" t="n">
+        <v>2384</v>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+        </is>
+      </c>
+      <c r="H231" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B232" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D232" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E232" s="11" t="n">
+        <v>5664</v>
+      </c>
+      <c r="F232" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G232" s="5" t="inlineStr">
+        <is>
+          <t>nuevo BOX (web: USD 480 a 11,80)</t>
+        </is>
+      </c>
+      <c r="H232" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E233" s="11" t="n">
+        <v>2218</v>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H233" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -15536,10 +15728,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId212"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId209"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId213"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O81" headerRowCount="1">
-  <autoFilter ref="A1:O81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O95" headerRowCount="1">
+  <autoFilter ref="A1:O95"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H233" headerRowCount="1">
-  <autoFilter ref="A1:H233"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H259" headerRowCount="1">
+  <autoFilter ref="A1:H259"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -633,7 +633,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>¿Qué conviene traer? · 16/10/2026</t>
+          <t>¿Qué conviene traer? · 17/10/2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -785,12 +785,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>209.99</v>
+        <v>140.26</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>161.99</v>
+        <v>120</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
-        <v>4060</v>
+        <v>2800</v>
       </c>
       <c r="I5" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="K5" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L5" s="11">
         <f>IF(D5="","",MIN(MAX(Supuestos!$B$5,CEILING((K5*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D5*Supuestos!$B$9))</f>
@@ -850,12 +850,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -864,17 +864,17 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>141.24</v>
+        <v>209.99</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
-        <v>2800</v>
+        <v>4060</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -885,7 +885,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>234.99</v>
+        <v>230</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="F7" s="7" t="n">
         <v>229</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>320</v>
+        <v>324.99</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>279.99</v>
+        <v>275</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>4800</v>
@@ -1047,12 +1047,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1061,19 +1061,17 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>1730</v>
-      </c>
+        <v>120.99</v>
+      </c>
+      <c r="G9" s="2" t="n"/>
       <c r="H9" s="8" t="n">
-        <v>1754</v>
+        <v>2260</v>
       </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1084,7 +1082,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1114,7 +1112,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1128,17 +1126,17 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>150</v>
+        <v>164.49</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>120.99</v>
+        <v>139.99</v>
       </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="8" t="n">
-        <v>2260</v>
+        <v>2384</v>
       </c>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1179,12 +1177,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1193,18 +1191,18 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>164.49</v>
+        <v>474.49</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>139.99</v>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="8" t="n">
-        <v>2384</v>
-      </c>
+        <v>399.99</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1214,7 +1212,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="L11" s="11">
         <f>IF(D11="","",MIN(MAX(Supuestos!$B$5,CEILING((K11*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D11*Supuestos!$B$9))</f>
@@ -1244,12 +1242,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1258,18 +1256,20 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>474.49</v>
+        <v>128.99</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>389.99</v>
+        <v>98.59</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H12" s="2" t="n"/>
+        <v>1730</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="L12" s="11">
         <f>IF(D12="","",MIN(MAX(Supuestos!$B$5,CEILING((K12*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D12*Supuestos!$B$9))</f>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>4500</v>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>149.99</v>
+        <v>125</v>
       </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="8" t="n">
@@ -1524,7 +1524,7 @@
         <v>9.99</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>73.95</v>
+        <v>71.95</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>900</v>
@@ -1650,7 +1650,7 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="7" t="n">
-        <v>298.01</v>
+        <v>315</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>209.99</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>161.99</v>
+        <v>160</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="K2" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L2" s="16">
         <f>IF(OR($K2="",D2=""),"",IF(COUNTIFS($B:$B,$B2,$A:$A,$K2,D:D,"&gt;=0")=0,"",D2-SUMIFS(D:D,$B:$B,$B2,$A:$A,$K2)))</f>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1940,14 +1940,12 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>110</v>
+        <v>128.99</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>1730</v>
-      </c>
+        <v>98.59</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
@@ -1963,7 +1961,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L3" s="16">
         <f>IF(OR($K3="",D3=""),"",IF(COUNTIFS($B:$B,$B3,$A:$A,$K3,D:D,"&gt;=0")=0,"",D3-SUMIFS(D:D,$B:$B,$B3,$A:$A,$K3)))</f>
@@ -1984,7 +1982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -2018,7 +2016,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L4" s="16">
         <f>IF(OR($K4="",D4=""),"",IF(COUNTIFS($B:$B,$B4,$A:$A,$K4,D:D,"&gt;=0")=0,"",D4-SUMIFS(D:D,$B:$B,$B4,$A:$A,$K4)))</f>
@@ -2039,7 +2037,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -2052,15 +2050,13 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>320</v>
+        <v>324.99</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>279.99</v>
+        <v>275</v>
       </c>
       <c r="F5" s="2" t="n"/>
-      <c r="G5" s="8" t="n">
-        <v>5664</v>
-      </c>
+      <c r="G5" s="2" t="n"/>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2075,7 +2071,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L5" s="16">
         <f>IF(OR($K5="",D5=""),"",IF(COUNTIFS($B:$B,$B5,$A:$A,$K5,D:D,"&gt;=0")=0,"",D5-SUMIFS(D:D,$B:$B,$B5,$A:$A,$K5)))</f>
@@ -2096,7 +2092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2110,7 +2106,7 @@
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="7" t="n">
-        <v>298.01</v>
+        <v>315</v>
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
@@ -2128,7 +2124,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
@@ -2149,7 +2145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2162,7 +2158,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>141.24</v>
+        <v>140.26</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>120</v>
@@ -2183,7 +2179,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L7" s="16">
         <f>IF(OR($K7="",D7=""),"",IF(COUNTIFS($B:$B,$B7,$A:$A,$K7,D:D,"&gt;=0")=0,"",D7-SUMIFS(D:D,$B:$B,$B7,$A:$A,$K7)))</f>
@@ -2204,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -2238,7 +2234,7 @@
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L8" s="16">
         <f>IF(OR($K8="",D8=""),"",IF(COUNTIFS($B:$B,$B8,$A:$A,$K8,D:D,"&gt;=0")=0,"",D8-SUMIFS(D:D,$B:$B,$B8,$A:$A,$K8)))</f>
@@ -2259,7 +2255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2275,7 +2271,7 @@
         <v>118.96</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>73.95</v>
+        <v>71.95</v>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
@@ -2293,7 +2289,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L9" s="16">
         <f>IF(OR($K9="",D9=""),"",IF(COUNTIFS($B:$B,$B9,$A:$A,$K9,D:D,"&gt;=0")=0,"",D9-SUMIFS(D:D,$B:$B,$B9,$A:$A,$K9)))</f>
@@ -2314,7 +2310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2333,9 +2329,7 @@
         <v>139.99</v>
       </c>
       <c r="F10" s="2" t="n"/>
-      <c r="G10" s="8" t="n">
-        <v>2384</v>
-      </c>
+      <c r="G10" s="2" t="n"/>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2350,7 +2344,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L10" s="16">
         <f>IF(OR($K10="",D10=""),"",IF(COUNTIFS($B:$B,$B10,$A:$A,$K10,D:D,"&gt;=0")=0,"",D10-SUMIFS(D:D,$B:$B,$B10,$A:$A,$K10)))</f>
@@ -2371,7 +2365,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2385,7 +2379,7 @@
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>149.99</v>
+        <v>125</v>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
@@ -2403,7 +2397,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L11" s="16">
         <f>IF(OR($K11="",D11=""),"",IF(COUNTIFS($B:$B,$B11,$A:$A,$K11,D:D,"&gt;=0")=0,"",D11-SUMIFS(D:D,$B:$B,$B11,$A:$A,$K11)))</f>
@@ -2424,7 +2418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2458,7 +2452,7 @@
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L12" s="16">
         <f>IF(OR($K12="",D12=""),"",IF(COUNTIFS($B:$B,$B12,$A:$A,$K12,D:D,"&gt;=0")=0,"",D12-SUMIFS(D:D,$B:$B,$B12,$A:$A,$K12)))</f>
@@ -2479,7 +2473,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2492,7 +2486,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>234.99</v>
+        <v>235.27</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>229</v>
@@ -2513,7 +2507,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L13" s="16">
         <f>IF(OR($K13="",D13=""),"",IF(COUNTIFS($B:$B,$B13,$A:$A,$K13,D:D,"&gt;=0")=0,"",D13-SUMIFS(D:D,$B:$B,$B13,$A:$A,$K13)))</f>
@@ -2534,7 +2528,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2550,7 +2544,7 @@
         <v>474.49</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>389.99</v>
+        <v>399.99</v>
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
@@ -2568,7 +2562,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L14" s="16">
         <f>IF(OR($K14="",D14=""),"",IF(COUNTIFS($B:$B,$B14,$A:$A,$K14,D:D,"&gt;=0")=0,"",D14-SUMIFS(D:D,$B:$B,$B14,$A:$A,$K14)))</f>
@@ -2589,7 +2583,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -2605,7 +2599,7 @@
         <v>429.97</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
@@ -2623,7 +2617,7 @@
         </is>
       </c>
       <c r="K15" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L15" s="16">
         <f>IF(OR($K15="",D15=""),"",IF(COUNTIFS($B:$B,$B15,$A:$A,$K15,D:D,"&gt;=0")=0,"",D15-SUMIFS(D:D,$B:$B,$B15,$A:$A,$K15)))</f>
@@ -2644,7 +2638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -2660,7 +2654,7 @@
         <v>209.99</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>175</v>
+        <v>161.99</v>
       </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
@@ -2678,7 +2672,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2699,7 +2693,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -2712,15 +2706,15 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>128.99</v>
+        <v>110</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="8" t="n">
-        <v>1754</v>
-      </c>
+      <c r="F17" s="8" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G17" s="2" t="n"/>
       <c r="H17" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2735,7 +2729,7 @@
         </is>
       </c>
       <c r="K17" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L17" s="16">
         <f>IF(OR($K17="",D17=""),"",IF(COUNTIFS($B:$B,$B17,$A:$A,$K17,D:D,"&gt;=0")=0,"",D17-SUMIFS(D:D,$B:$B,$B17,$A:$A,$K17)))</f>
@@ -2756,7 +2750,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -2769,10 +2763,10 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>689.34</v>
+        <v>549.99</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>375</v>
+        <v>454.99</v>
       </c>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
@@ -2790,7 +2784,7 @@
         </is>
       </c>
       <c r="K18" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L18" s="16">
         <f>IF(OR($K18="",D18=""),"",IF(COUNTIFS($B:$B,$B18,$A:$A,$K18,D:D,"&gt;=0")=0,"",D18-SUMIFS(D:D,$B:$B,$B18,$A:$A,$K18)))</f>
@@ -2811,7 +2805,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2831,7 +2825,7 @@
       </c>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="8" t="n">
-        <v>5890</v>
+        <v>5664</v>
       </c>
       <c r="H19" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))),"")</f>
@@ -2847,7 +2841,7 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L19" s="16">
         <f>IF(OR($K19="",D19=""),"",IF(COUNTIFS($B:$B,$B19,$A:$A,$K19,D:D,"&gt;=0")=0,"",D19-SUMIFS(D:D,$B:$B,$B19,$A:$A,$K19)))</f>
@@ -2868,7 +2862,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2882,7 +2876,7 @@
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>295</v>
+        <v>298.01</v>
       </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -2900,7 +2894,7 @@
         </is>
       </c>
       <c r="K20" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L20" s="16">
         <f>IF(OR($K20="",D20=""),"",IF(COUNTIFS($B:$B,$B20,$A:$A,$K20,D:D,"&gt;=0")=0,"",D20-SUMIFS(D:D,$B:$B,$B20,$A:$A,$K20)))</f>
@@ -2921,7 +2915,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -2934,15 +2928,13 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>142.24</v>
+        <v>141.24</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="8" t="n">
-        <v>2800</v>
-      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2957,7 +2949,7 @@
         </is>
       </c>
       <c r="K21" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L21" s="16">
         <f>IF(OR($K21="",D21=""),"",IF(COUNTIFS($B:$B,$B21,$A:$A,$K21,D:D,"&gt;=0")=0,"",D21-SUMIFS(D:D,$B:$B,$B21,$A:$A,$K21)))</f>
@@ -2978,7 +2970,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -2994,7 +2986,7 @@
         <v>138.9</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
@@ -3012,7 +3004,7 @@
         </is>
       </c>
       <c r="K22" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
@@ -3033,7 +3025,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -3046,7 +3038,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>75</v>
+        <v>118.96</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>73.95</v>
@@ -3067,7 +3059,7 @@
         </is>
       </c>
       <c r="K23" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L23" s="16">
         <f>IF(OR($K23="",D23=""),"",IF(COUNTIFS($B:$B,$B23,$A:$A,$K23,D:D,"&gt;=0")=0,"",D23-SUMIFS(D:D,$B:$B,$B23,$A:$A,$K23)))</f>
@@ -3088,7 +3080,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -3104,11 +3096,11 @@
         <v>164.49</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>134.99</v>
+        <v>139.99</v>
       </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="8" t="n">
-        <v>2750</v>
+        <v>2384</v>
       </c>
       <c r="H24" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))),"")</f>
@@ -3124,7 +3116,7 @@
         </is>
       </c>
       <c r="K24" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L24" s="16">
         <f>IF(OR($K24="",D24=""),"",IF(COUNTIFS($B:$B,$B24,$A:$A,$K24,D:D,"&gt;=0")=0,"",D24-SUMIFS(D:D,$B:$B,$B24,$A:$A,$K24)))</f>
@@ -3145,7 +3137,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -3177,7 +3169,7 @@
         </is>
       </c>
       <c r="K25" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L25" s="16">
         <f>IF(OR($K25="",D25=""),"",IF(COUNTIFS($B:$B,$B25,$A:$A,$K25,D:D,"&gt;=0")=0,"",D25-SUMIFS(D:D,$B:$B,$B25,$A:$A,$K25)))</f>
@@ -3198,7 +3190,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3214,12 +3206,10 @@
         <v>150</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>114.99</v>
+        <v>120.99</v>
       </c>
       <c r="F26" s="2" t="n"/>
-      <c r="G26" s="8" t="n">
-        <v>2260</v>
-      </c>
+      <c r="G26" s="2" t="n"/>
       <c r="H26" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A26,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A26,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3234,7 +3224,7 @@
         </is>
       </c>
       <c r="K26" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L26" s="16">
         <f>IF(OR($K26="",D26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,D:D,"&gt;=0")=0,"",D26-SUMIFS(D:D,$B:$B,$B26,$A:$A,$K26)))</f>
@@ -3255,7 +3245,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3289,7 +3279,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L27" s="16">
         <f>IF(OR($K27="",D27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,D:D,"&gt;=0")=0,"",D27-SUMIFS(D:D,$B:$B,$B27,$A:$A,$K27)))</f>
@@ -3310,7 +3300,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -3323,10 +3313,10 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>435.99</v>
+        <v>474.49</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>394.99</v>
+        <v>389.99</v>
       </c>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
@@ -3344,7 +3334,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L28" s="16">
         <f>IF(OR($K28="",D28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,D:D,"&gt;=0")=0,"",D28-SUMIFS(D:D,$B:$B,$B28,$A:$A,$K28)))</f>
@@ -3365,7 +3355,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -3381,7 +3371,7 @@
         <v>429.97</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
@@ -3399,7 +3389,7 @@
         </is>
       </c>
       <c r="K29" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L29" s="16">
         <f>IF(OR($K29="",D29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,D:D,"&gt;=0")=0,"",D29-SUMIFS(D:D,$B:$B,$B29,$A:$A,$K29)))</f>
@@ -3420,7 +3410,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3436,7 +3426,7 @@
         <v>209.99</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>164.99</v>
+        <v>175</v>
       </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
@@ -3454,7 +3444,7 @@
         </is>
       </c>
       <c r="K30" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L30" s="16">
         <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
@@ -3475,7 +3465,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3488,13 +3478,15 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>117.99</v>
+        <v>128.99</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
+      <c r="G31" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="H31" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3509,7 +3501,7 @@
         </is>
       </c>
       <c r="K31" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L31" s="16">
         <f>IF(OR($K31="",D31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,D:D,"&gt;=0")=0,"",D31-SUMIFS(D:D,$B:$B,$B31,$A:$A,$K31)))</f>
@@ -3530,7 +3522,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3543,10 +3535,10 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>499.99</v>
+        <v>689.34</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>454.99</v>
+        <v>375</v>
       </c>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
@@ -3564,7 +3556,7 @@
         </is>
       </c>
       <c r="K32" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L32" s="16">
         <f>IF(OR($K32="",D32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,D:D,"&gt;=0")=0,"",D32-SUMIFS(D:D,$B:$B,$B32,$A:$A,$K32)))</f>
@@ -3585,7 +3577,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3598,13 +3590,15 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>275.99</v>
+        <v>279.99</v>
       </c>
       <c r="F33" s="2" t="n"/>
-      <c r="G33" s="2" t="n"/>
+      <c r="G33" s="8" t="n">
+        <v>5890</v>
+      </c>
       <c r="H33" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3619,7 +3613,7 @@
         </is>
       </c>
       <c r="K33" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L33" s="16">
         <f>IF(OR($K33="",D33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,D:D,"&gt;=0")=0,"",D33-SUMIFS(D:D,$B:$B,$B33,$A:$A,$K33)))</f>
@@ -3640,7 +3634,7 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -3672,7 +3666,7 @@
         </is>
       </c>
       <c r="K34" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L34" s="16">
         <f>IF(OR($K34="",D34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,D:D,"&gt;=0")=0,"",D34-SUMIFS(D:D,$B:$B,$B34,$A:$A,$K34)))</f>
@@ -3693,7 +3687,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3709,10 +3703,12 @@
         <v>142.24</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>121.99</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="n"/>
-      <c r="G35" s="2" t="n"/>
+      <c r="G35" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H35" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3727,7 +3723,7 @@
         </is>
       </c>
       <c r="K35" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L35" s="16">
         <f>IF(OR($K35="",D35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,D:D,"&gt;=0")=0,"",D35-SUMIFS(D:D,$B:$B,$B35,$A:$A,$K35)))</f>
@@ -3748,7 +3744,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -3764,7 +3760,7 @@
         <v>138.9</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>129.99</v>
+        <v>135</v>
       </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
@@ -3782,7 +3778,7 @@
         </is>
       </c>
       <c r="K36" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L36" s="16">
         <f>IF(OR($K36="",D36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,D:D,"&gt;=0")=0,"",D36-SUMIFS(D:D,$B:$B,$B36,$A:$A,$K36)))</f>
@@ -3803,7 +3799,7 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -3816,10 +3812,10 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>72.98999999999999</v>
+        <v>75</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>65</v>
+        <v>73.95</v>
       </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
@@ -3837,7 +3833,7 @@
         </is>
       </c>
       <c r="K37" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L37" s="16">
         <f>IF(OR($K37="",D37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,D:D,"&gt;=0")=0,"",D37-SUMIFS(D:D,$B:$B,$B37,$A:$A,$K37)))</f>
@@ -3858,7 +3854,7 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3874,10 +3870,12 @@
         <v>164.49</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>134</v>
+        <v>134.99</v>
       </c>
       <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
+      <c r="G38" s="8" t="n">
+        <v>2750</v>
+      </c>
       <c r="H38" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3892,7 +3890,7 @@
         </is>
       </c>
       <c r="K38" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L38" s="16">
         <f>IF(OR($K38="",D38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,D:D,"&gt;=0")=0,"",D38-SUMIFS(D:D,$B:$B,$B38,$A:$A,$K38)))</f>
@@ -3913,7 +3911,7 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3945,7 +3943,7 @@
         </is>
       </c>
       <c r="K39" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L39" s="16">
         <f>IF(OR($K39="",D39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,D:D,"&gt;=0")=0,"",D39-SUMIFS(D:D,$B:$B,$B39,$A:$A,$K39)))</f>
@@ -3966,7 +3964,7 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3982,10 +3980,12 @@
         <v>150</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>120.99</v>
+        <v>114.99</v>
       </c>
       <c r="F40" s="2" t="n"/>
-      <c r="G40" s="2" t="n"/>
+      <c r="G40" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="H40" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A40,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A40,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="K40" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L40" s="16">
         <f>IF(OR($K40="",D40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,D:D,"&gt;=0")=0,"",D40-SUMIFS(D:D,$B:$B,$B40,$A:$A,$K40)))</f>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="K41" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L41" s="16">
         <f>IF(OR($K41="",D41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,D:D,"&gt;=0")=0,"",D41-SUMIFS(D:D,$B:$B,$B41,$A:$A,$K41)))</f>
@@ -4076,7 +4076,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>435.99</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>399.9</v>
+        <v>394.99</v>
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="K42" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L42" s="16">
         <f>IF(OR($K42="",D42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,D:D,"&gt;=0")=0,"",D42-SUMIFS(D:D,$B:$B,$B42,$A:$A,$K42)))</f>
@@ -4131,7 +4131,7 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>429.97</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
@@ -4165,7 +4165,7 @@
         </is>
       </c>
       <c r="K43" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L43" s="16">
         <f>IF(OR($K43="",D43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,D:D,"&gt;=0")=0,"",D43-SUMIFS(D:D,$B:$B,$B43,$A:$A,$K43)))</f>
@@ -4186,7 +4186,7 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>209.99</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>170</v>
+        <v>164.99</v>
       </c>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
@@ -4220,7 +4220,7 @@
         </is>
       </c>
       <c r="K44" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L44" s="16">
         <f>IF(OR($K44="",D44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,D:D,"&gt;=0")=0,"",D44-SUMIFS(D:D,$B:$B,$B44,$A:$A,$K44)))</f>
@@ -4241,7 +4241,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>114.99</v>
+        <v>117.99</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="K45" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L45" s="16">
         <f>IF(OR($K45="",D45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,D:D,"&gt;=0")=0,"",D45-SUMIFS(D:D,$B:$B,$B45,$A:$A,$K45)))</f>
@@ -4296,7 +4296,7 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="K46" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L46" s="16">
         <f>IF(OR($K46="",D46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,D:D,"&gt;=0")=0,"",D46-SUMIFS(D:D,$B:$B,$B46,$A:$A,$K46)))</f>
@@ -4351,7 +4351,7 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
@@ -4367,14 +4367,10 @@
         <v>329</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="F47" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>5350</v>
-      </c>
+        <v>275.99</v>
+      </c>
+      <c r="F47" s="2" t="n"/>
+      <c r="G47" s="2" t="n"/>
       <c r="H47" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4389,7 +4385,7 @@
         </is>
       </c>
       <c r="K47" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L47" s="16">
         <f>IF(OR($K47="",D47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,D:D,"&gt;=0")=0,"",D47-SUMIFS(D:D,$B:$B,$B47,$A:$A,$K47)))</f>
@@ -4410,7 +4406,7 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
@@ -4424,7 +4420,7 @@
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>299.99</v>
+        <v>295</v>
       </c>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
@@ -4442,7 +4438,7 @@
         </is>
       </c>
       <c r="K48" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L48" s="16">
         <f>IF(OR($K48="",D48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,D:D,"&gt;=0")=0,"",D48-SUMIFS(D:D,$B:$B,$B48,$A:$A,$K48)))</f>
@@ -4463,7 +4459,7 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
@@ -4476,10 +4472,10 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>143.24</v>
+        <v>142.24</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>122.99</v>
+        <v>121.99</v>
       </c>
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="n"/>
@@ -4497,7 +4493,7 @@
         </is>
       </c>
       <c r="K49" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L49" s="16">
         <f>IF(OR($K49="",D49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,D:D,"&gt;=0")=0,"",D49-SUMIFS(D:D,$B:$B,$B49,$A:$A,$K49)))</f>
@@ -4518,7 +4514,7 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
@@ -4534,7 +4530,7 @@
         <v>138.9</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
@@ -4552,7 +4548,7 @@
         </is>
       </c>
       <c r="K50" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L50" s="16">
         <f>IF(OR($K50="",D50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,D:D,"&gt;=0")=0,"",D50-SUMIFS(D:D,$B:$B,$B50,$A:$A,$K50)))</f>
@@ -4573,7 +4569,7 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
@@ -4586,10 +4582,10 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>65</v>
       </c>
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
@@ -4607,7 +4603,7 @@
         </is>
       </c>
       <c r="K51" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L51" s="16">
         <f>IF(OR($K51="",D51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,D:D,"&gt;=0")=0,"",D51-SUMIFS(D:D,$B:$B,$B51,$A:$A,$K51)))</f>
@@ -4628,7 +4624,7 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -4647,9 +4643,7 @@
         <v>134</v>
       </c>
       <c r="F52" s="2" t="n"/>
-      <c r="G52" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G52" s="2" t="n"/>
       <c r="H52" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4664,7 +4658,7 @@
         </is>
       </c>
       <c r="K52" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L52" s="16">
         <f>IF(OR($K52="",D52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,D:D,"&gt;=0")=0,"",D52-SUMIFS(D:D,$B:$B,$B52,$A:$A,$K52)))</f>
@@ -4685,7 +4679,7 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
@@ -4717,7 +4711,7 @@
         </is>
       </c>
       <c r="K53" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L53" s="16">
         <f>IF(OR($K53="",D53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,D:D,"&gt;=0")=0,"",D53-SUMIFS(D:D,$B:$B,$B53,$A:$A,$K53)))</f>
@@ -4738,7 +4732,7 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
@@ -4754,7 +4748,7 @@
         <v>150</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>99</v>
+        <v>120.99</v>
       </c>
       <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
@@ -4772,7 +4766,7 @@
         </is>
       </c>
       <c r="K54" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L54" s="16">
         <f>IF(OR($K54="",D54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,D:D,"&gt;=0")=0,"",D54-SUMIFS(D:D,$B:$B,$B54,$A:$A,$K54)))</f>
@@ -4793,7 +4787,7 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
@@ -4809,7 +4803,7 @@
         <v>234.99</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>209.99</v>
+        <v>229</v>
       </c>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
@@ -4827,7 +4821,7 @@
         </is>
       </c>
       <c r="K55" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L55" s="16">
         <f>IF(OR($K55="",D55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,D:D,"&gt;=0")=0,"",D55-SUMIFS(D:D,$B:$B,$B55,$A:$A,$K55)))</f>
@@ -4848,7 +4842,7 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
@@ -4882,7 +4876,7 @@
         </is>
       </c>
       <c r="K56" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L56" s="16">
         <f>IF(OR($K56="",D56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,D:D,"&gt;=0")=0,"",D56-SUMIFS(D:D,$B:$B,$B56,$A:$A,$K56)))</f>
@@ -4903,7 +4897,7 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
@@ -4916,10 +4910,10 @@
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>493</v>
+        <v>429.97</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>383.99</v>
+        <v>379.99</v>
       </c>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
@@ -4937,7 +4931,7 @@
         </is>
       </c>
       <c r="K57" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L57" s="16">
         <f>IF(OR($K57="",D57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,D:D,"&gt;=0")=0,"",D57-SUMIFS(D:D,$B:$B,$B57,$A:$A,$K57)))</f>
@@ -4958,7 +4952,7 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
@@ -4974,12 +4968,10 @@
         <v>209.99</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>179.99</v>
+        <v>170</v>
       </c>
       <c r="F58" s="2" t="n"/>
-      <c r="G58" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G58" s="2" t="n"/>
       <c r="H58" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A58,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A58,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4994,7 +4986,7 @@
         </is>
       </c>
       <c r="K58" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L58" s="16">
         <f>IF(OR($K58="",D58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,D:D,"&gt;=0")=0,"",D58-SUMIFS(D:D,$B:$B,$B58,$A:$A,$K58)))</f>
@@ -5015,7 +5007,7 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
@@ -5034,9 +5026,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F59" s="2" t="n"/>
-      <c r="G59" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G59" s="2" t="n"/>
       <c r="H59" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5051,7 +5041,7 @@
         </is>
       </c>
       <c r="K59" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L59" s="16">
         <f>IF(OR($K59="",D59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,D:D,"&gt;=0")=0,"",D59-SUMIFS(D:D,$B:$B,$B59,$A:$A,$K59)))</f>
@@ -5072,7 +5062,7 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
@@ -5091,9 +5081,7 @@
         <v>454.99</v>
       </c>
       <c r="F60" s="2" t="n"/>
-      <c r="G60" s="8" t="n">
-        <v>6140</v>
-      </c>
+      <c r="G60" s="2" t="n"/>
       <c r="H60" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A60,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A60,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5108,7 +5096,7 @@
         </is>
       </c>
       <c r="K60" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L60" s="16">
         <f>IF(OR($K60="",D60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,D:D,"&gt;=0")=0,"",D60-SUMIFS(D:D,$B:$B,$B60,$A:$A,$K60)))</f>
@@ -5129,7 +5117,7 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
@@ -5147,9 +5135,11 @@
       <c r="E61" s="7" t="n">
         <v>283.99</v>
       </c>
-      <c r="F61" s="2" t="n"/>
+      <c r="F61" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="G61" s="8" t="n">
-        <v>4760</v>
+        <v>5350</v>
       </c>
       <c r="H61" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))),"")</f>
@@ -5165,7 +5155,7 @@
         </is>
       </c>
       <c r="K61" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L61" s="16">
         <f>IF(OR($K61="",D61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,D:D,"&gt;=0")=0,"",D61-SUMIFS(D:D,$B:$B,$B61,$A:$A,$K61)))</f>
@@ -5186,7 +5176,7 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
@@ -5200,7 +5190,7 @@
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
@@ -5217,7 +5207,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K62" s="5" t="n"/>
+      <c r="K62" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L62" s="16">
         <f>IF(OR($K62="",D62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,D:D,"&gt;=0")=0,"",D62-SUMIFS(D:D,$B:$B,$B62,$A:$A,$K62)))</f>
         <v/>
@@ -5237,7 +5229,7 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
@@ -5250,15 +5242,13 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>144.25</v>
+        <v>143.24</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>122.99</v>
       </c>
       <c r="F63" s="2" t="n"/>
-      <c r="G63" s="8" t="n">
-        <v>2860</v>
-      </c>
+      <c r="G63" s="2" t="n"/>
       <c r="H63" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5273,7 +5263,7 @@
         </is>
       </c>
       <c r="K63" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L63" s="16">
         <f>IF(OR($K63="",D63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,D:D,"&gt;=0")=0,"",D63-SUMIFS(D:D,$B:$B,$B63,$A:$A,$K63)))</f>
@@ -5294,7 +5284,7 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
@@ -5327,7 +5317,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K64" s="5" t="n"/>
+      <c r="K64" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L64" s="16">
         <f>IF(OR($K64="",D64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,D:D,"&gt;=0")=0,"",D64-SUMIFS(D:D,$B:$B,$B64,$A:$A,$K64)))</f>
         <v/>
@@ -5347,7 +5339,7 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
@@ -5360,15 +5352,13 @@
         </is>
       </c>
       <c r="D65" s="7" t="n">
-        <v>75</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>59.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F65" s="2" t="n"/>
-      <c r="G65" s="8" t="n">
-        <v>2150</v>
-      </c>
+      <c r="G65" s="2" t="n"/>
       <c r="H65" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A65,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A65,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5383,7 +5373,7 @@
         </is>
       </c>
       <c r="K65" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L65" s="16">
         <f>IF(OR($K65="",D65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,D:D,"&gt;=0")=0,"",D65-SUMIFS(D:D,$B:$B,$B65,$A:$A,$K65)))</f>
@@ -5404,7 +5394,7 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
@@ -5420,11 +5410,11 @@
         <v>164.49</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="8" t="n">
-        <v>2520</v>
+        <v>2460</v>
       </c>
       <c r="H66" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))),"")</f>
@@ -5440,7 +5430,7 @@
         </is>
       </c>
       <c r="K66" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L66" s="16">
         <f>IF(OR($K66="",D66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,D:D,"&gt;=0")=0,"",D66-SUMIFS(D:D,$B:$B,$B66,$A:$A,$K66)))</f>
@@ -5461,7 +5451,7 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
@@ -5473,9 +5463,7 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D67" s="7" t="n">
-        <v>259.78</v>
-      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" s="7" t="n">
         <v>149.99</v>
       </c>
@@ -5495,7 +5483,7 @@
         </is>
       </c>
       <c r="K67" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L67" s="16">
         <f>IF(OR($K67="",D67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,D:D,"&gt;=0")=0,"",D67-SUMIFS(D:D,$B:$B,$B67,$A:$A,$K67)))</f>
@@ -5516,7 +5504,7 @@
     </row>
     <row r="68">
       <c r="A68" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
@@ -5532,12 +5520,10 @@
         <v>150</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="F68" s="2" t="n"/>
-      <c r="G68" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G68" s="2" t="n"/>
       <c r="H68" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A68,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A68,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5551,7 +5537,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K68" s="5" t="n"/>
+      <c r="K68" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L68" s="16">
         <f>IF(OR($K68="",D68=""),"",IF(COUNTIFS($B:$B,$B68,$A:$A,$K68,D:D,"&gt;=0")=0,"",D68-SUMIFS(D:D,$B:$B,$B68,$A:$A,$K68)))</f>
         <v/>
@@ -5571,7 +5559,7 @@
     </row>
     <row r="69">
       <c r="A69" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
@@ -5584,15 +5572,13 @@
         </is>
       </c>
       <c r="D69" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E69" s="7" t="n">
         <v>209.99</v>
       </c>
       <c r="F69" s="2" t="n"/>
-      <c r="G69" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G69" s="2" t="n"/>
       <c r="H69" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A69,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A69,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5607,7 +5593,7 @@
         </is>
       </c>
       <c r="K69" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L69" s="16">
         <f>IF(OR($K69="",D69=""),"",IF(COUNTIFS($B:$B,$B69,$A:$A,$K69,D:D,"&gt;=0")=0,"",D69-SUMIFS(D:D,$B:$B,$B69,$A:$A,$K69)))</f>
@@ -5628,7 +5614,7 @@
     </row>
     <row r="70">
       <c r="A70" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
@@ -5662,7 +5648,7 @@
         </is>
       </c>
       <c r="K70" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L70" s="16">
         <f>IF(OR($K70="",D70=""),"",IF(COUNTIFS($B:$B,$B70,$A:$A,$K70,D:D,"&gt;=0")=0,"",D70-SUMIFS(D:D,$B:$B,$B70,$A:$A,$K70)))</f>
@@ -5683,7 +5669,7 @@
     </row>
     <row r="71">
       <c r="A71" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
@@ -5699,11 +5685,9 @@
         <v>493</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F71" s="8" t="n">
-        <v>4500</v>
-      </c>
+        <v>383.99</v>
+      </c>
+      <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
       <c r="H71" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A71,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A71,Dólar!$A:$A,0))),"")</f>
@@ -5718,7 +5702,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K71" s="5" t="n"/>
+      <c r="K71" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L71" s="16">
         <f>IF(OR($K71="",D71=""),"",IF(COUNTIFS($B:$B,$B71,$A:$A,$K71,D:D,"&gt;=0")=0,"",D71-SUMIFS(D:D,$B:$B,$B71,$A:$A,$K71)))</f>
         <v/>
@@ -5738,7 +5724,7 @@
     </row>
     <row r="72">
       <c r="A72" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
@@ -5750,10 +5736,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
+      <c r="D72" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>179.99</v>
+      </c>
       <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
+      <c r="G72" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H72" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A72,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A72,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5762,8 +5754,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A72,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" s="5" t="n"/>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K72" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L72" s="16">
         <f>IF(OR($K72="",D72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,D:D,"&gt;=0")=0,"",D72-SUMIFS(D:D,$B:$B,$B72,$A:$A,$K72)))</f>
         <v/>
@@ -5783,7 +5781,7 @@
     </row>
     <row r="73">
       <c r="A73" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
@@ -5795,12 +5793,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
-      <c r="F73" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G73" s="2" t="n"/>
+      <c r="D73" s="7" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H73" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5814,7 +5816,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K73" s="5" t="n"/>
+      <c r="K73" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L73" s="16">
         <f>IF(OR($K73="",D73=""),"",IF(COUNTIFS($B:$B,$B73,$A:$A,$K73,D:D,"&gt;=0")=0,"",D73-SUMIFS(D:D,$B:$B,$B73,$A:$A,$K73)))</f>
         <v/>
@@ -5834,7 +5838,7 @@
     </row>
     <row r="74">
       <c r="A74" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
@@ -5846,11 +5850,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
+      <c r="D74" s="7" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>454.99</v>
+      </c>
       <c r="F74" s="2" t="n"/>
       <c r="G74" s="8" t="n">
-        <v>5580</v>
+        <v>6140</v>
       </c>
       <c r="H74" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A74,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A74,Dólar!$A:$A,0))),"")</f>
@@ -5865,7 +5873,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K74" s="5" t="n"/>
+      <c r="K74" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L74" s="16">
         <f>IF(OR($K74="",D74=""),"",IF(COUNTIFS($B:$B,$B74,$A:$A,$K74,D:D,"&gt;=0")=0,"",D74-SUMIFS(D:D,$B:$B,$B74,$A:$A,$K74)))</f>
         <v/>
@@ -5885,7 +5895,7 @@
     </row>
     <row r="75">
       <c r="A75" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
@@ -5897,12 +5907,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="n"/>
-      <c r="F75" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G75" s="2" t="n"/>
+      <c r="D75" s="7" t="n">
+        <v>329</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="H75" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5916,7 +5930,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K75" s="5" t="n"/>
+      <c r="K75" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L75" s="16">
         <f>IF(OR($K75="",D75=""),"",IF(COUNTIFS($B:$B,$B75,$A:$A,$K75,D:D,"&gt;=0")=0,"",D75-SUMIFS(D:D,$B:$B,$B75,$A:$A,$K75)))</f>
         <v/>
@@ -5936,11 +5952,11 @@
     </row>
     <row r="76">
       <c r="A76" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -5949,7 +5965,9 @@
         </is>
       </c>
       <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
+      <c r="E76" s="7" t="n">
+        <v>305</v>
+      </c>
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="9">
@@ -5960,7 +5978,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A76,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J76" s="2" t="n"/>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K76" s="5" t="n"/>
       <c r="L76" s="16">
         <f>IF(OR($K76="",D76=""),"",IF(COUNTIFS($B:$B,$B76,$A:$A,$K76,D:D,"&gt;=0")=0,"",D76-SUMIFS(D:D,$B:$B,$B76,$A:$A,$K76)))</f>
@@ -5981,24 +6003,28 @@
     </row>
     <row r="77">
       <c r="A77" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="G77" s="2" t="n"/>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="F77" s="2" t="n"/>
+      <c r="G77" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H77" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6012,7 +6038,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K77" s="5" t="n"/>
+      <c r="K77" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L77" s="16">
         <f>IF(OR($K77="",D77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,D:D,"&gt;=0")=0,"",D77-SUMIFS(D:D,$B:$B,$B77,$A:$A,$K77)))</f>
         <v/>
@@ -6032,11 +6060,11 @@
     </row>
     <row r="78">
       <c r="A78" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -6044,8 +6072,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
+      <c r="D78" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="9">
@@ -6056,7 +6088,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A78,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J78" s="2" t="n"/>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K78" s="5" t="n"/>
       <c r="L78" s="16">
         <f>IF(OR($K78="",D78=""),"",IF(COUNTIFS($B:$B,$B78,$A:$A,$K78,D:D,"&gt;=0")=0,"",D78-SUMIFS(D:D,$B:$B,$B78,$A:$A,$K78)))</f>
@@ -6077,23 +6113,27 @@
     </row>
     <row r="79">
       <c r="A79" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="n"/>
-      <c r="E79" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>59.99</v>
+      </c>
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="H79" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A79,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A79,Dólar!$A:$A,0))),"")</f>
@@ -6108,7 +6148,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K79" s="5" t="n"/>
+      <c r="K79" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L79" s="16">
         <f>IF(OR($K79="",D79=""),"",IF(COUNTIFS($B:$B,$B79,$A:$A,$K79,D:D,"&gt;=0")=0,"",D79-SUMIFS(D:D,$B:$B,$B79,$A:$A,$K79)))</f>
         <v/>
@@ -6128,11 +6170,11 @@
     </row>
     <row r="80">
       <c r="A80" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -6140,11 +6182,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
+      <c r="D80" s="7" t="n">
+        <v>164.49</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>136.99</v>
+      </c>
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="8" t="n">
-        <v>3950</v>
+        <v>2520</v>
       </c>
       <c r="H80" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))),"")</f>
@@ -6159,7 +6205,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K80" s="5" t="n"/>
+      <c r="K80" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L80" s="16">
         <f>IF(OR($K80="",D80=""),"",IF(COUNTIFS($B:$B,$B80,$A:$A,$K80,D:D,"&gt;=0")=0,"",D80-SUMIFS(D:D,$B:$B,$B80,$A:$A,$K80)))</f>
         <v/>
@@ -6179,23 +6227,25 @@
     </row>
     <row r="81">
       <c r="A81" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="n"/>
-      <c r="E81" s="2" t="n"/>
-      <c r="F81" s="8" t="n">
-        <v>6200</v>
-      </c>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
       <c r="H81" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A81,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A81,Dólar!$A:$A,0))),"")</f>
@@ -6210,7 +6260,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K81" s="5" t="n"/>
+      <c r="K81" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L81" s="16">
         <f>IF(OR($K81="",D81=""),"",IF(COUNTIFS($B:$B,$B81,$A:$A,$K81,D:D,"&gt;=0")=0,"",D81-SUMIFS(D:D,$B:$B,$B81,$A:$A,$K81)))</f>
         <v/>
@@ -6228,8 +6280,722 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="8" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H82" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A82,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A82,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A82,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="16">
+        <f>IF(OR($K82="",D82=""),"",IF(COUNTIFS($B:$B,$B82,$A:$A,$K82,D:D,"&gt;=0")=0,"",D82-SUMIFS(D:D,$B:$B,$B82,$A:$A,$K82)))</f>
+        <v/>
+      </c>
+      <c r="M82" s="16">
+        <f>IF(OR($K82="",E82=""),"",IF(COUNTIFS($B:$B,$B82,$A:$A,$K82,E:E,"&gt;=0")=0,"",E82-SUMIFS(E:E,$B:$B,$B82,$A:$A,$K82)))</f>
+        <v/>
+      </c>
+      <c r="N82" s="16">
+        <f>IF(OR($K82="",F82=""),"",IF(COUNTIFS($B:$B,$B82,$A:$A,$K82,F:F,"&gt;=0")=0,"",F82-SUMIFS(F:F,$B:$B,$B82,$A:$A,$K82)))</f>
+        <v/>
+      </c>
+      <c r="O82" s="16">
+        <f>IF(OR($K82="",G82=""),"",IF(COUNTIFS($B:$B,$B82,$A:$A,$K82,G:G,"&gt;=0")=0,"",G82-SUMIFS(G:G,$B:$B,$B82,$A:$A,$K82)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="F83" s="2" t="n"/>
+      <c r="G83" s="8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H83" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A83,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A83,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I83" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A83,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K83" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L83" s="16">
+        <f>IF(OR($K83="",D83=""),"",IF(COUNTIFS($B:$B,$B83,$A:$A,$K83,D:D,"&gt;=0")=0,"",D83-SUMIFS(D:D,$B:$B,$B83,$A:$A,$K83)))</f>
+        <v/>
+      </c>
+      <c r="M83" s="16">
+        <f>IF(OR($K83="",E83=""),"",IF(COUNTIFS($B:$B,$B83,$A:$A,$K83,E:E,"&gt;=0")=0,"",E83-SUMIFS(E:E,$B:$B,$B83,$A:$A,$K83)))</f>
+        <v/>
+      </c>
+      <c r="N83" s="16">
+        <f>IF(OR($K83="",F83=""),"",IF(COUNTIFS($B:$B,$B83,$A:$A,$K83,F:F,"&gt;=0")=0,"",F83-SUMIFS(F:F,$B:$B,$B83,$A:$A,$K83)))</f>
+        <v/>
+      </c>
+      <c r="O83" s="16">
+        <f>IF(OR($K83="",G83=""),"",IF(COUNTIFS($B:$B,$B83,$A:$A,$K83,G:G,"&gt;=0")=0,"",G83-SUMIFS(G:G,$B:$B,$B83,$A:$A,$K83)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A84,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A84,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I84" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A84,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K84" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L84" s="16">
+        <f>IF(OR($K84="",D84=""),"",IF(COUNTIFS($B:$B,$B84,$A:$A,$K84,D:D,"&gt;=0")=0,"",D84-SUMIFS(D:D,$B:$B,$B84,$A:$A,$K84)))</f>
+        <v/>
+      </c>
+      <c r="M84" s="16">
+        <f>IF(OR($K84="",E84=""),"",IF(COUNTIFS($B:$B,$B84,$A:$A,$K84,E:E,"&gt;=0")=0,"",E84-SUMIFS(E:E,$B:$B,$B84,$A:$A,$K84)))</f>
+        <v/>
+      </c>
+      <c r="N84" s="16">
+        <f>IF(OR($K84="",F84=""),"",IF(COUNTIFS($B:$B,$B84,$A:$A,$K84,F:F,"&gt;=0")=0,"",F84-SUMIFS(F:F,$B:$B,$B84,$A:$A,$K84)))</f>
+        <v/>
+      </c>
+      <c r="O84" s="16">
+        <f>IF(OR($K84="",G84=""),"",IF(COUNTIFS($B:$B,$B84,$A:$A,$K84,G:G,"&gt;=0")=0,"",G84-SUMIFS(G:G,$B:$B,$B84,$A:$A,$K84)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A85,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A85,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I85" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A85,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n"/>
+      <c r="L85" s="16">
+        <f>IF(OR($K85="",D85=""),"",IF(COUNTIFS($B:$B,$B85,$A:$A,$K85,D:D,"&gt;=0")=0,"",D85-SUMIFS(D:D,$B:$B,$B85,$A:$A,$K85)))</f>
+        <v/>
+      </c>
+      <c r="M85" s="16">
+        <f>IF(OR($K85="",E85=""),"",IF(COUNTIFS($B:$B,$B85,$A:$A,$K85,E:E,"&gt;=0")=0,"",E85-SUMIFS(E:E,$B:$B,$B85,$A:$A,$K85)))</f>
+        <v/>
+      </c>
+      <c r="N85" s="16">
+        <f>IF(OR($K85="",F85=""),"",IF(COUNTIFS($B:$B,$B85,$A:$A,$K85,F:F,"&gt;=0")=0,"",F85-SUMIFS(F:F,$B:$B,$B85,$A:$A,$K85)))</f>
+        <v/>
+      </c>
+      <c r="O85" s="16">
+        <f>IF(OR($K85="",G85=""),"",IF(COUNTIFS($B:$B,$B85,$A:$A,$K85,G:G,"&gt;=0")=0,"",G85-SUMIFS(G:G,$B:$B,$B85,$A:$A,$K85)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A86,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A86,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I86" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A86,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J86" s="2" t="n"/>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="16">
+        <f>IF(OR($K86="",D86=""),"",IF(COUNTIFS($B:$B,$B86,$A:$A,$K86,D:D,"&gt;=0")=0,"",D86-SUMIFS(D:D,$B:$B,$B86,$A:$A,$K86)))</f>
+        <v/>
+      </c>
+      <c r="M86" s="16">
+        <f>IF(OR($K86="",E86=""),"",IF(COUNTIFS($B:$B,$B86,$A:$A,$K86,E:E,"&gt;=0")=0,"",E86-SUMIFS(E:E,$B:$B,$B86,$A:$A,$K86)))</f>
+        <v/>
+      </c>
+      <c r="N86" s="16">
+        <f>IF(OR($K86="",F86=""),"",IF(COUNTIFS($B:$B,$B86,$A:$A,$K86,F:F,"&gt;=0")=0,"",F86-SUMIFS(F:F,$B:$B,$B86,$A:$A,$K86)))</f>
+        <v/>
+      </c>
+      <c r="O86" s="16">
+        <f>IF(OR($K86="",G86=""),"",IF(COUNTIFS($B:$B,$B86,$A:$A,$K86,G:G,"&gt;=0")=0,"",G86-SUMIFS(G:G,$B:$B,$B86,$A:$A,$K86)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A87,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A87,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I87" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A87,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="16">
+        <f>IF(OR($K87="",D87=""),"",IF(COUNTIFS($B:$B,$B87,$A:$A,$K87,D:D,"&gt;=0")=0,"",D87-SUMIFS(D:D,$B:$B,$B87,$A:$A,$K87)))</f>
+        <v/>
+      </c>
+      <c r="M87" s="16">
+        <f>IF(OR($K87="",E87=""),"",IF(COUNTIFS($B:$B,$B87,$A:$A,$K87,E:E,"&gt;=0")=0,"",E87-SUMIFS(E:E,$B:$B,$B87,$A:$A,$K87)))</f>
+        <v/>
+      </c>
+      <c r="N87" s="16">
+        <f>IF(OR($K87="",F87=""),"",IF(COUNTIFS($B:$B,$B87,$A:$A,$K87,F:F,"&gt;=0")=0,"",F87-SUMIFS(F:F,$B:$B,$B87,$A:$A,$K87)))</f>
+        <v/>
+      </c>
+      <c r="O87" s="16">
+        <f>IF(OR($K87="",G87=""),"",IF(COUNTIFS($B:$B,$B87,$A:$A,$K87,G:G,"&gt;=0")=0,"",G87-SUMIFS(G:G,$B:$B,$B87,$A:$A,$K87)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="H88" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A88,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A88,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I88" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A88,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="16">
+        <f>IF(OR($K88="",D88=""),"",IF(COUNTIFS($B:$B,$B88,$A:$A,$K88,D:D,"&gt;=0")=0,"",D88-SUMIFS(D:D,$B:$B,$B88,$A:$A,$K88)))</f>
+        <v/>
+      </c>
+      <c r="M88" s="16">
+        <f>IF(OR($K88="",E88=""),"",IF(COUNTIFS($B:$B,$B88,$A:$A,$K88,E:E,"&gt;=0")=0,"",E88-SUMIFS(E:E,$B:$B,$B88,$A:$A,$K88)))</f>
+        <v/>
+      </c>
+      <c r="N88" s="16">
+        <f>IF(OR($K88="",F88=""),"",IF(COUNTIFS($B:$B,$B88,$A:$A,$K88,F:F,"&gt;=0")=0,"",F88-SUMIFS(F:F,$B:$B,$B88,$A:$A,$K88)))</f>
+        <v/>
+      </c>
+      <c r="O88" s="16">
+        <f>IF(OR($K88="",G88=""),"",IF(COUNTIFS($B:$B,$B88,$A:$A,$K88,G:G,"&gt;=0")=0,"",G88-SUMIFS(G:G,$B:$B,$B88,$A:$A,$K88)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A89,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A89,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I89" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A89,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="16">
+        <f>IF(OR($K89="",D89=""),"",IF(COUNTIFS($B:$B,$B89,$A:$A,$K89,D:D,"&gt;=0")=0,"",D89-SUMIFS(D:D,$B:$B,$B89,$A:$A,$K89)))</f>
+        <v/>
+      </c>
+      <c r="M89" s="16">
+        <f>IF(OR($K89="",E89=""),"",IF(COUNTIFS($B:$B,$B89,$A:$A,$K89,E:E,"&gt;=0")=0,"",E89-SUMIFS(E:E,$B:$B,$B89,$A:$A,$K89)))</f>
+        <v/>
+      </c>
+      <c r="N89" s="16">
+        <f>IF(OR($K89="",F89=""),"",IF(COUNTIFS($B:$B,$B89,$A:$A,$K89,F:F,"&gt;=0")=0,"",F89-SUMIFS(F:F,$B:$B,$B89,$A:$A,$K89)))</f>
+        <v/>
+      </c>
+      <c r="O89" s="16">
+        <f>IF(OR($K89="",G89=""),"",IF(COUNTIFS($B:$B,$B89,$A:$A,$K89,G:G,"&gt;=0")=0,"",G89-SUMIFS(G:G,$B:$B,$B89,$A:$A,$K89)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A90,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A90,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I90" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A90,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J90" s="2" t="n"/>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="16">
+        <f>IF(OR($K90="",D90=""),"",IF(COUNTIFS($B:$B,$B90,$A:$A,$K90,D:D,"&gt;=0")=0,"",D90-SUMIFS(D:D,$B:$B,$B90,$A:$A,$K90)))</f>
+        <v/>
+      </c>
+      <c r="M90" s="16">
+        <f>IF(OR($K90="",E90=""),"",IF(COUNTIFS($B:$B,$B90,$A:$A,$K90,E:E,"&gt;=0")=0,"",E90-SUMIFS(E:E,$B:$B,$B90,$A:$A,$K90)))</f>
+        <v/>
+      </c>
+      <c r="N90" s="16">
+        <f>IF(OR($K90="",F90=""),"",IF(COUNTIFS($B:$B,$B90,$A:$A,$K90,F:F,"&gt;=0")=0,"",F90-SUMIFS(F:F,$B:$B,$B90,$A:$A,$K90)))</f>
+        <v/>
+      </c>
+      <c r="O90" s="16">
+        <f>IF(OR($K90="",G90=""),"",IF(COUNTIFS($B:$B,$B90,$A:$A,$K90,G:G,"&gt;=0")=0,"",G90-SUMIFS(G:G,$B:$B,$B90,$A:$A,$K90)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A91,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A91,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I91" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A91,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="16">
+        <f>IF(OR($K91="",D91=""),"",IF(COUNTIFS($B:$B,$B91,$A:$A,$K91,D:D,"&gt;=0")=0,"",D91-SUMIFS(D:D,$B:$B,$B91,$A:$A,$K91)))</f>
+        <v/>
+      </c>
+      <c r="M91" s="16">
+        <f>IF(OR($K91="",E91=""),"",IF(COUNTIFS($B:$B,$B91,$A:$A,$K91,E:E,"&gt;=0")=0,"",E91-SUMIFS(E:E,$B:$B,$B91,$A:$A,$K91)))</f>
+        <v/>
+      </c>
+      <c r="N91" s="16">
+        <f>IF(OR($K91="",F91=""),"",IF(COUNTIFS($B:$B,$B91,$A:$A,$K91,F:F,"&gt;=0")=0,"",F91-SUMIFS(F:F,$B:$B,$B91,$A:$A,$K91)))</f>
+        <v/>
+      </c>
+      <c r="O91" s="16">
+        <f>IF(OR($K91="",G91=""),"",IF(COUNTIFS($B:$B,$B91,$A:$A,$K91,G:G,"&gt;=0")=0,"",G91-SUMIFS(G:G,$B:$B,$B91,$A:$A,$K91)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A92,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A92,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I92" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A92,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J92" s="2" t="n"/>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="16">
+        <f>IF(OR($K92="",D92=""),"",IF(COUNTIFS($B:$B,$B92,$A:$A,$K92,D:D,"&gt;=0")=0,"",D92-SUMIFS(D:D,$B:$B,$B92,$A:$A,$K92)))</f>
+        <v/>
+      </c>
+      <c r="M92" s="16">
+        <f>IF(OR($K92="",E92=""),"",IF(COUNTIFS($B:$B,$B92,$A:$A,$K92,E:E,"&gt;=0")=0,"",E92-SUMIFS(E:E,$B:$B,$B92,$A:$A,$K92)))</f>
+        <v/>
+      </c>
+      <c r="N92" s="16">
+        <f>IF(OR($K92="",F92=""),"",IF(COUNTIFS($B:$B,$B92,$A:$A,$K92,F:F,"&gt;=0")=0,"",F92-SUMIFS(F:F,$B:$B,$B92,$A:$A,$K92)))</f>
+        <v/>
+      </c>
+      <c r="O92" s="16">
+        <f>IF(OR($K92="",G92=""),"",IF(COUNTIFS($B:$B,$B92,$A:$A,$K92,G:G,"&gt;=0")=0,"",G92-SUMIFS(G:G,$B:$B,$B92,$A:$A,$K92)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="n"/>
+      <c r="G93" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H93" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A93,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A93,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I93" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A93,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="16">
+        <f>IF(OR($K93="",D93=""),"",IF(COUNTIFS($B:$B,$B93,$A:$A,$K93,D:D,"&gt;=0")=0,"",D93-SUMIFS(D:D,$B:$B,$B93,$A:$A,$K93)))</f>
+        <v/>
+      </c>
+      <c r="M93" s="16">
+        <f>IF(OR($K93="",E93=""),"",IF(COUNTIFS($B:$B,$B93,$A:$A,$K93,E:E,"&gt;=0")=0,"",E93-SUMIFS(E:E,$B:$B,$B93,$A:$A,$K93)))</f>
+        <v/>
+      </c>
+      <c r="N93" s="16">
+        <f>IF(OR($K93="",F93=""),"",IF(COUNTIFS($B:$B,$B93,$A:$A,$K93,F:F,"&gt;=0")=0,"",F93-SUMIFS(F:F,$B:$B,$B93,$A:$A,$K93)))</f>
+        <v/>
+      </c>
+      <c r="O93" s="16">
+        <f>IF(OR($K93="",G93=""),"",IF(COUNTIFS($B:$B,$B93,$A:$A,$K93,G:G,"&gt;=0")=0,"",G93-SUMIFS(G:G,$B:$B,$B93,$A:$A,$K93)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H94" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A94,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A94,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I94" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A94,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="16">
+        <f>IF(OR($K94="",D94=""),"",IF(COUNTIFS($B:$B,$B94,$A:$A,$K94,D:D,"&gt;=0")=0,"",D94-SUMIFS(D:D,$B:$B,$B94,$A:$A,$K94)))</f>
+        <v/>
+      </c>
+      <c r="M94" s="16">
+        <f>IF(OR($K94="",E94=""),"",IF(COUNTIFS($B:$B,$B94,$A:$A,$K94,E:E,"&gt;=0")=0,"",E94-SUMIFS(E:E,$B:$B,$B94,$A:$A,$K94)))</f>
+        <v/>
+      </c>
+      <c r="N94" s="16">
+        <f>IF(OR($K94="",F94=""),"",IF(COUNTIFS($B:$B,$B94,$A:$A,$K94,F:F,"&gt;=0")=0,"",F94-SUMIFS(F:F,$B:$B,$B94,$A:$A,$K94)))</f>
+        <v/>
+      </c>
+      <c r="O94" s="16">
+        <f>IF(OR($K94="",G94=""),"",IF(COUNTIFS($B:$B,$B94,$A:$A,$K94,G:G,"&gt;=0")=0,"",G94-SUMIFS(G:G,$B:$B,$B94,$A:$A,$K94)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
+      <c r="F95" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G95" s="2" t="n"/>
+      <c r="H95" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A95,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A95,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I95" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A95,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="16">
+        <f>IF(OR($K95="",D95=""),"",IF(COUNTIFS($B:$B,$B95,$A:$A,$K95,D:D,"&gt;=0")=0,"",D95-SUMIFS(D:D,$B:$B,$B95,$A:$A,$K95)))</f>
+        <v/>
+      </c>
+      <c r="M95" s="16">
+        <f>IF(OR($K95="",E95=""),"",IF(COUNTIFS($B:$B,$B95,$A:$A,$K95,E:E,"&gt;=0")=0,"",E95-SUMIFS(E:E,$B:$B,$B95,$A:$A,$K95)))</f>
+        <v/>
+      </c>
+      <c r="N95" s="16">
+        <f>IF(OR($K95="",F95=""),"",IF(COUNTIFS($B:$B,$B95,$A:$A,$K95,F:F,"&gt;=0")=0,"",F95-SUMIFS(F:F,$B:$B,$B95,$A:$A,$K95)))</f>
+        <v/>
+      </c>
+      <c r="O95" s="16">
+        <f>IF(OR($K95="",G95=""),"",IF(COUNTIFS($B:$B,$B95,$A:$A,$K95,G:G,"&gt;=0")=0,"",G95-SUMIFS(G:G,$B:$B,$B95,$A:$A,$K95)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M81">
+  <conditionalFormatting sqref="L2:M95">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -6237,7 +7003,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O81">
+  <conditionalFormatting sqref="N2:O95">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -6316,17 +7082,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId78"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId92"/>
   </tableParts>
 </worksheet>
 </file>
@@ -6491,7 +7271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6716,6 +7496,32 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="E9" s="10">
+        <f>IF(COUNT(C9:D9)=2,AVERAGE(C9:D9),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>BCB oficial 11.68; paralelo dolarbolivia.net 17/10 (compra 11.83 / venta 11.79; la página es inconsistente entre compra y venta); usado = promedio del paralelo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6727,7 +7533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H233"/>
+  <dimension ref="A1:H259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12750,34 +13556,34 @@
     </row>
     <row r="159">
       <c r="A159" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
-        <v>5580</v>
+        <v>138.9</v>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; (New) AMD Ryzen 5 5600 Vermeer Zen3 6-Core 12-Thread AM4 CPU</t>
         </is>
       </c>
       <c r="H159" s="6" t="inlineStr">
@@ -12788,34 +13594,34 @@
     </row>
     <row r="160">
       <c r="A160" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E160" s="11" t="n">
-        <v>2300</v>
+        <v>140.26</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor silaxon 99.6%; AMD Ryzen 5 7600 3.80GHz 6 Core 12 Thread AM5 100-000001015</t>
         </is>
       </c>
       <c r="H160" s="6" t="inlineStr">
@@ -12826,34 +13632,34 @@
     </row>
     <row r="161">
       <c r="A161" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
-        <v>3950</v>
+        <v>324.99</v>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor geoelectronics7 99.4%; AMD Ryzen 7 7800X3D 100-00000910 - Processor No Cooler</t>
         </is>
       </c>
       <c r="H161" s="6" t="inlineStr">
@@ -12864,34 +13670,34 @@
     </row>
     <row r="162">
       <c r="A162" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E162" s="11" t="n">
-        <v>4800</v>
+        <v>549.99</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G162" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay API; vendedor newegg 99.6%; AMD Ryzen 9 9950X - Ryzen 9 9000 Series Granite Ridge (Zen 5</t>
         </is>
       </c>
       <c r="H162" s="6" t="inlineStr">
@@ -12902,34 +13708,34 @@
     </row>
     <row r="163">
       <c r="A163" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
-        <v>5190</v>
+        <v>150</v>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor algonz1137 100.0%; INTEL CPU Core i5-12400F / 6/12 / 2.5GHz / 6xxChipset / BX80; envío no indicado</t>
         </is>
       </c>
       <c r="H163" s="6" t="inlineStr">
@@ -12940,34 +13746,34 @@
     </row>
     <row r="164">
       <c r="A164" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E164" s="11" t="n">
-        <v>5390</v>
+        <v>164.49</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G164" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t xml:space="preserve">eBay API; vendedor newegg 99.6%; Intel Core i5-14400F - Core i5 14th Gen Raptor Lake 10-Core </t>
         </is>
       </c>
       <c r="H164" s="6" t="inlineStr">
@@ -12978,34 +13784,34 @@
     </row>
     <row r="165">
       <c r="A165" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
-        <v>2000</v>
+        <v>235.27</v>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor jos-980836 100.0%; Intel Core ULTRA 7 265K LGA 1851 Unlocked, 20 cores.</t>
         </is>
       </c>
       <c r="H165" s="6" t="inlineStr">
@@ -13016,34 +13822,34 @@
     </row>
     <row r="166">
       <c r="A166" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E166" s="11" t="n">
-        <v>2650</v>
+        <v>429.97</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G166" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor uventure 99.7%; NEW 32GB (2x16GB) Corsair Vengeance DDR5 PC5-5600 Desktop RA</t>
         </is>
       </c>
       <c r="H166" s="6" t="inlineStr">
@@ -13054,34 +13860,34 @@
     </row>
     <row r="167">
       <c r="A167" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
-        <v>2700</v>
+        <v>474.49</v>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G167" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>eBay API; vendedor hbk41096 100.0%; CORSAIR Vengence RGB DDR5 RAM 32GB (2x16GB) 6000MHz C36 UDIM; envío no indicado</t>
         </is>
       </c>
       <c r="H167" s="6" t="inlineStr">
@@ -13092,34 +13898,34 @@
     </row>
     <row r="168">
       <c r="A168" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E168" s="11" t="n">
-        <v>6200</v>
+        <v>118.96</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G168" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t xml:space="preserve">eBay API; vendedor bike_fix 99.0%; T-Force Vulcan Z DDR4 RAM 16GB (2x8GB) 3200MHz CL16 Desktop </t>
         </is>
       </c>
       <c r="H168" s="6" t="inlineStr">
@@ -13130,34 +13936,34 @@
     </row>
     <row r="169">
       <c r="A169" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
-        <v>540</v>
+        <v>128.99</v>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G169" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>eBay API; vendedor netac-official-store 99.9%; Netac M.2 2280 1TB PCIe3.0 NVMe 1.4 3D NAND Internal Solid S</t>
         </is>
       </c>
       <c r="H169" s="6" t="inlineStr">
@@ -13168,34 +13974,34 @@
     </row>
     <row r="170">
       <c r="A170" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E170" s="11" t="n">
-        <v>900</v>
+        <v>209.99</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>eBay API; vendedor ram_technologies 100.0%; RAM Tech 2TB NVMe SSD Gen4 M.2 2280 | 5000MB/s Read 4500MB/s</t>
         </is>
       </c>
       <c r="H170" s="6" t="inlineStr">
@@ -13206,34 +14012,34 @@
     </row>
     <row r="171">
       <c r="A171" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
-        <v>1500</v>
+        <v>129.99</v>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G171" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>eBay API; vendedor paymore_sugar_land 99.4%; AMD Ryzen 5 5600 3.50GHz 6 Core 100-000000927 12 Thread AM4</t>
         </is>
       </c>
       <c r="H171" s="6" t="inlineStr">
@@ -13244,34 +14050,34 @@
     </row>
     <row r="172">
       <c r="A172" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E172" s="11" t="n">
-        <v>1500</v>
+        <v>315</v>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>eBay API; vendedor senshi-gamer 100.0%; AMD Ryzen 7 5700X3D Desktop CPU Processor 3.0GHz, 8-Core, 16; envío no indicado</t>
         </is>
       </c>
       <c r="H172" s="6" t="inlineStr">
@@ -13282,34 +14088,34 @@
     </row>
     <row r="173">
       <c r="A173" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
-        <v>1850</v>
+        <v>120</v>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>eBay API; vendedor shenidss9ckq 99.1%; AMD Ryzen 5 7600 3.80GHz 6 Core 100-000001015 12 Thread AM5</t>
         </is>
       </c>
       <c r="H173" s="6" t="inlineStr">
@@ -13320,34 +14126,34 @@
     </row>
     <row r="174">
       <c r="A174" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E174" s="11" t="n">
-        <v>2000</v>
+        <v>275</v>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>eBay API; vendedor taspen 100.0%; Ryzen 7 7800X3D 8-Core, 16-Thread Desktop Processor; envío no indicado</t>
         </is>
       </c>
       <c r="H174" s="6" t="inlineStr">
@@ -13358,34 +14164,34 @@
     </row>
     <row r="175">
       <c r="A175" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E175" s="11" t="n">
-        <v>1800</v>
+        <v>454.99</v>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G175" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>eBay API; vendedor goodios_direct 99.6%; **  AMD Ryzen 9 9950X Processor - USED  **</t>
         </is>
       </c>
       <c r="H175" s="6" t="inlineStr">
@@ -13396,34 +14202,34 @@
     </row>
     <row r="176">
       <c r="A176" s="15" t="n">
-        <v>46306</v>
+        <v>46312</v>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E176" s="11" t="n">
-        <v>3550</v>
+        <v>120.99</v>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>eBay API; vendedor vendingollc_1 100.0%; Intel Core i5-12400F 6-Core 2.5GHz SRL4W 65W LGA1700 Desktop</t>
         </is>
       </c>
       <c r="H176" s="6" t="inlineStr">
@@ -13434,34 +14240,34 @@
     </row>
     <row r="177">
       <c r="A177" s="15" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E177" s="11" t="n">
-        <v>5664</v>
+        <v>125</v>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G177" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>eBay API; vendedor secure_processors 99.8%; Intel Core i5-13400 SRMBP</t>
         </is>
       </c>
       <c r="H177" s="6" t="inlineStr">
@@ -13472,11 +14278,11 @@
     </row>
     <row r="178">
       <c r="A178" s="15" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
@@ -13486,20 +14292,20 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E178" s="11" t="n">
-        <v>2537</v>
+        <v>139.99</v>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>eBay API; vendedor paymore_cary 99.7%; Intel Core i5-14400F 2.50GHz 10 Core SRN47 16 Thread LGA 170</t>
         </is>
       </c>
       <c r="H178" s="6" t="inlineStr">
@@ -13510,34 +14316,34 @@
     </row>
     <row r="179">
       <c r="A179" s="15" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E179" s="11" t="n">
-        <v>3127</v>
+        <v>229</v>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G179" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t>eBay API; vendedor archyinva 99.7%; Intel Core Ultra 7 265K 3.90GHz 20 Core Processor LGA 1851 S</t>
         </is>
       </c>
       <c r="H179" s="6" t="inlineStr">
@@ -13548,34 +14354,34 @@
     </row>
     <row r="180">
       <c r="A180" s="15" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E180" s="11" t="n">
-        <v>2150</v>
+        <v>375</v>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t>eBay API; vendedor jaydeetuning 100.0%; Corsair Vengeance 32GB (2x16GB) RAM DDR5 5600MHz CMK32GX5M2B</t>
         </is>
       </c>
       <c r="H180" s="6" t="inlineStr">
@@ -13586,34 +14392,34 @@
     </row>
     <row r="181">
       <c r="A181" s="15" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E181" s="11" t="n">
-        <v>6140</v>
+        <v>399.99</v>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G181" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t xml:space="preserve">eBay API; vendedor ermerl-5mq1rn 99.7%; ITEMPOWERS 32GB (2x16GB) DDR5 6000MHz RGB Desktop RAM Kit - </t>
         </is>
       </c>
       <c r="H181" s="6" t="inlineStr">
@@ -13624,34 +14430,34 @@
     </row>
     <row r="182">
       <c r="A182" s="15" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E182" s="11" t="n">
-        <v>4760</v>
+        <v>71.95</v>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>eBay API; vendedor btcsales0 99.8%; OLOy WarHawk 16GB (2x8GB) DDR4 3200MHz (MD4U0832160BJ0DA); envío no indicado</t>
         </is>
       </c>
       <c r="H182" s="6" t="inlineStr">
@@ -13662,34 +14468,34 @@
     </row>
     <row r="183">
       <c r="A183" s="15" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
-        <v>6800</v>
+        <v>98.59</v>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G183" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor techrefurb4u 99.3%; Western Digital PC SN720 NVMe SSD 1TB</t>
         </is>
       </c>
       <c r="H183" s="6" t="inlineStr">
@@ -13700,34 +14506,34 @@
     </row>
     <row r="184">
       <c r="A184" s="15" t="n">
-        <v>46307</v>
+        <v>46312</v>
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E184" s="11" t="n">
-        <v>2100</v>
+        <v>160</v>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>eBay API; vendedor irefurbish-cincinnati 100.0%; KingSpec 2tb Nvme Ssd 4x4; envío no indicado</t>
         </is>
       </c>
       <c r="H184" s="6" t="inlineStr">
@@ -13738,7 +14544,7 @@
     </row>
     <row r="185">
       <c r="A185" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
@@ -13747,16 +14553,16 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
-        <v>1800</v>
+        <v>5580</v>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
@@ -13765,7 +14571,7 @@
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
@@ -13776,25 +14582,25 @@
     </row>
     <row r="186">
       <c r="A186" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E186" s="11" t="n">
-        <v>4500</v>
+        <v>2300</v>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
@@ -13803,7 +14609,7 @@
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
@@ -13814,7 +14620,7 @@
     </row>
     <row r="187">
       <c r="A187" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
@@ -13823,16 +14629,16 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
-        <v>6700</v>
+        <v>3950</v>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
@@ -13841,7 +14647,7 @@
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
@@ -13852,25 +14658,25 @@
     </row>
     <row r="188">
       <c r="A188" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E188" s="11" t="n">
-        <v>2520</v>
+        <v>4800</v>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
@@ -13879,7 +14685,7 @@
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
@@ -13890,25 +14696,25 @@
     </row>
     <row r="189">
       <c r="A189" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
-        <v>4290</v>
+        <v>5190</v>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
@@ -13917,7 +14723,7 @@
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H189" s="6" t="inlineStr">
@@ -13928,25 +14734,25 @@
     </row>
     <row r="190">
       <c r="A190" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E190" s="11" t="n">
-        <v>2860</v>
+        <v>5390</v>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
@@ -13955,7 +14761,7 @@
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H190" s="6" t="inlineStr">
@@ -13966,25 +14772,25 @@
     </row>
     <row r="191">
       <c r="A191" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2460</v>
+        <v>2000</v>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
@@ -13993,7 +14799,7 @@
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H191" s="6" t="inlineStr">
@@ -14004,25 +14810,25 @@
     </row>
     <row r="192">
       <c r="A192" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E192" s="11" t="n">
-        <v>5360</v>
+        <v>2650</v>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
@@ -14031,7 +14837,7 @@
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H192" s="6" t="inlineStr">
@@ -14042,25 +14848,25 @@
     </row>
     <row r="193">
       <c r="A193" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
-        <v>1710</v>
+        <v>2700</v>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
@@ -14069,7 +14875,7 @@
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H193" s="6" t="inlineStr">
@@ -14080,25 +14886,25 @@
     </row>
     <row r="194">
       <c r="A194" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E194" s="11" t="n">
-        <v>2310</v>
+        <v>6200</v>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
@@ -14107,7 +14913,7 @@
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H194" s="6" t="inlineStr">
@@ -14118,11 +14924,11 @@
     </row>
     <row r="195">
       <c r="A195" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
@@ -14132,11 +14938,11 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
-        <v>2160</v>
+        <v>540</v>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
@@ -14145,7 +14951,7 @@
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H195" s="6" t="inlineStr">
@@ -14156,25 +14962,25 @@
     </row>
     <row r="196">
       <c r="A196" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E196" s="11" t="n">
-        <v>5360</v>
+        <v>900</v>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
@@ -14183,7 +14989,7 @@
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H196" s="6" t="inlineStr">
@@ -14194,25 +15000,25 @@
     </row>
     <row r="197">
       <c r="A197" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
-        <v>5660</v>
+        <v>1500</v>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
@@ -14221,7 +15027,7 @@
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H197" s="6" t="inlineStr">
@@ -14232,25 +15038,25 @@
     </row>
     <row r="198">
       <c r="A198" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E198" s="11" t="n">
-        <v>5860</v>
+        <v>1500</v>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
@@ -14259,7 +15065,7 @@
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H198" s="6" t="inlineStr">
@@ -14270,11 +15076,11 @@
     </row>
     <row r="199">
       <c r="A199" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
@@ -14284,11 +15090,11 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
@@ -14297,7 +15103,7 @@
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H199" s="6" t="inlineStr">
@@ -14308,11 +15114,11 @@
     </row>
     <row r="200">
       <c r="A200" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
@@ -14322,11 +15128,11 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E200" s="11" t="n">
-        <v>2060</v>
+        <v>2000</v>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
@@ -14335,7 +15141,7 @@
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr">
@@ -14346,11 +15152,11 @@
     </row>
     <row r="201">
       <c r="A201" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
@@ -14360,11 +15166,11 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
-        <v>2152</v>
+        <v>1800</v>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
@@ -14373,7 +15179,7 @@
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr">
@@ -14384,11 +15190,11 @@
     </row>
     <row r="202">
       <c r="A202" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
@@ -14398,11 +15204,11 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E202" s="11" t="n">
-        <v>4060</v>
+        <v>3550</v>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
@@ -14411,7 +15217,7 @@
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H202" s="6" t="inlineStr">
@@ -14431,16 +15237,16 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
-        <v>4560</v>
+        <v>5664</v>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
@@ -14449,7 +15255,7 @@
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H203" s="6" t="inlineStr">
@@ -14469,16 +15275,16 @@
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E204" s="11" t="n">
-        <v>5500</v>
+        <v>2537</v>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
@@ -14487,7 +15293,7 @@
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H204" s="6" t="inlineStr">
@@ -14507,16 +15313,16 @@
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
-        <v>2500</v>
+        <v>3127</v>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
@@ -14525,7 +15331,7 @@
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H205" s="6" t="inlineStr">
@@ -14545,16 +15351,16 @@
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Compucenter (WhatsApp)</t>
         </is>
       </c>
       <c r="E206" s="11" t="n">
-        <v>5200</v>
+        <v>2150</v>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
@@ -14563,7 +15369,7 @@
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
         </is>
       </c>
       <c r="H206" s="6" t="inlineStr">
@@ -14574,7 +15380,7 @@
     </row>
     <row r="207">
       <c r="A207" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
@@ -14583,16 +15389,16 @@
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
-        <v>5500</v>
+        <v>6140</v>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
@@ -14601,14 +15407,18 @@
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
-        </is>
-      </c>
-      <c r="H207" s="2" t="n"/>
+          <t>nuevo OEM (garantía 6 meses)</t>
+        </is>
+      </c>
+      <c r="H207" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
@@ -14617,16 +15427,16 @@
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E208" s="11" t="n">
-        <v>2460</v>
+        <v>4760</v>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
@@ -14635,14 +15445,18 @@
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H208" s="2" t="n"/>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H208" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
@@ -14651,16 +15465,16 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
-        <v>2500</v>
+        <v>6800</v>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
@@ -14669,14 +15483,18 @@
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H209" s="2" t="n"/>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H209" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
@@ -14685,16 +15503,16 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E210" s="11" t="n">
-        <v>6840</v>
+        <v>2100</v>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
@@ -14703,32 +15521,36 @@
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
-        </is>
-      </c>
-      <c r="H210" s="2" t="n"/>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H210" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
@@ -14737,7 +15559,7 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
@@ -14748,25 +15570,25 @@
     </row>
     <row r="212">
       <c r="A212" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E212" s="11" t="n">
-        <v>5350</v>
+        <v>4500</v>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
@@ -14775,32 +15597,36 @@
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
-        </is>
-      </c>
-      <c r="H212" s="2" t="n"/>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+        </is>
+      </c>
+      <c r="H212" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
-        <v>7400</v>
+        <v>6700</v>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
@@ -14809,7 +15635,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H213" s="6" t="inlineStr">
@@ -14820,7 +15646,7 @@
     </row>
     <row r="214">
       <c r="A214" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
@@ -14834,11 +15660,11 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (web)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E214" s="11" t="n">
-        <v>2953</v>
+        <v>2520</v>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
@@ -14847,7 +15673,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+          <t>disponible (web)</t>
         </is>
       </c>
       <c r="H214" s="6" t="inlineStr">
@@ -14858,7 +15684,7 @@
     </row>
     <row r="215">
       <c r="A215" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
@@ -14867,16 +15693,16 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900K</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Crazy Store (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
-        <v>6013</v>
+        <v>4290</v>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
@@ -14885,14 +15711,18 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H215" s="2" t="n"/>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+        </is>
+      </c>
+      <c r="H215" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
@@ -14901,16 +15731,16 @@
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E216" s="11" t="n">
-        <v>5890</v>
+        <v>2860</v>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
@@ -14919,14 +15749,18 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
-        </is>
-      </c>
-      <c r="H216" s="2" t="n"/>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H216" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
@@ -14935,16 +15769,16 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
-        <v>3080</v>
+        <v>2460</v>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
@@ -14953,14 +15787,18 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="n"/>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H217" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
@@ -14969,16 +15807,16 @@
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E218" s="11" t="n">
-        <v>3650</v>
+        <v>5360</v>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
@@ -14987,14 +15825,18 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H218" s="2" t="n"/>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H218" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
@@ -15003,16 +15845,16 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>PC Factor (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E219" s="11" t="n">
-        <v>3792</v>
+        <v>1710</v>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
@@ -15021,14 +15863,18 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H219" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H219" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
@@ -15037,16 +15883,16 @@
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E220" s="11" t="n">
-        <v>2800</v>
+        <v>2310</v>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
@@ -15055,14 +15901,18 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="H220" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H220" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
@@ -15071,16 +15921,16 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
-        <v>2260</v>
+        <v>2160</v>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
@@ -15089,14 +15939,18 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H221" s="2" t="n"/>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H221" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
@@ -15105,16 +15959,16 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E222" s="11" t="n">
-        <v>2750</v>
+        <v>5360</v>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
@@ -15123,14 +15977,18 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H222" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H222" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
@@ -15139,16 +15997,16 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7700X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E223" s="11" t="n">
-        <v>3480</v>
+        <v>5660</v>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
@@ -15157,14 +16015,18 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>sin confirmar si es sellado (se preguntó)</t>
-        </is>
-      </c>
-      <c r="H223" s="2" t="n"/>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H223" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
@@ -15173,16 +16035,16 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E224" s="11" t="n">
-        <v>2900</v>
+        <v>5860</v>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
@@ -15191,14 +16053,18 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
-        </is>
-      </c>
-      <c r="H224" s="2" t="n"/>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H224" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
@@ -15212,11 +16078,11 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E225" s="11" t="n">
-        <v>1754</v>
+        <v>1860</v>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
@@ -15225,14 +16091,18 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
-        </is>
-      </c>
-      <c r="H225" s="2" t="n"/>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H225" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
@@ -15241,16 +16111,16 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E226" s="11" t="n">
-        <v>2785</v>
+        <v>2060</v>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
@@ -15259,14 +16129,18 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H226" s="2" t="n"/>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H226" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
@@ -15275,16 +16149,16 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E227" s="11" t="n">
-        <v>1778</v>
+        <v>2152</v>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
@@ -15293,14 +16167,18 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H227" s="2" t="n"/>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H227" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
@@ -15309,16 +16187,16 @@
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E228" s="11" t="n">
-        <v>1600</v>
+        <v>4060</v>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
@@ -15327,14 +16205,18 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H228" s="2" t="n"/>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H228" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
@@ -15343,16 +16225,16 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E229" s="11" t="n">
-        <v>2500</v>
+        <v>4560</v>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
@@ -15361,32 +16243,36 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
-        </is>
-      </c>
-      <c r="H229" s="2" t="n"/>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H229" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E230" s="11" t="n">
-        <v>1730</v>
+        <v>5500</v>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
@@ -15395,7 +16281,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+          <t>nuevo OEM (solo el chip)</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
@@ -15406,7 +16292,7 @@
     </row>
     <row r="231">
       <c r="A231" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
@@ -15415,16 +16301,16 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
-        <v>2384</v>
+        <v>2500</v>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
@@ -15433,7 +16319,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
@@ -15444,7 +16330,7 @@
     </row>
     <row r="232">
       <c r="A232" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
@@ -15453,16 +16339,16 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E232" s="11" t="n">
-        <v>5664</v>
+        <v>5200</v>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
@@ -15471,7 +16357,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>nuevo BOX (web: USD 480 a 11,80)</t>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H232" s="6" t="inlineStr">
@@ -15482,37 +16368,945 @@
     </row>
     <row r="233">
       <c r="A233" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B233" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C233" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E233" s="11" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G233" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B234" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C234" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D234" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E234" s="11" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F234" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G234" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B235" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C235" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E235" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G235" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B236" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C236" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D236" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E236" s="11" t="n">
+        <v>6840</v>
+      </c>
+      <c r="F236" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G236" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B237" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+        </is>
+      </c>
+      <c r="E237" s="11" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G237" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+        </is>
+      </c>
+      <c r="H237" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="15" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D238" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E238" s="11" t="n">
+        <v>5350</v>
+      </c>
+      <c r="F238" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G238" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E239" s="11" t="n">
+        <v>7400</v>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G239" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H239" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C240" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D240" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (web)</t>
+        </is>
+      </c>
+      <c r="E240" s="11" t="n">
+        <v>2953</v>
+      </c>
+      <c r="F240" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G240" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H240" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B241" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C241" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i9-14900K</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>Crazy Store (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E241" s="11" t="n">
+        <v>6013</v>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G241" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E242" s="11" t="n">
+        <v>5890</v>
+      </c>
+      <c r="F242" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G242" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E243" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G243" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B244" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C244" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+        </is>
+      </c>
+      <c r="D244" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E244" s="11" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F244" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G244" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B245" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>PC Factor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E245" s="11" t="n">
+        <v>3792</v>
+      </c>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G245" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E246" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F246" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G246" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C247" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E247" s="11" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G247" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B248" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C248" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D248" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E248" s="11" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F248" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G248" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B249" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C249" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7700X</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E249" s="11" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G249" s="5" t="inlineStr">
+        <is>
+          <t>sin confirmar si es sellado (se preguntó)</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B250" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C250" s="5" t="inlineStr">
+        <is>
+          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+        </is>
+      </c>
+      <c r="D250" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E250" s="11" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F250" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G250" s="5" t="inlineStr">
+        <is>
+          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B251" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E251" s="11" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F251" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G251" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B252" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C252" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D252" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E252" s="11" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F252" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G252" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C253" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D253" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E253" s="11" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F253" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G253" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B254" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C254" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D254" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E254" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F254" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G254" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="15" t="n">
         <v>46311</v>
       </c>
-      <c r="B233" s="5" t="inlineStr">
+      <c r="B255" s="5" t="inlineStr">
         <is>
           <t>Tienda</t>
         </is>
       </c>
-      <c r="C233" s="5" t="inlineStr">
+      <c r="C255" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D255" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E255" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F255" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G255" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B256" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C256" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D256" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E256" s="11" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F256" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G256" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+        </is>
+      </c>
+      <c r="H256" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B257" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C257" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D257" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E257" s="11" t="n">
+        <v>2384</v>
+      </c>
+      <c r="F257" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G257" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+        </is>
+      </c>
+      <c r="H257" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B258" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C258" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D258" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E258" s="11" t="n">
+        <v>5664</v>
+      </c>
+      <c r="F258" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G258" s="5" t="inlineStr">
+        <is>
+          <t>nuevo BOX (web: USD 480 a 11,80)</t>
+        </is>
+      </c>
+      <c r="H258" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B259" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C259" s="5" t="inlineStr">
         <is>
           <t>Intel Core i5-13400</t>
         </is>
       </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="D259" s="5" t="inlineStr">
         <is>
           <t>Cyrex Store (web)</t>
         </is>
       </c>
-      <c r="E233" s="11" t="n">
+      <c r="E259" s="11" t="n">
         <v>2218</v>
       </c>
-      <c r="F233" s="5" t="inlineStr">
+      <c r="F259" s="5" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
       </c>
-      <c r="G233" s="5" t="inlineStr">
+      <c r="G259" s="5" t="inlineStr">
         <is>
           <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
         </is>
       </c>
-      <c r="H233" s="6" t="inlineStr">
+      <c r="H259" s="6" t="inlineStr">
         <is>
           <t>ver</t>
         </is>
@@ -15725,17 +17519,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId238"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId213"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId239"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H259" headerRowCount="1">
-  <autoFilter ref="A1:H259"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H265" headerRowCount="1">
+  <autoFilter ref="A1:H265"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -1242,12 +1242,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1256,20 +1256,18 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>128.99</v>
+        <v>429.97</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>98.59</v>
+        <v>375</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>1730</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1754</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1279,7 +1277,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="L12" s="11">
         <f>IF(D12="","",MIN(MAX(Supuestos!$B$5,CEILING((K12*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D12*Supuestos!$B$9))</f>
@@ -1309,12 +1307,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1323,18 +1321,18 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>429.97</v>
+        <v>549.99</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>375</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H13" s="2" t="n"/>
+        <v>454.99</v>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="8" t="n">
+        <v>5580</v>
+      </c>
       <c r="I13" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1344,7 +1342,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L13" s="11">
         <f>IF(D13="","",MIN(MAX(Supuestos!$B$5,CEILING((K13*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D13*Supuestos!$B$9))</f>
@@ -1374,12 +1372,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1388,17 +1386,19 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>549.99</v>
+        <v>128.99</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="G14" s="2" t="n"/>
+        <v>98.59</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>1230</v>
+      </c>
       <c r="H14" s="8" t="n">
-        <v>5580</v>
+        <v>1754</v>
       </c>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1409,7 +1409,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1945,7 +1945,9 @@
       <c r="E3" s="7" t="n">
         <v>98.59</v>
       </c>
-      <c r="F3" s="2" t="n"/>
+      <c r="F3" s="8" t="n">
+        <v>1230</v>
+      </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
@@ -2934,7 +2936,9 @@
         <v>120</v>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="G21" s="8" t="n">
+        <v>2850</v>
+      </c>
       <c r="H21" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7533,7 +7537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H259"/>
+  <dimension ref="A1:H265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17307,6 +17311,222 @@
         </is>
       </c>
       <c r="H259" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D260" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E260" s="11" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G260" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B261" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C261" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D261" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E261" s="11" t="n">
+        <v>5960</v>
+      </c>
+      <c r="F261" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G261" s="5" t="inlineStr">
+        <is>
+          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D262" s="5" t="inlineStr">
+        <is>
+          <t>Gamer Store Cbba (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E262" s="11" t="n">
+        <v>2067</v>
+      </c>
+      <c r="F262" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G262" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D263" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E263" s="11" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F263" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G263" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E264" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F264" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G264" s="5" t="inlineStr">
+        <is>
+          <t>sin dato de estado ni marca (recién publicado)</t>
+        </is>
+      </c>
+      <c r="H264" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E265" s="11" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>Kingston NV3 1TB (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H265" s="6" t="inlineStr">
         <is>
           <t>ver</t>
         </is>
@@ -17552,10 +17772,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId237"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId241"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId239"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId242"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O95" headerRowCount="1">
-  <autoFilter ref="A1:O95"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O109" headerRowCount="1">
+  <autoFilter ref="A1:O109"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H265" headerRowCount="1">
-  <autoFilter ref="A1:H265"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H292" headerRowCount="1">
+  <autoFilter ref="A1:H292"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -633,7 +633,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>¿Qué conviene traer? · 17/10/2026</t>
+          <t>¿Qué conviene traer? · 18/10/2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -785,12 +785,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>140.26</v>
+        <v>209.99</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
-        <v>2800</v>
+        <v>4060</v>
       </c>
       <c r="I5" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="K5" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L5" s="11">
         <f>IF(D5="","",MIN(MAX(Supuestos!$B$5,CEILING((K5*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D5*Supuestos!$B$9))</f>
@@ -850,12 +850,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -864,17 +864,17 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>209.99</v>
+        <v>230</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>160</v>
+        <v>209.68</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
-        <v>4060</v>
+        <v>3950</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -885,7 +885,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -915,7 +915,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -929,17 +929,19 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>230</v>
+        <v>324.99</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>229</v>
-      </c>
-      <c r="G7" s="2" t="n"/>
+        <v>289.99</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="H7" s="8" t="n">
-        <v>3950</v>
+        <v>4760</v>
       </c>
       <c r="I7" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -950,7 +952,7 @@
         <v/>
       </c>
       <c r="K7" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L7" s="11">
         <f>IF(D7="","",MIN(MAX(Supuestos!$B$5,CEILING((K7*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D7*Supuestos!$B$9))</f>
@@ -980,7 +982,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -994,19 +996,17 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>324.99</v>
+        <v>150</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>275</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>4800</v>
-      </c>
+        <v>124.99</v>
+      </c>
+      <c r="G8" s="2" t="n"/>
       <c r="H8" s="8" t="n">
-        <v>4760</v>
+        <v>2260</v>
       </c>
       <c r="I8" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1017,7 +1017,7 @@
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="L8" s="11">
         <f>IF(D8="","",MIN(MAX(Supuestos!$B$5,CEILING((K8*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D8*Supuestos!$B$9))</f>
@@ -1047,12 +1047,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1061,18 +1061,18 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>120.99</v>
-      </c>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="8" t="n">
-        <v>2260</v>
-      </c>
+        <v>419.99</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="H9" s="2" t="n"/>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1082,7 +1082,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1177,12 +1177,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1191,18 +1191,18 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>474.49</v>
+        <v>213.95</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H11" s="2" t="n"/>
+        <v>120</v>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L11" s="11">
         <f>IF(D11="","",MIN(MAX(Supuestos!$B$5,CEILING((K11*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D11*Supuestos!$B$9))</f>
@@ -1242,12 +1242,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1256,18 +1256,20 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>429.97</v>
+        <v>93.5</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>375</v>
+        <v>96.94</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H12" s="2" t="n"/>
+        <v>1230</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1277,7 +1279,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="L12" s="11">
         <f>IF(D12="","",MIN(MAX(Supuestos!$B$5,CEILING((K12*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D12*Supuestos!$B$9))</f>
@@ -1307,12 +1309,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1321,18 +1323,18 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>549.99</v>
+        <v>429.97</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="8" t="n">
-        <v>5580</v>
-      </c>
+        <v>379.99</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H13" s="2" t="n"/>
       <c r="I13" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1342,7 +1344,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="L13" s="11">
         <f>IF(D13="","",MIN(MAX(Supuestos!$B$5,CEILING((K13*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D13*Supuestos!$B$9))</f>
@@ -1372,12 +1374,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1386,19 +1388,17 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>128.99</v>
+        <v>549.99</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>98.59</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>1230</v>
-      </c>
+        <v>454.99</v>
+      </c>
+      <c r="G14" s="2" t="n"/>
       <c r="H14" s="8" t="n">
-        <v>1754</v>
+        <v>5580</v>
       </c>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1409,7 +1409,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1524,7 +1524,7 @@
         <v>9.99</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>71.95</v>
+        <v>72.95</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>900</v>
@@ -1773,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="K2" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L2" s="16">
         <f>IF(OR($K2="",D2=""),"",IF(COUNTIFS($B:$B,$B2,$A:$A,$K2,D:D,"&gt;=0")=0,"",D2-SUMIFS(D:D,$B:$B,$B2,$A:$A,$K2)))</f>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1940,14 +1940,12 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>128.99</v>
+        <v>93.5</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>98.59</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>1230</v>
-      </c>
+        <v>96.94</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
@@ -1963,7 +1961,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L3" s="16">
         <f>IF(OR($K3="",D3=""),"",IF(COUNTIFS($B:$B,$B3,$A:$A,$K3,D:D,"&gt;=0")=0,"",D3-SUMIFS(D:D,$B:$B,$B3,$A:$A,$K3)))</f>
@@ -1984,7 +1982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -2018,7 +2016,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L4" s="16">
         <f>IF(OR($K4="",D4=""),"",IF(COUNTIFS($B:$B,$B4,$A:$A,$K4,D:D,"&gt;=0")=0,"",D4-SUMIFS(D:D,$B:$B,$B4,$A:$A,$K4)))</f>
@@ -2039,7 +2037,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -2055,7 +2053,7 @@
         <v>324.99</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>275</v>
+        <v>289.99</v>
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
@@ -2073,7 +2071,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L5" s="16">
         <f>IF(OR($K5="",D5=""),"",IF(COUNTIFS($B:$B,$B5,$A:$A,$K5,D:D,"&gt;=0")=0,"",D5-SUMIFS(D:D,$B:$B,$B5,$A:$A,$K5)))</f>
@@ -2094,7 +2092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2126,7 +2124,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
@@ -2147,7 +2145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2160,7 +2158,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>140.26</v>
+        <v>213.95</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>120</v>
@@ -2181,7 +2179,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L7" s="16">
         <f>IF(OR($K7="",D7=""),"",IF(COUNTIFS($B:$B,$B7,$A:$A,$K7,D:D,"&gt;=0")=0,"",D7-SUMIFS(D:D,$B:$B,$B7,$A:$A,$K7)))</f>
@@ -2202,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -2236,7 +2234,7 @@
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L8" s="16">
         <f>IF(OR($K8="",D8=""),"",IF(COUNTIFS($B:$B,$B8,$A:$A,$K8,D:D,"&gt;=0")=0,"",D8-SUMIFS(D:D,$B:$B,$B8,$A:$A,$K8)))</f>
@@ -2257,7 +2255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2273,7 +2271,7 @@
         <v>118.96</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>71.95</v>
+        <v>72.95</v>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
@@ -2291,7 +2289,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L9" s="16">
         <f>IF(OR($K9="",D9=""),"",IF(COUNTIFS($B:$B,$B9,$A:$A,$K9,D:D,"&gt;=0")=0,"",D9-SUMIFS(D:D,$B:$B,$B9,$A:$A,$K9)))</f>
@@ -2312,7 +2310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2346,7 +2344,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L10" s="16">
         <f>IF(OR($K10="",D10=""),"",IF(COUNTIFS($B:$B,$B10,$A:$A,$K10,D:D,"&gt;=0")=0,"",D10-SUMIFS(D:D,$B:$B,$B10,$A:$A,$K10)))</f>
@@ -2367,7 +2365,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2399,7 +2397,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L11" s="16">
         <f>IF(OR($K11="",D11=""),"",IF(COUNTIFS($B:$B,$B11,$A:$A,$K11,D:D,"&gt;=0")=0,"",D11-SUMIFS(D:D,$B:$B,$B11,$A:$A,$K11)))</f>
@@ -2420,7 +2418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2436,7 +2434,7 @@
         <v>150</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>120.99</v>
+        <v>124.99</v>
       </c>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
@@ -2454,7 +2452,7 @@
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L12" s="16">
         <f>IF(OR($K12="",D12=""),"",IF(COUNTIFS($B:$B,$B12,$A:$A,$K12,D:D,"&gt;=0")=0,"",D12-SUMIFS(D:D,$B:$B,$B12,$A:$A,$K12)))</f>
@@ -2475,7 +2473,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2491,7 +2489,7 @@
         <v>235.27</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>229</v>
+        <v>209.68</v>
       </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
@@ -2509,7 +2507,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L13" s="16">
         <f>IF(OR($K13="",D13=""),"",IF(COUNTIFS($B:$B,$B13,$A:$A,$K13,D:D,"&gt;=0")=0,"",D13-SUMIFS(D:D,$B:$B,$B13,$A:$A,$K13)))</f>
@@ -2530,7 +2528,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2543,10 +2541,10 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>474.49</v>
+        <v>450</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>399.99</v>
+        <v>419.99</v>
       </c>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
@@ -2564,7 +2562,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L14" s="16">
         <f>IF(OR($K14="",D14=""),"",IF(COUNTIFS($B:$B,$B14,$A:$A,$K14,D:D,"&gt;=0")=0,"",D14-SUMIFS(D:D,$B:$B,$B14,$A:$A,$K14)))</f>
@@ -2585,7 +2583,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -2601,7 +2599,7 @@
         <v>429.97</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
@@ -2619,7 +2617,7 @@
         </is>
       </c>
       <c r="K15" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L15" s="16">
         <f>IF(OR($K15="",D15=""),"",IF(COUNTIFS($B:$B,$B15,$A:$A,$K15,D:D,"&gt;=0")=0,"",D15-SUMIFS(D:D,$B:$B,$B15,$A:$A,$K15)))</f>
@@ -2640,7 +2638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -2656,7 +2654,7 @@
         <v>209.99</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>161.99</v>
+        <v>160</v>
       </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
@@ -2674,7 +2672,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2695,7 +2693,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -2708,13 +2706,13 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>110</v>
+        <v>128.99</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>80</v>
+        <v>98.59</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1730</v>
+        <v>1230</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="9">
@@ -2731,7 +2729,7 @@
         </is>
       </c>
       <c r="K17" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L17" s="16">
         <f>IF(OR($K17="",D17=""),"",IF(COUNTIFS($B:$B,$B17,$A:$A,$K17,D:D,"&gt;=0")=0,"",D17-SUMIFS(D:D,$B:$B,$B17,$A:$A,$K17)))</f>
@@ -2752,7 +2750,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -2786,7 +2784,7 @@
         </is>
       </c>
       <c r="K18" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L18" s="16">
         <f>IF(OR($K18="",D18=""),"",IF(COUNTIFS($B:$B,$B18,$A:$A,$K18,D:D,"&gt;=0")=0,"",D18-SUMIFS(D:D,$B:$B,$B18,$A:$A,$K18)))</f>
@@ -2807,7 +2805,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2820,15 +2818,13 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>320</v>
+        <v>324.99</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>279.99</v>
+        <v>275</v>
       </c>
       <c r="F19" s="2" t="n"/>
-      <c r="G19" s="8" t="n">
-        <v>5664</v>
-      </c>
+      <c r="G19" s="2" t="n"/>
       <c r="H19" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A19,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2843,7 +2839,7 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L19" s="16">
         <f>IF(OR($K19="",D19=""),"",IF(COUNTIFS($B:$B,$B19,$A:$A,$K19,D:D,"&gt;=0")=0,"",D19-SUMIFS(D:D,$B:$B,$B19,$A:$A,$K19)))</f>
@@ -2864,7 +2860,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2878,7 +2874,7 @@
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>298.01</v>
+        <v>315</v>
       </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -2896,7 +2892,7 @@
         </is>
       </c>
       <c r="K20" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L20" s="16">
         <f>IF(OR($K20="",D20=""),"",IF(COUNTIFS($B:$B,$B20,$A:$A,$K20,D:D,"&gt;=0")=0,"",D20-SUMIFS(D:D,$B:$B,$B20,$A:$A,$K20)))</f>
@@ -2917,7 +2913,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -2930,15 +2926,13 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>141.24</v>
+        <v>140.26</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="8" t="n">
-        <v>2850</v>
-      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2953,7 +2947,7 @@
         </is>
       </c>
       <c r="K21" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L21" s="16">
         <f>IF(OR($K21="",D21=""),"",IF(COUNTIFS($B:$B,$B21,$A:$A,$K21,D:D,"&gt;=0")=0,"",D21-SUMIFS(D:D,$B:$B,$B21,$A:$A,$K21)))</f>
@@ -2974,7 +2968,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3008,7 +3002,7 @@
         </is>
       </c>
       <c r="K22" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
@@ -3029,7 +3023,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -3045,7 +3039,7 @@
         <v>118.96</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>73.95</v>
+        <v>71.95</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -3063,7 +3057,7 @@
         </is>
       </c>
       <c r="K23" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L23" s="16">
         <f>IF(OR($K23="",D23=""),"",IF(COUNTIFS($B:$B,$B23,$A:$A,$K23,D:D,"&gt;=0")=0,"",D23-SUMIFS(D:D,$B:$B,$B23,$A:$A,$K23)))</f>
@@ -3084,7 +3078,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -3103,9 +3097,7 @@
         <v>139.99</v>
       </c>
       <c r="F24" s="2" t="n"/>
-      <c r="G24" s="8" t="n">
-        <v>2384</v>
-      </c>
+      <c r="G24" s="2" t="n"/>
       <c r="H24" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A24,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3120,7 +3112,7 @@
         </is>
       </c>
       <c r="K24" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L24" s="16">
         <f>IF(OR($K24="",D24=""),"",IF(COUNTIFS($B:$B,$B24,$A:$A,$K24,D:D,"&gt;=0")=0,"",D24-SUMIFS(D:D,$B:$B,$B24,$A:$A,$K24)))</f>
@@ -3141,7 +3133,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -3155,7 +3147,7 @@
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>149.99</v>
+        <v>125</v>
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
@@ -3173,7 +3165,7 @@
         </is>
       </c>
       <c r="K25" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L25" s="16">
         <f>IF(OR($K25="",D25=""),"",IF(COUNTIFS($B:$B,$B25,$A:$A,$K25,D:D,"&gt;=0")=0,"",D25-SUMIFS(D:D,$B:$B,$B25,$A:$A,$K25)))</f>
@@ -3194,7 +3186,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3228,7 +3220,7 @@
         </is>
       </c>
       <c r="K26" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L26" s="16">
         <f>IF(OR($K26="",D26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,D:D,"&gt;=0")=0,"",D26-SUMIFS(D:D,$B:$B,$B26,$A:$A,$K26)))</f>
@@ -3249,7 +3241,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3262,7 +3254,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>234.99</v>
+        <v>235.27</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>229</v>
@@ -3283,7 +3275,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L27" s="16">
         <f>IF(OR($K27="",D27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,D:D,"&gt;=0")=0,"",D27-SUMIFS(D:D,$B:$B,$B27,$A:$A,$K27)))</f>
@@ -3304,7 +3296,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -3320,7 +3312,7 @@
         <v>474.49</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>389.99</v>
+        <v>399.99</v>
       </c>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
@@ -3338,7 +3330,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L28" s="16">
         <f>IF(OR($K28="",D28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,D:D,"&gt;=0")=0,"",D28-SUMIFS(D:D,$B:$B,$B28,$A:$A,$K28)))</f>
@@ -3359,7 +3351,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -3375,7 +3367,7 @@
         <v>429.97</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
@@ -3393,7 +3385,7 @@
         </is>
       </c>
       <c r="K29" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L29" s="16">
         <f>IF(OR($K29="",D29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,D:D,"&gt;=0")=0,"",D29-SUMIFS(D:D,$B:$B,$B29,$A:$A,$K29)))</f>
@@ -3414,7 +3406,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3430,7 +3422,7 @@
         <v>209.99</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>175</v>
+        <v>161.99</v>
       </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
@@ -3448,7 +3440,7 @@
         </is>
       </c>
       <c r="K30" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L30" s="16">
         <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
@@ -3469,7 +3461,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3482,15 +3474,15 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>128.99</v>
+        <v>110</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="8" t="n">
-        <v>1754</v>
-      </c>
+      <c r="F31" s="8" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G31" s="2" t="n"/>
       <c r="H31" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3505,7 +3497,7 @@
         </is>
       </c>
       <c r="K31" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L31" s="16">
         <f>IF(OR($K31="",D31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,D:D,"&gt;=0")=0,"",D31-SUMIFS(D:D,$B:$B,$B31,$A:$A,$K31)))</f>
@@ -3526,7 +3518,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3539,10 +3531,10 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>689.34</v>
+        <v>549.99</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>375</v>
+        <v>454.99</v>
       </c>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
@@ -3560,7 +3552,7 @@
         </is>
       </c>
       <c r="K32" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L32" s="16">
         <f>IF(OR($K32="",D32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,D:D,"&gt;=0")=0,"",D32-SUMIFS(D:D,$B:$B,$B32,$A:$A,$K32)))</f>
@@ -3581,7 +3573,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3601,7 +3593,7 @@
       </c>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="8" t="n">
-        <v>5890</v>
+        <v>5664</v>
       </c>
       <c r="H33" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))),"")</f>
@@ -3617,7 +3609,7 @@
         </is>
       </c>
       <c r="K33" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L33" s="16">
         <f>IF(OR($K33="",D33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,D:D,"&gt;=0")=0,"",D33-SUMIFS(D:D,$B:$B,$B33,$A:$A,$K33)))</f>
@@ -3638,7 +3630,7 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -3652,7 +3644,7 @@
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>295</v>
+        <v>298.01</v>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
@@ -3670,7 +3662,7 @@
         </is>
       </c>
       <c r="K34" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L34" s="16">
         <f>IF(OR($K34="",D34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,D:D,"&gt;=0")=0,"",D34-SUMIFS(D:D,$B:$B,$B34,$A:$A,$K34)))</f>
@@ -3691,7 +3683,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3704,14 +3696,14 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>142.24</v>
+        <v>141.24</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="8" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="H35" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))),"")</f>
@@ -3727,7 +3719,7 @@
         </is>
       </c>
       <c r="K35" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L35" s="16">
         <f>IF(OR($K35="",D35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,D:D,"&gt;=0")=0,"",D35-SUMIFS(D:D,$B:$B,$B35,$A:$A,$K35)))</f>
@@ -3748,7 +3740,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -3764,7 +3756,7 @@
         <v>138.9</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
@@ -3782,7 +3774,7 @@
         </is>
       </c>
       <c r="K36" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L36" s="16">
         <f>IF(OR($K36="",D36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,D:D,"&gt;=0")=0,"",D36-SUMIFS(D:D,$B:$B,$B36,$A:$A,$K36)))</f>
@@ -3803,7 +3795,7 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -3816,7 +3808,7 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>75</v>
+        <v>118.96</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>73.95</v>
@@ -3837,7 +3829,7 @@
         </is>
       </c>
       <c r="K37" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L37" s="16">
         <f>IF(OR($K37="",D37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,D:D,"&gt;=0")=0,"",D37-SUMIFS(D:D,$B:$B,$B37,$A:$A,$K37)))</f>
@@ -3858,7 +3850,7 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3874,11 +3866,11 @@
         <v>164.49</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>134.99</v>
+        <v>139.99</v>
       </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="8" t="n">
-        <v>2750</v>
+        <v>2384</v>
       </c>
       <c r="H38" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))),"")</f>
@@ -3894,7 +3886,7 @@
         </is>
       </c>
       <c r="K38" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L38" s="16">
         <f>IF(OR($K38="",D38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,D:D,"&gt;=0")=0,"",D38-SUMIFS(D:D,$B:$B,$B38,$A:$A,$K38)))</f>
@@ -3915,7 +3907,7 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3947,7 +3939,7 @@
         </is>
       </c>
       <c r="K39" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L39" s="16">
         <f>IF(OR($K39="",D39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,D:D,"&gt;=0")=0,"",D39-SUMIFS(D:D,$B:$B,$B39,$A:$A,$K39)))</f>
@@ -3968,7 +3960,7 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3984,12 +3976,10 @@
         <v>150</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>114.99</v>
+        <v>120.99</v>
       </c>
       <c r="F40" s="2" t="n"/>
-      <c r="G40" s="8" t="n">
-        <v>2260</v>
-      </c>
+      <c r="G40" s="2" t="n"/>
       <c r="H40" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A40,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A40,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4004,7 +3994,7 @@
         </is>
       </c>
       <c r="K40" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L40" s="16">
         <f>IF(OR($K40="",D40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,D:D,"&gt;=0")=0,"",D40-SUMIFS(D:D,$B:$B,$B40,$A:$A,$K40)))</f>
@@ -4025,7 +4015,7 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -4059,7 +4049,7 @@
         </is>
       </c>
       <c r="K41" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L41" s="16">
         <f>IF(OR($K41="",D41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,D:D,"&gt;=0")=0,"",D41-SUMIFS(D:D,$B:$B,$B41,$A:$A,$K41)))</f>
@@ -4080,7 +4070,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4093,10 +4083,10 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>435.99</v>
+        <v>474.49</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>394.99</v>
+        <v>389.99</v>
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
@@ -4114,7 +4104,7 @@
         </is>
       </c>
       <c r="K42" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L42" s="16">
         <f>IF(OR($K42="",D42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,D:D,"&gt;=0")=0,"",D42-SUMIFS(D:D,$B:$B,$B42,$A:$A,$K42)))</f>
@@ -4135,7 +4125,7 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4151,7 +4141,7 @@
         <v>429.97</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
@@ -4169,7 +4159,7 @@
         </is>
       </c>
       <c r="K43" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L43" s="16">
         <f>IF(OR($K43="",D43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,D:D,"&gt;=0")=0,"",D43-SUMIFS(D:D,$B:$B,$B43,$A:$A,$K43)))</f>
@@ -4190,7 +4180,7 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4206,7 +4196,7 @@
         <v>209.99</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>164.99</v>
+        <v>175</v>
       </c>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
@@ -4224,7 +4214,7 @@
         </is>
       </c>
       <c r="K44" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L44" s="16">
         <f>IF(OR($K44="",D44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,D:D,"&gt;=0")=0,"",D44-SUMIFS(D:D,$B:$B,$B44,$A:$A,$K44)))</f>
@@ -4245,7 +4235,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
@@ -4258,13 +4248,15 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>117.99</v>
+        <v>128.99</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="F45" s="2" t="n"/>
-      <c r="G45" s="2" t="n"/>
+      <c r="G45" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="H45" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4279,7 +4271,7 @@
         </is>
       </c>
       <c r="K45" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L45" s="16">
         <f>IF(OR($K45="",D45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,D:D,"&gt;=0")=0,"",D45-SUMIFS(D:D,$B:$B,$B45,$A:$A,$K45)))</f>
@@ -4300,7 +4292,7 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -4313,10 +4305,10 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>499.99</v>
+        <v>689.34</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>454.99</v>
+        <v>375</v>
       </c>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
@@ -4334,7 +4326,7 @@
         </is>
       </c>
       <c r="K46" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L46" s="16">
         <f>IF(OR($K46="",D46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,D:D,"&gt;=0")=0,"",D46-SUMIFS(D:D,$B:$B,$B46,$A:$A,$K46)))</f>
@@ -4355,7 +4347,7 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
@@ -4368,13 +4360,15 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>275.99</v>
+        <v>279.99</v>
       </c>
       <c r="F47" s="2" t="n"/>
-      <c r="G47" s="2" t="n"/>
+      <c r="G47" s="8" t="n">
+        <v>5890</v>
+      </c>
       <c r="H47" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4389,7 +4383,7 @@
         </is>
       </c>
       <c r="K47" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L47" s="16">
         <f>IF(OR($K47="",D47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,D:D,"&gt;=0")=0,"",D47-SUMIFS(D:D,$B:$B,$B47,$A:$A,$K47)))</f>
@@ -4410,7 +4404,7 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
@@ -4442,7 +4436,7 @@
         </is>
       </c>
       <c r="K48" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L48" s="16">
         <f>IF(OR($K48="",D48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,D:D,"&gt;=0")=0,"",D48-SUMIFS(D:D,$B:$B,$B48,$A:$A,$K48)))</f>
@@ -4463,7 +4457,7 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
@@ -4479,10 +4473,12 @@
         <v>142.24</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>121.99</v>
+        <v>120</v>
       </c>
       <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
+      <c r="G49" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H49" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4497,7 +4493,7 @@
         </is>
       </c>
       <c r="K49" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L49" s="16">
         <f>IF(OR($K49="",D49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,D:D,"&gt;=0")=0,"",D49-SUMIFS(D:D,$B:$B,$B49,$A:$A,$K49)))</f>
@@ -4518,7 +4514,7 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
@@ -4534,7 +4530,7 @@
         <v>138.9</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>129.99</v>
+        <v>135</v>
       </c>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
@@ -4552,7 +4548,7 @@
         </is>
       </c>
       <c r="K50" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L50" s="16">
         <f>IF(OR($K50="",D50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,D:D,"&gt;=0")=0,"",D50-SUMIFS(D:D,$B:$B,$B50,$A:$A,$K50)))</f>
@@ -4573,7 +4569,7 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
@@ -4586,10 +4582,10 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>72.98999999999999</v>
+        <v>75</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>65</v>
+        <v>73.95</v>
       </c>
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
@@ -4607,7 +4603,7 @@
         </is>
       </c>
       <c r="K51" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L51" s="16">
         <f>IF(OR($K51="",D51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,D:D,"&gt;=0")=0,"",D51-SUMIFS(D:D,$B:$B,$B51,$A:$A,$K51)))</f>
@@ -4628,7 +4624,7 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -4644,10 +4640,12 @@
         <v>164.49</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>134</v>
+        <v>134.99</v>
       </c>
       <c r="F52" s="2" t="n"/>
-      <c r="G52" s="2" t="n"/>
+      <c r="G52" s="8" t="n">
+        <v>2750</v>
+      </c>
       <c r="H52" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4662,7 +4660,7 @@
         </is>
       </c>
       <c r="K52" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L52" s="16">
         <f>IF(OR($K52="",D52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,D:D,"&gt;=0")=0,"",D52-SUMIFS(D:D,$B:$B,$B52,$A:$A,$K52)))</f>
@@ -4683,7 +4681,7 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
@@ -4715,7 +4713,7 @@
         </is>
       </c>
       <c r="K53" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L53" s="16">
         <f>IF(OR($K53="",D53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,D:D,"&gt;=0")=0,"",D53-SUMIFS(D:D,$B:$B,$B53,$A:$A,$K53)))</f>
@@ -4736,7 +4734,7 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
@@ -4752,10 +4750,12 @@
         <v>150</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>120.99</v>
+        <v>114.99</v>
       </c>
       <c r="F54" s="2" t="n"/>
-      <c r="G54" s="2" t="n"/>
+      <c r="G54" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="H54" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A54,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A54,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="K54" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L54" s="16">
         <f>IF(OR($K54="",D54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,D:D,"&gt;=0")=0,"",D54-SUMIFS(D:D,$B:$B,$B54,$A:$A,$K54)))</f>
@@ -4791,7 +4791,7 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="K55" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L55" s="16">
         <f>IF(OR($K55="",D55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,D:D,"&gt;=0")=0,"",D55-SUMIFS(D:D,$B:$B,$B55,$A:$A,$K55)))</f>
@@ -4846,7 +4846,7 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>435.99</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>399.9</v>
+        <v>394.99</v>
       </c>
       <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="n"/>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="K56" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L56" s="16">
         <f>IF(OR($K56="",D56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,D:D,"&gt;=0")=0,"",D56-SUMIFS(D:D,$B:$B,$B56,$A:$A,$K56)))</f>
@@ -4901,7 +4901,7 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>429.97</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="K57" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L57" s="16">
         <f>IF(OR($K57="",D57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,D:D,"&gt;=0")=0,"",D57-SUMIFS(D:D,$B:$B,$B57,$A:$A,$K57)))</f>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>209.99</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>170</v>
+        <v>164.99</v>
       </c>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="K58" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L58" s="16">
         <f>IF(OR($K58="",D58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,D:D,"&gt;=0")=0,"",D58-SUMIFS(D:D,$B:$B,$B58,$A:$A,$K58)))</f>
@@ -5011,7 +5011,7 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>114.99</v>
+        <v>117.99</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="n"/>
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="K59" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L59" s="16">
         <f>IF(OR($K59="",D59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,D:D,"&gt;=0")=0,"",D59-SUMIFS(D:D,$B:$B,$B59,$A:$A,$K59)))</f>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="K60" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L60" s="16">
         <f>IF(OR($K60="",D60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,D:D,"&gt;=0")=0,"",D60-SUMIFS(D:D,$B:$B,$B60,$A:$A,$K60)))</f>
@@ -5121,7 +5121,7 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
@@ -5137,14 +5137,10 @@
         <v>329</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G61" s="8" t="n">
-        <v>5350</v>
-      </c>
+        <v>275.99</v>
+      </c>
+      <c r="F61" s="2" t="n"/>
+      <c r="G61" s="2" t="n"/>
       <c r="H61" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5159,7 +5155,7 @@
         </is>
       </c>
       <c r="K61" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L61" s="16">
         <f>IF(OR($K61="",D61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,D:D,"&gt;=0")=0,"",D61-SUMIFS(D:D,$B:$B,$B61,$A:$A,$K61)))</f>
@@ -5180,7 +5176,7 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
@@ -5194,7 +5190,7 @@
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>299.99</v>
+        <v>295</v>
       </c>
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
@@ -5212,7 +5208,7 @@
         </is>
       </c>
       <c r="K62" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L62" s="16">
         <f>IF(OR($K62="",D62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,D:D,"&gt;=0")=0,"",D62-SUMIFS(D:D,$B:$B,$B62,$A:$A,$K62)))</f>
@@ -5233,7 +5229,7 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
@@ -5246,10 +5242,10 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>143.24</v>
+        <v>142.24</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>122.99</v>
+        <v>121.99</v>
       </c>
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="2" t="n"/>
@@ -5267,7 +5263,7 @@
         </is>
       </c>
       <c r="K63" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L63" s="16">
         <f>IF(OR($K63="",D63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,D:D,"&gt;=0")=0,"",D63-SUMIFS(D:D,$B:$B,$B63,$A:$A,$K63)))</f>
@@ -5288,7 +5284,7 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
@@ -5304,7 +5300,7 @@
         <v>138.9</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="n"/>
@@ -5322,7 +5318,7 @@
         </is>
       </c>
       <c r="K64" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L64" s="16">
         <f>IF(OR($K64="",D64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,D:D,"&gt;=0")=0,"",D64-SUMIFS(D:D,$B:$B,$B64,$A:$A,$K64)))</f>
@@ -5343,7 +5339,7 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
@@ -5356,10 +5352,10 @@
         </is>
       </c>
       <c r="D65" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>65</v>
       </c>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="n"/>
@@ -5377,7 +5373,7 @@
         </is>
       </c>
       <c r="K65" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L65" s="16">
         <f>IF(OR($K65="",D65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,D:D,"&gt;=0")=0,"",D65-SUMIFS(D:D,$B:$B,$B65,$A:$A,$K65)))</f>
@@ -5398,7 +5394,7 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
@@ -5417,9 +5413,7 @@
         <v>134</v>
       </c>
       <c r="F66" s="2" t="n"/>
-      <c r="G66" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G66" s="2" t="n"/>
       <c r="H66" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5434,7 +5428,7 @@
         </is>
       </c>
       <c r="K66" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L66" s="16">
         <f>IF(OR($K66="",D66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,D:D,"&gt;=0")=0,"",D66-SUMIFS(D:D,$B:$B,$B66,$A:$A,$K66)))</f>
@@ -5455,7 +5449,7 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
@@ -5487,7 +5481,7 @@
         </is>
       </c>
       <c r="K67" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L67" s="16">
         <f>IF(OR($K67="",D67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,D:D,"&gt;=0")=0,"",D67-SUMIFS(D:D,$B:$B,$B67,$A:$A,$K67)))</f>
@@ -5508,7 +5502,7 @@
     </row>
     <row r="68">
       <c r="A68" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
@@ -5524,7 +5518,7 @@
         <v>150</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>99</v>
+        <v>120.99</v>
       </c>
       <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="n"/>
@@ -5542,7 +5536,7 @@
         </is>
       </c>
       <c r="K68" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L68" s="16">
         <f>IF(OR($K68="",D68=""),"",IF(COUNTIFS($B:$B,$B68,$A:$A,$K68,D:D,"&gt;=0")=0,"",D68-SUMIFS(D:D,$B:$B,$B68,$A:$A,$K68)))</f>
@@ -5563,7 +5557,7 @@
     </row>
     <row r="69">
       <c r="A69" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
@@ -5579,7 +5573,7 @@
         <v>234.99</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>209.99</v>
+        <v>229</v>
       </c>
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
@@ -5597,7 +5591,7 @@
         </is>
       </c>
       <c r="K69" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L69" s="16">
         <f>IF(OR($K69="",D69=""),"",IF(COUNTIFS($B:$B,$B69,$A:$A,$K69,D:D,"&gt;=0")=0,"",D69-SUMIFS(D:D,$B:$B,$B69,$A:$A,$K69)))</f>
@@ -5618,7 +5612,7 @@
     </row>
     <row r="70">
       <c r="A70" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
@@ -5652,7 +5646,7 @@
         </is>
       </c>
       <c r="K70" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L70" s="16">
         <f>IF(OR($K70="",D70=""),"",IF(COUNTIFS($B:$B,$B70,$A:$A,$K70,D:D,"&gt;=0")=0,"",D70-SUMIFS(D:D,$B:$B,$B70,$A:$A,$K70)))</f>
@@ -5673,7 +5667,7 @@
     </row>
     <row r="71">
       <c r="A71" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
@@ -5686,10 +5680,10 @@
         </is>
       </c>
       <c r="D71" s="7" t="n">
-        <v>493</v>
+        <v>429.97</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>383.99</v>
+        <v>379.99</v>
       </c>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
@@ -5707,7 +5701,7 @@
         </is>
       </c>
       <c r="K71" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L71" s="16">
         <f>IF(OR($K71="",D71=""),"",IF(COUNTIFS($B:$B,$B71,$A:$A,$K71,D:D,"&gt;=0")=0,"",D71-SUMIFS(D:D,$B:$B,$B71,$A:$A,$K71)))</f>
@@ -5728,7 +5722,7 @@
     </row>
     <row r="72">
       <c r="A72" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
@@ -5744,12 +5738,10 @@
         <v>209.99</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>179.99</v>
+        <v>170</v>
       </c>
       <c r="F72" s="2" t="n"/>
-      <c r="G72" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G72" s="2" t="n"/>
       <c r="H72" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A72,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A72,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5764,7 +5756,7 @@
         </is>
       </c>
       <c r="K72" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L72" s="16">
         <f>IF(OR($K72="",D72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,D:D,"&gt;=0")=0,"",D72-SUMIFS(D:D,$B:$B,$B72,$A:$A,$K72)))</f>
@@ -5785,7 +5777,7 @@
     </row>
     <row r="73">
       <c r="A73" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
@@ -5804,9 +5796,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F73" s="2" t="n"/>
-      <c r="G73" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G73" s="2" t="n"/>
       <c r="H73" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5821,7 +5811,7 @@
         </is>
       </c>
       <c r="K73" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L73" s="16">
         <f>IF(OR($K73="",D73=""),"",IF(COUNTIFS($B:$B,$B73,$A:$A,$K73,D:D,"&gt;=0")=0,"",D73-SUMIFS(D:D,$B:$B,$B73,$A:$A,$K73)))</f>
@@ -5842,7 +5832,7 @@
     </row>
     <row r="74">
       <c r="A74" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
@@ -5861,9 +5851,7 @@
         <v>454.99</v>
       </c>
       <c r="F74" s="2" t="n"/>
-      <c r="G74" s="8" t="n">
-        <v>6140</v>
-      </c>
+      <c r="G74" s="2" t="n"/>
       <c r="H74" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A74,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A74,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5878,7 +5866,7 @@
         </is>
       </c>
       <c r="K74" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L74" s="16">
         <f>IF(OR($K74="",D74=""),"",IF(COUNTIFS($B:$B,$B74,$A:$A,$K74,D:D,"&gt;=0")=0,"",D74-SUMIFS(D:D,$B:$B,$B74,$A:$A,$K74)))</f>
@@ -5899,7 +5887,7 @@
     </row>
     <row r="75">
       <c r="A75" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
@@ -5917,9 +5905,11 @@
       <c r="E75" s="7" t="n">
         <v>283.99</v>
       </c>
-      <c r="F75" s="2" t="n"/>
+      <c r="F75" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="G75" s="8" t="n">
-        <v>4760</v>
+        <v>5350</v>
       </c>
       <c r="H75" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))),"")</f>
@@ -5935,7 +5925,7 @@
         </is>
       </c>
       <c r="K75" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L75" s="16">
         <f>IF(OR($K75="",D75=""),"",IF(COUNTIFS($B:$B,$B75,$A:$A,$K75,D:D,"&gt;=0")=0,"",D75-SUMIFS(D:D,$B:$B,$B75,$A:$A,$K75)))</f>
@@ -5956,7 +5946,7 @@
     </row>
     <row r="76">
       <c r="A76" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
@@ -5970,7 +5960,7 @@
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
@@ -5987,7 +5977,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K76" s="5" t="n"/>
+      <c r="K76" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L76" s="16">
         <f>IF(OR($K76="",D76=""),"",IF(COUNTIFS($B:$B,$B76,$A:$A,$K76,D:D,"&gt;=0")=0,"",D76-SUMIFS(D:D,$B:$B,$B76,$A:$A,$K76)))</f>
         <v/>
@@ -6007,7 +5999,7 @@
     </row>
     <row r="77">
       <c r="A77" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
@@ -6020,15 +6012,13 @@
         </is>
       </c>
       <c r="D77" s="7" t="n">
-        <v>144.25</v>
+        <v>143.24</v>
       </c>
       <c r="E77" s="7" t="n">
         <v>122.99</v>
       </c>
       <c r="F77" s="2" t="n"/>
-      <c r="G77" s="8" t="n">
-        <v>2860</v>
-      </c>
+      <c r="G77" s="2" t="n"/>
       <c r="H77" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6043,7 +6033,7 @@
         </is>
       </c>
       <c r="K77" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L77" s="16">
         <f>IF(OR($K77="",D77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,D:D,"&gt;=0")=0,"",D77-SUMIFS(D:D,$B:$B,$B77,$A:$A,$K77)))</f>
@@ -6064,7 +6054,7 @@
     </row>
     <row r="78">
       <c r="A78" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
@@ -6097,7 +6087,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K78" s="5" t="n"/>
+      <c r="K78" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L78" s="16">
         <f>IF(OR($K78="",D78=""),"",IF(COUNTIFS($B:$B,$B78,$A:$A,$K78,D:D,"&gt;=0")=0,"",D78-SUMIFS(D:D,$B:$B,$B78,$A:$A,$K78)))</f>
         <v/>
@@ -6117,7 +6109,7 @@
     </row>
     <row r="79">
       <c r="A79" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
@@ -6130,15 +6122,13 @@
         </is>
       </c>
       <c r="D79" s="7" t="n">
-        <v>75</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>59.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F79" s="2" t="n"/>
-      <c r="G79" s="8" t="n">
-        <v>2150</v>
-      </c>
+      <c r="G79" s="2" t="n"/>
       <c r="H79" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A79,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A79,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6153,7 +6143,7 @@
         </is>
       </c>
       <c r="K79" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L79" s="16">
         <f>IF(OR($K79="",D79=""),"",IF(COUNTIFS($B:$B,$B79,$A:$A,$K79,D:D,"&gt;=0")=0,"",D79-SUMIFS(D:D,$B:$B,$B79,$A:$A,$K79)))</f>
@@ -6174,7 +6164,7 @@
     </row>
     <row r="80">
       <c r="A80" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
@@ -6190,11 +6180,11 @@
         <v>164.49</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="F80" s="2" t="n"/>
       <c r="G80" s="8" t="n">
-        <v>2520</v>
+        <v>2460</v>
       </c>
       <c r="H80" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))),"")</f>
@@ -6210,7 +6200,7 @@
         </is>
       </c>
       <c r="K80" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L80" s="16">
         <f>IF(OR($K80="",D80=""),"",IF(COUNTIFS($B:$B,$B80,$A:$A,$K80,D:D,"&gt;=0")=0,"",D80-SUMIFS(D:D,$B:$B,$B80,$A:$A,$K80)))</f>
@@ -6231,7 +6221,7 @@
     </row>
     <row r="81">
       <c r="A81" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
@@ -6243,9 +6233,7 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D81" s="7" t="n">
-        <v>259.78</v>
-      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" s="7" t="n">
         <v>149.99</v>
       </c>
@@ -6265,7 +6253,7 @@
         </is>
       </c>
       <c r="K81" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L81" s="16">
         <f>IF(OR($K81="",D81=""),"",IF(COUNTIFS($B:$B,$B81,$A:$A,$K81,D:D,"&gt;=0")=0,"",D81-SUMIFS(D:D,$B:$B,$B81,$A:$A,$K81)))</f>
@@ -6286,7 +6274,7 @@
     </row>
     <row r="82">
       <c r="A82" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
@@ -6302,12 +6290,10 @@
         <v>150</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="F82" s="2" t="n"/>
-      <c r="G82" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G82" s="2" t="n"/>
       <c r="H82" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A82,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A82,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6321,7 +6307,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K82" s="5" t="n"/>
+      <c r="K82" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L82" s="16">
         <f>IF(OR($K82="",D82=""),"",IF(COUNTIFS($B:$B,$B82,$A:$A,$K82,D:D,"&gt;=0")=0,"",D82-SUMIFS(D:D,$B:$B,$B82,$A:$A,$K82)))</f>
         <v/>
@@ -6341,7 +6329,7 @@
     </row>
     <row r="83">
       <c r="A83" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
@@ -6354,15 +6342,13 @@
         </is>
       </c>
       <c r="D83" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E83" s="7" t="n">
         <v>209.99</v>
       </c>
       <c r="F83" s="2" t="n"/>
-      <c r="G83" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G83" s="2" t="n"/>
       <c r="H83" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A83,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A83,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6377,7 +6363,7 @@
         </is>
       </c>
       <c r="K83" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L83" s="16">
         <f>IF(OR($K83="",D83=""),"",IF(COUNTIFS($B:$B,$B83,$A:$A,$K83,D:D,"&gt;=0")=0,"",D83-SUMIFS(D:D,$B:$B,$B83,$A:$A,$K83)))</f>
@@ -6398,7 +6384,7 @@
     </row>
     <row r="84">
       <c r="A84" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
@@ -6432,7 +6418,7 @@
         </is>
       </c>
       <c r="K84" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L84" s="16">
         <f>IF(OR($K84="",D84=""),"",IF(COUNTIFS($B:$B,$B84,$A:$A,$K84,D:D,"&gt;=0")=0,"",D84-SUMIFS(D:D,$B:$B,$B84,$A:$A,$K84)))</f>
@@ -6453,7 +6439,7 @@
     </row>
     <row r="85">
       <c r="A85" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
@@ -6469,11 +6455,9 @@
         <v>493</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F85" s="8" t="n">
-        <v>4500</v>
-      </c>
+        <v>383.99</v>
+      </c>
+      <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
       <c r="H85" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A85,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A85,Dólar!$A:$A,0))),"")</f>
@@ -6488,7 +6472,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K85" s="5" t="n"/>
+      <c r="K85" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L85" s="16">
         <f>IF(OR($K85="",D85=""),"",IF(COUNTIFS($B:$B,$B85,$A:$A,$K85,D:D,"&gt;=0")=0,"",D85-SUMIFS(D:D,$B:$B,$B85,$A:$A,$K85)))</f>
         <v/>
@@ -6508,7 +6494,7 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
@@ -6520,10 +6506,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
+      <c r="D86" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>179.99</v>
+      </c>
       <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
+      <c r="G86" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H86" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A86,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A86,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6532,8 +6524,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A86,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J86" s="2" t="n"/>
-      <c r="K86" s="5" t="n"/>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K86" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L86" s="16">
         <f>IF(OR($K86="",D86=""),"",IF(COUNTIFS($B:$B,$B86,$A:$A,$K86,D:D,"&gt;=0")=0,"",D86-SUMIFS(D:D,$B:$B,$B86,$A:$A,$K86)))</f>
         <v/>
@@ -6553,7 +6551,7 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
@@ -6565,12 +6563,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D87" s="2" t="n"/>
-      <c r="E87" s="2" t="n"/>
-      <c r="F87" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G87" s="2" t="n"/>
+      <c r="D87" s="7" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H87" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A87,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A87,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6584,7 +6586,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K87" s="5" t="n"/>
+      <c r="K87" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L87" s="16">
         <f>IF(OR($K87="",D87=""),"",IF(COUNTIFS($B:$B,$B87,$A:$A,$K87,D:D,"&gt;=0")=0,"",D87-SUMIFS(D:D,$B:$B,$B87,$A:$A,$K87)))</f>
         <v/>
@@ -6604,7 +6608,7 @@
     </row>
     <row r="88">
       <c r="A88" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
@@ -6616,11 +6620,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
+      <c r="D88" s="7" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>454.99</v>
+      </c>
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="8" t="n">
-        <v>5580</v>
+        <v>6140</v>
       </c>
       <c r="H88" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A88,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A88,Dólar!$A:$A,0))),"")</f>
@@ -6635,7 +6643,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K88" s="5" t="n"/>
+      <c r="K88" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L88" s="16">
         <f>IF(OR($K88="",D88=""),"",IF(COUNTIFS($B:$B,$B88,$A:$A,$K88,D:D,"&gt;=0")=0,"",D88-SUMIFS(D:D,$B:$B,$B88,$A:$A,$K88)))</f>
         <v/>
@@ -6655,7 +6665,7 @@
     </row>
     <row r="89">
       <c r="A89" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
@@ -6667,12 +6677,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D89" s="2" t="n"/>
-      <c r="E89" s="2" t="n"/>
-      <c r="F89" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G89" s="2" t="n"/>
+      <c r="D89" s="7" t="n">
+        <v>329</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="H89" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A89,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A89,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6686,7 +6700,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K89" s="5" t="n"/>
+      <c r="K89" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L89" s="16">
         <f>IF(OR($K89="",D89=""),"",IF(COUNTIFS($B:$B,$B89,$A:$A,$K89,D:D,"&gt;=0")=0,"",D89-SUMIFS(D:D,$B:$B,$B89,$A:$A,$K89)))</f>
         <v/>
@@ -6706,11 +6722,11 @@
     </row>
     <row r="90">
       <c r="A90" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -6719,7 +6735,9 @@
         </is>
       </c>
       <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
+      <c r="E90" s="7" t="n">
+        <v>305</v>
+      </c>
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="9">
@@ -6730,7 +6748,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A90,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J90" s="2" t="n"/>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K90" s="5" t="n"/>
       <c r="L90" s="16">
         <f>IF(OR($K90="",D90=""),"",IF(COUNTIFS($B:$B,$B90,$A:$A,$K90,D:D,"&gt;=0")=0,"",D90-SUMIFS(D:D,$B:$B,$B90,$A:$A,$K90)))</f>
@@ -6751,24 +6773,28 @@
     </row>
     <row r="91">
       <c r="A91" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="n"/>
-      <c r="E91" s="2" t="n"/>
-      <c r="F91" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="G91" s="2" t="n"/>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="F91" s="2" t="n"/>
+      <c r="G91" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H91" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A91,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A91,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6782,7 +6808,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K91" s="5" t="n"/>
+      <c r="K91" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L91" s="16">
         <f>IF(OR($K91="",D91=""),"",IF(COUNTIFS($B:$B,$B91,$A:$A,$K91,D:D,"&gt;=0")=0,"",D91-SUMIFS(D:D,$B:$B,$B91,$A:$A,$K91)))</f>
         <v/>
@@ -6802,11 +6830,11 @@
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -6814,8 +6842,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
+      <c r="D92" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="9">
@@ -6826,7 +6858,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A92,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J92" s="2" t="n"/>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="16">
         <f>IF(OR($K92="",D92=""),"",IF(COUNTIFS($B:$B,$B92,$A:$A,$K92,D:D,"&gt;=0")=0,"",D92-SUMIFS(D:D,$B:$B,$B92,$A:$A,$K92)))</f>
@@ -6847,23 +6883,27 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="n"/>
-      <c r="E93" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <v>59.99</v>
+      </c>
       <c r="F93" s="2" t="n"/>
       <c r="G93" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="H93" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A93,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A93,Dólar!$A:$A,0))),"")</f>
@@ -6878,7 +6918,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K93" s="5" t="n"/>
+      <c r="K93" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L93" s="16">
         <f>IF(OR($K93="",D93=""),"",IF(COUNTIFS($B:$B,$B93,$A:$A,$K93,D:D,"&gt;=0")=0,"",D93-SUMIFS(D:D,$B:$B,$B93,$A:$A,$K93)))</f>
         <v/>
@@ -6898,11 +6940,11 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -6910,11 +6952,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
+      <c r="D94" s="7" t="n">
+        <v>164.49</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <v>136.99</v>
+      </c>
       <c r="F94" s="2" t="n"/>
       <c r="G94" s="8" t="n">
-        <v>3950</v>
+        <v>2520</v>
       </c>
       <c r="H94" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A94,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A94,Dólar!$A:$A,0))),"")</f>
@@ -6929,7 +6975,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K94" s="5" t="n"/>
+      <c r="K94" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L94" s="16">
         <f>IF(OR($K94="",D94=""),"",IF(COUNTIFS($B:$B,$B94,$A:$A,$K94,D:D,"&gt;=0")=0,"",D94-SUMIFS(D:D,$B:$B,$B94,$A:$A,$K94)))</f>
         <v/>
@@ -6949,23 +6997,25 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="n"/>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="8" t="n">
-        <v>6200</v>
-      </c>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="n"/>
       <c r="H95" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A95,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A95,Dólar!$A:$A,0))),"")</f>
@@ -6980,7 +7030,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K95" s="5" t="n"/>
+      <c r="K95" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L95" s="16">
         <f>IF(OR($K95="",D95=""),"",IF(COUNTIFS($B:$B,$B95,$A:$A,$K95,D:D,"&gt;=0")=0,"",D95-SUMIFS(D:D,$B:$B,$B95,$A:$A,$K95)))</f>
         <v/>
@@ -6998,8 +7050,722 @@
         <v/>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="8" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H96" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A96,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A96,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I96" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A96,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="16">
+        <f>IF(OR($K96="",D96=""),"",IF(COUNTIFS($B:$B,$B96,$A:$A,$K96,D:D,"&gt;=0")=0,"",D96-SUMIFS(D:D,$B:$B,$B96,$A:$A,$K96)))</f>
+        <v/>
+      </c>
+      <c r="M96" s="16">
+        <f>IF(OR($K96="",E96=""),"",IF(COUNTIFS($B:$B,$B96,$A:$A,$K96,E:E,"&gt;=0")=0,"",E96-SUMIFS(E:E,$B:$B,$B96,$A:$A,$K96)))</f>
+        <v/>
+      </c>
+      <c r="N96" s="16">
+        <f>IF(OR($K96="",F96=""),"",IF(COUNTIFS($B:$B,$B96,$A:$A,$K96,F:F,"&gt;=0")=0,"",F96-SUMIFS(F:F,$B:$B,$B96,$A:$A,$K96)))</f>
+        <v/>
+      </c>
+      <c r="O96" s="16">
+        <f>IF(OR($K96="",G96=""),"",IF(COUNTIFS($B:$B,$B96,$A:$A,$K96,G:G,"&gt;=0")=0,"",G96-SUMIFS(G:G,$B:$B,$B96,$A:$A,$K96)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H97" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A97,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A97,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I97" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A97,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K97" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L97" s="16">
+        <f>IF(OR($K97="",D97=""),"",IF(COUNTIFS($B:$B,$B97,$A:$A,$K97,D:D,"&gt;=0")=0,"",D97-SUMIFS(D:D,$B:$B,$B97,$A:$A,$K97)))</f>
+        <v/>
+      </c>
+      <c r="M97" s="16">
+        <f>IF(OR($K97="",E97=""),"",IF(COUNTIFS($B:$B,$B97,$A:$A,$K97,E:E,"&gt;=0")=0,"",E97-SUMIFS(E:E,$B:$B,$B97,$A:$A,$K97)))</f>
+        <v/>
+      </c>
+      <c r="N97" s="16">
+        <f>IF(OR($K97="",F97=""),"",IF(COUNTIFS($B:$B,$B97,$A:$A,$K97,F:F,"&gt;=0")=0,"",F97-SUMIFS(F:F,$B:$B,$B97,$A:$A,$K97)))</f>
+        <v/>
+      </c>
+      <c r="O97" s="16">
+        <f>IF(OR($K97="",G97=""),"",IF(COUNTIFS($B:$B,$B97,$A:$A,$K97,G:G,"&gt;=0")=0,"",G97-SUMIFS(G:G,$B:$B,$B97,$A:$A,$K97)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A98,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A98,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I98" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A98,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L98" s="16">
+        <f>IF(OR($K98="",D98=""),"",IF(COUNTIFS($B:$B,$B98,$A:$A,$K98,D:D,"&gt;=0")=0,"",D98-SUMIFS(D:D,$B:$B,$B98,$A:$A,$K98)))</f>
+        <v/>
+      </c>
+      <c r="M98" s="16">
+        <f>IF(OR($K98="",E98=""),"",IF(COUNTIFS($B:$B,$B98,$A:$A,$K98,E:E,"&gt;=0")=0,"",E98-SUMIFS(E:E,$B:$B,$B98,$A:$A,$K98)))</f>
+        <v/>
+      </c>
+      <c r="N98" s="16">
+        <f>IF(OR($K98="",F98=""),"",IF(COUNTIFS($B:$B,$B98,$A:$A,$K98,F:F,"&gt;=0")=0,"",F98-SUMIFS(F:F,$B:$B,$B98,$A:$A,$K98)))</f>
+        <v/>
+      </c>
+      <c r="O98" s="16">
+        <f>IF(OR($K98="",G98=""),"",IF(COUNTIFS($B:$B,$B98,$A:$A,$K98,G:G,"&gt;=0")=0,"",G98-SUMIFS(G:G,$B:$B,$B98,$A:$A,$K98)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="F99" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G99" s="2" t="n"/>
+      <c r="H99" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A99,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A99,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I99" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A99,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n"/>
+      <c r="L99" s="16">
+        <f>IF(OR($K99="",D99=""),"",IF(COUNTIFS($B:$B,$B99,$A:$A,$K99,D:D,"&gt;=0")=0,"",D99-SUMIFS(D:D,$B:$B,$B99,$A:$A,$K99)))</f>
+        <v/>
+      </c>
+      <c r="M99" s="16">
+        <f>IF(OR($K99="",E99=""),"",IF(COUNTIFS($B:$B,$B99,$A:$A,$K99,E:E,"&gt;=0")=0,"",E99-SUMIFS(E:E,$B:$B,$B99,$A:$A,$K99)))</f>
+        <v/>
+      </c>
+      <c r="N99" s="16">
+        <f>IF(OR($K99="",F99=""),"",IF(COUNTIFS($B:$B,$B99,$A:$A,$K99,F:F,"&gt;=0")=0,"",F99-SUMIFS(F:F,$B:$B,$B99,$A:$A,$K99)))</f>
+        <v/>
+      </c>
+      <c r="O99" s="16">
+        <f>IF(OR($K99="",G99=""),"",IF(COUNTIFS($B:$B,$B99,$A:$A,$K99,G:G,"&gt;=0")=0,"",G99-SUMIFS(G:G,$B:$B,$B99,$A:$A,$K99)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A100,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A100,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I100" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A100,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J100" s="2" t="n"/>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="16">
+        <f>IF(OR($K100="",D100=""),"",IF(COUNTIFS($B:$B,$B100,$A:$A,$K100,D:D,"&gt;=0")=0,"",D100-SUMIFS(D:D,$B:$B,$B100,$A:$A,$K100)))</f>
+        <v/>
+      </c>
+      <c r="M100" s="16">
+        <f>IF(OR($K100="",E100=""),"",IF(COUNTIFS($B:$B,$B100,$A:$A,$K100,E:E,"&gt;=0")=0,"",E100-SUMIFS(E:E,$B:$B,$B100,$A:$A,$K100)))</f>
+        <v/>
+      </c>
+      <c r="N100" s="16">
+        <f>IF(OR($K100="",F100=""),"",IF(COUNTIFS($B:$B,$B100,$A:$A,$K100,F:F,"&gt;=0")=0,"",F100-SUMIFS(F:F,$B:$B,$B100,$A:$A,$K100)))</f>
+        <v/>
+      </c>
+      <c r="O100" s="16">
+        <f>IF(OR($K100="",G100=""),"",IF(COUNTIFS($B:$B,$B100,$A:$A,$K100,G:G,"&gt;=0")=0,"",G100-SUMIFS(G:G,$B:$B,$B100,$A:$A,$K100)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G101" s="2" t="n"/>
+      <c r="H101" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A101,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A101,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I101" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A101,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="16">
+        <f>IF(OR($K101="",D101=""),"",IF(COUNTIFS($B:$B,$B101,$A:$A,$K101,D:D,"&gt;=0")=0,"",D101-SUMIFS(D:D,$B:$B,$B101,$A:$A,$K101)))</f>
+        <v/>
+      </c>
+      <c r="M101" s="16">
+        <f>IF(OR($K101="",E101=""),"",IF(COUNTIFS($B:$B,$B101,$A:$A,$K101,E:E,"&gt;=0")=0,"",E101-SUMIFS(E:E,$B:$B,$B101,$A:$A,$K101)))</f>
+        <v/>
+      </c>
+      <c r="N101" s="16">
+        <f>IF(OR($K101="",F101=""),"",IF(COUNTIFS($B:$B,$B101,$A:$A,$K101,F:F,"&gt;=0")=0,"",F101-SUMIFS(F:F,$B:$B,$B101,$A:$A,$K101)))</f>
+        <v/>
+      </c>
+      <c r="O101" s="16">
+        <f>IF(OR($K101="",G101=""),"",IF(COUNTIFS($B:$B,$B101,$A:$A,$K101,G:G,"&gt;=0")=0,"",G101-SUMIFS(G:G,$B:$B,$B101,$A:$A,$K101)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="H102" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A102,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A102,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I102" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A102,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="16">
+        <f>IF(OR($K102="",D102=""),"",IF(COUNTIFS($B:$B,$B102,$A:$A,$K102,D:D,"&gt;=0")=0,"",D102-SUMIFS(D:D,$B:$B,$B102,$A:$A,$K102)))</f>
+        <v/>
+      </c>
+      <c r="M102" s="16">
+        <f>IF(OR($K102="",E102=""),"",IF(COUNTIFS($B:$B,$B102,$A:$A,$K102,E:E,"&gt;=0")=0,"",E102-SUMIFS(E:E,$B:$B,$B102,$A:$A,$K102)))</f>
+        <v/>
+      </c>
+      <c r="N102" s="16">
+        <f>IF(OR($K102="",F102=""),"",IF(COUNTIFS($B:$B,$B102,$A:$A,$K102,F:F,"&gt;=0")=0,"",F102-SUMIFS(F:F,$B:$B,$B102,$A:$A,$K102)))</f>
+        <v/>
+      </c>
+      <c r="O102" s="16">
+        <f>IF(OR($K102="",G102=""),"",IF(COUNTIFS($B:$B,$B102,$A:$A,$K102,G:G,"&gt;=0")=0,"",G102-SUMIFS(G:G,$B:$B,$B102,$A:$A,$K102)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A103,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A103,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I103" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A103,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n"/>
+      <c r="L103" s="16">
+        <f>IF(OR($K103="",D103=""),"",IF(COUNTIFS($B:$B,$B103,$A:$A,$K103,D:D,"&gt;=0")=0,"",D103-SUMIFS(D:D,$B:$B,$B103,$A:$A,$K103)))</f>
+        <v/>
+      </c>
+      <c r="M103" s="16">
+        <f>IF(OR($K103="",E103=""),"",IF(COUNTIFS($B:$B,$B103,$A:$A,$K103,E:E,"&gt;=0")=0,"",E103-SUMIFS(E:E,$B:$B,$B103,$A:$A,$K103)))</f>
+        <v/>
+      </c>
+      <c r="N103" s="16">
+        <f>IF(OR($K103="",F103=""),"",IF(COUNTIFS($B:$B,$B103,$A:$A,$K103,F:F,"&gt;=0")=0,"",F103-SUMIFS(F:F,$B:$B,$B103,$A:$A,$K103)))</f>
+        <v/>
+      </c>
+      <c r="O103" s="16">
+        <f>IF(OR($K103="",G103=""),"",IF(COUNTIFS($B:$B,$B103,$A:$A,$K103,G:G,"&gt;=0")=0,"",G103-SUMIFS(G:G,$B:$B,$B103,$A:$A,$K103)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A104,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A104,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I104" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A104,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J104" s="2" t="n"/>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="16">
+        <f>IF(OR($K104="",D104=""),"",IF(COUNTIFS($B:$B,$B104,$A:$A,$K104,D:D,"&gt;=0")=0,"",D104-SUMIFS(D:D,$B:$B,$B104,$A:$A,$K104)))</f>
+        <v/>
+      </c>
+      <c r="M104" s="16">
+        <f>IF(OR($K104="",E104=""),"",IF(COUNTIFS($B:$B,$B104,$A:$A,$K104,E:E,"&gt;=0")=0,"",E104-SUMIFS(E:E,$B:$B,$B104,$A:$A,$K104)))</f>
+        <v/>
+      </c>
+      <c r="N104" s="16">
+        <f>IF(OR($K104="",F104=""),"",IF(COUNTIFS($B:$B,$B104,$A:$A,$K104,F:F,"&gt;=0")=0,"",F104-SUMIFS(F:F,$B:$B,$B104,$A:$A,$K104)))</f>
+        <v/>
+      </c>
+      <c r="O104" s="16">
+        <f>IF(OR($K104="",G104=""),"",IF(COUNTIFS($B:$B,$B104,$A:$A,$K104,G:G,"&gt;=0")=0,"",G104-SUMIFS(G:G,$B:$B,$B104,$A:$A,$K104)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
+      <c r="F105" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G105" s="2" t="n"/>
+      <c r="H105" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A105,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A105,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I105" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A105,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="16">
+        <f>IF(OR($K105="",D105=""),"",IF(COUNTIFS($B:$B,$B105,$A:$A,$K105,D:D,"&gt;=0")=0,"",D105-SUMIFS(D:D,$B:$B,$B105,$A:$A,$K105)))</f>
+        <v/>
+      </c>
+      <c r="M105" s="16">
+        <f>IF(OR($K105="",E105=""),"",IF(COUNTIFS($B:$B,$B105,$A:$A,$K105,E:E,"&gt;=0")=0,"",E105-SUMIFS(E:E,$B:$B,$B105,$A:$A,$K105)))</f>
+        <v/>
+      </c>
+      <c r="N105" s="16">
+        <f>IF(OR($K105="",F105=""),"",IF(COUNTIFS($B:$B,$B105,$A:$A,$K105,F:F,"&gt;=0")=0,"",F105-SUMIFS(F:F,$B:$B,$B105,$A:$A,$K105)))</f>
+        <v/>
+      </c>
+      <c r="O105" s="16">
+        <f>IF(OR($K105="",G105=""),"",IF(COUNTIFS($B:$B,$B105,$A:$A,$K105,G:G,"&gt;=0")=0,"",G105-SUMIFS(G:G,$B:$B,$B105,$A:$A,$K105)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="C106" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A106,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A106,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I106" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A106,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="16">
+        <f>IF(OR($K106="",D106=""),"",IF(COUNTIFS($B:$B,$B106,$A:$A,$K106,D:D,"&gt;=0")=0,"",D106-SUMIFS(D:D,$B:$B,$B106,$A:$A,$K106)))</f>
+        <v/>
+      </c>
+      <c r="M106" s="16">
+        <f>IF(OR($K106="",E106=""),"",IF(COUNTIFS($B:$B,$B106,$A:$A,$K106,E:E,"&gt;=0")=0,"",E106-SUMIFS(E:E,$B:$B,$B106,$A:$A,$K106)))</f>
+        <v/>
+      </c>
+      <c r="N106" s="16">
+        <f>IF(OR($K106="",F106=""),"",IF(COUNTIFS($B:$B,$B106,$A:$A,$K106,F:F,"&gt;=0")=0,"",F106-SUMIFS(F:F,$B:$B,$B106,$A:$A,$K106)))</f>
+        <v/>
+      </c>
+      <c r="O106" s="16">
+        <f>IF(OR($K106="",G106=""),"",IF(COUNTIFS($B:$B,$B106,$A:$A,$K106,G:G,"&gt;=0")=0,"",G106-SUMIFS(G:G,$B:$B,$B106,$A:$A,$K106)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H107" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A107,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A107,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I107" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A107,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="16">
+        <f>IF(OR($K107="",D107=""),"",IF(COUNTIFS($B:$B,$B107,$A:$A,$K107,D:D,"&gt;=0")=0,"",D107-SUMIFS(D:D,$B:$B,$B107,$A:$A,$K107)))</f>
+        <v/>
+      </c>
+      <c r="M107" s="16">
+        <f>IF(OR($K107="",E107=""),"",IF(COUNTIFS($B:$B,$B107,$A:$A,$K107,E:E,"&gt;=0")=0,"",E107-SUMIFS(E:E,$B:$B,$B107,$A:$A,$K107)))</f>
+        <v/>
+      </c>
+      <c r="N107" s="16">
+        <f>IF(OR($K107="",F107=""),"",IF(COUNTIFS($B:$B,$B107,$A:$A,$K107,F:F,"&gt;=0")=0,"",F107-SUMIFS(F:F,$B:$B,$B107,$A:$A,$K107)))</f>
+        <v/>
+      </c>
+      <c r="O107" s="16">
+        <f>IF(OR($K107="",G107=""),"",IF(COUNTIFS($B:$B,$B107,$A:$A,$K107,G:G,"&gt;=0")=0,"",G107-SUMIFS(G:G,$B:$B,$B107,$A:$A,$K107)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n"/>
+      <c r="G108" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H108" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A108,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A108,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I108" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A108,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J108" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n"/>
+      <c r="L108" s="16">
+        <f>IF(OR($K108="",D108=""),"",IF(COUNTIFS($B:$B,$B108,$A:$A,$K108,D:D,"&gt;=0")=0,"",D108-SUMIFS(D:D,$B:$B,$B108,$A:$A,$K108)))</f>
+        <v/>
+      </c>
+      <c r="M108" s="16">
+        <f>IF(OR($K108="",E108=""),"",IF(COUNTIFS($B:$B,$B108,$A:$A,$K108,E:E,"&gt;=0")=0,"",E108-SUMIFS(E:E,$B:$B,$B108,$A:$A,$K108)))</f>
+        <v/>
+      </c>
+      <c r="N108" s="16">
+        <f>IF(OR($K108="",F108=""),"",IF(COUNTIFS($B:$B,$B108,$A:$A,$K108,F:F,"&gt;=0")=0,"",F108-SUMIFS(F:F,$B:$B,$B108,$A:$A,$K108)))</f>
+        <v/>
+      </c>
+      <c r="O108" s="16">
+        <f>IF(OR($K108="",G108=""),"",IF(COUNTIFS($B:$B,$B108,$A:$A,$K108,G:G,"&gt;=0")=0,"",G108-SUMIFS(G:G,$B:$B,$B108,$A:$A,$K108)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C109" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G109" s="2" t="n"/>
+      <c r="H109" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A109,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A109,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I109" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A109,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n"/>
+      <c r="L109" s="16">
+        <f>IF(OR($K109="",D109=""),"",IF(COUNTIFS($B:$B,$B109,$A:$A,$K109,D:D,"&gt;=0")=0,"",D109-SUMIFS(D:D,$B:$B,$B109,$A:$A,$K109)))</f>
+        <v/>
+      </c>
+      <c r="M109" s="16">
+        <f>IF(OR($K109="",E109=""),"",IF(COUNTIFS($B:$B,$B109,$A:$A,$K109,E:E,"&gt;=0")=0,"",E109-SUMIFS(E:E,$B:$B,$B109,$A:$A,$K109)))</f>
+        <v/>
+      </c>
+      <c r="N109" s="16">
+        <f>IF(OR($K109="",F109=""),"",IF(COUNTIFS($B:$B,$B109,$A:$A,$K109,F:F,"&gt;=0")=0,"",F109-SUMIFS(F:F,$B:$B,$B109,$A:$A,$K109)))</f>
+        <v/>
+      </c>
+      <c r="O109" s="16">
+        <f>IF(OR($K109="",G109=""),"",IF(COUNTIFS($B:$B,$B109,$A:$A,$K109,G:G,"&gt;=0")=0,"",G109-SUMIFS(G:G,$B:$B,$B109,$A:$A,$K109)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M95">
+  <conditionalFormatting sqref="L2:M109">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -7007,7 +7773,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O95">
+  <conditionalFormatting sqref="N2:O109">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -7100,17 +7866,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId92"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId106"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7275,7 +8055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7526,6 +8306,32 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(COUNT(C10:D10)=2,AVERAGE(C10:D10),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>BCB oficial 11.69; paralelo dolarbolivia.net 18/10 (compra 11.85 / venta 11.81; la página es inconsistente entre compra y venta); usado = promedio del paralelo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7537,7 +8343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H265"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14548,34 +15354,34 @@
     </row>
     <row r="185">
       <c r="A185" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
-        <v>5580</v>
+        <v>138.9</v>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G185" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; (New) AMD Ryzen 5 5600 Vermeer Zen3 6-Core 12-Thread AM4 CPU</t>
         </is>
       </c>
       <c r="H185" s="6" t="inlineStr">
@@ -14586,34 +15392,34 @@
     </row>
     <row r="186">
       <c r="A186" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E186" s="11" t="n">
-        <v>2300</v>
+        <v>213.95</v>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor bra_dewaa 99.8%; AMD Ryzen 5 7600 6-Core 12-Thread Unlocked Desktop Processor</t>
         </is>
       </c>
       <c r="H186" s="6" t="inlineStr">
@@ -14624,34 +15430,34 @@
     </row>
     <row r="187">
       <c r="A187" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
-        <v>3950</v>
+        <v>324.99</v>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G187" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor geoelectronics7 99.4%; AMD Ryzen 7 7800X3D 100-00000910 - Processor No Cooler</t>
         </is>
       </c>
       <c r="H187" s="6" t="inlineStr">
@@ -14662,34 +15468,34 @@
     </row>
     <row r="188">
       <c r="A188" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E188" s="11" t="n">
-        <v>4800</v>
+        <v>549.99</v>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay API; vendedor newegg 99.6%; AMD Ryzen 9 9950X - Ryzen 9 9000 Series Granite Ridge (Zen 5</t>
         </is>
       </c>
       <c r="H188" s="6" t="inlineStr">
@@ -14700,34 +15506,34 @@
     </row>
     <row r="189">
       <c r="A189" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
-        <v>5190</v>
+        <v>150</v>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G189" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor algonz1137 100.0%; INTEL CPU Core i5-12400F / 6/12 / 2.5GHz / 6xxChipset / BX80; envío no indicado</t>
         </is>
       </c>
       <c r="H189" s="6" t="inlineStr">
@@ -14738,34 +15544,34 @@
     </row>
     <row r="190">
       <c r="A190" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E190" s="11" t="n">
-        <v>5390</v>
+        <v>164.49</v>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t xml:space="preserve">eBay API; vendedor newegg 99.6%; Intel Core i5-14400F - Core i5 14th Gen Raptor Lake 10-Core </t>
         </is>
       </c>
       <c r="H190" s="6" t="inlineStr">
@@ -14776,34 +15582,34 @@
     </row>
     <row r="191">
       <c r="A191" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E191" s="11" t="n">
-        <v>2000</v>
+        <v>235.27</v>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G191" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor jos-980836 100.0%; Intel Core ULTRA 7 265K LGA 1851 Unlocked, 20 cores.</t>
         </is>
       </c>
       <c r="H191" s="6" t="inlineStr">
@@ -14814,34 +15620,34 @@
     </row>
     <row r="192">
       <c r="A192" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E192" s="11" t="n">
-        <v>2650</v>
+        <v>429.97</v>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor uventure 99.7%; NEW 32GB (2x16GB) Corsair Vengeance DDR5 PC5-5600 Desktop RA</t>
         </is>
       </c>
       <c r="H192" s="6" t="inlineStr">
@@ -14852,34 +15658,34 @@
     </row>
     <row r="193">
       <c r="A193" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
-        <v>2700</v>
+        <v>450</v>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G193" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>eBay API; vendedor kn32451 99.9%; CORSAIR Vengeance RGB 32GB (2x16GB) DDR5 6000MHz CL36 AMD EX</t>
         </is>
       </c>
       <c r="H193" s="6" t="inlineStr">
@@ -14890,34 +15696,34 @@
     </row>
     <row r="194">
       <c r="A194" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E194" s="11" t="n">
-        <v>6200</v>
+        <v>118.96</v>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G194" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t xml:space="preserve">eBay API; vendedor bike_fix 99.0%; T-Force Vulcan Z DDR4 RAM 16GB (2x8GB) 3200MHz CL16 Desktop </t>
         </is>
       </c>
       <c r="H194" s="6" t="inlineStr">
@@ -14928,34 +15734,34 @@
     </row>
     <row r="195">
       <c r="A195" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
-        <v>540</v>
+        <v>93.5</v>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G195" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>eBay API; vendedor danche1978 99.4%; MP33 1TB SLC Cache 3D NAND TLC Nvme 1.3 Pcie Gen3X4 M.2 2280</t>
         </is>
       </c>
       <c r="H195" s="6" t="inlineStr">
@@ -14966,34 +15772,34 @@
     </row>
     <row r="196">
       <c r="A196" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E196" s="11" t="n">
-        <v>900</v>
+        <v>209.99</v>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G196" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>eBay API; vendedor ram_technologies 100.0%; RAM Tech 2TB NVMe SSD Gen4 M.2 2280 | 5000MB/s Read 4500MB/s</t>
         </is>
       </c>
       <c r="H196" s="6" t="inlineStr">
@@ -15004,34 +15810,34 @@
     </row>
     <row r="197">
       <c r="A197" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
-        <v>1500</v>
+        <v>129.99</v>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G197" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>eBay API; vendedor paymore_sugar_land 99.4%; AMD Ryzen 5 5600 3.50GHz 6 Core 100-000000927 12 Thread AM4</t>
         </is>
       </c>
       <c r="H197" s="6" t="inlineStr">
@@ -15042,34 +15848,34 @@
     </row>
     <row r="198">
       <c r="A198" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E198" s="11" t="n">
-        <v>1500</v>
+        <v>315</v>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G198" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>eBay API; vendedor senshi-gamer 100.0%; AMD Ryzen 7 5700X3D Desktop CPU Processor 3.0GHz, 8-Core, 16; envío no indicado</t>
         </is>
       </c>
       <c r="H198" s="6" t="inlineStr">
@@ -15080,34 +15886,34 @@
     </row>
     <row r="199">
       <c r="A199" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E199" s="11" t="n">
-        <v>1850</v>
+        <v>120</v>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G199" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>eBay API; vendedor shenidss9ckq 99.1%; AMD Ryzen 5 7600 3.80GHz 6 Core 100-000001015 12 Thread AM5</t>
         </is>
       </c>
       <c r="H199" s="6" t="inlineStr">
@@ -15118,34 +15924,34 @@
     </row>
     <row r="200">
       <c r="A200" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E200" s="11" t="n">
-        <v>2000</v>
+        <v>289.99</v>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>eBay API; vendedor paymore_gurnee 99.7%; AMD Ryzen 7 7800X3D 4.20GHz 8 Core 100-000000910 16 Thread A</t>
         </is>
       </c>
       <c r="H200" s="6" t="inlineStr">
@@ -15156,34 +15962,34 @@
     </row>
     <row r="201">
       <c r="A201" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
-        <v>1800</v>
+        <v>454.99</v>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>eBay API; vendedor goodios_direct 99.6%; **  AMD Ryzen 9 9950X Processor - USED  **</t>
         </is>
       </c>
       <c r="H201" s="6" t="inlineStr">
@@ -15194,34 +16000,34 @@
     </row>
     <row r="202">
       <c r="A202" s="15" t="n">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E202" s="11" t="n">
-        <v>3550</v>
+        <v>124.99</v>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G202" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>eBay API; vendedor silencedpp7 100.0%; Intel Core i5-12400F 2.50GHz 6 Core SRL4W 12 Thread LGA 1700; envío no indicado</t>
         </is>
       </c>
       <c r="H202" s="6" t="inlineStr">
@@ -15232,34 +16038,34 @@
     </row>
     <row r="203">
       <c r="A203" s="15" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
-        <v>5664</v>
+        <v>125</v>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G203" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>eBay API; vendedor secure_processors 99.9%; Intel Core i5-13400 SRMBP</t>
         </is>
       </c>
       <c r="H203" s="6" t="inlineStr">
@@ -15270,11 +16076,11 @@
     </row>
     <row r="204">
       <c r="A204" s="15" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C204" s="5" t="inlineStr">
@@ -15284,20 +16090,20 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E204" s="11" t="n">
-        <v>2537</v>
+        <v>139.99</v>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G204" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>eBay API; vendedor paymore_bustleton 99.4%; Intel Core i5-14400F 2.50GHz 10 Core SRN3R 16 Thread LGA 170</t>
         </is>
       </c>
       <c r="H204" s="6" t="inlineStr">
@@ -15308,34 +16114,34 @@
     </row>
     <row r="205">
       <c r="A205" s="15" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
-        <v>3127</v>
+        <v>209.68</v>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G205" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t>eBay API; vendedor ericsites 100.0%; Intel Core Ultra 7 265K Desktop Processor, 20 Cores, 3.3 GHz</t>
         </is>
       </c>
       <c r="H205" s="6" t="inlineStr">
@@ -15346,34 +16152,34 @@
     </row>
     <row r="206">
       <c r="A206" s="15" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E206" s="11" t="n">
-        <v>2150</v>
+        <v>379.99</v>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G206" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t>eBay API; vendedor nn-red 100.0%; Corsair Vengeance RGB Pro 32GB (2x16GB) RAM DDR5 5600MHz CMH; envío no indicado</t>
         </is>
       </c>
       <c r="H206" s="6" t="inlineStr">
@@ -15384,34 +16190,34 @@
     </row>
     <row r="207">
       <c r="A207" s="15" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
-        <v>6140</v>
+        <v>419.99</v>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G207" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t>eBay API; vendedor wazno 99.7%; Corsair Vengeance RGB 32GB 2x16GB DDR5 RAM 6000MHz CMH32GX5M</t>
         </is>
       </c>
       <c r="H207" s="6" t="inlineStr">
@@ -15422,34 +16228,34 @@
     </row>
     <row r="208">
       <c r="A208" s="15" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E208" s="11" t="n">
-        <v>4760</v>
+        <v>72.95</v>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G208" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>eBay API; vendedor lmunaco91 98.5%; G.SKILL RipJaws V DDR4-3200 16GB (2x8GB) DIMM Desktop RAM; envío no indicado</t>
         </is>
       </c>
       <c r="H208" s="6" t="inlineStr">
@@ -15460,34 +16266,34 @@
     </row>
     <row r="209">
       <c r="A209" s="15" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
-        <v>6800</v>
+        <v>96.94</v>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G209" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor sellyourgadgetssodo 99.5%; KingSpec NE-1TB 2280 M.2 NVMe Solid State Drive Used With Bo</t>
         </is>
       </c>
       <c r="H209" s="6" t="inlineStr">
@@ -15498,34 +16304,34 @@
     </row>
     <row r="210">
       <c r="A210" s="15" t="n">
-        <v>46307</v>
+        <v>46313</v>
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E210" s="11" t="n">
-        <v>2100</v>
+        <v>160</v>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G210" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>eBay API; vendedor irefurbish-cincinnati 100.0%; KingSpec 2tb Nvme Ssd 4x4; envío no indicado</t>
         </is>
       </c>
       <c r="H210" s="6" t="inlineStr">
@@ -15536,7 +16342,7 @@
     </row>
     <row r="211">
       <c r="A211" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
@@ -15545,16 +16351,16 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
-        <v>1800</v>
+        <v>5580</v>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
@@ -15563,7 +16369,7 @@
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
@@ -15574,25 +16380,25 @@
     </row>
     <row r="212">
       <c r="A212" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E212" s="11" t="n">
-        <v>4500</v>
+        <v>2300</v>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
@@ -15601,7 +16407,7 @@
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H212" s="6" t="inlineStr">
@@ -15612,7 +16418,7 @@
     </row>
     <row r="213">
       <c r="A213" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
@@ -15621,16 +16427,16 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
-        <v>6700</v>
+        <v>3950</v>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
@@ -15639,7 +16445,7 @@
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H213" s="6" t="inlineStr">
@@ -15650,25 +16456,25 @@
     </row>
     <row r="214">
       <c r="A214" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E214" s="11" t="n">
-        <v>2520</v>
+        <v>4800</v>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
@@ -15677,7 +16483,7 @@
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H214" s="6" t="inlineStr">
@@ -15688,25 +16494,25 @@
     </row>
     <row r="215">
       <c r="A215" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
-        <v>4290</v>
+        <v>5190</v>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
@@ -15715,7 +16521,7 @@
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H215" s="6" t="inlineStr">
@@ -15726,25 +16532,25 @@
     </row>
     <row r="216">
       <c r="A216" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E216" s="11" t="n">
-        <v>2860</v>
+        <v>5390</v>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
@@ -15753,7 +16559,7 @@
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr">
@@ -15764,25 +16570,25 @@
     </row>
     <row r="217">
       <c r="A217" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
-        <v>2460</v>
+        <v>2000</v>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
@@ -15791,7 +16597,7 @@
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
@@ -15802,25 +16608,25 @@
     </row>
     <row r="218">
       <c r="A218" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E218" s="11" t="n">
-        <v>5360</v>
+        <v>2650</v>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
@@ -15829,7 +16635,7 @@
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr">
@@ -15840,25 +16646,25 @@
     </row>
     <row r="219">
       <c r="A219" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E219" s="11" t="n">
-        <v>1710</v>
+        <v>2700</v>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
@@ -15867,7 +16673,7 @@
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H219" s="6" t="inlineStr">
@@ -15878,25 +16684,25 @@
     </row>
     <row r="220">
       <c r="A220" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E220" s="11" t="n">
-        <v>2310</v>
+        <v>6200</v>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
@@ -15905,7 +16711,7 @@
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
@@ -15916,11 +16722,11 @@
     </row>
     <row r="221">
       <c r="A221" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
@@ -15930,11 +16736,11 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
-        <v>2160</v>
+        <v>540</v>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
@@ -15943,7 +16749,7 @@
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
@@ -15954,25 +16760,25 @@
     </row>
     <row r="222">
       <c r="A222" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E222" s="11" t="n">
-        <v>5360</v>
+        <v>900</v>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
@@ -15981,7 +16787,7 @@
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
@@ -15992,25 +16798,25 @@
     </row>
     <row r="223">
       <c r="A223" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E223" s="11" t="n">
-        <v>5660</v>
+        <v>1500</v>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
@@ -16019,7 +16825,7 @@
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
@@ -16030,25 +16836,25 @@
     </row>
     <row r="224">
       <c r="A224" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E224" s="11" t="n">
-        <v>5860</v>
+        <v>1500</v>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
@@ -16057,7 +16863,7 @@
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H224" s="6" t="inlineStr">
@@ -16068,11 +16874,11 @@
     </row>
     <row r="225">
       <c r="A225" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
@@ -16082,11 +16888,11 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E225" s="11" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
@@ -16095,7 +16901,7 @@
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr">
@@ -16106,11 +16912,11 @@
     </row>
     <row r="226">
       <c r="A226" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
@@ -16120,11 +16926,11 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E226" s="11" t="n">
-        <v>2060</v>
+        <v>2000</v>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
@@ -16133,7 +16939,7 @@
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H226" s="6" t="inlineStr">
@@ -16144,11 +16950,11 @@
     </row>
     <row r="227">
       <c r="A227" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
@@ -16158,11 +16964,11 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E227" s="11" t="n">
-        <v>2152</v>
+        <v>1800</v>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
@@ -16171,7 +16977,7 @@
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr">
@@ -16182,11 +16988,11 @@
     </row>
     <row r="228">
       <c r="A228" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
@@ -16196,11 +17002,11 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E228" s="11" t="n">
-        <v>4060</v>
+        <v>3550</v>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
@@ -16209,7 +17015,7 @@
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr">
@@ -16229,16 +17035,16 @@
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E229" s="11" t="n">
-        <v>4560</v>
+        <v>5664</v>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
@@ -16247,7 +17053,7 @@
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr">
@@ -16267,16 +17073,16 @@
       </c>
       <c r="C230" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E230" s="11" t="n">
-        <v>5500</v>
+        <v>2537</v>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
@@ -16285,7 +17091,7 @@
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
@@ -16305,16 +17111,16 @@
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
-        <v>2500</v>
+        <v>3127</v>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
@@ -16323,7 +17129,7 @@
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
@@ -16343,16 +17149,16 @@
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Compucenter (WhatsApp)</t>
         </is>
       </c>
       <c r="E232" s="11" t="n">
-        <v>5200</v>
+        <v>2150</v>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
@@ -16361,7 +17167,7 @@
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
         </is>
       </c>
       <c r="H232" s="6" t="inlineStr">
@@ -16372,7 +17178,7 @@
     </row>
     <row r="233">
       <c r="A233" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
@@ -16381,16 +17187,16 @@
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E233" s="11" t="n">
-        <v>5500</v>
+        <v>6140</v>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
@@ -16399,14 +17205,18 @@
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
-        </is>
-      </c>
-      <c r="H233" s="2" t="n"/>
+          <t>nuevo OEM (garantía 6 meses)</t>
+        </is>
+      </c>
+      <c r="H233" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
@@ -16415,16 +17225,16 @@
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E234" s="11" t="n">
-        <v>2460</v>
+        <v>4760</v>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
@@ -16433,14 +17243,18 @@
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H234" s="2" t="n"/>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H234" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
@@ -16449,16 +17263,16 @@
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E235" s="11" t="n">
-        <v>2500</v>
+        <v>6800</v>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
@@ -16467,14 +17281,18 @@
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H235" s="2" t="n"/>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H235" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
@@ -16483,16 +17301,16 @@
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E236" s="11" t="n">
-        <v>6840</v>
+        <v>2100</v>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
@@ -16501,32 +17319,36 @@
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
-        </is>
-      </c>
-      <c r="H236" s="2" t="n"/>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H236" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E237" s="11" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
@@ -16535,7 +17357,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
@@ -16546,25 +17368,25 @@
     </row>
     <row r="238">
       <c r="A238" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E238" s="11" t="n">
-        <v>5350</v>
+        <v>4500</v>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
@@ -16573,32 +17395,36 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
-        </is>
-      </c>
-      <c r="H238" s="2" t="n"/>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+        </is>
+      </c>
+      <c r="H238" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
-        <v>7400</v>
+        <v>6700</v>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
@@ -16607,7 +17433,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H239" s="6" t="inlineStr">
@@ -16618,7 +17444,7 @@
     </row>
     <row r="240">
       <c r="A240" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
@@ -16632,11 +17458,11 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (web)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E240" s="11" t="n">
-        <v>2953</v>
+        <v>2520</v>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
@@ -16645,7 +17471,7 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+          <t>disponible (web)</t>
         </is>
       </c>
       <c r="H240" s="6" t="inlineStr">
@@ -16656,7 +17482,7 @@
     </row>
     <row r="241">
       <c r="A241" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
@@ -16665,16 +17491,16 @@
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900K</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Crazy Store (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
-        <v>6013</v>
+        <v>4290</v>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
@@ -16683,14 +17509,18 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H241" s="2" t="n"/>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+        </is>
+      </c>
+      <c r="H241" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
@@ -16699,16 +17529,16 @@
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E242" s="11" t="n">
-        <v>5890</v>
+        <v>2860</v>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
@@ -16717,14 +17547,18 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
-        </is>
-      </c>
-      <c r="H242" s="2" t="n"/>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H242" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
@@ -16733,16 +17567,16 @@
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E243" s="11" t="n">
-        <v>3080</v>
+        <v>2460</v>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
@@ -16751,14 +17585,18 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
-        </is>
-      </c>
-      <c r="H243" s="2" t="n"/>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H243" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
@@ -16767,16 +17605,16 @@
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E244" s="11" t="n">
-        <v>3650</v>
+        <v>5360</v>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
@@ -16785,14 +17623,18 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H244" s="2" t="n"/>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H244" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
@@ -16801,16 +17643,16 @@
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>PC Factor (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E245" s="11" t="n">
-        <v>3792</v>
+        <v>1710</v>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
@@ -16819,14 +17661,18 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H245" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H245" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
@@ -16835,16 +17681,16 @@
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E246" s="11" t="n">
-        <v>2800</v>
+        <v>2310</v>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
@@ -16853,14 +17699,18 @@
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="H246" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H246" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
@@ -16869,16 +17719,16 @@
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
-        <v>2260</v>
+        <v>2160</v>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
@@ -16887,14 +17737,18 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H247" s="2" t="n"/>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H247" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
@@ -16903,16 +17757,16 @@
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E248" s="11" t="n">
-        <v>2750</v>
+        <v>5360</v>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
@@ -16921,14 +17775,18 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H248" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H248" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
@@ -16937,16 +17795,16 @@
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7700X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
-        <v>3480</v>
+        <v>5660</v>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
@@ -16955,14 +17813,18 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>sin confirmar si es sellado (se preguntó)</t>
-        </is>
-      </c>
-      <c r="H249" s="2" t="n"/>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H249" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
@@ -16971,16 +17833,16 @@
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E250" s="11" t="n">
-        <v>2900</v>
+        <v>5860</v>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
@@ -16989,14 +17851,18 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
-        </is>
-      </c>
-      <c r="H250" s="2" t="n"/>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H250" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
@@ -17010,11 +17876,11 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
-        <v>1754</v>
+        <v>1860</v>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
@@ -17023,14 +17889,18 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
-        </is>
-      </c>
-      <c r="H251" s="2" t="n"/>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H251" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
@@ -17039,16 +17909,16 @@
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E252" s="11" t="n">
-        <v>2785</v>
+        <v>2060</v>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
@@ -17057,14 +17927,18 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H252" s="2" t="n"/>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H252" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
@@ -17073,16 +17947,16 @@
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
-        <v>1778</v>
+        <v>2152</v>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
@@ -17091,14 +17965,18 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H253" s="2" t="n"/>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H253" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
@@ -17107,16 +17985,16 @@
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E254" s="11" t="n">
-        <v>1600</v>
+        <v>4060</v>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
@@ -17125,14 +18003,18 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H254" s="2" t="n"/>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H254" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
@@ -17141,16 +18023,16 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E255" s="11" t="n">
-        <v>2500</v>
+        <v>4560</v>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
@@ -17159,32 +18041,36 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
-        </is>
-      </c>
-      <c r="H255" s="2" t="n"/>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H255" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E256" s="11" t="n">
-        <v>1730</v>
+        <v>5500</v>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
@@ -17193,7 +18079,7 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+          <t>nuevo OEM (solo el chip)</t>
         </is>
       </c>
       <c r="H256" s="6" t="inlineStr">
@@ -17204,7 +18090,7 @@
     </row>
     <row r="257">
       <c r="A257" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
@@ -17213,16 +18099,16 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E257" s="11" t="n">
-        <v>2384</v>
+        <v>2500</v>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
@@ -17231,7 +18117,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H257" s="6" t="inlineStr">
@@ -17242,7 +18128,7 @@
     </row>
     <row r="258">
       <c r="A258" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
@@ -17251,16 +18137,16 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E258" s="11" t="n">
-        <v>5664</v>
+        <v>5200</v>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
@@ -17269,7 +18155,7 @@
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>nuevo BOX (web: USD 480 a 11,80)</t>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H258" s="6" t="inlineStr">
@@ -17280,7 +18166,7 @@
     </row>
     <row r="259">
       <c r="A259" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
@@ -17289,16 +18175,16 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E259" s="11" t="n">
-        <v>2218</v>
+        <v>5500</v>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
@@ -17307,18 +18193,14 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H259" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
@@ -17327,16 +18209,16 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico (WhatsApp)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E260" s="11" t="n">
-        <v>2850</v>
+        <v>2460</v>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
@@ -17345,14 +18227,14 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
+          <t>nuevo OEM</t>
         </is>
       </c>
       <c r="H260" s="2" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
@@ -17361,16 +18243,16 @@
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico (WhatsApp)</t>
+          <t>Soft Computers (WhatsApp)</t>
         </is>
       </c>
       <c r="E261" s="11" t="n">
-        <v>5960</v>
+        <v>2500</v>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
@@ -17379,14 +18261,14 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+          <t>nuevo OEM</t>
         </is>
       </c>
       <c r="H261" s="2" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
@@ -17395,16 +18277,16 @@
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Gamer Store Cbba (WhatsApp)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E262" s="11" t="n">
-        <v>2067</v>
+        <v>6840</v>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
@@ -17413,14 +18295,14 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
         </is>
       </c>
       <c r="H262" s="2" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="15" t="n">
-        <v>46312</v>
+        <v>46308</v>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
@@ -17429,16 +18311,16 @@
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
-        <v>1230</v>
+        <v>4800</v>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
@@ -17447,7 +18329,7 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
         </is>
       </c>
       <c r="H263" s="6" t="inlineStr">
@@ -17458,25 +18340,25 @@
     </row>
     <row r="264">
       <c r="A264" s="15" t="n">
-        <v>46312</v>
+        <v>46308</v>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E264" s="11" t="n">
-        <v>1500</v>
+        <v>5350</v>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
@@ -17485,52 +18367,998 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>sin dato de estado ni marca (recién publicado)</t>
-        </is>
-      </c>
-      <c r="H264" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="D265" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E265" s="11" t="n">
+        <v>7400</v>
+      </c>
+      <c r="F265" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G265" s="5" t="inlineStr">
+        <is>
+          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H265" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D266" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (web)</t>
+        </is>
+      </c>
+      <c r="E266" s="11" t="n">
+        <v>2953</v>
+      </c>
+      <c r="F266" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G266" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H266" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C267" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i9-14900K</t>
+        </is>
+      </c>
+      <c r="D267" s="5" t="inlineStr">
+        <is>
+          <t>Crazy Store (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E267" s="11" t="n">
+        <v>6013</v>
+      </c>
+      <c r="F267" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G267" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B268" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C268" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D268" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E268" s="11" t="n">
+        <v>5890</v>
+      </c>
+      <c r="F268" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G268" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B269" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C269" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D269" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E269" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="F269" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G269" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B270" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C270" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+        </is>
+      </c>
+      <c r="D270" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E270" s="11" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F270" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G270" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B271" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C271" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB</t>
+        </is>
+      </c>
+      <c r="D271" s="5" t="inlineStr">
+        <is>
+          <t>PC Factor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E271" s="11" t="n">
+        <v>3792</v>
+      </c>
+      <c r="F271" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B272" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C272" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D272" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E272" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F272" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E273" s="11" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F273" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G273" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B274" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C274" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D274" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E274" s="11" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F274" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G274" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7700X</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E275" s="11" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G275" s="5" t="inlineStr">
+        <is>
+          <t>sin confirmar si es sellado (se preguntó)</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B276" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C276" s="5" t="inlineStr">
+        <is>
+          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+        </is>
+      </c>
+      <c r="D276" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E276" s="11" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F276" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G276" s="5" t="inlineStr">
+        <is>
+          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B277" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C277" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D277" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E277" s="11" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F277" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G277" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B278" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C278" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D278" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E278" s="11" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F278" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G278" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B279" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C279" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D279" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E279" s="11" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F279" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G279" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B280" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C280" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D280" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E280" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F280" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G280" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B281" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C281" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D281" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E281" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F281" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G281" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B282" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C282" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D282" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E282" s="11" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F282" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G282" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+        </is>
+      </c>
+      <c r="H282" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B283" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C283" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D283" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E283" s="11" t="n">
+        <v>2384</v>
+      </c>
+      <c r="F283" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G283" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+        </is>
+      </c>
+      <c r="H283" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B284" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C284" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D284" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E284" s="11" t="n">
+        <v>5664</v>
+      </c>
+      <c r="F284" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G284" s="5" t="inlineStr">
+        <is>
+          <t>nuevo BOX (web: USD 480 a 11,80)</t>
+        </is>
+      </c>
+      <c r="H284" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B285" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C285" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D285" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E285" s="11" t="n">
+        <v>2218</v>
+      </c>
+      <c r="F285" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G285" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H285" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B286" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C286" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D286" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E286" s="11" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F286" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G286" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D287" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E287" s="11" t="n">
+        <v>5960</v>
+      </c>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G287" s="5" t="inlineStr">
+        <is>
+          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B288" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C288" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D288" s="5" t="inlineStr">
+        <is>
+          <t>Gamer Store Cbba (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E288" s="11" t="n">
+        <v>2067</v>
+      </c>
+      <c r="F288" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G288" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="15" t="n">
         <v>46312</v>
       </c>
-      <c r="B265" s="5" t="inlineStr">
+      <c r="B289" s="5" t="inlineStr">
         <is>
           <t>Marketplace</t>
         </is>
       </c>
-      <c r="C265" s="5" t="inlineStr">
+      <c r="C289" s="5" t="inlineStr">
         <is>
           <t>SSD NVMe 1TB</t>
         </is>
       </c>
-      <c r="D265" s="5" t="inlineStr">
+      <c r="D289" s="5" t="inlineStr">
         <is>
           <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
-      <c r="E265" s="11" t="n">
+      <c r="E289" s="11" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F289" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G289" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
+        </is>
+      </c>
+      <c r="H289" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B290" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C290" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D290" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E290" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F290" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G290" s="5" t="inlineStr">
+        <is>
+          <t>sin dato de estado ni marca (recién publicado)</t>
+        </is>
+      </c>
+      <c r="H290" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C291" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D291" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E291" s="11" t="n">
         <v>1850</v>
       </c>
-      <c r="F265" s="5" t="inlineStr">
+      <c r="F291" s="5" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
       </c>
-      <c r="G265" s="5" t="inlineStr">
+      <c r="G291" s="5" t="inlineStr">
         <is>
           <t>Kingston NV3 1TB (estado sin dato)</t>
         </is>
       </c>
-      <c r="H265" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+      <c r="H291" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E292" s="11" t="n">
+        <v>2726</v>
+      </c>
+      <c r="F292" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G292" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otro modelo (Crucial BX500 2TB es SATA, no NVMe; nuevo; lista mayorista USD 230 × 11,85 del 12/10, sin factura; 35 en stock; garantía solo de prueba; solo referencia)</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -17765,20 +19593,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId267"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId242"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId268"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O109" headerRowCount="1">
-  <autoFilter ref="A1:O109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O123" headerRowCount="1">
+  <autoFilter ref="A1:O123"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H292" headerRowCount="1">
-  <autoFilter ref="A1:H292"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H318" headerRowCount="1">
+  <autoFilter ref="A1:H318"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -633,7 +633,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>¿Qué conviene traer? · 18/10/2026</t>
+          <t>¿Qué conviene traer? · 19/10/2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>160</v>
+        <v>154.99</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
@@ -870,7 +870,7 @@
         <v>5.27</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>209.68</v>
+        <v>239.99</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
@@ -935,7 +935,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>289.99</v>
+        <v>285</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>4800</v>
@@ -1242,12 +1242,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1256,20 +1256,18 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>93.5</v>
+        <v>429.97</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>96.94</v>
+        <v>379.99</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>1230</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>1754</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="H12" s="2" t="n"/>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1279,7 +1277,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="L12" s="11">
         <f>IF(D12="","",MIN(MAX(Supuestos!$B$5,CEILING((K12*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D12*Supuestos!$B$9))</f>
@@ -1309,12 +1307,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1323,18 +1321,18 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>429.97</v>
+        <v>549.99</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>379.99</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H13" s="2" t="n"/>
+        <v>454.99</v>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="8" t="n">
+        <v>5580</v>
+      </c>
       <c r="I13" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1344,7 +1342,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L13" s="11">
         <f>IF(D13="","",MIN(MAX(Supuestos!$B$5,CEILING((K13*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D13*Supuestos!$B$9))</f>
@@ -1374,12 +1372,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1388,17 +1386,19 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>549.99</v>
+        <v>109.99</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="G14" s="2" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>1230</v>
+      </c>
       <c r="H14" s="8" t="n">
-        <v>5580</v>
+        <v>1754</v>
       </c>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1409,7 +1409,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>125</v>
+        <v>149.99</v>
       </c>
       <c r="G15" s="2" t="n"/>
       <c r="H15" s="8" t="n">
@@ -1524,7 +1524,7 @@
         <v>9.99</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>72.95</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>900</v>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>129.99</v>
+        <v>107.99</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1650,7 +1650,7 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="7" t="n">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O109"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>209.99</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>160</v>
+        <v>154.99</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="K2" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L2" s="16">
         <f>IF(OR($K2="",D2=""),"",IF(COUNTIFS($B:$B,$B2,$A:$A,$K2,D:D,"&gt;=0")=0,"",D2-SUMIFS(D:D,$B:$B,$B2,$A:$A,$K2)))</f>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>93.5</v>
+        <v>117.94</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>96.94</v>
+        <v>95</v>
       </c>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L3" s="16">
         <f>IF(OR($K3="",D3=""),"",IF(COUNTIFS($B:$B,$B3,$A:$A,$K3,D:D,"&gt;=0")=0,"",D3-SUMIFS(D:D,$B:$B,$B3,$A:$A,$K3)))</f>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L4" s="16">
         <f>IF(OR($K4="",D4=""),"",IF(COUNTIFS($B:$B,$B4,$A:$A,$K4,D:D,"&gt;=0")=0,"",D4-SUMIFS(D:D,$B:$B,$B4,$A:$A,$K4)))</f>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>324.99</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>289.99</v>
+        <v>285</v>
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L5" s="16">
         <f>IF(OR($K5="",D5=""),"",IF(COUNTIFS($B:$B,$B5,$A:$A,$K5,D:D,"&gt;=0")=0,"",D5-SUMIFS(D:D,$B:$B,$B5,$A:$A,$K5)))</f>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="7" t="n">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L7" s="16">
         <f>IF(OR($K7="",D7=""),"",IF(COUNTIFS($B:$B,$B7,$A:$A,$K7,D:D,"&gt;=0")=0,"",D7-SUMIFS(D:D,$B:$B,$B7,$A:$A,$K7)))</f>
@@ -2200,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         <v>138.9</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>129.99</v>
+        <v>107.99</v>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L8" s="16">
         <f>IF(OR($K8="",D8=""),"",IF(COUNTIFS($B:$B,$B8,$A:$A,$K8,D:D,"&gt;=0")=0,"",D8-SUMIFS(D:D,$B:$B,$B8,$A:$A,$K8)))</f>
@@ -2255,7 +2255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>118.96</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>72.95</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L9" s="16">
         <f>IF(OR($K9="",D9=""),"",IF(COUNTIFS($B:$B,$B9,$A:$A,$K9,D:D,"&gt;=0")=0,"",D9-SUMIFS(D:D,$B:$B,$B9,$A:$A,$K9)))</f>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L10" s="16">
         <f>IF(OR($K10="",D10=""),"",IF(COUNTIFS($B:$B,$B10,$A:$A,$K10,D:D,"&gt;=0")=0,"",D10-SUMIFS(D:D,$B:$B,$B10,$A:$A,$K10)))</f>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>125</v>
+        <v>149.99</v>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L11" s="16">
         <f>IF(OR($K11="",D11=""),"",IF(COUNTIFS($B:$B,$B11,$A:$A,$K11,D:D,"&gt;=0")=0,"",D11-SUMIFS(D:D,$B:$B,$B11,$A:$A,$K11)))</f>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L12" s="16">
         <f>IF(OR($K12="",D12=""),"",IF(COUNTIFS($B:$B,$B12,$A:$A,$K12,D:D,"&gt;=0")=0,"",D12-SUMIFS(D:D,$B:$B,$B12,$A:$A,$K12)))</f>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>235.27</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>209.68</v>
+        <v>239.99</v>
       </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L13" s="16">
         <f>IF(OR($K13="",D13=""),"",IF(COUNTIFS($B:$B,$B13,$A:$A,$K13,D:D,"&gt;=0")=0,"",D13-SUMIFS(D:D,$B:$B,$B13,$A:$A,$K13)))</f>
@@ -2528,7 +2528,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L14" s="16">
         <f>IF(OR($K14="",D14=""),"",IF(COUNTIFS($B:$B,$B14,$A:$A,$K14,D:D,"&gt;=0")=0,"",D14-SUMIFS(D:D,$B:$B,$B14,$A:$A,$K14)))</f>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="K15" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L15" s="16">
         <f>IF(OR($K15="",D15=""),"",IF(COUNTIFS($B:$B,$B15,$A:$A,$K15,D:D,"&gt;=0")=0,"",D15-SUMIFS(D:D,$B:$B,$B15,$A:$A,$K15)))</f>
@@ -2638,7 +2638,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -2706,14 +2706,12 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>128.99</v>
+        <v>93.5</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>98.59</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>1230</v>
-      </c>
+        <v>96.94</v>
+      </c>
+      <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))),"")</f>
@@ -2729,7 +2727,7 @@
         </is>
       </c>
       <c r="K17" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L17" s="16">
         <f>IF(OR($K17="",D17=""),"",IF(COUNTIFS($B:$B,$B17,$A:$A,$K17,D:D,"&gt;=0")=0,"",D17-SUMIFS(D:D,$B:$B,$B17,$A:$A,$K17)))</f>
@@ -2750,7 +2748,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -2784,7 +2782,7 @@
         </is>
       </c>
       <c r="K18" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L18" s="16">
         <f>IF(OR($K18="",D18=""),"",IF(COUNTIFS($B:$B,$B18,$A:$A,$K18,D:D,"&gt;=0")=0,"",D18-SUMIFS(D:D,$B:$B,$B18,$A:$A,$K18)))</f>
@@ -2805,7 +2803,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2821,7 +2819,7 @@
         <v>324.99</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>275</v>
+        <v>289.99</v>
       </c>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
@@ -2839,7 +2837,7 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L19" s="16">
         <f>IF(OR($K19="",D19=""),"",IF(COUNTIFS($B:$B,$B19,$A:$A,$K19,D:D,"&gt;=0")=0,"",D19-SUMIFS(D:D,$B:$B,$B19,$A:$A,$K19)))</f>
@@ -2860,7 +2858,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2892,7 +2890,7 @@
         </is>
       </c>
       <c r="K20" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L20" s="16">
         <f>IF(OR($K20="",D20=""),"",IF(COUNTIFS($B:$B,$B20,$A:$A,$K20,D:D,"&gt;=0")=0,"",D20-SUMIFS(D:D,$B:$B,$B20,$A:$A,$K20)))</f>
@@ -2913,7 +2911,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -2926,7 +2924,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>140.26</v>
+        <v>213.95</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>120</v>
@@ -2947,7 +2945,7 @@
         </is>
       </c>
       <c r="K21" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L21" s="16">
         <f>IF(OR($K21="",D21=""),"",IF(COUNTIFS($B:$B,$B21,$A:$A,$K21,D:D,"&gt;=0")=0,"",D21-SUMIFS(D:D,$B:$B,$B21,$A:$A,$K21)))</f>
@@ -2968,7 +2966,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -3002,7 +3000,7 @@
         </is>
       </c>
       <c r="K22" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
@@ -3023,7 +3021,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -3039,7 +3037,7 @@
         <v>118.96</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>71.95</v>
+        <v>72.95</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -3057,7 +3055,7 @@
         </is>
       </c>
       <c r="K23" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L23" s="16">
         <f>IF(OR($K23="",D23=""),"",IF(COUNTIFS($B:$B,$B23,$A:$A,$K23,D:D,"&gt;=0")=0,"",D23-SUMIFS(D:D,$B:$B,$B23,$A:$A,$K23)))</f>
@@ -3078,7 +3076,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -3112,7 +3110,7 @@
         </is>
       </c>
       <c r="K24" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L24" s="16">
         <f>IF(OR($K24="",D24=""),"",IF(COUNTIFS($B:$B,$B24,$A:$A,$K24,D:D,"&gt;=0")=0,"",D24-SUMIFS(D:D,$B:$B,$B24,$A:$A,$K24)))</f>
@@ -3133,7 +3131,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -3165,7 +3163,7 @@
         </is>
       </c>
       <c r="K25" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L25" s="16">
         <f>IF(OR($K25="",D25=""),"",IF(COUNTIFS($B:$B,$B25,$A:$A,$K25,D:D,"&gt;=0")=0,"",D25-SUMIFS(D:D,$B:$B,$B25,$A:$A,$K25)))</f>
@@ -3186,7 +3184,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3202,7 +3200,7 @@
         <v>150</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>120.99</v>
+        <v>124.99</v>
       </c>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
@@ -3220,7 +3218,7 @@
         </is>
       </c>
       <c r="K26" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L26" s="16">
         <f>IF(OR($K26="",D26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,D:D,"&gt;=0")=0,"",D26-SUMIFS(D:D,$B:$B,$B26,$A:$A,$K26)))</f>
@@ -3241,7 +3239,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3257,7 +3255,7 @@
         <v>235.27</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>229</v>
+        <v>209.68</v>
       </c>
       <c r="F27" s="2" t="n"/>
       <c r="G27" s="2" t="n"/>
@@ -3275,7 +3273,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L27" s="16">
         <f>IF(OR($K27="",D27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,D:D,"&gt;=0")=0,"",D27-SUMIFS(D:D,$B:$B,$B27,$A:$A,$K27)))</f>
@@ -3296,7 +3294,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -3309,10 +3307,10 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>474.49</v>
+        <v>450</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>399.99</v>
+        <v>419.99</v>
       </c>
       <c r="F28" s="2" t="n"/>
       <c r="G28" s="2" t="n"/>
@@ -3330,7 +3328,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L28" s="16">
         <f>IF(OR($K28="",D28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,D:D,"&gt;=0")=0,"",D28-SUMIFS(D:D,$B:$B,$B28,$A:$A,$K28)))</f>
@@ -3351,7 +3349,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -3367,7 +3365,7 @@
         <v>429.97</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
@@ -3385,7 +3383,7 @@
         </is>
       </c>
       <c r="K29" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L29" s="16">
         <f>IF(OR($K29="",D29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,D:D,"&gt;=0")=0,"",D29-SUMIFS(D:D,$B:$B,$B29,$A:$A,$K29)))</f>
@@ -3406,7 +3404,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3422,7 +3420,7 @@
         <v>209.99</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>161.99</v>
+        <v>160</v>
       </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
@@ -3440,7 +3438,7 @@
         </is>
       </c>
       <c r="K30" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L30" s="16">
         <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
@@ -3461,7 +3459,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3474,13 +3472,13 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>110</v>
+        <v>128.99</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>80</v>
+        <v>98.59</v>
       </c>
       <c r="F31" s="8" t="n">
-        <v>1730</v>
+        <v>1230</v>
       </c>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="9">
@@ -3497,7 +3495,7 @@
         </is>
       </c>
       <c r="K31" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L31" s="16">
         <f>IF(OR($K31="",D31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,D:D,"&gt;=0")=0,"",D31-SUMIFS(D:D,$B:$B,$B31,$A:$A,$K31)))</f>
@@ -3518,7 +3516,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3552,7 +3550,7 @@
         </is>
       </c>
       <c r="K32" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L32" s="16">
         <f>IF(OR($K32="",D32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,D:D,"&gt;=0")=0,"",D32-SUMIFS(D:D,$B:$B,$B32,$A:$A,$K32)))</f>
@@ -3573,7 +3571,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3586,15 +3584,13 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>320</v>
+        <v>324.99</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>279.99</v>
+        <v>275</v>
       </c>
       <c r="F33" s="2" t="n"/>
-      <c r="G33" s="8" t="n">
-        <v>5664</v>
-      </c>
+      <c r="G33" s="2" t="n"/>
       <c r="H33" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A33,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3609,7 +3605,7 @@
         </is>
       </c>
       <c r="K33" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L33" s="16">
         <f>IF(OR($K33="",D33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,D:D,"&gt;=0")=0,"",D33-SUMIFS(D:D,$B:$B,$B33,$A:$A,$K33)))</f>
@@ -3630,7 +3626,7 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -3644,7 +3640,7 @@
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="7" t="n">
-        <v>298.01</v>
+        <v>315</v>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
@@ -3662,7 +3658,7 @@
         </is>
       </c>
       <c r="K34" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L34" s="16">
         <f>IF(OR($K34="",D34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,D:D,"&gt;=0")=0,"",D34-SUMIFS(D:D,$B:$B,$B34,$A:$A,$K34)))</f>
@@ -3683,7 +3679,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3696,15 +3692,13 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>141.24</v>
+        <v>140.26</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F35" s="2" t="n"/>
-      <c r="G35" s="8" t="n">
-        <v>2850</v>
-      </c>
+      <c r="G35" s="2" t="n"/>
       <c r="H35" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A35,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3719,7 +3713,7 @@
         </is>
       </c>
       <c r="K35" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L35" s="16">
         <f>IF(OR($K35="",D35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,D:D,"&gt;=0")=0,"",D35-SUMIFS(D:D,$B:$B,$B35,$A:$A,$K35)))</f>
@@ -3740,7 +3734,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -3774,7 +3768,7 @@
         </is>
       </c>
       <c r="K36" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L36" s="16">
         <f>IF(OR($K36="",D36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,D:D,"&gt;=0")=0,"",D36-SUMIFS(D:D,$B:$B,$B36,$A:$A,$K36)))</f>
@@ -3795,7 +3789,7 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -3811,7 +3805,7 @@
         <v>118.96</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>73.95</v>
+        <v>71.95</v>
       </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
@@ -3829,7 +3823,7 @@
         </is>
       </c>
       <c r="K37" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L37" s="16">
         <f>IF(OR($K37="",D37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,D:D,"&gt;=0")=0,"",D37-SUMIFS(D:D,$B:$B,$B37,$A:$A,$K37)))</f>
@@ -3850,7 +3844,7 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3869,9 +3863,7 @@
         <v>139.99</v>
       </c>
       <c r="F38" s="2" t="n"/>
-      <c r="G38" s="8" t="n">
-        <v>2384</v>
-      </c>
+      <c r="G38" s="2" t="n"/>
       <c r="H38" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A38,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3886,7 +3878,7 @@
         </is>
       </c>
       <c r="K38" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L38" s="16">
         <f>IF(OR($K38="",D38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,D:D,"&gt;=0")=0,"",D38-SUMIFS(D:D,$B:$B,$B38,$A:$A,$K38)))</f>
@@ -3907,7 +3899,7 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3921,7 +3913,7 @@
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="7" t="n">
-        <v>149.99</v>
+        <v>125</v>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
@@ -3939,7 +3931,7 @@
         </is>
       </c>
       <c r="K39" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L39" s="16">
         <f>IF(OR($K39="",D39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,D:D,"&gt;=0")=0,"",D39-SUMIFS(D:D,$B:$B,$B39,$A:$A,$K39)))</f>
@@ -3960,7 +3952,7 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3994,7 +3986,7 @@
         </is>
       </c>
       <c r="K40" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L40" s="16">
         <f>IF(OR($K40="",D40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,D:D,"&gt;=0")=0,"",D40-SUMIFS(D:D,$B:$B,$B40,$A:$A,$K40)))</f>
@@ -4015,7 +4007,7 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -4028,7 +4020,7 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>234.99</v>
+        <v>235.27</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>229</v>
@@ -4049,7 +4041,7 @@
         </is>
       </c>
       <c r="K41" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L41" s="16">
         <f>IF(OR($K41="",D41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,D:D,"&gt;=0")=0,"",D41-SUMIFS(D:D,$B:$B,$B41,$A:$A,$K41)))</f>
@@ -4070,7 +4062,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4086,7 +4078,7 @@
         <v>474.49</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>389.99</v>
+        <v>399.99</v>
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
@@ -4104,7 +4096,7 @@
         </is>
       </c>
       <c r="K42" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L42" s="16">
         <f>IF(OR($K42="",D42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,D:D,"&gt;=0")=0,"",D42-SUMIFS(D:D,$B:$B,$B42,$A:$A,$K42)))</f>
@@ -4125,7 +4117,7 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4141,7 +4133,7 @@
         <v>429.97</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
@@ -4159,7 +4151,7 @@
         </is>
       </c>
       <c r="K43" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L43" s="16">
         <f>IF(OR($K43="",D43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,D:D,"&gt;=0")=0,"",D43-SUMIFS(D:D,$B:$B,$B43,$A:$A,$K43)))</f>
@@ -4180,7 +4172,7 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4196,7 +4188,7 @@
         <v>209.99</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>175</v>
+        <v>161.99</v>
       </c>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
@@ -4214,7 +4206,7 @@
         </is>
       </c>
       <c r="K44" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L44" s="16">
         <f>IF(OR($K44="",D44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,D:D,"&gt;=0")=0,"",D44-SUMIFS(D:D,$B:$B,$B44,$A:$A,$K44)))</f>
@@ -4235,7 +4227,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
@@ -4248,15 +4240,15 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>128.99</v>
+        <v>110</v>
       </c>
       <c r="E45" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F45" s="2" t="n"/>
-      <c r="G45" s="8" t="n">
-        <v>1754</v>
-      </c>
+      <c r="F45" s="8" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G45" s="2" t="n"/>
       <c r="H45" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4271,7 +4263,7 @@
         </is>
       </c>
       <c r="K45" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L45" s="16">
         <f>IF(OR($K45="",D45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,D:D,"&gt;=0")=0,"",D45-SUMIFS(D:D,$B:$B,$B45,$A:$A,$K45)))</f>
@@ -4292,7 +4284,7 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -4305,10 +4297,10 @@
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>689.34</v>
+        <v>549.99</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>375</v>
+        <v>454.99</v>
       </c>
       <c r="F46" s="2" t="n"/>
       <c r="G46" s="2" t="n"/>
@@ -4326,7 +4318,7 @@
         </is>
       </c>
       <c r="K46" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L46" s="16">
         <f>IF(OR($K46="",D46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,D:D,"&gt;=0")=0,"",D46-SUMIFS(D:D,$B:$B,$B46,$A:$A,$K46)))</f>
@@ -4347,7 +4339,7 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
@@ -4367,7 +4359,7 @@
       </c>
       <c r="F47" s="2" t="n"/>
       <c r="G47" s="8" t="n">
-        <v>5890</v>
+        <v>5664</v>
       </c>
       <c r="H47" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))),"")</f>
@@ -4383,7 +4375,7 @@
         </is>
       </c>
       <c r="K47" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L47" s="16">
         <f>IF(OR($K47="",D47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,D:D,"&gt;=0")=0,"",D47-SUMIFS(D:D,$B:$B,$B47,$A:$A,$K47)))</f>
@@ -4404,7 +4396,7 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
@@ -4418,7 +4410,7 @@
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>295</v>
+        <v>298.01</v>
       </c>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
@@ -4436,7 +4428,7 @@
         </is>
       </c>
       <c r="K48" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L48" s="16">
         <f>IF(OR($K48="",D48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,D:D,"&gt;=0")=0,"",D48-SUMIFS(D:D,$B:$B,$B48,$A:$A,$K48)))</f>
@@ -4457,7 +4449,7 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
@@ -4470,14 +4462,14 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>142.24</v>
+        <v>141.24</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="8" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="H49" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))),"")</f>
@@ -4493,7 +4485,7 @@
         </is>
       </c>
       <c r="K49" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L49" s="16">
         <f>IF(OR($K49="",D49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,D:D,"&gt;=0")=0,"",D49-SUMIFS(D:D,$B:$B,$B49,$A:$A,$K49)))</f>
@@ -4514,7 +4506,7 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
@@ -4530,7 +4522,7 @@
         <v>138.9</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
@@ -4548,7 +4540,7 @@
         </is>
       </c>
       <c r="K50" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L50" s="16">
         <f>IF(OR($K50="",D50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,D:D,"&gt;=0")=0,"",D50-SUMIFS(D:D,$B:$B,$B50,$A:$A,$K50)))</f>
@@ -4569,7 +4561,7 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
@@ -4582,7 +4574,7 @@
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>75</v>
+        <v>118.96</v>
       </c>
       <c r="E51" s="7" t="n">
         <v>73.95</v>
@@ -4603,7 +4595,7 @@
         </is>
       </c>
       <c r="K51" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L51" s="16">
         <f>IF(OR($K51="",D51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,D:D,"&gt;=0")=0,"",D51-SUMIFS(D:D,$B:$B,$B51,$A:$A,$K51)))</f>
@@ -4624,7 +4616,7 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -4640,11 +4632,11 @@
         <v>164.49</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>134.99</v>
+        <v>139.99</v>
       </c>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="8" t="n">
-        <v>2750</v>
+        <v>2384</v>
       </c>
       <c r="H52" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))),"")</f>
@@ -4660,7 +4652,7 @@
         </is>
       </c>
       <c r="K52" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L52" s="16">
         <f>IF(OR($K52="",D52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,D:D,"&gt;=0")=0,"",D52-SUMIFS(D:D,$B:$B,$B52,$A:$A,$K52)))</f>
@@ -4681,7 +4673,7 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
@@ -4713,7 +4705,7 @@
         </is>
       </c>
       <c r="K53" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L53" s="16">
         <f>IF(OR($K53="",D53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,D:D,"&gt;=0")=0,"",D53-SUMIFS(D:D,$B:$B,$B53,$A:$A,$K53)))</f>
@@ -4734,7 +4726,7 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
@@ -4750,12 +4742,10 @@
         <v>150</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>114.99</v>
+        <v>120.99</v>
       </c>
       <c r="F54" s="2" t="n"/>
-      <c r="G54" s="8" t="n">
-        <v>2260</v>
-      </c>
+      <c r="G54" s="2" t="n"/>
       <c r="H54" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A54,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A54,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4770,7 +4760,7 @@
         </is>
       </c>
       <c r="K54" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L54" s="16">
         <f>IF(OR($K54="",D54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,D:D,"&gt;=0")=0,"",D54-SUMIFS(D:D,$B:$B,$B54,$A:$A,$K54)))</f>
@@ -4791,7 +4781,7 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
@@ -4825,7 +4815,7 @@
         </is>
       </c>
       <c r="K55" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L55" s="16">
         <f>IF(OR($K55="",D55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,D:D,"&gt;=0")=0,"",D55-SUMIFS(D:D,$B:$B,$B55,$A:$A,$K55)))</f>
@@ -4846,7 +4836,7 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
@@ -4859,10 +4849,10 @@
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>435.99</v>
+        <v>474.49</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>394.99</v>
+        <v>389.99</v>
       </c>
       <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="n"/>
@@ -4880,7 +4870,7 @@
         </is>
       </c>
       <c r="K56" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L56" s="16">
         <f>IF(OR($K56="",D56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,D:D,"&gt;=0")=0,"",D56-SUMIFS(D:D,$B:$B,$B56,$A:$A,$K56)))</f>
@@ -4901,7 +4891,7 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
@@ -4917,7 +4907,7 @@
         <v>429.97</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
@@ -4935,7 +4925,7 @@
         </is>
       </c>
       <c r="K57" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L57" s="16">
         <f>IF(OR($K57="",D57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,D:D,"&gt;=0")=0,"",D57-SUMIFS(D:D,$B:$B,$B57,$A:$A,$K57)))</f>
@@ -4956,7 +4946,7 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
@@ -4972,7 +4962,7 @@
         <v>209.99</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>164.99</v>
+        <v>175</v>
       </c>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
@@ -4990,7 +4980,7 @@
         </is>
       </c>
       <c r="K58" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L58" s="16">
         <f>IF(OR($K58="",D58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,D:D,"&gt;=0")=0,"",D58-SUMIFS(D:D,$B:$B,$B58,$A:$A,$K58)))</f>
@@ -5011,7 +5001,7 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
@@ -5024,13 +5014,15 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>117.99</v>
+        <v>128.99</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="F59" s="2" t="n"/>
-      <c r="G59" s="2" t="n"/>
+      <c r="G59" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="H59" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5045,7 +5037,7 @@
         </is>
       </c>
       <c r="K59" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L59" s="16">
         <f>IF(OR($K59="",D59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,D:D,"&gt;=0")=0,"",D59-SUMIFS(D:D,$B:$B,$B59,$A:$A,$K59)))</f>
@@ -5066,7 +5058,7 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
@@ -5079,10 +5071,10 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>499.99</v>
+        <v>689.34</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>454.99</v>
+        <v>375</v>
       </c>
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="n"/>
@@ -5100,7 +5092,7 @@
         </is>
       </c>
       <c r="K60" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L60" s="16">
         <f>IF(OR($K60="",D60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,D:D,"&gt;=0")=0,"",D60-SUMIFS(D:D,$B:$B,$B60,$A:$A,$K60)))</f>
@@ -5121,7 +5113,7 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
@@ -5134,13 +5126,15 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>275.99</v>
+        <v>279.99</v>
       </c>
       <c r="F61" s="2" t="n"/>
-      <c r="G61" s="2" t="n"/>
+      <c r="G61" s="8" t="n">
+        <v>5890</v>
+      </c>
       <c r="H61" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5155,7 +5149,7 @@
         </is>
       </c>
       <c r="K61" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L61" s="16">
         <f>IF(OR($K61="",D61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,D:D,"&gt;=0")=0,"",D61-SUMIFS(D:D,$B:$B,$B61,$A:$A,$K61)))</f>
@@ -5176,7 +5170,7 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
@@ -5208,7 +5202,7 @@
         </is>
       </c>
       <c r="K62" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L62" s="16">
         <f>IF(OR($K62="",D62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,D:D,"&gt;=0")=0,"",D62-SUMIFS(D:D,$B:$B,$B62,$A:$A,$K62)))</f>
@@ -5229,7 +5223,7 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
@@ -5245,10 +5239,12 @@
         <v>142.24</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>121.99</v>
+        <v>120</v>
       </c>
       <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
+      <c r="G63" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H63" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5263,7 +5259,7 @@
         </is>
       </c>
       <c r="K63" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L63" s="16">
         <f>IF(OR($K63="",D63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,D:D,"&gt;=0")=0,"",D63-SUMIFS(D:D,$B:$B,$B63,$A:$A,$K63)))</f>
@@ -5284,7 +5280,7 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
@@ -5300,7 +5296,7 @@
         <v>138.9</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>129.99</v>
+        <v>135</v>
       </c>
       <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="n"/>
@@ -5318,7 +5314,7 @@
         </is>
       </c>
       <c r="K64" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L64" s="16">
         <f>IF(OR($K64="",D64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,D:D,"&gt;=0")=0,"",D64-SUMIFS(D:D,$B:$B,$B64,$A:$A,$K64)))</f>
@@ -5339,7 +5335,7 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
@@ -5352,10 +5348,10 @@
         </is>
       </c>
       <c r="D65" s="7" t="n">
-        <v>72.98999999999999</v>
+        <v>75</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>65</v>
+        <v>73.95</v>
       </c>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="n"/>
@@ -5373,7 +5369,7 @@
         </is>
       </c>
       <c r="K65" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L65" s="16">
         <f>IF(OR($K65="",D65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,D:D,"&gt;=0")=0,"",D65-SUMIFS(D:D,$B:$B,$B65,$A:$A,$K65)))</f>
@@ -5394,7 +5390,7 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
@@ -5410,10 +5406,12 @@
         <v>164.49</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>134</v>
+        <v>134.99</v>
       </c>
       <c r="F66" s="2" t="n"/>
-      <c r="G66" s="2" t="n"/>
+      <c r="G66" s="8" t="n">
+        <v>2750</v>
+      </c>
       <c r="H66" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5428,7 +5426,7 @@
         </is>
       </c>
       <c r="K66" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L66" s="16">
         <f>IF(OR($K66="",D66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,D:D,"&gt;=0")=0,"",D66-SUMIFS(D:D,$B:$B,$B66,$A:$A,$K66)))</f>
@@ -5449,7 +5447,7 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
@@ -5481,7 +5479,7 @@
         </is>
       </c>
       <c r="K67" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L67" s="16">
         <f>IF(OR($K67="",D67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,D:D,"&gt;=0")=0,"",D67-SUMIFS(D:D,$B:$B,$B67,$A:$A,$K67)))</f>
@@ -5502,7 +5500,7 @@
     </row>
     <row r="68">
       <c r="A68" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
@@ -5518,10 +5516,12 @@
         <v>150</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>120.99</v>
+        <v>114.99</v>
       </c>
       <c r="F68" s="2" t="n"/>
-      <c r="G68" s="2" t="n"/>
+      <c r="G68" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="H68" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A68,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A68,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="K68" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L68" s="16">
         <f>IF(OR($K68="",D68=""),"",IF(COUNTIFS($B:$B,$B68,$A:$A,$K68,D:D,"&gt;=0")=0,"",D68-SUMIFS(D:D,$B:$B,$B68,$A:$A,$K68)))</f>
@@ -5557,7 +5557,7 @@
     </row>
     <row r="69">
       <c r="A69" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="K69" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L69" s="16">
         <f>IF(OR($K69="",D69=""),"",IF(COUNTIFS($B:$B,$B69,$A:$A,$K69,D:D,"&gt;=0")=0,"",D69-SUMIFS(D:D,$B:$B,$B69,$A:$A,$K69)))</f>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="70">
       <c r="A70" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>435.99</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>399.9</v>
+        <v>394.99</v>
       </c>
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
@@ -5646,7 +5646,7 @@
         </is>
       </c>
       <c r="K70" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L70" s="16">
         <f>IF(OR($K70="",D70=""),"",IF(COUNTIFS($B:$B,$B70,$A:$A,$K70,D:D,"&gt;=0")=0,"",D70-SUMIFS(D:D,$B:$B,$B70,$A:$A,$K70)))</f>
@@ -5667,7 +5667,7 @@
     </row>
     <row r="71">
       <c r="A71" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>429.97</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="K71" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L71" s="16">
         <f>IF(OR($K71="",D71=""),"",IF(COUNTIFS($B:$B,$B71,$A:$A,$K71,D:D,"&gt;=0")=0,"",D71-SUMIFS(D:D,$B:$B,$B71,$A:$A,$K71)))</f>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="72">
       <c r="A72" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>209.99</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>170</v>
+        <v>164.99</v>
       </c>
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
@@ -5756,7 +5756,7 @@
         </is>
       </c>
       <c r="K72" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L72" s="16">
         <f>IF(OR($K72="",D72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,D:D,"&gt;=0")=0,"",D72-SUMIFS(D:D,$B:$B,$B72,$A:$A,$K72)))</f>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="73">
       <c r="A73" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
@@ -5790,10 +5790,10 @@
         </is>
       </c>
       <c r="D73" s="7" t="n">
-        <v>114.99</v>
+        <v>117.99</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F73" s="2" t="n"/>
       <c r="G73" s="2" t="n"/>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="K73" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L73" s="16">
         <f>IF(OR($K73="",D73=""),"",IF(COUNTIFS($B:$B,$B73,$A:$A,$K73,D:D,"&gt;=0")=0,"",D73-SUMIFS(D:D,$B:$B,$B73,$A:$A,$K73)))</f>
@@ -5832,7 +5832,7 @@
     </row>
     <row r="74">
       <c r="A74" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="K74" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L74" s="16">
         <f>IF(OR($K74="",D74=""),"",IF(COUNTIFS($B:$B,$B74,$A:$A,$K74,D:D,"&gt;=0")=0,"",D74-SUMIFS(D:D,$B:$B,$B74,$A:$A,$K74)))</f>
@@ -5887,7 +5887,7 @@
     </row>
     <row r="75">
       <c r="A75" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
@@ -5903,14 +5903,10 @@
         <v>329</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G75" s="8" t="n">
-        <v>5350</v>
-      </c>
+        <v>275.99</v>
+      </c>
+      <c r="F75" s="2" t="n"/>
+      <c r="G75" s="2" t="n"/>
       <c r="H75" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5925,7 +5921,7 @@
         </is>
       </c>
       <c r="K75" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L75" s="16">
         <f>IF(OR($K75="",D75=""),"",IF(COUNTIFS($B:$B,$B75,$A:$A,$K75,D:D,"&gt;=0")=0,"",D75-SUMIFS(D:D,$B:$B,$B75,$A:$A,$K75)))</f>
@@ -5946,7 +5942,7 @@
     </row>
     <row r="76">
       <c r="A76" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
@@ -5960,7 +5956,7 @@
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="7" t="n">
-        <v>299.99</v>
+        <v>295</v>
       </c>
       <c r="F76" s="2" t="n"/>
       <c r="G76" s="2" t="n"/>
@@ -5978,7 +5974,7 @@
         </is>
       </c>
       <c r="K76" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L76" s="16">
         <f>IF(OR($K76="",D76=""),"",IF(COUNTIFS($B:$B,$B76,$A:$A,$K76,D:D,"&gt;=0")=0,"",D76-SUMIFS(D:D,$B:$B,$B76,$A:$A,$K76)))</f>
@@ -5999,7 +5995,7 @@
     </row>
     <row r="77">
       <c r="A77" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
@@ -6012,10 +6008,10 @@
         </is>
       </c>
       <c r="D77" s="7" t="n">
-        <v>143.24</v>
+        <v>142.24</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>122.99</v>
+        <v>121.99</v>
       </c>
       <c r="F77" s="2" t="n"/>
       <c r="G77" s="2" t="n"/>
@@ -6033,7 +6029,7 @@
         </is>
       </c>
       <c r="K77" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L77" s="16">
         <f>IF(OR($K77="",D77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,D:D,"&gt;=0")=0,"",D77-SUMIFS(D:D,$B:$B,$B77,$A:$A,$K77)))</f>
@@ -6054,7 +6050,7 @@
     </row>
     <row r="78">
       <c r="A78" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
@@ -6070,7 +6066,7 @@
         <v>138.9</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
@@ -6088,7 +6084,7 @@
         </is>
       </c>
       <c r="K78" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L78" s="16">
         <f>IF(OR($K78="",D78=""),"",IF(COUNTIFS($B:$B,$B78,$A:$A,$K78,D:D,"&gt;=0")=0,"",D78-SUMIFS(D:D,$B:$B,$B78,$A:$A,$K78)))</f>
@@ -6109,7 +6105,7 @@
     </row>
     <row r="79">
       <c r="A79" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
@@ -6122,10 +6118,10 @@
         </is>
       </c>
       <c r="D79" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>65</v>
       </c>
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
@@ -6143,7 +6139,7 @@
         </is>
       </c>
       <c r="K79" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L79" s="16">
         <f>IF(OR($K79="",D79=""),"",IF(COUNTIFS($B:$B,$B79,$A:$A,$K79,D:D,"&gt;=0")=0,"",D79-SUMIFS(D:D,$B:$B,$B79,$A:$A,$K79)))</f>
@@ -6164,7 +6160,7 @@
     </row>
     <row r="80">
       <c r="A80" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
@@ -6183,9 +6179,7 @@
         <v>134</v>
       </c>
       <c r="F80" s="2" t="n"/>
-      <c r="G80" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G80" s="2" t="n"/>
       <c r="H80" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6200,7 +6194,7 @@
         </is>
       </c>
       <c r="K80" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L80" s="16">
         <f>IF(OR($K80="",D80=""),"",IF(COUNTIFS($B:$B,$B80,$A:$A,$K80,D:D,"&gt;=0")=0,"",D80-SUMIFS(D:D,$B:$B,$B80,$A:$A,$K80)))</f>
@@ -6221,7 +6215,7 @@
     </row>
     <row r="81">
       <c r="A81" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
@@ -6253,7 +6247,7 @@
         </is>
       </c>
       <c r="K81" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L81" s="16">
         <f>IF(OR($K81="",D81=""),"",IF(COUNTIFS($B:$B,$B81,$A:$A,$K81,D:D,"&gt;=0")=0,"",D81-SUMIFS(D:D,$B:$B,$B81,$A:$A,$K81)))</f>
@@ -6274,7 +6268,7 @@
     </row>
     <row r="82">
       <c r="A82" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
@@ -6290,7 +6284,7 @@
         <v>150</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>99</v>
+        <v>120.99</v>
       </c>
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="2" t="n"/>
@@ -6308,7 +6302,7 @@
         </is>
       </c>
       <c r="K82" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L82" s="16">
         <f>IF(OR($K82="",D82=""),"",IF(COUNTIFS($B:$B,$B82,$A:$A,$K82,D:D,"&gt;=0")=0,"",D82-SUMIFS(D:D,$B:$B,$B82,$A:$A,$K82)))</f>
@@ -6329,7 +6323,7 @@
     </row>
     <row r="83">
       <c r="A83" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
@@ -6345,7 +6339,7 @@
         <v>234.99</v>
       </c>
       <c r="E83" s="7" t="n">
-        <v>209.99</v>
+        <v>229</v>
       </c>
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="2" t="n"/>
@@ -6363,7 +6357,7 @@
         </is>
       </c>
       <c r="K83" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L83" s="16">
         <f>IF(OR($K83="",D83=""),"",IF(COUNTIFS($B:$B,$B83,$A:$A,$K83,D:D,"&gt;=0")=0,"",D83-SUMIFS(D:D,$B:$B,$B83,$A:$A,$K83)))</f>
@@ -6384,7 +6378,7 @@
     </row>
     <row r="84">
       <c r="A84" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
@@ -6418,7 +6412,7 @@
         </is>
       </c>
       <c r="K84" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L84" s="16">
         <f>IF(OR($K84="",D84=""),"",IF(COUNTIFS($B:$B,$B84,$A:$A,$K84,D:D,"&gt;=0")=0,"",D84-SUMIFS(D:D,$B:$B,$B84,$A:$A,$K84)))</f>
@@ -6439,7 +6433,7 @@
     </row>
     <row r="85">
       <c r="A85" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
@@ -6452,10 +6446,10 @@
         </is>
       </c>
       <c r="D85" s="7" t="n">
-        <v>493</v>
+        <v>429.97</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>383.99</v>
+        <v>379.99</v>
       </c>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
@@ -6473,7 +6467,7 @@
         </is>
       </c>
       <c r="K85" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L85" s="16">
         <f>IF(OR($K85="",D85=""),"",IF(COUNTIFS($B:$B,$B85,$A:$A,$K85,D:D,"&gt;=0")=0,"",D85-SUMIFS(D:D,$B:$B,$B85,$A:$A,$K85)))</f>
@@ -6494,7 +6488,7 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
@@ -6510,12 +6504,10 @@
         <v>209.99</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>179.99</v>
+        <v>170</v>
       </c>
       <c r="F86" s="2" t="n"/>
-      <c r="G86" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G86" s="2" t="n"/>
       <c r="H86" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A86,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A86,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6530,7 +6522,7 @@
         </is>
       </c>
       <c r="K86" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L86" s="16">
         <f>IF(OR($K86="",D86=""),"",IF(COUNTIFS($B:$B,$B86,$A:$A,$K86,D:D,"&gt;=0")=0,"",D86-SUMIFS(D:D,$B:$B,$B86,$A:$A,$K86)))</f>
@@ -6551,7 +6543,7 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
@@ -6570,9 +6562,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F87" s="2" t="n"/>
-      <c r="G87" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G87" s="2" t="n"/>
       <c r="H87" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A87,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A87,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6587,7 +6577,7 @@
         </is>
       </c>
       <c r="K87" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L87" s="16">
         <f>IF(OR($K87="",D87=""),"",IF(COUNTIFS($B:$B,$B87,$A:$A,$K87,D:D,"&gt;=0")=0,"",D87-SUMIFS(D:D,$B:$B,$B87,$A:$A,$K87)))</f>
@@ -6608,7 +6598,7 @@
     </row>
     <row r="88">
       <c r="A88" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
@@ -6627,9 +6617,7 @@
         <v>454.99</v>
       </c>
       <c r="F88" s="2" t="n"/>
-      <c r="G88" s="8" t="n">
-        <v>6140</v>
-      </c>
+      <c r="G88" s="2" t="n"/>
       <c r="H88" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A88,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A88,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6644,7 +6632,7 @@
         </is>
       </c>
       <c r="K88" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L88" s="16">
         <f>IF(OR($K88="",D88=""),"",IF(COUNTIFS($B:$B,$B88,$A:$A,$K88,D:D,"&gt;=0")=0,"",D88-SUMIFS(D:D,$B:$B,$B88,$A:$A,$K88)))</f>
@@ -6665,7 +6653,7 @@
     </row>
     <row r="89">
       <c r="A89" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
@@ -6683,9 +6671,11 @@
       <c r="E89" s="7" t="n">
         <v>283.99</v>
       </c>
-      <c r="F89" s="2" t="n"/>
+      <c r="F89" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="G89" s="8" t="n">
-        <v>4760</v>
+        <v>5350</v>
       </c>
       <c r="H89" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A89,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A89,Dólar!$A:$A,0))),"")</f>
@@ -6701,7 +6691,7 @@
         </is>
       </c>
       <c r="K89" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L89" s="16">
         <f>IF(OR($K89="",D89=""),"",IF(COUNTIFS($B:$B,$B89,$A:$A,$K89,D:D,"&gt;=0")=0,"",D89-SUMIFS(D:D,$B:$B,$B89,$A:$A,$K89)))</f>
@@ -6722,7 +6712,7 @@
     </row>
     <row r="90">
       <c r="A90" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
@@ -6736,7 +6726,7 @@
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
@@ -6753,7 +6743,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K90" s="5" t="n"/>
+      <c r="K90" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L90" s="16">
         <f>IF(OR($K90="",D90=""),"",IF(COUNTIFS($B:$B,$B90,$A:$A,$K90,D:D,"&gt;=0")=0,"",D90-SUMIFS(D:D,$B:$B,$B90,$A:$A,$K90)))</f>
         <v/>
@@ -6773,7 +6765,7 @@
     </row>
     <row r="91">
       <c r="A91" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
@@ -6786,15 +6778,13 @@
         </is>
       </c>
       <c r="D91" s="7" t="n">
-        <v>144.25</v>
+        <v>143.24</v>
       </c>
       <c r="E91" s="7" t="n">
         <v>122.99</v>
       </c>
       <c r="F91" s="2" t="n"/>
-      <c r="G91" s="8" t="n">
-        <v>2860</v>
-      </c>
+      <c r="G91" s="2" t="n"/>
       <c r="H91" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A91,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A91,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6809,7 +6799,7 @@
         </is>
       </c>
       <c r="K91" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L91" s="16">
         <f>IF(OR($K91="",D91=""),"",IF(COUNTIFS($B:$B,$B91,$A:$A,$K91,D:D,"&gt;=0")=0,"",D91-SUMIFS(D:D,$B:$B,$B91,$A:$A,$K91)))</f>
@@ -6830,7 +6820,7 @@
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
@@ -6863,7 +6853,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K92" s="5" t="n"/>
+      <c r="K92" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L92" s="16">
         <f>IF(OR($K92="",D92=""),"",IF(COUNTIFS($B:$B,$B92,$A:$A,$K92,D:D,"&gt;=0")=0,"",D92-SUMIFS(D:D,$B:$B,$B92,$A:$A,$K92)))</f>
         <v/>
@@ -6883,7 +6875,7 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
@@ -6896,15 +6888,13 @@
         </is>
       </c>
       <c r="D93" s="7" t="n">
-        <v>75</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>59.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F93" s="2" t="n"/>
-      <c r="G93" s="8" t="n">
-        <v>2150</v>
-      </c>
+      <c r="G93" s="2" t="n"/>
       <c r="H93" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A93,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A93,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6919,7 +6909,7 @@
         </is>
       </c>
       <c r="K93" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L93" s="16">
         <f>IF(OR($K93="",D93=""),"",IF(COUNTIFS($B:$B,$B93,$A:$A,$K93,D:D,"&gt;=0")=0,"",D93-SUMIFS(D:D,$B:$B,$B93,$A:$A,$K93)))</f>
@@ -6940,7 +6930,7 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
@@ -6956,11 +6946,11 @@
         <v>164.49</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="F94" s="2" t="n"/>
       <c r="G94" s="8" t="n">
-        <v>2520</v>
+        <v>2460</v>
       </c>
       <c r="H94" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A94,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A94,Dólar!$A:$A,0))),"")</f>
@@ -6976,7 +6966,7 @@
         </is>
       </c>
       <c r="K94" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L94" s="16">
         <f>IF(OR($K94="",D94=""),"",IF(COUNTIFS($B:$B,$B94,$A:$A,$K94,D:D,"&gt;=0")=0,"",D94-SUMIFS(D:D,$B:$B,$B94,$A:$A,$K94)))</f>
@@ -6997,7 +6987,7 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
@@ -7009,9 +6999,7 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D95" s="7" t="n">
-        <v>259.78</v>
-      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" s="7" t="n">
         <v>149.99</v>
       </c>
@@ -7031,7 +7019,7 @@
         </is>
       </c>
       <c r="K95" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L95" s="16">
         <f>IF(OR($K95="",D95=""),"",IF(COUNTIFS($B:$B,$B95,$A:$A,$K95,D:D,"&gt;=0")=0,"",D95-SUMIFS(D:D,$B:$B,$B95,$A:$A,$K95)))</f>
@@ -7052,7 +7040,7 @@
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
@@ -7068,12 +7056,10 @@
         <v>150</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="F96" s="2" t="n"/>
-      <c r="G96" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G96" s="2" t="n"/>
       <c r="H96" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A96,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A96,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7087,7 +7073,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K96" s="5" t="n"/>
+      <c r="K96" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L96" s="16">
         <f>IF(OR($K96="",D96=""),"",IF(COUNTIFS($B:$B,$B96,$A:$A,$K96,D:D,"&gt;=0")=0,"",D96-SUMIFS(D:D,$B:$B,$B96,$A:$A,$K96)))</f>
         <v/>
@@ -7107,7 +7095,7 @@
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
@@ -7120,15 +7108,13 @@
         </is>
       </c>
       <c r="D97" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E97" s="7" t="n">
         <v>209.99</v>
       </c>
       <c r="F97" s="2" t="n"/>
-      <c r="G97" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G97" s="2" t="n"/>
       <c r="H97" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A97,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A97,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7143,7 +7129,7 @@
         </is>
       </c>
       <c r="K97" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L97" s="16">
         <f>IF(OR($K97="",D97=""),"",IF(COUNTIFS($B:$B,$B97,$A:$A,$K97,D:D,"&gt;=0")=0,"",D97-SUMIFS(D:D,$B:$B,$B97,$A:$A,$K97)))</f>
@@ -7164,7 +7150,7 @@
     </row>
     <row r="98">
       <c r="A98" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
@@ -7198,7 +7184,7 @@
         </is>
       </c>
       <c r="K98" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L98" s="16">
         <f>IF(OR($K98="",D98=""),"",IF(COUNTIFS($B:$B,$B98,$A:$A,$K98,D:D,"&gt;=0")=0,"",D98-SUMIFS(D:D,$B:$B,$B98,$A:$A,$K98)))</f>
@@ -7219,7 +7205,7 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
@@ -7235,11 +7221,9 @@
         <v>493</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F99" s="8" t="n">
-        <v>4500</v>
-      </c>
+        <v>383.99</v>
+      </c>
+      <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
       <c r="H99" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A99,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A99,Dólar!$A:$A,0))),"")</f>
@@ -7254,7 +7238,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K99" s="5" t="n"/>
+      <c r="K99" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L99" s="16">
         <f>IF(OR($K99="",D99=""),"",IF(COUNTIFS($B:$B,$B99,$A:$A,$K99,D:D,"&gt;=0")=0,"",D99-SUMIFS(D:D,$B:$B,$B99,$A:$A,$K99)))</f>
         <v/>
@@ -7274,7 +7260,7 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
@@ -7286,10 +7272,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
+      <c r="D100" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <v>179.99</v>
+      </c>
       <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="n"/>
+      <c r="G100" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H100" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A100,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A100,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7298,8 +7290,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A100,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J100" s="2" t="n"/>
-      <c r="K100" s="5" t="n"/>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K100" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L100" s="16">
         <f>IF(OR($K100="",D100=""),"",IF(COUNTIFS($B:$B,$B100,$A:$A,$K100,D:D,"&gt;=0")=0,"",D100-SUMIFS(D:D,$B:$B,$B100,$A:$A,$K100)))</f>
         <v/>
@@ -7319,7 +7317,7 @@
     </row>
     <row r="101">
       <c r="A101" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
@@ -7331,12 +7329,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D101" s="2" t="n"/>
-      <c r="E101" s="2" t="n"/>
-      <c r="F101" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G101" s="2" t="n"/>
+      <c r="D101" s="7" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F101" s="2" t="n"/>
+      <c r="G101" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H101" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A101,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A101,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7350,7 +7352,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K101" s="5" t="n"/>
+      <c r="K101" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L101" s="16">
         <f>IF(OR($K101="",D101=""),"",IF(COUNTIFS($B:$B,$B101,$A:$A,$K101,D:D,"&gt;=0")=0,"",D101-SUMIFS(D:D,$B:$B,$B101,$A:$A,$K101)))</f>
         <v/>
@@ -7370,7 +7374,7 @@
     </row>
     <row r="102">
       <c r="A102" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
@@ -7382,11 +7386,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="n"/>
+      <c r="D102" s="7" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>454.99</v>
+      </c>
       <c r="F102" s="2" t="n"/>
       <c r="G102" s="8" t="n">
-        <v>5580</v>
+        <v>6140</v>
       </c>
       <c r="H102" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A102,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A102,Dólar!$A:$A,0))),"")</f>
@@ -7401,7 +7409,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K102" s="5" t="n"/>
+      <c r="K102" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L102" s="16">
         <f>IF(OR($K102="",D102=""),"",IF(COUNTIFS($B:$B,$B102,$A:$A,$K102,D:D,"&gt;=0")=0,"",D102-SUMIFS(D:D,$B:$B,$B102,$A:$A,$K102)))</f>
         <v/>
@@ -7421,7 +7431,7 @@
     </row>
     <row r="103">
       <c r="A103" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
@@ -7433,12 +7443,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n"/>
-      <c r="E103" s="2" t="n"/>
-      <c r="F103" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G103" s="2" t="n"/>
+      <c r="D103" s="7" t="n">
+        <v>329</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="H103" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A103,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A103,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7452,7 +7466,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K103" s="5" t="n"/>
+      <c r="K103" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L103" s="16">
         <f>IF(OR($K103="",D103=""),"",IF(COUNTIFS($B:$B,$B103,$A:$A,$K103,D:D,"&gt;=0")=0,"",D103-SUMIFS(D:D,$B:$B,$B103,$A:$A,$K103)))</f>
         <v/>
@@ -7472,11 +7488,11 @@
     </row>
     <row r="104">
       <c r="A104" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -7485,7 +7501,9 @@
         </is>
       </c>
       <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
+      <c r="E104" s="7" t="n">
+        <v>305</v>
+      </c>
       <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="n"/>
       <c r="H104" s="9">
@@ -7496,7 +7514,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A104,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J104" s="2" t="n"/>
+      <c r="J104" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K104" s="5" t="n"/>
       <c r="L104" s="16">
         <f>IF(OR($K104="",D104=""),"",IF(COUNTIFS($B:$B,$B104,$A:$A,$K104,D:D,"&gt;=0")=0,"",D104-SUMIFS(D:D,$B:$B,$B104,$A:$A,$K104)))</f>
@@ -7517,24 +7539,28 @@
     </row>
     <row r="105">
       <c r="A105" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="n"/>
-      <c r="E105" s="2" t="n"/>
-      <c r="F105" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="G105" s="2" t="n"/>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="F105" s="2" t="n"/>
+      <c r="G105" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H105" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A105,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A105,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7548,7 +7574,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K105" s="5" t="n"/>
+      <c r="K105" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L105" s="16">
         <f>IF(OR($K105="",D105=""),"",IF(COUNTIFS($B:$B,$B105,$A:$A,$K105,D:D,"&gt;=0")=0,"",D105-SUMIFS(D:D,$B:$B,$B105,$A:$A,$K105)))</f>
         <v/>
@@ -7568,11 +7596,11 @@
     </row>
     <row r="106">
       <c r="A106" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -7580,8 +7608,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
+      <c r="D106" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="F106" s="2" t="n"/>
       <c r="G106" s="2" t="n"/>
       <c r="H106" s="9">
@@ -7592,7 +7624,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A106,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J106" s="2" t="n"/>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K106" s="5" t="n"/>
       <c r="L106" s="16">
         <f>IF(OR($K106="",D106=""),"",IF(COUNTIFS($B:$B,$B106,$A:$A,$K106,D:D,"&gt;=0")=0,"",D106-SUMIFS(D:D,$B:$B,$B106,$A:$A,$K106)))</f>
@@ -7613,23 +7649,27 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="n"/>
-      <c r="E107" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <v>59.99</v>
+      </c>
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="H107" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A107,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A107,Dólar!$A:$A,0))),"")</f>
@@ -7644,7 +7684,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K107" s="5" t="n"/>
+      <c r="K107" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L107" s="16">
         <f>IF(OR($K107="",D107=""),"",IF(COUNTIFS($B:$B,$B107,$A:$A,$K107,D:D,"&gt;=0")=0,"",D107-SUMIFS(D:D,$B:$B,$B107,$A:$A,$K107)))</f>
         <v/>
@@ -7664,11 +7706,11 @@
     </row>
     <row r="108">
       <c r="A108" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -7676,11 +7718,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="2" t="n"/>
+      <c r="D108" s="7" t="n">
+        <v>164.49</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>136.99</v>
+      </c>
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="8" t="n">
-        <v>3950</v>
+        <v>2520</v>
       </c>
       <c r="H108" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A108,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A108,Dólar!$A:$A,0))),"")</f>
@@ -7695,7 +7741,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K108" s="5" t="n"/>
+      <c r="K108" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L108" s="16">
         <f>IF(OR($K108="",D108=""),"",IF(COUNTIFS($B:$B,$B108,$A:$A,$K108,D:D,"&gt;=0")=0,"",D108-SUMIFS(D:D,$B:$B,$B108,$A:$A,$K108)))</f>
         <v/>
@@ -7715,23 +7763,25 @@
     </row>
     <row r="109">
       <c r="A109" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="n"/>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="8" t="n">
-        <v>6200</v>
-      </c>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
       <c r="H109" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A109,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A109,Dólar!$A:$A,0))),"")</f>
@@ -7746,7 +7796,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K109" s="5" t="n"/>
+      <c r="K109" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L109" s="16">
         <f>IF(OR($K109="",D109=""),"",IF(COUNTIFS($B:$B,$B109,$A:$A,$K109,D:D,"&gt;=0")=0,"",D109-SUMIFS(D:D,$B:$B,$B109,$A:$A,$K109)))</f>
         <v/>
@@ -7764,8 +7816,722 @@
         <v/>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="8" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H110" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A110,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A110,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I110" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A110,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="16">
+        <f>IF(OR($K110="",D110=""),"",IF(COUNTIFS($B:$B,$B110,$A:$A,$K110,D:D,"&gt;=0")=0,"",D110-SUMIFS(D:D,$B:$B,$B110,$A:$A,$K110)))</f>
+        <v/>
+      </c>
+      <c r="M110" s="16">
+        <f>IF(OR($K110="",E110=""),"",IF(COUNTIFS($B:$B,$B110,$A:$A,$K110,E:E,"&gt;=0")=0,"",E110-SUMIFS(E:E,$B:$B,$B110,$A:$A,$K110)))</f>
+        <v/>
+      </c>
+      <c r="N110" s="16">
+        <f>IF(OR($K110="",F110=""),"",IF(COUNTIFS($B:$B,$B110,$A:$A,$K110,F:F,"&gt;=0")=0,"",F110-SUMIFS(F:F,$B:$B,$B110,$A:$A,$K110)))</f>
+        <v/>
+      </c>
+      <c r="O110" s="16">
+        <f>IF(OR($K110="",G110=""),"",IF(COUNTIFS($B:$B,$B110,$A:$A,$K110,G:G,"&gt;=0")=0,"",G110-SUMIFS(G:G,$B:$B,$B110,$A:$A,$K110)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C111" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="F111" s="2" t="n"/>
+      <c r="G111" s="8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H111" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A111,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A111,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I111" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A111,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K111" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L111" s="16">
+        <f>IF(OR($K111="",D111=""),"",IF(COUNTIFS($B:$B,$B111,$A:$A,$K111,D:D,"&gt;=0")=0,"",D111-SUMIFS(D:D,$B:$B,$B111,$A:$A,$K111)))</f>
+        <v/>
+      </c>
+      <c r="M111" s="16">
+        <f>IF(OR($K111="",E111=""),"",IF(COUNTIFS($B:$B,$B111,$A:$A,$K111,E:E,"&gt;=0")=0,"",E111-SUMIFS(E:E,$B:$B,$B111,$A:$A,$K111)))</f>
+        <v/>
+      </c>
+      <c r="N111" s="16">
+        <f>IF(OR($K111="",F111=""),"",IF(COUNTIFS($B:$B,$B111,$A:$A,$K111,F:F,"&gt;=0")=0,"",F111-SUMIFS(F:F,$B:$B,$B111,$A:$A,$K111)))</f>
+        <v/>
+      </c>
+      <c r="O111" s="16">
+        <f>IF(OR($K111="",G111=""),"",IF(COUNTIFS($B:$B,$B111,$A:$A,$K111,G:G,"&gt;=0")=0,"",G111-SUMIFS(G:G,$B:$B,$B111,$A:$A,$K111)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C112" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A112,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A112,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I112" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A112,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K112" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L112" s="16">
+        <f>IF(OR($K112="",D112=""),"",IF(COUNTIFS($B:$B,$B112,$A:$A,$K112,D:D,"&gt;=0")=0,"",D112-SUMIFS(D:D,$B:$B,$B112,$A:$A,$K112)))</f>
+        <v/>
+      </c>
+      <c r="M112" s="16">
+        <f>IF(OR($K112="",E112=""),"",IF(COUNTIFS($B:$B,$B112,$A:$A,$K112,E:E,"&gt;=0")=0,"",E112-SUMIFS(E:E,$B:$B,$B112,$A:$A,$K112)))</f>
+        <v/>
+      </c>
+      <c r="N112" s="16">
+        <f>IF(OR($K112="",F112=""),"",IF(COUNTIFS($B:$B,$B112,$A:$A,$K112,F:F,"&gt;=0")=0,"",F112-SUMIFS(F:F,$B:$B,$B112,$A:$A,$K112)))</f>
+        <v/>
+      </c>
+      <c r="O112" s="16">
+        <f>IF(OR($K112="",G112=""),"",IF(COUNTIFS($B:$B,$B112,$A:$A,$K112,G:G,"&gt;=0")=0,"",G112-SUMIFS(G:G,$B:$B,$B112,$A:$A,$K112)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E113" s="7" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="F113" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A113,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A113,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I113" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A113,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n"/>
+      <c r="L113" s="16">
+        <f>IF(OR($K113="",D113=""),"",IF(COUNTIFS($B:$B,$B113,$A:$A,$K113,D:D,"&gt;=0")=0,"",D113-SUMIFS(D:D,$B:$B,$B113,$A:$A,$K113)))</f>
+        <v/>
+      </c>
+      <c r="M113" s="16">
+        <f>IF(OR($K113="",E113=""),"",IF(COUNTIFS($B:$B,$B113,$A:$A,$K113,E:E,"&gt;=0")=0,"",E113-SUMIFS(E:E,$B:$B,$B113,$A:$A,$K113)))</f>
+        <v/>
+      </c>
+      <c r="N113" s="16">
+        <f>IF(OR($K113="",F113=""),"",IF(COUNTIFS($B:$B,$B113,$A:$A,$K113,F:F,"&gt;=0")=0,"",F113-SUMIFS(F:F,$B:$B,$B113,$A:$A,$K113)))</f>
+        <v/>
+      </c>
+      <c r="O113" s="16">
+        <f>IF(OR($K113="",G113=""),"",IF(COUNTIFS($B:$B,$B113,$A:$A,$K113,G:G,"&gt;=0")=0,"",G113-SUMIFS(G:G,$B:$B,$B113,$A:$A,$K113)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A114,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A114,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I114" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A114,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="16">
+        <f>IF(OR($K114="",D114=""),"",IF(COUNTIFS($B:$B,$B114,$A:$A,$K114,D:D,"&gt;=0")=0,"",D114-SUMIFS(D:D,$B:$B,$B114,$A:$A,$K114)))</f>
+        <v/>
+      </c>
+      <c r="M114" s="16">
+        <f>IF(OR($K114="",E114=""),"",IF(COUNTIFS($B:$B,$B114,$A:$A,$K114,E:E,"&gt;=0")=0,"",E114-SUMIFS(E:E,$B:$B,$B114,$A:$A,$K114)))</f>
+        <v/>
+      </c>
+      <c r="N114" s="16">
+        <f>IF(OR($K114="",F114=""),"",IF(COUNTIFS($B:$B,$B114,$A:$A,$K114,F:F,"&gt;=0")=0,"",F114-SUMIFS(F:F,$B:$B,$B114,$A:$A,$K114)))</f>
+        <v/>
+      </c>
+      <c r="O114" s="16">
+        <f>IF(OR($K114="",G114=""),"",IF(COUNTIFS($B:$B,$B114,$A:$A,$K114,G:G,"&gt;=0")=0,"",G114-SUMIFS(G:G,$B:$B,$B114,$A:$A,$K114)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A115,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A115,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I115" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A115,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n"/>
+      <c r="L115" s="16">
+        <f>IF(OR($K115="",D115=""),"",IF(COUNTIFS($B:$B,$B115,$A:$A,$K115,D:D,"&gt;=0")=0,"",D115-SUMIFS(D:D,$B:$B,$B115,$A:$A,$K115)))</f>
+        <v/>
+      </c>
+      <c r="M115" s="16">
+        <f>IF(OR($K115="",E115=""),"",IF(COUNTIFS($B:$B,$B115,$A:$A,$K115,E:E,"&gt;=0")=0,"",E115-SUMIFS(E:E,$B:$B,$B115,$A:$A,$K115)))</f>
+        <v/>
+      </c>
+      <c r="N115" s="16">
+        <f>IF(OR($K115="",F115=""),"",IF(COUNTIFS($B:$B,$B115,$A:$A,$K115,F:F,"&gt;=0")=0,"",F115-SUMIFS(F:F,$B:$B,$B115,$A:$A,$K115)))</f>
+        <v/>
+      </c>
+      <c r="O115" s="16">
+        <f>IF(OR($K115="",G115=""),"",IF(COUNTIFS($B:$B,$B115,$A:$A,$K115,G:G,"&gt;=0")=0,"",G115-SUMIFS(G:G,$B:$B,$B115,$A:$A,$K115)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="H116" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A116,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A116,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I116" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A116,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n"/>
+      <c r="L116" s="16">
+        <f>IF(OR($K116="",D116=""),"",IF(COUNTIFS($B:$B,$B116,$A:$A,$K116,D:D,"&gt;=0")=0,"",D116-SUMIFS(D:D,$B:$B,$B116,$A:$A,$K116)))</f>
+        <v/>
+      </c>
+      <c r="M116" s="16">
+        <f>IF(OR($K116="",E116=""),"",IF(COUNTIFS($B:$B,$B116,$A:$A,$K116,E:E,"&gt;=0")=0,"",E116-SUMIFS(E:E,$B:$B,$B116,$A:$A,$K116)))</f>
+        <v/>
+      </c>
+      <c r="N116" s="16">
+        <f>IF(OR($K116="",F116=""),"",IF(COUNTIFS($B:$B,$B116,$A:$A,$K116,F:F,"&gt;=0")=0,"",F116-SUMIFS(F:F,$B:$B,$B116,$A:$A,$K116)))</f>
+        <v/>
+      </c>
+      <c r="O116" s="16">
+        <f>IF(OR($K116="",G116=""),"",IF(COUNTIFS($B:$B,$B116,$A:$A,$K116,G:G,"&gt;=0")=0,"",G116-SUMIFS(G:G,$B:$B,$B116,$A:$A,$K116)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G117" s="2" t="n"/>
+      <c r="H117" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A117,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A117,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A117,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n"/>
+      <c r="L117" s="16">
+        <f>IF(OR($K117="",D117=""),"",IF(COUNTIFS($B:$B,$B117,$A:$A,$K117,D:D,"&gt;=0")=0,"",D117-SUMIFS(D:D,$B:$B,$B117,$A:$A,$K117)))</f>
+        <v/>
+      </c>
+      <c r="M117" s="16">
+        <f>IF(OR($K117="",E117=""),"",IF(COUNTIFS($B:$B,$B117,$A:$A,$K117,E:E,"&gt;=0")=0,"",E117-SUMIFS(E:E,$B:$B,$B117,$A:$A,$K117)))</f>
+        <v/>
+      </c>
+      <c r="N117" s="16">
+        <f>IF(OR($K117="",F117=""),"",IF(COUNTIFS($B:$B,$B117,$A:$A,$K117,F:F,"&gt;=0")=0,"",F117-SUMIFS(F:F,$B:$B,$B117,$A:$A,$K117)))</f>
+        <v/>
+      </c>
+      <c r="O117" s="16">
+        <f>IF(OR($K117="",G117=""),"",IF(COUNTIFS($B:$B,$B117,$A:$A,$K117,G:G,"&gt;=0")=0,"",G117-SUMIFS(G:G,$B:$B,$B117,$A:$A,$K117)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A118,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A118,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I118" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A118,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J118" s="2" t="n"/>
+      <c r="K118" s="5" t="n"/>
+      <c r="L118" s="16">
+        <f>IF(OR($K118="",D118=""),"",IF(COUNTIFS($B:$B,$B118,$A:$A,$K118,D:D,"&gt;=0")=0,"",D118-SUMIFS(D:D,$B:$B,$B118,$A:$A,$K118)))</f>
+        <v/>
+      </c>
+      <c r="M118" s="16">
+        <f>IF(OR($K118="",E118=""),"",IF(COUNTIFS($B:$B,$B118,$A:$A,$K118,E:E,"&gt;=0")=0,"",E118-SUMIFS(E:E,$B:$B,$B118,$A:$A,$K118)))</f>
+        <v/>
+      </c>
+      <c r="N118" s="16">
+        <f>IF(OR($K118="",F118=""),"",IF(COUNTIFS($B:$B,$B118,$A:$A,$K118,F:F,"&gt;=0")=0,"",F118-SUMIFS(F:F,$B:$B,$B118,$A:$A,$K118)))</f>
+        <v/>
+      </c>
+      <c r="O118" s="16">
+        <f>IF(OR($K118="",G118=""),"",IF(COUNTIFS($B:$B,$B118,$A:$A,$K118,G:G,"&gt;=0")=0,"",G118-SUMIFS(G:G,$B:$B,$B118,$A:$A,$K118)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A119,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A119,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I119" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A119,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n"/>
+      <c r="L119" s="16">
+        <f>IF(OR($K119="",D119=""),"",IF(COUNTIFS($B:$B,$B119,$A:$A,$K119,D:D,"&gt;=0")=0,"",D119-SUMIFS(D:D,$B:$B,$B119,$A:$A,$K119)))</f>
+        <v/>
+      </c>
+      <c r="M119" s="16">
+        <f>IF(OR($K119="",E119=""),"",IF(COUNTIFS($B:$B,$B119,$A:$A,$K119,E:E,"&gt;=0")=0,"",E119-SUMIFS(E:E,$B:$B,$B119,$A:$A,$K119)))</f>
+        <v/>
+      </c>
+      <c r="N119" s="16">
+        <f>IF(OR($K119="",F119=""),"",IF(COUNTIFS($B:$B,$B119,$A:$A,$K119,F:F,"&gt;=0")=0,"",F119-SUMIFS(F:F,$B:$B,$B119,$A:$A,$K119)))</f>
+        <v/>
+      </c>
+      <c r="O119" s="16">
+        <f>IF(OR($K119="",G119=""),"",IF(COUNTIFS($B:$B,$B119,$A:$A,$K119,G:G,"&gt;=0")=0,"",G119-SUMIFS(G:G,$B:$B,$B119,$A:$A,$K119)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A120,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A120,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I120" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A120,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J120" s="2" t="n"/>
+      <c r="K120" s="5" t="n"/>
+      <c r="L120" s="16">
+        <f>IF(OR($K120="",D120=""),"",IF(COUNTIFS($B:$B,$B120,$A:$A,$K120,D:D,"&gt;=0")=0,"",D120-SUMIFS(D:D,$B:$B,$B120,$A:$A,$K120)))</f>
+        <v/>
+      </c>
+      <c r="M120" s="16">
+        <f>IF(OR($K120="",E120=""),"",IF(COUNTIFS($B:$B,$B120,$A:$A,$K120,E:E,"&gt;=0")=0,"",E120-SUMIFS(E:E,$B:$B,$B120,$A:$A,$K120)))</f>
+        <v/>
+      </c>
+      <c r="N120" s="16">
+        <f>IF(OR($K120="",F120=""),"",IF(COUNTIFS($B:$B,$B120,$A:$A,$K120,F:F,"&gt;=0")=0,"",F120-SUMIFS(F:F,$B:$B,$B120,$A:$A,$K120)))</f>
+        <v/>
+      </c>
+      <c r="O120" s="16">
+        <f>IF(OR($K120="",G120=""),"",IF(COUNTIFS($B:$B,$B120,$A:$A,$K120,G:G,"&gt;=0")=0,"",G120-SUMIFS(G:G,$B:$B,$B120,$A:$A,$K120)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="n"/>
+      <c r="G121" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H121" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A121,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A121,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I121" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A121,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n"/>
+      <c r="L121" s="16">
+        <f>IF(OR($K121="",D121=""),"",IF(COUNTIFS($B:$B,$B121,$A:$A,$K121,D:D,"&gt;=0")=0,"",D121-SUMIFS(D:D,$B:$B,$B121,$A:$A,$K121)))</f>
+        <v/>
+      </c>
+      <c r="M121" s="16">
+        <f>IF(OR($K121="",E121=""),"",IF(COUNTIFS($B:$B,$B121,$A:$A,$K121,E:E,"&gt;=0")=0,"",E121-SUMIFS(E:E,$B:$B,$B121,$A:$A,$K121)))</f>
+        <v/>
+      </c>
+      <c r="N121" s="16">
+        <f>IF(OR($K121="",F121=""),"",IF(COUNTIFS($B:$B,$B121,$A:$A,$K121,F:F,"&gt;=0")=0,"",F121-SUMIFS(F:F,$B:$B,$B121,$A:$A,$K121)))</f>
+        <v/>
+      </c>
+      <c r="O121" s="16">
+        <f>IF(OR($K121="",G121=""),"",IF(COUNTIFS($B:$B,$B121,$A:$A,$K121,G:G,"&gt;=0")=0,"",G121-SUMIFS(G:G,$B:$B,$B121,$A:$A,$K121)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="n"/>
+      <c r="G122" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H122" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A122,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A122,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I122" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A122,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n"/>
+      <c r="L122" s="16">
+        <f>IF(OR($K122="",D122=""),"",IF(COUNTIFS($B:$B,$B122,$A:$A,$K122,D:D,"&gt;=0")=0,"",D122-SUMIFS(D:D,$B:$B,$B122,$A:$A,$K122)))</f>
+        <v/>
+      </c>
+      <c r="M122" s="16">
+        <f>IF(OR($K122="",E122=""),"",IF(COUNTIFS($B:$B,$B122,$A:$A,$K122,E:E,"&gt;=0")=0,"",E122-SUMIFS(E:E,$B:$B,$B122,$A:$A,$K122)))</f>
+        <v/>
+      </c>
+      <c r="N122" s="16">
+        <f>IF(OR($K122="",F122=""),"",IF(COUNTIFS($B:$B,$B122,$A:$A,$K122,F:F,"&gt;=0")=0,"",F122-SUMIFS(F:F,$B:$B,$B122,$A:$A,$K122)))</f>
+        <v/>
+      </c>
+      <c r="O122" s="16">
+        <f>IF(OR($K122="",G122=""),"",IF(COUNTIFS($B:$B,$B122,$A:$A,$K122,G:G,"&gt;=0")=0,"",G122-SUMIFS(G:G,$B:$B,$B122,$A:$A,$K122)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G123" s="2" t="n"/>
+      <c r="H123" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A123,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A123,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I123" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A123,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n"/>
+      <c r="L123" s="16">
+        <f>IF(OR($K123="",D123=""),"",IF(COUNTIFS($B:$B,$B123,$A:$A,$K123,D:D,"&gt;=0")=0,"",D123-SUMIFS(D:D,$B:$B,$B123,$A:$A,$K123)))</f>
+        <v/>
+      </c>
+      <c r="M123" s="16">
+        <f>IF(OR($K123="",E123=""),"",IF(COUNTIFS($B:$B,$B123,$A:$A,$K123,E:E,"&gt;=0")=0,"",E123-SUMIFS(E:E,$B:$B,$B123,$A:$A,$K123)))</f>
+        <v/>
+      </c>
+      <c r="N123" s="16">
+        <f>IF(OR($K123="",F123=""),"",IF(COUNTIFS($B:$B,$B123,$A:$A,$K123,F:F,"&gt;=0")=0,"",F123-SUMIFS(F:F,$B:$B,$B123,$A:$A,$K123)))</f>
+        <v/>
+      </c>
+      <c r="O123" s="16">
+        <f>IF(OR($K123="",G123=""),"",IF(COUNTIFS($B:$B,$B123,$A:$A,$K123,G:G,"&gt;=0")=0,"",G123-SUMIFS(G:G,$B:$B,$B123,$A:$A,$K123)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M109">
+  <conditionalFormatting sqref="L2:M123">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -7773,7 +8539,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O109">
+  <conditionalFormatting sqref="N2:O123">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -7880,17 +8646,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId106"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId120"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8055,7 +8835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8332,6 +9112,32 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E11" s="10">
+        <f>IF(COUNT(C11:D11)=2,AVERAGE(C11:D11),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>BCB oficial 11.69; paralelo dolarbolivia.net 19/10 11:55 (compra 11.83 / venta 11.80); usado = promedio del paralelo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8343,7 +9149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16342,34 +17148,34 @@
     </row>
     <row r="211">
       <c r="A211" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
-        <v>5580</v>
+        <v>138.9</v>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G211" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; (New) AMD Ryzen 5 5600 Vermeer Zen3 6-Core 12-Thread AM4 CPU</t>
         </is>
       </c>
       <c r="H211" s="6" t="inlineStr">
@@ -16380,34 +17186,34 @@
     </row>
     <row r="212">
       <c r="A212" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E212" s="11" t="n">
-        <v>2300</v>
+        <v>213.95</v>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor bra_dewaa 99.8%; AMD Ryzen 5 7600 6-Core 12-Thread Unlocked Desktop Processor</t>
         </is>
       </c>
       <c r="H212" s="6" t="inlineStr">
@@ -16418,34 +17224,34 @@
     </row>
     <row r="213">
       <c r="A213" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
-        <v>3950</v>
+        <v>324.99</v>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G213" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor geoelectronics7 99.4%; AMD Ryzen 7 7800X3D 100-00000910 - Processor No Cooler</t>
         </is>
       </c>
       <c r="H213" s="6" t="inlineStr">
@@ -16456,34 +17262,34 @@
     </row>
     <row r="214">
       <c r="A214" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E214" s="11" t="n">
-        <v>4800</v>
+        <v>549.99</v>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G214" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay API; vendedor newegg 99.6%; AMD Ryzen 9 9950X - Ryzen 9 9000 Series Granite Ridge (Zen 5</t>
         </is>
       </c>
       <c r="H214" s="6" t="inlineStr">
@@ -16494,34 +17300,34 @@
     </row>
     <row r="215">
       <c r="A215" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
-        <v>5190</v>
+        <v>150</v>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G215" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor algonz1137 100.0%; INTEL CPU Core i5-12400F / 6/12 / 2.5GHz / 6xxChipset / BX80; envío no indicado</t>
         </is>
       </c>
       <c r="H215" s="6" t="inlineStr">
@@ -16532,34 +17338,34 @@
     </row>
     <row r="216">
       <c r="A216" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E216" s="11" t="n">
-        <v>5390</v>
+        <v>164.49</v>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G216" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t xml:space="preserve">eBay API; vendedor newegg 99.6%; Intel Core i5-14400F - Core i5 14th Gen Raptor Lake 10-Core </t>
         </is>
       </c>
       <c r="H216" s="6" t="inlineStr">
@@ -16570,34 +17376,34 @@
     </row>
     <row r="217">
       <c r="A217" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
-        <v>2000</v>
+        <v>235.27</v>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G217" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor jos-980836 100.0%; Intel Core ULTRA 7 265K LGA 1851 Unlocked, 20 cores.</t>
         </is>
       </c>
       <c r="H217" s="6" t="inlineStr">
@@ -16608,34 +17414,34 @@
     </row>
     <row r="218">
       <c r="A218" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E218" s="11" t="n">
-        <v>2650</v>
+        <v>429.97</v>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor uventure 99.7%; NEW 32GB (2x16GB) Corsair Vengeance DDR5 PC5-5600 Desktop RA</t>
         </is>
       </c>
       <c r="H218" s="6" t="inlineStr">
@@ -16646,34 +17452,34 @@
     </row>
     <row r="219">
       <c r="A219" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E219" s="11" t="n">
-        <v>2700</v>
+        <v>450</v>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>eBay API; vendedor kn32451 99.9%; CORSAIR Vengeance RGB 32GB (2x16GB) DDR5 6000MHz CL36 AMD EX</t>
         </is>
       </c>
       <c r="H219" s="6" t="inlineStr">
@@ -16684,34 +17490,34 @@
     </row>
     <row r="220">
       <c r="A220" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E220" s="11" t="n">
-        <v>6200</v>
+        <v>118.96</v>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G220" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t xml:space="preserve">eBay API; vendedor bike_fix 99.0%; T-Force Vulcan Z DDR4 RAM 16GB (2x8GB) 3200MHz CL16 Desktop </t>
         </is>
       </c>
       <c r="H220" s="6" t="inlineStr">
@@ -16722,34 +17528,34 @@
     </row>
     <row r="221">
       <c r="A221" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
-        <v>540</v>
+        <v>117.94</v>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G221" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>eBay API; vendedor sellyourgadgetssodo 99.5%; KingSpec NE-1TB 2280 M.2 NVMe 1TB New In Box</t>
         </is>
       </c>
       <c r="H221" s="6" t="inlineStr">
@@ -16760,34 +17566,34 @@
     </row>
     <row r="222">
       <c r="A222" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E222" s="11" t="n">
-        <v>900</v>
+        <v>209.99</v>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G222" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>eBay API; vendedor ram_technologies 100.0%; RAM Tech 2TB NVMe SSD Gen4 M.2 2280 | 5000MB/s Read 4500MB/s</t>
         </is>
       </c>
       <c r="H222" s="6" t="inlineStr">
@@ -16798,34 +17604,34 @@
     </row>
     <row r="223">
       <c r="A223" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E223" s="11" t="n">
-        <v>1500</v>
+        <v>107.99</v>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G223" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>eBay API; vendedor jb.sales 99.2%; AMD Ryzen 5 5600 6-Core 12-Thread Unlocked Desktop Processor</t>
         </is>
       </c>
       <c r="H223" s="6" t="inlineStr">
@@ -16836,34 +17642,34 @@
     </row>
     <row r="224">
       <c r="A224" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E224" s="11" t="n">
-        <v>1500</v>
+        <v>336</v>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G224" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>eBay API; vendedor jariah_tomko 100.0%; AMD Ryzen 7 5700X3D 8-Core 16-Thread AM4 CPU | 96MB 3D V-Cac; envío no indicado</t>
         </is>
       </c>
       <c r="H224" s="6" t="inlineStr">
@@ -16874,34 +17680,34 @@
     </row>
     <row r="225">
       <c r="A225" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E225" s="11" t="n">
-        <v>1850</v>
+        <v>120</v>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G225" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>eBay API; vendedor shenidss9ckq 99.1%; AMD Ryzen 5 7600 3.80GHz 6 Core 100-000001015 12 Thread AM5</t>
         </is>
       </c>
       <c r="H225" s="6" t="inlineStr">
@@ -16912,34 +17718,34 @@
     </row>
     <row r="226">
       <c r="A226" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E226" s="11" t="n">
-        <v>2000</v>
+        <v>285</v>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G226" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>eBay API; vendedor dszpe 100.0%; AMD Ryzen 7 7800X3D 8-Cores 4.2GHz Socket AM5 Gaming CPU Pro; envío no indicado</t>
         </is>
       </c>
       <c r="H226" s="6" t="inlineStr">
@@ -16950,34 +17756,34 @@
     </row>
     <row r="227">
       <c r="A227" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E227" s="11" t="n">
-        <v>1800</v>
+        <v>454.99</v>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>eBay API; vendedor goodios_direct 99.6%; **  AMD Ryzen 9 9950X Processor - USED  **</t>
         </is>
       </c>
       <c r="H227" s="6" t="inlineStr">
@@ -16988,34 +17794,34 @@
     </row>
     <row r="228">
       <c r="A228" s="15" t="n">
-        <v>46306</v>
+        <v>46314</v>
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E228" s="11" t="n">
-        <v>3550</v>
+        <v>124.99</v>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>eBay API; vendedor silencedpp7 100.0%; Intel Core i5-12400F 2.50GHz 6 Core SRL4W 12 Thread LGA 1700; envío no indicado</t>
         </is>
       </c>
       <c r="H228" s="6" t="inlineStr">
@@ -17026,34 +17832,34 @@
     </row>
     <row r="229">
       <c r="A229" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E229" s="11" t="n">
-        <v>5664</v>
+        <v>149.99</v>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>eBay API; vendedor techrec-recycling 99.6%; Intel Core i5-13400 2.50GHz 10-Core LGA1700 20MB Desktop Pro</t>
         </is>
       </c>
       <c r="H229" s="6" t="inlineStr">
@@ -17064,11 +17870,11 @@
     </row>
     <row r="230">
       <c r="A230" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C230" s="5" t="inlineStr">
@@ -17078,20 +17884,20 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E230" s="11" t="n">
-        <v>2537</v>
+        <v>139.99</v>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G230" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>eBay API; vendedor paymore_bustleton 99.4%; Intel Core i5-14400F 2.50GHz 10 Core SRN3R 16 Thread LGA 170</t>
         </is>
       </c>
       <c r="H230" s="6" t="inlineStr">
@@ -17102,34 +17908,34 @@
     </row>
     <row r="231">
       <c r="A231" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C231" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
-        <v>3127</v>
+        <v>239.99</v>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t xml:space="preserve">eBay API; vendedor paymore_taylor 99.6%; Intel Core Ultra 7 265K 3.90GHz 20 Core SRQCW 20 Thread LGA </t>
         </is>
       </c>
       <c r="H231" s="6" t="inlineStr">
@@ -17140,34 +17946,34 @@
     </row>
     <row r="232">
       <c r="A232" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E232" s="11" t="n">
-        <v>2150</v>
+        <v>379.99</v>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G232" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t>eBay API; vendedor nn-red 100.0%; Corsair Vengeance RGB Pro 32GB (2x16GB) RAM DDR5 5600MHz CMH; envío no indicado</t>
         </is>
       </c>
       <c r="H232" s="6" t="inlineStr">
@@ -17178,34 +17984,34 @@
     </row>
     <row r="233">
       <c r="A233" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E233" s="11" t="n">
-        <v>6140</v>
+        <v>419.99</v>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G233" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t>eBay API; vendedor wazno 99.7%; Corsair Vengeance RGB 32GB 2x16GB DDR5 RAM 6000MHz CMH32GX5M</t>
         </is>
       </c>
       <c r="H233" s="6" t="inlineStr">
@@ -17216,34 +18022,34 @@
     </row>
     <row r="234">
       <c r="A234" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E234" s="11" t="n">
-        <v>4760</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G234" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>eBay API; vendedor memory-eagle 99.8%; G.Skill Ripjaws V F4-3200C16D-16GVKB 16GB (2x8GB) DDR4 Deskt</t>
         </is>
       </c>
       <c r="H234" s="6" t="inlineStr">
@@ -17254,34 +18060,34 @@
     </row>
     <row r="235">
       <c r="A235" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E235" s="11" t="n">
-        <v>6800</v>
+        <v>95</v>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G235" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor fabulouscomputers 98.3%; 1tb ssd nvme; envío no indicado</t>
         </is>
       </c>
       <c r="H235" s="6" t="inlineStr">
@@ -17292,34 +18098,34 @@
     </row>
     <row r="236">
       <c r="A236" s="15" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E236" s="11" t="n">
-        <v>2100</v>
+        <v>154.99</v>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G236" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>eBay API; vendedor nixs-surplus 100.0%; WD Black SN750 2TB NVMe PCIe3.0 M.2 2280 Internal SSD WDBRPG</t>
         </is>
       </c>
       <c r="H236" s="6" t="inlineStr">
@@ -17330,7 +18136,7 @@
     </row>
     <row r="237">
       <c r="A237" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
@@ -17339,16 +18145,16 @@
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E237" s="11" t="n">
-        <v>1800</v>
+        <v>5580</v>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
@@ -17357,7 +18163,7 @@
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
@@ -17368,25 +18174,25 @@
     </row>
     <row r="238">
       <c r="A238" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E238" s="11" t="n">
-        <v>4500</v>
+        <v>2300</v>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
@@ -17395,7 +18201,7 @@
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
@@ -17406,7 +18212,7 @@
     </row>
     <row r="239">
       <c r="A239" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
@@ -17415,16 +18221,16 @@
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
-        <v>6700</v>
+        <v>3950</v>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
@@ -17433,7 +18239,7 @@
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H239" s="6" t="inlineStr">
@@ -17444,25 +18250,25 @@
     </row>
     <row r="240">
       <c r="A240" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E240" s="11" t="n">
-        <v>2520</v>
+        <v>4800</v>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
@@ -17471,7 +18277,7 @@
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H240" s="6" t="inlineStr">
@@ -17482,25 +18288,25 @@
     </row>
     <row r="241">
       <c r="A241" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
-        <v>4290</v>
+        <v>5190</v>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
@@ -17509,7 +18315,7 @@
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H241" s="6" t="inlineStr">
@@ -17520,25 +18326,25 @@
     </row>
     <row r="242">
       <c r="A242" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E242" s="11" t="n">
-        <v>2860</v>
+        <v>5390</v>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
@@ -17547,7 +18353,7 @@
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H242" s="6" t="inlineStr">
@@ -17558,25 +18364,25 @@
     </row>
     <row r="243">
       <c r="A243" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E243" s="11" t="n">
-        <v>2460</v>
+        <v>2000</v>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
@@ -17585,7 +18391,7 @@
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H243" s="6" t="inlineStr">
@@ -17596,25 +18402,25 @@
     </row>
     <row r="244">
       <c r="A244" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E244" s="11" t="n">
-        <v>5360</v>
+        <v>2650</v>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
@@ -17623,7 +18429,7 @@
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H244" s="6" t="inlineStr">
@@ -17634,25 +18440,25 @@
     </row>
     <row r="245">
       <c r="A245" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E245" s="11" t="n">
-        <v>1710</v>
+        <v>2700</v>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
@@ -17661,7 +18467,7 @@
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr">
@@ -17672,25 +18478,25 @@
     </row>
     <row r="246">
       <c r="A246" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E246" s="11" t="n">
-        <v>2310</v>
+        <v>6200</v>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
@@ -17699,7 +18505,7 @@
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H246" s="6" t="inlineStr">
@@ -17710,11 +18516,11 @@
     </row>
     <row r="247">
       <c r="A247" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
@@ -17724,11 +18530,11 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
-        <v>2160</v>
+        <v>540</v>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
@@ -17737,7 +18543,7 @@
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
@@ -17748,25 +18554,25 @@
     </row>
     <row r="248">
       <c r="A248" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E248" s="11" t="n">
-        <v>5360</v>
+        <v>900</v>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
@@ -17775,7 +18581,7 @@
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H248" s="6" t="inlineStr">
@@ -17786,25 +18592,25 @@
     </row>
     <row r="249">
       <c r="A249" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
-        <v>5660</v>
+        <v>1500</v>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
@@ -17813,7 +18619,7 @@
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H249" s="6" t="inlineStr">
@@ -17824,25 +18630,25 @@
     </row>
     <row r="250">
       <c r="A250" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E250" s="11" t="n">
-        <v>5860</v>
+        <v>1500</v>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
@@ -17851,7 +18657,7 @@
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H250" s="6" t="inlineStr">
@@ -17862,11 +18668,11 @@
     </row>
     <row r="251">
       <c r="A251" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
@@ -17876,11 +18682,11 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
-        <v>1860</v>
+        <v>1850</v>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
@@ -17889,7 +18695,7 @@
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H251" s="6" t="inlineStr">
@@ -17900,11 +18706,11 @@
     </row>
     <row r="252">
       <c r="A252" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
@@ -17914,11 +18720,11 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E252" s="11" t="n">
-        <v>2060</v>
+        <v>2000</v>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
@@ -17927,7 +18733,7 @@
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H252" s="6" t="inlineStr">
@@ -17938,11 +18744,11 @@
     </row>
     <row r="253">
       <c r="A253" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
@@ -17952,11 +18758,11 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
-        <v>2152</v>
+        <v>1800</v>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
@@ -17965,7 +18771,7 @@
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H253" s="6" t="inlineStr">
@@ -17976,11 +18782,11 @@
     </row>
     <row r="254">
       <c r="A254" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
@@ -17990,11 +18796,11 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E254" s="11" t="n">
-        <v>4060</v>
+        <v>3550</v>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
@@ -18003,7 +18809,7 @@
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H254" s="6" t="inlineStr">
@@ -18023,16 +18829,16 @@
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E255" s="11" t="n">
-        <v>4560</v>
+        <v>5664</v>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
@@ -18041,7 +18847,7 @@
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H255" s="6" t="inlineStr">
@@ -18061,16 +18867,16 @@
       </c>
       <c r="C256" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E256" s="11" t="n">
-        <v>5500</v>
+        <v>2537</v>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
@@ -18079,7 +18885,7 @@
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H256" s="6" t="inlineStr">
@@ -18099,16 +18905,16 @@
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E257" s="11" t="n">
-        <v>2500</v>
+        <v>3127</v>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
@@ -18117,7 +18923,7 @@
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H257" s="6" t="inlineStr">
@@ -18137,16 +18943,16 @@
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Compucenter (WhatsApp)</t>
         </is>
       </c>
       <c r="E258" s="11" t="n">
-        <v>5200</v>
+        <v>2150</v>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
@@ -18155,7 +18961,7 @@
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
         </is>
       </c>
       <c r="H258" s="6" t="inlineStr">
@@ -18166,7 +18972,7 @@
     </row>
     <row r="259">
       <c r="A259" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
@@ -18175,16 +18981,16 @@
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E259" s="11" t="n">
-        <v>5500</v>
+        <v>6140</v>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
@@ -18193,14 +18999,18 @@
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
-        </is>
-      </c>
-      <c r="H259" s="2" t="n"/>
+          <t>nuevo OEM (garantía 6 meses)</t>
+        </is>
+      </c>
+      <c r="H259" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
@@ -18209,16 +19019,16 @@
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E260" s="11" t="n">
-        <v>2460</v>
+        <v>4760</v>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
@@ -18227,14 +19037,18 @@
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H260" s="2" t="n"/>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H260" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
@@ -18243,16 +19057,16 @@
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E261" s="11" t="n">
-        <v>2500</v>
+        <v>6800</v>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
@@ -18261,14 +19075,18 @@
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H261" s="2" t="n"/>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H261" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
@@ -18277,16 +19095,16 @@
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E262" s="11" t="n">
-        <v>6840</v>
+        <v>2100</v>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
@@ -18295,32 +19113,36 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
-        </is>
-      </c>
-      <c r="H262" s="2" t="n"/>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H262" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
@@ -18329,7 +19151,7 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H263" s="6" t="inlineStr">
@@ -18340,25 +19162,25 @@
     </row>
     <row r="264">
       <c r="A264" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E264" s="11" t="n">
-        <v>5350</v>
+        <v>4500</v>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
@@ -18367,32 +19189,36 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
-        </is>
-      </c>
-      <c r="H264" s="2" t="n"/>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+        </is>
+      </c>
+      <c r="H264" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E265" s="11" t="n">
-        <v>7400</v>
+        <v>6700</v>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
@@ -18401,7 +19227,7 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H265" s="6" t="inlineStr">
@@ -18412,7 +19238,7 @@
     </row>
     <row r="266">
       <c r="A266" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
@@ -18426,11 +19252,11 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (web)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E266" s="11" t="n">
-        <v>2953</v>
+        <v>2520</v>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
@@ -18439,7 +19265,7 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+          <t>disponible (web)</t>
         </is>
       </c>
       <c r="H266" s="6" t="inlineStr">
@@ -18450,7 +19276,7 @@
     </row>
     <row r="267">
       <c r="A267" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
@@ -18459,16 +19285,16 @@
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900K</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Crazy Store (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E267" s="11" t="n">
-        <v>6013</v>
+        <v>4290</v>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
@@ -18477,14 +19303,18 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H267" s="2" t="n"/>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+        </is>
+      </c>
+      <c r="H267" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
@@ -18493,16 +19323,16 @@
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E268" s="11" t="n">
-        <v>5890</v>
+        <v>2860</v>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
@@ -18511,14 +19341,18 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
-        </is>
-      </c>
-      <c r="H268" s="2" t="n"/>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H268" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
@@ -18527,16 +19361,16 @@
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E269" s="11" t="n">
-        <v>3080</v>
+        <v>2460</v>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
@@ -18545,14 +19379,18 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
-        </is>
-      </c>
-      <c r="H269" s="2" t="n"/>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H269" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
@@ -18561,16 +19399,16 @@
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E270" s="11" t="n">
-        <v>3650</v>
+        <v>5360</v>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
@@ -18579,14 +19417,18 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H270" s="2" t="n"/>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H270" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
@@ -18595,16 +19437,16 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>PC Factor (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E271" s="11" t="n">
-        <v>3792</v>
+        <v>1710</v>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
@@ -18613,14 +19455,18 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H271" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H271" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
@@ -18629,16 +19475,16 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E272" s="11" t="n">
-        <v>2800</v>
+        <v>2310</v>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
@@ -18647,14 +19493,18 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="H272" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H272" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
@@ -18663,16 +19513,16 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E273" s="11" t="n">
-        <v>2260</v>
+        <v>2160</v>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
@@ -18681,14 +19531,18 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H273" s="2" t="n"/>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H273" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
@@ -18697,16 +19551,16 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E274" s="11" t="n">
-        <v>2750</v>
+        <v>5360</v>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
@@ -18715,14 +19569,18 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H274" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H274" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
@@ -18731,16 +19589,16 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7700X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E275" s="11" t="n">
-        <v>3480</v>
+        <v>5660</v>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
@@ -18749,14 +19607,18 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>sin confirmar si es sellado (se preguntó)</t>
-        </is>
-      </c>
-      <c r="H275" s="2" t="n"/>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H275" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
@@ -18765,16 +19627,16 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E276" s="11" t="n">
-        <v>2900</v>
+        <v>5860</v>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
@@ -18783,14 +19645,18 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
-        </is>
-      </c>
-      <c r="H276" s="2" t="n"/>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H276" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
@@ -18804,11 +19670,11 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E277" s="11" t="n">
-        <v>1754</v>
+        <v>1860</v>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
@@ -18817,14 +19683,18 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
-        </is>
-      </c>
-      <c r="H277" s="2" t="n"/>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H277" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
@@ -18833,16 +19703,16 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E278" s="11" t="n">
-        <v>2785</v>
+        <v>2060</v>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
@@ -18851,14 +19721,18 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H278" s="2" t="n"/>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H278" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
@@ -18867,16 +19741,16 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E279" s="11" t="n">
-        <v>1778</v>
+        <v>2152</v>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
@@ -18885,14 +19759,18 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H279" s="2" t="n"/>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H279" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
@@ -18901,16 +19779,16 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E280" s="11" t="n">
-        <v>1600</v>
+        <v>4060</v>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
@@ -18919,14 +19797,18 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H280" s="2" t="n"/>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H280" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
@@ -18935,16 +19817,16 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E281" s="11" t="n">
-        <v>2500</v>
+        <v>4560</v>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
@@ -18953,32 +19835,36 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
-        </is>
-      </c>
-      <c r="H281" s="2" t="n"/>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H281" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E282" s="11" t="n">
-        <v>1730</v>
+        <v>5500</v>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
@@ -18987,7 +19873,7 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+          <t>nuevo OEM (solo el chip)</t>
         </is>
       </c>
       <c r="H282" s="6" t="inlineStr">
@@ -18998,7 +19884,7 @@
     </row>
     <row r="283">
       <c r="A283" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
@@ -19007,16 +19893,16 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E283" s="11" t="n">
-        <v>2384</v>
+        <v>2500</v>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
@@ -19025,7 +19911,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H283" s="6" t="inlineStr">
@@ -19036,7 +19922,7 @@
     </row>
     <row r="284">
       <c r="A284" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
@@ -19045,16 +19931,16 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E284" s="11" t="n">
-        <v>5664</v>
+        <v>5200</v>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
@@ -19063,7 +19949,7 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>nuevo BOX (web: USD 480 a 11,80)</t>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H284" s="6" t="inlineStr">
@@ -19074,7 +19960,7 @@
     </row>
     <row r="285">
       <c r="A285" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
@@ -19083,16 +19969,16 @@
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E285" s="11" t="n">
-        <v>2218</v>
+        <v>5500</v>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
@@ -19101,18 +19987,14 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H285" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
@@ -19121,16 +20003,16 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico (WhatsApp)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E286" s="11" t="n">
-        <v>2850</v>
+        <v>2460</v>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
@@ -19139,14 +20021,14 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
+          <t>nuevo OEM</t>
         </is>
       </c>
       <c r="H286" s="2" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
@@ -19155,16 +20037,16 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico (WhatsApp)</t>
+          <t>Soft Computers (WhatsApp)</t>
         </is>
       </c>
       <c r="E287" s="11" t="n">
-        <v>5960</v>
+        <v>2500</v>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
@@ -19173,14 +20055,14 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+          <t>nuevo OEM</t>
         </is>
       </c>
       <c r="H287" s="2" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
@@ -19189,16 +20071,16 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Gamer Store Cbba (WhatsApp)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E288" s="11" t="n">
-        <v>2067</v>
+        <v>6840</v>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
@@ -19207,14 +20089,14 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
         </is>
       </c>
       <c r="H288" s="2" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="15" t="n">
-        <v>46312</v>
+        <v>46308</v>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
@@ -19223,16 +20105,16 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
         </is>
       </c>
       <c r="E289" s="11" t="n">
-        <v>1230</v>
+        <v>4800</v>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
@@ -19241,7 +20123,7 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
         </is>
       </c>
       <c r="H289" s="6" t="inlineStr">
@@ -19252,25 +20134,25 @@
     </row>
     <row r="290">
       <c r="A290" s="15" t="n">
-        <v>46312</v>
+        <v>46308</v>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E290" s="11" t="n">
-        <v>1500</v>
+        <v>5350</v>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
@@ -19279,18 +20161,14 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>sin dato de estado ni marca (recién publicado)</t>
-        </is>
-      </c>
-      <c r="H290" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="15" t="n">
-        <v>46312</v>
+        <v>46309</v>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
@@ -19299,16 +20177,16 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E291" s="11" t="n">
-        <v>1850</v>
+        <v>7400</v>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
@@ -19317,7 +20195,7 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>Kingston NV3 1TB (estado sin dato)</t>
+          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H291" s="6" t="inlineStr">
@@ -19328,37 +20206,953 @@
     </row>
     <row r="292">
       <c r="A292" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B292" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C292" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D292" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (web)</t>
+        </is>
+      </c>
+      <c r="E292" s="11" t="n">
+        <v>2953</v>
+      </c>
+      <c r="F292" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G292" s="5" t="inlineStr">
+        <is>
+          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H292" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="15" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B293" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C293" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i9-14900K</t>
+        </is>
+      </c>
+      <c r="D293" s="5" t="inlineStr">
+        <is>
+          <t>Crazy Store (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E293" s="11" t="n">
+        <v>6013</v>
+      </c>
+      <c r="F293" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G293" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="15" t="n">
         <v>46310</v>
       </c>
-      <c r="B292" s="5" t="inlineStr">
+      <c r="B294" s="5" t="inlineStr">
         <is>
           <t>Tienda</t>
         </is>
       </c>
-      <c r="C292" s="5" t="inlineStr">
+      <c r="C294" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D294" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E294" s="11" t="n">
+        <v>5890</v>
+      </c>
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G294" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B295" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D295" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E295" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="F295" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G295" s="5" t="inlineStr">
+        <is>
+          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B296" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C296" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+        </is>
+      </c>
+      <c r="D296" s="5" t="inlineStr">
+        <is>
+          <t>SMART CUBE (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E296" s="11" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F296" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G296" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B297" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C297" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR5 16GB</t>
+        </is>
+      </c>
+      <c r="D297" s="5" t="inlineStr">
+        <is>
+          <t>PC Factor (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E297" s="11" t="n">
+        <v>3792</v>
+      </c>
+      <c r="F297" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G297" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B298" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C298" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D298" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E298" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F298" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G298" s="5" t="inlineStr">
+        <is>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B299" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C299" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="D299" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E299" s="11" t="n">
+        <v>2260</v>
+      </c>
+      <c r="F299" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G299" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B300" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C300" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D300" s="5" t="inlineStr">
+        <is>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E300" s="11" t="n">
+        <v>2750</v>
+      </c>
+      <c r="F300" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G300" s="5" t="inlineStr">
+        <is>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B301" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C301" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7700X</t>
+        </is>
+      </c>
+      <c r="D301" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E301" s="11" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F301" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G301" s="5" t="inlineStr">
+        <is>
+          <t>sin confirmar si es sellado (se preguntó)</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B302" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C302" s="5" t="inlineStr">
+        <is>
+          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+        </is>
+      </c>
+      <c r="D302" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E302" s="11" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F302" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G302" s="5" t="inlineStr">
+        <is>
+          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C303" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D303" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E303" s="11" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G303" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
+        </is>
+      </c>
+      <c r="H303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B304" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C304" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D304" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E304" s="11" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F304" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G304" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H304" s="2" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B305" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C305" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D305" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E305" s="11" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F305" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G305" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H305" s="2" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B306" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C306" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D306" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E306" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F306" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G306" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B307" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C307" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D307" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E307" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F307" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G307" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
+        </is>
+      </c>
+      <c r="H307" s="2" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B308" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C308" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D308" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E308" s="11" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F308" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G308" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+        </is>
+      </c>
+      <c r="H308" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B309" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C309" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D309" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E309" s="11" t="n">
+        <v>2384</v>
+      </c>
+      <c r="F309" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G309" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+        </is>
+      </c>
+      <c r="H309" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B310" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C310" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D310" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E310" s="11" t="n">
+        <v>5664</v>
+      </c>
+      <c r="F310" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G310" s="5" t="inlineStr">
+        <is>
+          <t>nuevo BOX (web: USD 480 a 11,80)</t>
+        </is>
+      </c>
+      <c r="H310" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B311" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C311" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D311" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E311" s="11" t="n">
+        <v>2218</v>
+      </c>
+      <c r="F311" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G311" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H311" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B312" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D312" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E312" s="11" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F312" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G312" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B313" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C313" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D313" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E313" s="11" t="n">
+        <v>5960</v>
+      </c>
+      <c r="F313" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G313" s="5" t="inlineStr">
+        <is>
+          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B314" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C314" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D314" s="5" t="inlineStr">
+        <is>
+          <t>Gamer Store Cbba (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E314" s="11" t="n">
+        <v>2067</v>
+      </c>
+      <c r="F314" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G314" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B315" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C315" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D315" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E315" s="11" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F315" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G315" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
+        </is>
+      </c>
+      <c r="H315" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B316" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C316" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D316" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E316" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F316" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G316" s="5" t="inlineStr">
+        <is>
+          <t>sin dato de estado ni marca (recién publicado)</t>
+        </is>
+      </c>
+      <c r="H316" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B317" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C317" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D317" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E317" s="11" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F317" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G317" s="5" t="inlineStr">
+        <is>
+          <t>Kingston NV3 1TB (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H317" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B318" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C318" s="5" t="inlineStr">
         <is>
           <t>SSD NVMe 2TB</t>
         </is>
       </c>
-      <c r="D292" s="5" t="inlineStr">
+      <c r="D318" s="5" t="inlineStr">
         <is>
           <t>Shopping PC (catálogo PDF)</t>
         </is>
       </c>
-      <c r="E292" s="11" t="n">
+      <c r="E318" s="11" t="n">
         <v>2726</v>
       </c>
-      <c r="F292" s="5" t="inlineStr">
+      <c r="F318" s="5" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
       </c>
-      <c r="G292" s="5" t="inlineStr">
+      <c r="G318" s="5" t="inlineStr">
         <is>
           <t>no cuenta: otro modelo (Crucial BX500 2TB es SATA, no NVMe; nuevo; lista mayorista USD 230 × 11,85 del 12/10, sin factura; 35 en stock; garantía solo de prueba; solo referencia)</t>
         </is>
       </c>
-      <c r="H292" s="2" t="n"/>
+      <c r="H318" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -19619,20 +21413,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId255"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId293"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId268"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId294"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H318" headerRowCount="1">
-  <autoFilter ref="A1:H318"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H324" headerRowCount="1">
+  <autoFilter ref="A1:H324"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -785,12 +785,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>209.99</v>
+        <v>140.26</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>154.99</v>
+        <v>120</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
-        <v>4060</v>
+        <v>2800</v>
       </c>
       <c r="I5" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="K5" s="8" t="n">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="L5" s="11">
         <f>IF(D5="","",MIN(MAX(Supuestos!$B$5,CEILING((K5*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D5*Supuestos!$B$9))</f>
@@ -850,12 +850,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -864,17 +864,17 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>230</v>
+        <v>209.99</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>239.99</v>
+        <v>154.99</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
-        <v>3950</v>
+        <v>4060</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -885,7 +885,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -915,7 +915,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -929,19 +929,17 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>324.99</v>
+        <v>230</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>285</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>4800</v>
-      </c>
+        <v>239.99</v>
+      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="8" t="n">
-        <v>4760</v>
+        <v>3950</v>
       </c>
       <c r="I7" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -952,7 +950,7 @@
         <v/>
       </c>
       <c r="K7" s="8" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="L7" s="11">
         <f>IF(D7="","",MIN(MAX(Supuestos!$B$5,CEILING((K7*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D7*Supuestos!$B$9))</f>
@@ -982,7 +980,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -996,17 +994,19 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>150</v>
+        <v>324.99</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="G8" s="2" t="n"/>
+        <v>285</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="H8" s="8" t="n">
-        <v>2260</v>
+        <v>4760</v>
       </c>
       <c r="I8" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1017,7 +1017,7 @@
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="L8" s="11">
         <f>IF(D8="","",MIN(MAX(Supuestos!$B$5,CEILING((K8*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D8*Supuestos!$B$9))</f>
@@ -1047,12 +1047,12 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -1061,18 +1061,18 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>419.99</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H9" s="2" t="n"/>
+        <v>124.99</v>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1082,7 +1082,7 @@
         <v/>
       </c>
       <c r="K9" s="8" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="L9" s="11">
         <f>IF(D9="","",MIN(MAX(Supuestos!$B$5,CEILING((K9*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D9*Supuestos!$B$9))</f>
@@ -1177,12 +1177,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1191,18 +1191,18 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>213.95</v>
+        <v>450</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="8" t="n">
-        <v>2800</v>
-      </c>
+        <v>419.99</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="L11" s="11">
         <f>IF(D11="","",MIN(MAX(Supuestos!$B$5,CEILING((K11*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D11*Supuestos!$B$9))</f>
@@ -1945,7 +1945,9 @@
       <c r="E3" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="F3" s="2" t="n"/>
+      <c r="F3" s="8" t="n">
+        <v>2050</v>
+      </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
@@ -2158,7 +2160,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>213.95</v>
+        <v>140.26</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>120</v>
@@ -2546,7 +2548,9 @@
       <c r="E14" s="7" t="n">
         <v>419.99</v>
       </c>
-      <c r="F14" s="2" t="n"/>
+      <c r="F14" s="8" t="n">
+        <v>5800</v>
+      </c>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A14,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A14,Dólar!$A:$A,0))),"")</f>
@@ -9149,7 +9153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H318"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17204,7 +17208,7 @@
         </is>
       </c>
       <c r="E212" s="11" t="n">
-        <v>213.95</v>
+        <v>140.26</v>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
@@ -17213,7 +17217,7 @@
       </c>
       <c r="G212" s="5" t="inlineStr">
         <is>
-          <t>eBay API; vendedor bra_dewaa 99.8%; AMD Ryzen 5 7600 6-Core 12-Thread Unlocked Desktop Processor</t>
+          <t>eBay Chrome 19/10 10:40: anuncio activo de Silaxon_Electronics 99.6% (20.397 valoraciones), Nuevo, envío gratis, ubicado en NJ, verificado en la página y en búsqueda; la API traía 213.95 (bra_dewaa 99.8%) y el 140.26 apareció después (anuncio nuevo)</t>
         </is>
       </c>
       <c r="H212" s="6" t="inlineStr">
@@ -21153,6 +21157,234 @@
         </is>
       </c>
       <c r="H318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B319" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C319" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D319" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E319" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F319" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G319" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otro modelo (es 5600X, solo procesador, recién publicado)</t>
+        </is>
+      </c>
+      <c r="H319" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B320" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C320" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D320" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E320" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F320" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G320" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otro modelo (i5-13400F, precio fijo)</t>
+        </is>
+      </c>
+      <c r="H320" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B321" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C321" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D321" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E321" s="11" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F321" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G321" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otro modelo (i5-14400 sin F)</t>
+        </is>
+      </c>
+      <c r="H321" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B322" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C322" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D322" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E322" s="11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F322" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G322" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB 2x16 6000 MHz (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H322" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B323" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C323" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D323" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E323" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F323" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G323" s="5" t="inlineStr">
+        <is>
+          <t>Lexar NM790 1TB con disipador (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H323" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B324" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C324" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D324" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E324" s="11" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F324" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G324" s="5" t="inlineStr">
+        <is>
+          <t>WD Green SN3000 1TB (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H324" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21449,10 +21681,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId291"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId292"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId299"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId294"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId300"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H324" headerRowCount="1">
-  <autoFilter ref="A1:H324"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H326" headerRowCount="1">
+  <autoFilter ref="A1:H326"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -2166,7 +2166,9 @@
         <v>120</v>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
+      <c r="G7" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H7" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2494,7 +2496,9 @@
         <v>239.99</v>
       </c>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
+      <c r="G13" s="8" t="n">
+        <v>4100</v>
+      </c>
       <c r="H13" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A13,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A13,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -9153,7 +9157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21385,6 +21389,74 @@
           <t>ver</t>
         </is>
       </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C325" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D325" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E325" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G325" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (reconfirmado 16:09)</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B326" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D326" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E326" s="11" t="n">
+        <v>4100</v>
+      </c>
+      <c r="F326" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G326" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O123" headerRowCount="1">
-  <autoFilter ref="A1:O123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O137" headerRowCount="1">
+  <autoFilter ref="A1:O137"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H326" headerRowCount="1">
-  <autoFilter ref="A1:H326"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H351" headerRowCount="1">
+  <autoFilter ref="A1:H351"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -633,7 +633,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>¿Qué conviene traer? · 19/10/2026</t>
+          <t>¿Qué conviene traer? · 20/10/2026</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -785,12 +785,12 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -799,17 +799,17 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>140.26</v>
+        <v>163.11</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>120</v>
+        <v>184.99</v>
       </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="8" t="n">
-        <v>2800</v>
+        <v>4060</v>
       </c>
       <c r="I5" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -820,7 +820,7 @@
         <v/>
       </c>
       <c r="K5" s="8" t="n">
-        <v>350</v>
+        <v>80</v>
       </c>
       <c r="L5" s="11">
         <f>IF(D5="","",MIN(MAX(Supuestos!$B$5,CEILING((K5*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D5*Supuestos!$B$9))</f>
@@ -850,12 +850,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -864,17 +864,17 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>209.99</v>
+        <v>244.88</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>154.99</v>
+        <v>239.99</v>
       </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="8" t="n">
-        <v>4060</v>
+        <v>3950</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -885,7 +885,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -915,7 +915,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -929,17 +929,19 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>230</v>
+        <v>324.99</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>239.99</v>
-      </c>
-      <c r="G7" s="2" t="n"/>
+        <v>289.99</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="H7" s="8" t="n">
-        <v>3950</v>
+        <v>4760</v>
       </c>
       <c r="I7" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -950,7 +952,7 @@
         <v/>
       </c>
       <c r="K7" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L7" s="11">
         <f>IF(D7="","",MIN(MAX(Supuestos!$B$5,CEILING((K7*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D7*Supuestos!$B$9))</f>
@@ -980,7 +982,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -994,19 +996,17 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>324.99</v>
+        <v>150</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>285</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>4800</v>
-      </c>
+        <v>124.99</v>
+      </c>
+      <c r="G8" s="2" t="n"/>
       <c r="H8" s="8" t="n">
-        <v>4760</v>
+        <v>2260</v>
       </c>
       <c r="I8" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1017,7 +1017,7 @@
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="L8" s="11">
         <f>IF(D8="","",MIN(MAX(Supuestos!$B$5,CEILING((K8*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D8*Supuestos!$B$9))</f>
@@ -1047,7 +1047,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1061,17 +1061,17 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>150</v>
+        <v>164.49</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>124.99</v>
+        <v>134.99</v>
       </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="8" t="n">
-        <v>2260</v>
+        <v>2384</v>
       </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1112,12 +1112,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1126,18 +1126,18 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>164.49</v>
+        <v>444.99</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>139.99</v>
-      </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="8" t="n">
-        <v>2384</v>
-      </c>
+        <v>399.99</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="H10" s="2" t="n"/>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1147,7 +1147,7 @@
         <v/>
       </c>
       <c r="K10" s="8" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="L10" s="11">
         <f>IF(D10="","",MIN(MAX(Supuestos!$B$5,CEILING((K10*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D10*Supuestos!$B$9))</f>
@@ -1177,12 +1177,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1191,18 +1191,18 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>450</v>
+        <v>213.95</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>419.99</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="H11" s="2" t="n"/>
+        <v>120</v>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1212,7 +1212,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L11" s="11">
         <f>IF(D11="","",MIN(MAX(Supuestos!$B$5,CEILING((K11*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D11*Supuestos!$B$9))</f>
@@ -1242,12 +1242,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1256,18 +1256,18 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>429.97</v>
+        <v>549.99</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>379.99</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H12" s="2" t="n"/>
+        <v>454.99</v>
+      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="8" t="n">
+        <v>5580</v>
+      </c>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1277,7 +1277,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="n">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="L12" s="11">
         <f>IF(D12="","",MIN(MAX(Supuestos!$B$5,CEILING((K12*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D12*Supuestos!$B$9))</f>
@@ -1307,12 +1307,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1321,17 +1321,19 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>549.99</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="G13" s="2" t="n"/>
+        <v>69.95</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>900</v>
+      </c>
       <c r="H13" s="8" t="n">
-        <v>5580</v>
+        <v>2150</v>
       </c>
       <c r="I13" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1342,7 +1344,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>350</v>
+        <v>120</v>
       </c>
       <c r="L13" s="11">
         <f>IF(D13="","",MIN(MAX(Supuestos!$B$5,CEILING((K13*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D13*Supuestos!$B$9))</f>
@@ -1386,13 +1388,13 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>109.99</v>
+        <v>114.99</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>7.95</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>1230</v>
@@ -1439,12 +1441,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1453,18 +1455,18 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>259.78</v>
+        <v>479.99</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>149.99</v>
-      </c>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="8" t="n">
-        <v>2300</v>
-      </c>
+        <v>379.99</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1474,7 +1476,7 @@
         <v/>
       </c>
       <c r="K15" s="8" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L15" s="11">
         <f>IF(D15="","",MIN(MAX(Supuestos!$B$5,CEILING((K15*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D15*Supuestos!$B$9))</f>
@@ -1504,12 +1506,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1518,19 +1520,17 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>108.97</v>
+        <v>259.78</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>9.99</v>
+        <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>69.98999999999999</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>900</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="G16" s="2" t="n"/>
       <c r="H16" s="8" t="n">
-        <v>2150</v>
+        <v>2300</v>
       </c>
       <c r="I16" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1541,7 +1541,7 @@
         <v/>
       </c>
       <c r="K16" s="8" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="L16" s="11">
         <f>IF(D16="","",MIN(MAX(Supuestos!$B$5,CEILING((K16*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D16*Supuestos!$B$9))</f>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>107.99</v>
+        <v>129.99</v>
       </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="2" t="n"/>
@@ -1773,7 +1773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>209.99</v>
+        <v>163.11</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>154.99</v>
+        <v>184.99</v>
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="K2" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L2" s="16">
         <f>IF(OR($K2="",D2=""),"",IF(COUNTIFS($B:$B,$B2,$A:$A,$K2,D:D,"&gt;=0")=0,"",D2-SUMIFS(D:D,$B:$B,$B2,$A:$A,$K2)))</f>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
@@ -1940,14 +1940,12 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>117.94</v>
+        <v>114.99</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="F3" s="8" t="n">
-        <v>2050</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A3,Dólar!$A:$A,0))),"")</f>
@@ -1963,7 +1961,7 @@
         </is>
       </c>
       <c r="K3" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L3" s="16">
         <f>IF(OR($K3="",D3=""),"",IF(COUNTIFS($B:$B,$B3,$A:$A,$K3,D:D,"&gt;=0")=0,"",D3-SUMIFS(D:D,$B:$B,$B3,$A:$A,$K3)))</f>
@@ -1984,7 +1982,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -2018,7 +2016,7 @@
         </is>
       </c>
       <c r="K4" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L4" s="16">
         <f>IF(OR($K4="",D4=""),"",IF(COUNTIFS($B:$B,$B4,$A:$A,$K4,D:D,"&gt;=0")=0,"",D4-SUMIFS(D:D,$B:$B,$B4,$A:$A,$K4)))</f>
@@ -2039,7 +2037,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
@@ -2055,7 +2053,7 @@
         <v>324.99</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>285</v>
+        <v>289.99</v>
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
@@ -2073,7 +2071,7 @@
         </is>
       </c>
       <c r="K5" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L5" s="16">
         <f>IF(OR($K5="",D5=""),"",IF(COUNTIFS($B:$B,$B5,$A:$A,$K5,D:D,"&gt;=0")=0,"",D5-SUMIFS(D:D,$B:$B,$B5,$A:$A,$K5)))</f>
@@ -2094,7 +2092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -2126,7 +2124,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
@@ -2147,7 +2145,7 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -2160,15 +2158,13 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>140.26</v>
+        <v>213.95</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F7" s="2" t="n"/>
-      <c r="G7" s="8" t="n">
-        <v>2800</v>
-      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A7,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2183,7 +2179,7 @@
         </is>
       </c>
       <c r="K7" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L7" s="16">
         <f>IF(OR($K7="",D7=""),"",IF(COUNTIFS($B:$B,$B7,$A:$A,$K7,D:D,"&gt;=0")=0,"",D7-SUMIFS(D:D,$B:$B,$B7,$A:$A,$K7)))</f>
@@ -2204,7 +2200,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -2220,7 +2216,7 @@
         <v>138.9</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>107.99</v>
+        <v>129.99</v>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
@@ -2238,7 +2234,7 @@
         </is>
       </c>
       <c r="K8" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L8" s="16">
         <f>IF(OR($K8="",D8=""),"",IF(COUNTIFS($B:$B,$B8,$A:$A,$K8,D:D,"&gt;=0")=0,"",D8-SUMIFS(D:D,$B:$B,$B8,$A:$A,$K8)))</f>
@@ -2259,7 +2255,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -2272,10 +2268,10 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>118.96</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>69.98999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
@@ -2293,7 +2289,7 @@
         </is>
       </c>
       <c r="K9" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L9" s="16">
         <f>IF(OR($K9="",D9=""),"",IF(COUNTIFS($B:$B,$B9,$A:$A,$K9,D:D,"&gt;=0")=0,"",D9-SUMIFS(D:D,$B:$B,$B9,$A:$A,$K9)))</f>
@@ -2314,7 +2310,7 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -2330,7 +2326,7 @@
         <v>164.49</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>139.99</v>
+        <v>134.99</v>
       </c>
       <c r="F10" s="2" t="n"/>
       <c r="G10" s="2" t="n"/>
@@ -2348,7 +2344,7 @@
         </is>
       </c>
       <c r="K10" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L10" s="16">
         <f>IF(OR($K10="",D10=""),"",IF(COUNTIFS($B:$B,$B10,$A:$A,$K10,D:D,"&gt;=0")=0,"",D10-SUMIFS(D:D,$B:$B,$B10,$A:$A,$K10)))</f>
@@ -2369,7 +2365,7 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -2383,7 +2379,7 @@
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="7" t="n">
-        <v>149.99</v>
+        <v>150</v>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
@@ -2401,7 +2397,7 @@
         </is>
       </c>
       <c r="K11" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L11" s="16">
         <f>IF(OR($K11="",D11=""),"",IF(COUNTIFS($B:$B,$B11,$A:$A,$K11,D:D,"&gt;=0")=0,"",D11-SUMIFS(D:D,$B:$B,$B11,$A:$A,$K11)))</f>
@@ -2422,7 +2418,7 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -2456,7 +2452,7 @@
         </is>
       </c>
       <c r="K12" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L12" s="16">
         <f>IF(OR($K12="",D12=""),"",IF(COUNTIFS($B:$B,$B12,$A:$A,$K12,D:D,"&gt;=0")=0,"",D12-SUMIFS(D:D,$B:$B,$B12,$A:$A,$K12)))</f>
@@ -2477,7 +2473,7 @@
     </row>
     <row r="13">
       <c r="A13" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -2490,15 +2486,11 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>235.27</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>239.99</v>
-      </c>
+        <v>244.88</v>
+      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
-      <c r="G13" s="8" t="n">
-        <v>4100</v>
-      </c>
+      <c r="G13" s="2" t="n"/>
       <c r="H13" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A13,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A13,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2513,7 +2505,7 @@
         </is>
       </c>
       <c r="K13" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L13" s="16">
         <f>IF(OR($K13="",D13=""),"",IF(COUNTIFS($B:$B,$B13,$A:$A,$K13,D:D,"&gt;=0")=0,"",D13-SUMIFS(D:D,$B:$B,$B13,$A:$A,$K13)))</f>
@@ -2534,7 +2526,7 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -2547,14 +2539,12 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>450</v>
+        <v>444.99</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>419.99</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>5800</v>
-      </c>
+        <v>399.99</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A14,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A14,Dólar!$A:$A,0))),"")</f>
@@ -2570,7 +2560,7 @@
         </is>
       </c>
       <c r="K14" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L14" s="16">
         <f>IF(OR($K14="",D14=""),"",IF(COUNTIFS($B:$B,$B14,$A:$A,$K14,D:D,"&gt;=0")=0,"",D14-SUMIFS(D:D,$B:$B,$B14,$A:$A,$K14)))</f>
@@ -2591,7 +2581,7 @@
     </row>
     <row r="15">
       <c r="A15" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -2604,7 +2594,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>429.97</v>
+        <v>479.99</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>379.99</v>
@@ -2625,7 +2615,7 @@
         </is>
       </c>
       <c r="K15" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L15" s="16">
         <f>IF(OR($K15="",D15=""),"",IF(COUNTIFS($B:$B,$B15,$A:$A,$K15,D:D,"&gt;=0")=0,"",D15-SUMIFS(D:D,$B:$B,$B15,$A:$A,$K15)))</f>
@@ -2646,7 +2636,7 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -2662,7 +2652,7 @@
         <v>209.99</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>160</v>
+        <v>154.99</v>
       </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
@@ -2680,7 +2670,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2701,7 +2691,7 @@
     </row>
     <row r="17">
       <c r="A17" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -2714,12 +2704,14 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>93.5</v>
+        <v>117.94</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>96.94</v>
-      </c>
-      <c r="F17" s="2" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>2050</v>
+      </c>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))),"")</f>
@@ -2735,7 +2727,7 @@
         </is>
       </c>
       <c r="K17" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L17" s="16">
         <f>IF(OR($K17="",D17=""),"",IF(COUNTIFS($B:$B,$B17,$A:$A,$K17,D:D,"&gt;=0")=0,"",D17-SUMIFS(D:D,$B:$B,$B17,$A:$A,$K17)))</f>
@@ -2756,7 +2748,7 @@
     </row>
     <row r="18">
       <c r="A18" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -2790,7 +2782,7 @@
         </is>
       </c>
       <c r="K18" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L18" s="16">
         <f>IF(OR($K18="",D18=""),"",IF(COUNTIFS($B:$B,$B18,$A:$A,$K18,D:D,"&gt;=0")=0,"",D18-SUMIFS(D:D,$B:$B,$B18,$A:$A,$K18)))</f>
@@ -2811,7 +2803,7 @@
     </row>
     <row r="19">
       <c r="A19" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2827,7 +2819,7 @@
         <v>324.99</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>289.99</v>
+        <v>285</v>
       </c>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
@@ -2845,7 +2837,7 @@
         </is>
       </c>
       <c r="K19" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L19" s="16">
         <f>IF(OR($K19="",D19=""),"",IF(COUNTIFS($B:$B,$B19,$A:$A,$K19,D:D,"&gt;=0")=0,"",D19-SUMIFS(D:D,$B:$B,$B19,$A:$A,$K19)))</f>
@@ -2866,7 +2858,7 @@
     </row>
     <row r="20">
       <c r="A20" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -2880,7 +2872,7 @@
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" s="7" t="n">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -2898,7 +2890,7 @@
         </is>
       </c>
       <c r="K20" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L20" s="16">
         <f>IF(OR($K20="",D20=""),"",IF(COUNTIFS($B:$B,$B20,$A:$A,$K20,D:D,"&gt;=0")=0,"",D20-SUMIFS(D:D,$B:$B,$B20,$A:$A,$K20)))</f>
@@ -2919,7 +2911,7 @@
     </row>
     <row r="21">
       <c r="A21" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -2932,13 +2924,15 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>213.95</v>
+        <v>140.26</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
+      <c r="G21" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H21" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2953,7 +2947,7 @@
         </is>
       </c>
       <c r="K21" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L21" s="16">
         <f>IF(OR($K21="",D21=""),"",IF(COUNTIFS($B:$B,$B21,$A:$A,$K21,D:D,"&gt;=0")=0,"",D21-SUMIFS(D:D,$B:$B,$B21,$A:$A,$K21)))</f>
@@ -2974,7 +2968,7 @@
     </row>
     <row r="22">
       <c r="A22" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -2990,7 +2984,7 @@
         <v>138.9</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>129.99</v>
+        <v>107.99</v>
       </c>
       <c r="F22" s="2" t="n"/>
       <c r="G22" s="2" t="n"/>
@@ -3008,7 +3002,7 @@
         </is>
       </c>
       <c r="K22" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L22" s="16">
         <f>IF(OR($K22="",D22=""),"",IF(COUNTIFS($B:$B,$B22,$A:$A,$K22,D:D,"&gt;=0")=0,"",D22-SUMIFS(D:D,$B:$B,$B22,$A:$A,$K22)))</f>
@@ -3029,7 +3023,7 @@
     </row>
     <row r="23">
       <c r="A23" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -3045,7 +3039,7 @@
         <v>118.96</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>72.95</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -3063,7 +3057,7 @@
         </is>
       </c>
       <c r="K23" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L23" s="16">
         <f>IF(OR($K23="",D23=""),"",IF(COUNTIFS($B:$B,$B23,$A:$A,$K23,D:D,"&gt;=0")=0,"",D23-SUMIFS(D:D,$B:$B,$B23,$A:$A,$K23)))</f>
@@ -3084,7 +3078,7 @@
     </row>
     <row r="24">
       <c r="A24" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -3118,7 +3112,7 @@
         </is>
       </c>
       <c r="K24" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L24" s="16">
         <f>IF(OR($K24="",D24=""),"",IF(COUNTIFS($B:$B,$B24,$A:$A,$K24,D:D,"&gt;=0")=0,"",D24-SUMIFS(D:D,$B:$B,$B24,$A:$A,$K24)))</f>
@@ -3139,7 +3133,7 @@
     </row>
     <row r="25">
       <c r="A25" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -3153,7 +3147,7 @@
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="7" t="n">
-        <v>125</v>
+        <v>149.99</v>
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
@@ -3171,7 +3165,7 @@
         </is>
       </c>
       <c r="K25" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L25" s="16">
         <f>IF(OR($K25="",D25=""),"",IF(COUNTIFS($B:$B,$B25,$A:$A,$K25,D:D,"&gt;=0")=0,"",D25-SUMIFS(D:D,$B:$B,$B25,$A:$A,$K25)))</f>
@@ -3192,7 +3186,7 @@
     </row>
     <row r="26">
       <c r="A26" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -3226,7 +3220,7 @@
         </is>
       </c>
       <c r="K26" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L26" s="16">
         <f>IF(OR($K26="",D26=""),"",IF(COUNTIFS($B:$B,$B26,$A:$A,$K26,D:D,"&gt;=0")=0,"",D26-SUMIFS(D:D,$B:$B,$B26,$A:$A,$K26)))</f>
@@ -3247,7 +3241,7 @@
     </row>
     <row r="27">
       <c r="A27" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -3263,10 +3257,12 @@
         <v>235.27</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>209.68</v>
+        <v>239.99</v>
       </c>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
+      <c r="G27" s="8" t="n">
+        <v>4100</v>
+      </c>
       <c r="H27" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A27,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A27,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3281,7 +3277,7 @@
         </is>
       </c>
       <c r="K27" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L27" s="16">
         <f>IF(OR($K27="",D27=""),"",IF(COUNTIFS($B:$B,$B27,$A:$A,$K27,D:D,"&gt;=0")=0,"",D27-SUMIFS(D:D,$B:$B,$B27,$A:$A,$K27)))</f>
@@ -3302,7 +3298,7 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -3320,7 +3316,9 @@
       <c r="E28" s="7" t="n">
         <v>419.99</v>
       </c>
-      <c r="F28" s="2" t="n"/>
+      <c r="F28" s="8" t="n">
+        <v>5800</v>
+      </c>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A28,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A28,Dólar!$A:$A,0))),"")</f>
@@ -3336,7 +3334,7 @@
         </is>
       </c>
       <c r="K28" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L28" s="16">
         <f>IF(OR($K28="",D28=""),"",IF(COUNTIFS($B:$B,$B28,$A:$A,$K28,D:D,"&gt;=0")=0,"",D28-SUMIFS(D:D,$B:$B,$B28,$A:$A,$K28)))</f>
@@ -3357,7 +3355,7 @@
     </row>
     <row r="29">
       <c r="A29" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -3391,7 +3389,7 @@
         </is>
       </c>
       <c r="K29" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L29" s="16">
         <f>IF(OR($K29="",D29=""),"",IF(COUNTIFS($B:$B,$B29,$A:$A,$K29,D:D,"&gt;=0")=0,"",D29-SUMIFS(D:D,$B:$B,$B29,$A:$A,$K29)))</f>
@@ -3412,7 +3410,7 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -3446,7 +3444,7 @@
         </is>
       </c>
       <c r="K30" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L30" s="16">
         <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
@@ -3467,7 +3465,7 @@
     </row>
     <row r="31">
       <c r="A31" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -3480,14 +3478,12 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>128.99</v>
+        <v>93.5</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>98.59</v>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>1230</v>
-      </c>
+        <v>96.94</v>
+      </c>
+      <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A31,Dólar!$A:$A,0))),"")</f>
@@ -3503,7 +3499,7 @@
         </is>
       </c>
       <c r="K31" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L31" s="16">
         <f>IF(OR($K31="",D31=""),"",IF(COUNTIFS($B:$B,$B31,$A:$A,$K31,D:D,"&gt;=0")=0,"",D31-SUMIFS(D:D,$B:$B,$B31,$A:$A,$K31)))</f>
@@ -3524,7 +3520,7 @@
     </row>
     <row r="32">
       <c r="A32" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -3558,7 +3554,7 @@
         </is>
       </c>
       <c r="K32" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L32" s="16">
         <f>IF(OR($K32="",D32=""),"",IF(COUNTIFS($B:$B,$B32,$A:$A,$K32,D:D,"&gt;=0")=0,"",D32-SUMIFS(D:D,$B:$B,$B32,$A:$A,$K32)))</f>
@@ -3579,7 +3575,7 @@
     </row>
     <row r="33">
       <c r="A33" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -3595,7 +3591,7 @@
         <v>324.99</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>275</v>
+        <v>289.99</v>
       </c>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
@@ -3613,7 +3609,7 @@
         </is>
       </c>
       <c r="K33" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L33" s="16">
         <f>IF(OR($K33="",D33=""),"",IF(COUNTIFS($B:$B,$B33,$A:$A,$K33,D:D,"&gt;=0")=0,"",D33-SUMIFS(D:D,$B:$B,$B33,$A:$A,$K33)))</f>
@@ -3634,7 +3630,7 @@
     </row>
     <row r="34">
       <c r="A34" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
@@ -3666,7 +3662,7 @@
         </is>
       </c>
       <c r="K34" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L34" s="16">
         <f>IF(OR($K34="",D34=""),"",IF(COUNTIFS($B:$B,$B34,$A:$A,$K34,D:D,"&gt;=0")=0,"",D34-SUMIFS(D:D,$B:$B,$B34,$A:$A,$K34)))</f>
@@ -3687,7 +3683,7 @@
     </row>
     <row r="35">
       <c r="A35" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -3700,7 +3696,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>140.26</v>
+        <v>213.95</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>120</v>
@@ -3721,7 +3717,7 @@
         </is>
       </c>
       <c r="K35" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L35" s="16">
         <f>IF(OR($K35="",D35=""),"",IF(COUNTIFS($B:$B,$B35,$A:$A,$K35,D:D,"&gt;=0")=0,"",D35-SUMIFS(D:D,$B:$B,$B35,$A:$A,$K35)))</f>
@@ -3742,7 +3738,7 @@
     </row>
     <row r="36">
       <c r="A36" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
@@ -3776,7 +3772,7 @@
         </is>
       </c>
       <c r="K36" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L36" s="16">
         <f>IF(OR($K36="",D36=""),"",IF(COUNTIFS($B:$B,$B36,$A:$A,$K36,D:D,"&gt;=0")=0,"",D36-SUMIFS(D:D,$B:$B,$B36,$A:$A,$K36)))</f>
@@ -3797,7 +3793,7 @@
     </row>
     <row r="37">
       <c r="A37" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
@@ -3813,7 +3809,7 @@
         <v>118.96</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>71.95</v>
+        <v>72.95</v>
       </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
@@ -3831,7 +3827,7 @@
         </is>
       </c>
       <c r="K37" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L37" s="16">
         <f>IF(OR($K37="",D37=""),"",IF(COUNTIFS($B:$B,$B37,$A:$A,$K37,D:D,"&gt;=0")=0,"",D37-SUMIFS(D:D,$B:$B,$B37,$A:$A,$K37)))</f>
@@ -3852,7 +3848,7 @@
     </row>
     <row r="38">
       <c r="A38" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
@@ -3886,7 +3882,7 @@
         </is>
       </c>
       <c r="K38" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L38" s="16">
         <f>IF(OR($K38="",D38=""),"",IF(COUNTIFS($B:$B,$B38,$A:$A,$K38,D:D,"&gt;=0")=0,"",D38-SUMIFS(D:D,$B:$B,$B38,$A:$A,$K38)))</f>
@@ -3907,7 +3903,7 @@
     </row>
     <row r="39">
       <c r="A39" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -3939,7 +3935,7 @@
         </is>
       </c>
       <c r="K39" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L39" s="16">
         <f>IF(OR($K39="",D39=""),"",IF(COUNTIFS($B:$B,$B39,$A:$A,$K39,D:D,"&gt;=0")=0,"",D39-SUMIFS(D:D,$B:$B,$B39,$A:$A,$K39)))</f>
@@ -3960,7 +3956,7 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
@@ -3976,7 +3972,7 @@
         <v>150</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>120.99</v>
+        <v>124.99</v>
       </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
@@ -3994,7 +3990,7 @@
         </is>
       </c>
       <c r="K40" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L40" s="16">
         <f>IF(OR($K40="",D40=""),"",IF(COUNTIFS($B:$B,$B40,$A:$A,$K40,D:D,"&gt;=0")=0,"",D40-SUMIFS(D:D,$B:$B,$B40,$A:$A,$K40)))</f>
@@ -4015,7 +4011,7 @@
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -4031,7 +4027,7 @@
         <v>235.27</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>229</v>
+        <v>209.68</v>
       </c>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
@@ -4049,7 +4045,7 @@
         </is>
       </c>
       <c r="K41" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L41" s="16">
         <f>IF(OR($K41="",D41=""),"",IF(COUNTIFS($B:$B,$B41,$A:$A,$K41,D:D,"&gt;=0")=0,"",D41-SUMIFS(D:D,$B:$B,$B41,$A:$A,$K41)))</f>
@@ -4070,7 +4066,7 @@
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
@@ -4083,10 +4079,10 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>474.49</v>
+        <v>450</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>399.99</v>
+        <v>419.99</v>
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
@@ -4104,7 +4100,7 @@
         </is>
       </c>
       <c r="K42" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L42" s="16">
         <f>IF(OR($K42="",D42=""),"",IF(COUNTIFS($B:$B,$B42,$A:$A,$K42,D:D,"&gt;=0")=0,"",D42-SUMIFS(D:D,$B:$B,$B42,$A:$A,$K42)))</f>
@@ -4125,7 +4121,7 @@
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
@@ -4141,7 +4137,7 @@
         <v>429.97</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
@@ -4159,7 +4155,7 @@
         </is>
       </c>
       <c r="K43" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L43" s="16">
         <f>IF(OR($K43="",D43=""),"",IF(COUNTIFS($B:$B,$B43,$A:$A,$K43,D:D,"&gt;=0")=0,"",D43-SUMIFS(D:D,$B:$B,$B43,$A:$A,$K43)))</f>
@@ -4180,7 +4176,7 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
@@ -4196,7 +4192,7 @@
         <v>209.99</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>161.99</v>
+        <v>160</v>
       </c>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
@@ -4214,7 +4210,7 @@
         </is>
       </c>
       <c r="K44" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L44" s="16">
         <f>IF(OR($K44="",D44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,D:D,"&gt;=0")=0,"",D44-SUMIFS(D:D,$B:$B,$B44,$A:$A,$K44)))</f>
@@ -4235,7 +4231,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
@@ -4248,13 +4244,13 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>110</v>
+        <v>128.99</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>80</v>
+        <v>98.59</v>
       </c>
       <c r="F45" s="8" t="n">
-        <v>1730</v>
+        <v>1230</v>
       </c>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="9">
@@ -4271,7 +4267,7 @@
         </is>
       </c>
       <c r="K45" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L45" s="16">
         <f>IF(OR($K45="",D45=""),"",IF(COUNTIFS($B:$B,$B45,$A:$A,$K45,D:D,"&gt;=0")=0,"",D45-SUMIFS(D:D,$B:$B,$B45,$A:$A,$K45)))</f>
@@ -4292,7 +4288,7 @@
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
@@ -4326,7 +4322,7 @@
         </is>
       </c>
       <c r="K46" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L46" s="16">
         <f>IF(OR($K46="",D46=""),"",IF(COUNTIFS($B:$B,$B46,$A:$A,$K46,D:D,"&gt;=0")=0,"",D46-SUMIFS(D:D,$B:$B,$B46,$A:$A,$K46)))</f>
@@ -4347,7 +4343,7 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
@@ -4360,15 +4356,13 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>320</v>
+        <v>324.99</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>279.99</v>
+        <v>275</v>
       </c>
       <c r="F47" s="2" t="n"/>
-      <c r="G47" s="8" t="n">
-        <v>5664</v>
-      </c>
+      <c r="G47" s="2" t="n"/>
       <c r="H47" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A47,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4383,7 +4377,7 @@
         </is>
       </c>
       <c r="K47" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L47" s="16">
         <f>IF(OR($K47="",D47=""),"",IF(COUNTIFS($B:$B,$B47,$A:$A,$K47,D:D,"&gt;=0")=0,"",D47-SUMIFS(D:D,$B:$B,$B47,$A:$A,$K47)))</f>
@@ -4404,7 +4398,7 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
@@ -4418,7 +4412,7 @@
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" s="7" t="n">
-        <v>298.01</v>
+        <v>315</v>
       </c>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
@@ -4436,7 +4430,7 @@
         </is>
       </c>
       <c r="K48" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L48" s="16">
         <f>IF(OR($K48="",D48=""),"",IF(COUNTIFS($B:$B,$B48,$A:$A,$K48,D:D,"&gt;=0")=0,"",D48-SUMIFS(D:D,$B:$B,$B48,$A:$A,$K48)))</f>
@@ -4457,7 +4451,7 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
@@ -4470,15 +4464,13 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>141.24</v>
+        <v>140.26</v>
       </c>
       <c r="E49" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F49" s="2" t="n"/>
-      <c r="G49" s="8" t="n">
-        <v>2850</v>
-      </c>
+      <c r="G49" s="2" t="n"/>
       <c r="H49" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A49,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4493,7 +4485,7 @@
         </is>
       </c>
       <c r="K49" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L49" s="16">
         <f>IF(OR($K49="",D49=""),"",IF(COUNTIFS($B:$B,$B49,$A:$A,$K49,D:D,"&gt;=0")=0,"",D49-SUMIFS(D:D,$B:$B,$B49,$A:$A,$K49)))</f>
@@ -4514,7 +4506,7 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
@@ -4548,7 +4540,7 @@
         </is>
       </c>
       <c r="K50" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L50" s="16">
         <f>IF(OR($K50="",D50=""),"",IF(COUNTIFS($B:$B,$B50,$A:$A,$K50,D:D,"&gt;=0")=0,"",D50-SUMIFS(D:D,$B:$B,$B50,$A:$A,$K50)))</f>
@@ -4569,7 +4561,7 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
@@ -4585,7 +4577,7 @@
         <v>118.96</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>73.95</v>
+        <v>71.95</v>
       </c>
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
@@ -4603,7 +4595,7 @@
         </is>
       </c>
       <c r="K51" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L51" s="16">
         <f>IF(OR($K51="",D51=""),"",IF(COUNTIFS($B:$B,$B51,$A:$A,$K51,D:D,"&gt;=0")=0,"",D51-SUMIFS(D:D,$B:$B,$B51,$A:$A,$K51)))</f>
@@ -4624,7 +4616,7 @@
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
@@ -4643,9 +4635,7 @@
         <v>139.99</v>
       </c>
       <c r="F52" s="2" t="n"/>
-      <c r="G52" s="8" t="n">
-        <v>2384</v>
-      </c>
+      <c r="G52" s="2" t="n"/>
       <c r="H52" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A52,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -4660,7 +4650,7 @@
         </is>
       </c>
       <c r="K52" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L52" s="16">
         <f>IF(OR($K52="",D52=""),"",IF(COUNTIFS($B:$B,$B52,$A:$A,$K52,D:D,"&gt;=0")=0,"",D52-SUMIFS(D:D,$B:$B,$B52,$A:$A,$K52)))</f>
@@ -4681,7 +4671,7 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
@@ -4695,7 +4685,7 @@
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="7" t="n">
-        <v>149.99</v>
+        <v>125</v>
       </c>
       <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
@@ -4713,7 +4703,7 @@
         </is>
       </c>
       <c r="K53" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L53" s="16">
         <f>IF(OR($K53="",D53=""),"",IF(COUNTIFS($B:$B,$B53,$A:$A,$K53,D:D,"&gt;=0")=0,"",D53-SUMIFS(D:D,$B:$B,$B53,$A:$A,$K53)))</f>
@@ -4734,7 +4724,7 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
@@ -4768,7 +4758,7 @@
         </is>
       </c>
       <c r="K54" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L54" s="16">
         <f>IF(OR($K54="",D54=""),"",IF(COUNTIFS($B:$B,$B54,$A:$A,$K54,D:D,"&gt;=0")=0,"",D54-SUMIFS(D:D,$B:$B,$B54,$A:$A,$K54)))</f>
@@ -4789,7 +4779,7 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
@@ -4802,7 +4792,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>234.99</v>
+        <v>235.27</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>229</v>
@@ -4823,7 +4813,7 @@
         </is>
       </c>
       <c r="K55" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L55" s="16">
         <f>IF(OR($K55="",D55=""),"",IF(COUNTIFS($B:$B,$B55,$A:$A,$K55,D:D,"&gt;=0")=0,"",D55-SUMIFS(D:D,$B:$B,$B55,$A:$A,$K55)))</f>
@@ -4844,7 +4834,7 @@
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
@@ -4860,7 +4850,7 @@
         <v>474.49</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>389.99</v>
+        <v>399.99</v>
       </c>
       <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="n"/>
@@ -4878,7 +4868,7 @@
         </is>
       </c>
       <c r="K56" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L56" s="16">
         <f>IF(OR($K56="",D56=""),"",IF(COUNTIFS($B:$B,$B56,$A:$A,$K56,D:D,"&gt;=0")=0,"",D56-SUMIFS(D:D,$B:$B,$B56,$A:$A,$K56)))</f>
@@ -4899,7 +4889,7 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
@@ -4915,7 +4905,7 @@
         <v>429.97</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
@@ -4933,7 +4923,7 @@
         </is>
       </c>
       <c r="K57" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L57" s="16">
         <f>IF(OR($K57="",D57=""),"",IF(COUNTIFS($B:$B,$B57,$A:$A,$K57,D:D,"&gt;=0")=0,"",D57-SUMIFS(D:D,$B:$B,$B57,$A:$A,$K57)))</f>
@@ -4954,7 +4944,7 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
@@ -4970,7 +4960,7 @@
         <v>209.99</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>175</v>
+        <v>161.99</v>
       </c>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
@@ -4988,7 +4978,7 @@
         </is>
       </c>
       <c r="K58" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L58" s="16">
         <f>IF(OR($K58="",D58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,D:D,"&gt;=0")=0,"",D58-SUMIFS(D:D,$B:$B,$B58,$A:$A,$K58)))</f>
@@ -5009,7 +4999,7 @@
     </row>
     <row r="59">
       <c r="A59" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
@@ -5022,15 +5012,15 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>128.99</v>
+        <v>110</v>
       </c>
       <c r="E59" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F59" s="2" t="n"/>
-      <c r="G59" s="8" t="n">
-        <v>1754</v>
-      </c>
+      <c r="F59" s="8" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G59" s="2" t="n"/>
       <c r="H59" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5045,7 +5035,7 @@
         </is>
       </c>
       <c r="K59" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L59" s="16">
         <f>IF(OR($K59="",D59=""),"",IF(COUNTIFS($B:$B,$B59,$A:$A,$K59,D:D,"&gt;=0")=0,"",D59-SUMIFS(D:D,$B:$B,$B59,$A:$A,$K59)))</f>
@@ -5066,7 +5056,7 @@
     </row>
     <row r="60">
       <c r="A60" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
@@ -5079,10 +5069,10 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>689.34</v>
+        <v>549.99</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>375</v>
+        <v>454.99</v>
       </c>
       <c r="F60" s="2" t="n"/>
       <c r="G60" s="2" t="n"/>
@@ -5100,7 +5090,7 @@
         </is>
       </c>
       <c r="K60" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L60" s="16">
         <f>IF(OR($K60="",D60=""),"",IF(COUNTIFS($B:$B,$B60,$A:$A,$K60,D:D,"&gt;=0")=0,"",D60-SUMIFS(D:D,$B:$B,$B60,$A:$A,$K60)))</f>
@@ -5121,7 +5111,7 @@
     </row>
     <row r="61">
       <c r="A61" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
@@ -5141,7 +5131,7 @@
       </c>
       <c r="F61" s="2" t="n"/>
       <c r="G61" s="8" t="n">
-        <v>5890</v>
+        <v>5664</v>
       </c>
       <c r="H61" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))),"")</f>
@@ -5157,7 +5147,7 @@
         </is>
       </c>
       <c r="K61" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L61" s="16">
         <f>IF(OR($K61="",D61=""),"",IF(COUNTIFS($B:$B,$B61,$A:$A,$K61,D:D,"&gt;=0")=0,"",D61-SUMIFS(D:D,$B:$B,$B61,$A:$A,$K61)))</f>
@@ -5178,7 +5168,7 @@
     </row>
     <row r="62">
       <c r="A62" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
@@ -5192,7 +5182,7 @@
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="7" t="n">
-        <v>295</v>
+        <v>298.01</v>
       </c>
       <c r="F62" s="2" t="n"/>
       <c r="G62" s="2" t="n"/>
@@ -5210,7 +5200,7 @@
         </is>
       </c>
       <c r="K62" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L62" s="16">
         <f>IF(OR($K62="",D62=""),"",IF(COUNTIFS($B:$B,$B62,$A:$A,$K62,D:D,"&gt;=0")=0,"",D62-SUMIFS(D:D,$B:$B,$B62,$A:$A,$K62)))</f>
@@ -5231,7 +5221,7 @@
     </row>
     <row r="63">
       <c r="A63" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
@@ -5244,14 +5234,14 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>142.24</v>
+        <v>141.24</v>
       </c>
       <c r="E63" s="7" t="n">
         <v>120</v>
       </c>
       <c r="F63" s="2" t="n"/>
       <c r="G63" s="8" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="H63" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))),"")</f>
@@ -5267,7 +5257,7 @@
         </is>
       </c>
       <c r="K63" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L63" s="16">
         <f>IF(OR($K63="",D63=""),"",IF(COUNTIFS($B:$B,$B63,$A:$A,$K63,D:D,"&gt;=0")=0,"",D63-SUMIFS(D:D,$B:$B,$B63,$A:$A,$K63)))</f>
@@ -5288,7 +5278,7 @@
     </row>
     <row r="64">
       <c r="A64" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
@@ -5304,7 +5294,7 @@
         <v>138.9</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F64" s="2" t="n"/>
       <c r="G64" s="2" t="n"/>
@@ -5322,7 +5312,7 @@
         </is>
       </c>
       <c r="K64" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L64" s="16">
         <f>IF(OR($K64="",D64=""),"",IF(COUNTIFS($B:$B,$B64,$A:$A,$K64,D:D,"&gt;=0")=0,"",D64-SUMIFS(D:D,$B:$B,$B64,$A:$A,$K64)))</f>
@@ -5343,7 +5333,7 @@
     </row>
     <row r="65">
       <c r="A65" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
@@ -5356,7 +5346,7 @@
         </is>
       </c>
       <c r="D65" s="7" t="n">
-        <v>75</v>
+        <v>118.96</v>
       </c>
       <c r="E65" s="7" t="n">
         <v>73.95</v>
@@ -5377,7 +5367,7 @@
         </is>
       </c>
       <c r="K65" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L65" s="16">
         <f>IF(OR($K65="",D65=""),"",IF(COUNTIFS($B:$B,$B65,$A:$A,$K65,D:D,"&gt;=0")=0,"",D65-SUMIFS(D:D,$B:$B,$B65,$A:$A,$K65)))</f>
@@ -5398,7 +5388,7 @@
     </row>
     <row r="66">
       <c r="A66" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
@@ -5414,11 +5404,11 @@
         <v>164.49</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>134.99</v>
+        <v>139.99</v>
       </c>
       <c r="F66" s="2" t="n"/>
       <c r="G66" s="8" t="n">
-        <v>2750</v>
+        <v>2384</v>
       </c>
       <c r="H66" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))),"")</f>
@@ -5434,7 +5424,7 @@
         </is>
       </c>
       <c r="K66" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L66" s="16">
         <f>IF(OR($K66="",D66=""),"",IF(COUNTIFS($B:$B,$B66,$A:$A,$K66,D:D,"&gt;=0")=0,"",D66-SUMIFS(D:D,$B:$B,$B66,$A:$A,$K66)))</f>
@@ -5455,7 +5445,7 @@
     </row>
     <row r="67">
       <c r="A67" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
@@ -5487,7 +5477,7 @@
         </is>
       </c>
       <c r="K67" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L67" s="16">
         <f>IF(OR($K67="",D67=""),"",IF(COUNTIFS($B:$B,$B67,$A:$A,$K67,D:D,"&gt;=0")=0,"",D67-SUMIFS(D:D,$B:$B,$B67,$A:$A,$K67)))</f>
@@ -5508,7 +5498,7 @@
     </row>
     <row r="68">
       <c r="A68" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
@@ -5524,12 +5514,10 @@
         <v>150</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>114.99</v>
+        <v>120.99</v>
       </c>
       <c r="F68" s="2" t="n"/>
-      <c r="G68" s="8" t="n">
-        <v>2260</v>
-      </c>
+      <c r="G68" s="2" t="n"/>
       <c r="H68" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A68,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A68,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5544,7 +5532,7 @@
         </is>
       </c>
       <c r="K68" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L68" s="16">
         <f>IF(OR($K68="",D68=""),"",IF(COUNTIFS($B:$B,$B68,$A:$A,$K68,D:D,"&gt;=0")=0,"",D68-SUMIFS(D:D,$B:$B,$B68,$A:$A,$K68)))</f>
@@ -5565,7 +5553,7 @@
     </row>
     <row r="69">
       <c r="A69" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
@@ -5599,7 +5587,7 @@
         </is>
       </c>
       <c r="K69" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L69" s="16">
         <f>IF(OR($K69="",D69=""),"",IF(COUNTIFS($B:$B,$B69,$A:$A,$K69,D:D,"&gt;=0")=0,"",D69-SUMIFS(D:D,$B:$B,$B69,$A:$A,$K69)))</f>
@@ -5620,7 +5608,7 @@
     </row>
     <row r="70">
       <c r="A70" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
@@ -5633,10 +5621,10 @@
         </is>
       </c>
       <c r="D70" s="7" t="n">
-        <v>435.99</v>
+        <v>474.49</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>394.99</v>
+        <v>389.99</v>
       </c>
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
@@ -5654,7 +5642,7 @@
         </is>
       </c>
       <c r="K70" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L70" s="16">
         <f>IF(OR($K70="",D70=""),"",IF(COUNTIFS($B:$B,$B70,$A:$A,$K70,D:D,"&gt;=0")=0,"",D70-SUMIFS(D:D,$B:$B,$B70,$A:$A,$K70)))</f>
@@ -5675,7 +5663,7 @@
     </row>
     <row r="71">
       <c r="A71" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
@@ -5691,7 +5679,7 @@
         <v>429.97</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>375</v>
+        <v>379.99</v>
       </c>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
@@ -5709,7 +5697,7 @@
         </is>
       </c>
       <c r="K71" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L71" s="16">
         <f>IF(OR($K71="",D71=""),"",IF(COUNTIFS($B:$B,$B71,$A:$A,$K71,D:D,"&gt;=0")=0,"",D71-SUMIFS(D:D,$B:$B,$B71,$A:$A,$K71)))</f>
@@ -5730,7 +5718,7 @@
     </row>
     <row r="72">
       <c r="A72" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
@@ -5746,7 +5734,7 @@
         <v>209.99</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>164.99</v>
+        <v>175</v>
       </c>
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
@@ -5764,7 +5752,7 @@
         </is>
       </c>
       <c r="K72" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L72" s="16">
         <f>IF(OR($K72="",D72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,D:D,"&gt;=0")=0,"",D72-SUMIFS(D:D,$B:$B,$B72,$A:$A,$K72)))</f>
@@ -5785,7 +5773,7 @@
     </row>
     <row r="73">
       <c r="A73" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
@@ -5798,13 +5786,15 @@
         </is>
       </c>
       <c r="D73" s="7" t="n">
-        <v>117.99</v>
+        <v>128.99</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>80</v>
       </c>
       <c r="F73" s="2" t="n"/>
-      <c r="G73" s="2" t="n"/>
+      <c r="G73" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="H73" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5819,7 +5809,7 @@
         </is>
       </c>
       <c r="K73" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L73" s="16">
         <f>IF(OR($K73="",D73=""),"",IF(COUNTIFS($B:$B,$B73,$A:$A,$K73,D:D,"&gt;=0")=0,"",D73-SUMIFS(D:D,$B:$B,$B73,$A:$A,$K73)))</f>
@@ -5840,7 +5830,7 @@
     </row>
     <row r="74">
       <c r="A74" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
@@ -5853,10 +5843,10 @@
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>499.99</v>
+        <v>689.34</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>454.99</v>
+        <v>375</v>
       </c>
       <c r="F74" s="2" t="n"/>
       <c r="G74" s="2" t="n"/>
@@ -5874,7 +5864,7 @@
         </is>
       </c>
       <c r="K74" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L74" s="16">
         <f>IF(OR($K74="",D74=""),"",IF(COUNTIFS($B:$B,$B74,$A:$A,$K74,D:D,"&gt;=0")=0,"",D74-SUMIFS(D:D,$B:$B,$B74,$A:$A,$K74)))</f>
@@ -5895,7 +5885,7 @@
     </row>
     <row r="75">
       <c r="A75" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
@@ -5908,13 +5898,15 @@
         </is>
       </c>
       <c r="D75" s="7" t="n">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>275.99</v>
+        <v>279.99</v>
       </c>
       <c r="F75" s="2" t="n"/>
-      <c r="G75" s="2" t="n"/>
+      <c r="G75" s="8" t="n">
+        <v>5890</v>
+      </c>
       <c r="H75" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5929,7 +5921,7 @@
         </is>
       </c>
       <c r="K75" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L75" s="16">
         <f>IF(OR($K75="",D75=""),"",IF(COUNTIFS($B:$B,$B75,$A:$A,$K75,D:D,"&gt;=0")=0,"",D75-SUMIFS(D:D,$B:$B,$B75,$A:$A,$K75)))</f>
@@ -5950,7 +5942,7 @@
     </row>
     <row r="76">
       <c r="A76" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
@@ -5982,7 +5974,7 @@
         </is>
       </c>
       <c r="K76" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L76" s="16">
         <f>IF(OR($K76="",D76=""),"",IF(COUNTIFS($B:$B,$B76,$A:$A,$K76,D:D,"&gt;=0")=0,"",D76-SUMIFS(D:D,$B:$B,$B76,$A:$A,$K76)))</f>
@@ -6003,7 +5995,7 @@
     </row>
     <row r="77">
       <c r="A77" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
@@ -6019,10 +6011,12 @@
         <v>142.24</v>
       </c>
       <c r="E77" s="7" t="n">
-        <v>121.99</v>
+        <v>120</v>
       </c>
       <c r="F77" s="2" t="n"/>
-      <c r="G77" s="2" t="n"/>
+      <c r="G77" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H77" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6037,7 +6031,7 @@
         </is>
       </c>
       <c r="K77" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L77" s="16">
         <f>IF(OR($K77="",D77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,D:D,"&gt;=0")=0,"",D77-SUMIFS(D:D,$B:$B,$B77,$A:$A,$K77)))</f>
@@ -6058,7 +6052,7 @@
     </row>
     <row r="78">
       <c r="A78" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
@@ -6074,7 +6068,7 @@
         <v>138.9</v>
       </c>
       <c r="E78" s="7" t="n">
-        <v>129.99</v>
+        <v>135</v>
       </c>
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
@@ -6092,7 +6086,7 @@
         </is>
       </c>
       <c r="K78" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L78" s="16">
         <f>IF(OR($K78="",D78=""),"",IF(COUNTIFS($B:$B,$B78,$A:$A,$K78,D:D,"&gt;=0")=0,"",D78-SUMIFS(D:D,$B:$B,$B78,$A:$A,$K78)))</f>
@@ -6113,7 +6107,7 @@
     </row>
     <row r="79">
       <c r="A79" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
@@ -6126,10 +6120,10 @@
         </is>
       </c>
       <c r="D79" s="7" t="n">
-        <v>72.98999999999999</v>
+        <v>75</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>65</v>
+        <v>73.95</v>
       </c>
       <c r="F79" s="2" t="n"/>
       <c r="G79" s="2" t="n"/>
@@ -6147,7 +6141,7 @@
         </is>
       </c>
       <c r="K79" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L79" s="16">
         <f>IF(OR($K79="",D79=""),"",IF(COUNTIFS($B:$B,$B79,$A:$A,$K79,D:D,"&gt;=0")=0,"",D79-SUMIFS(D:D,$B:$B,$B79,$A:$A,$K79)))</f>
@@ -6168,7 +6162,7 @@
     </row>
     <row r="80">
       <c r="A80" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
@@ -6184,10 +6178,12 @@
         <v>164.49</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>134</v>
+        <v>134.99</v>
       </c>
       <c r="F80" s="2" t="n"/>
-      <c r="G80" s="2" t="n"/>
+      <c r="G80" s="8" t="n">
+        <v>2750</v>
+      </c>
       <c r="H80" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6202,7 +6198,7 @@
         </is>
       </c>
       <c r="K80" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L80" s="16">
         <f>IF(OR($K80="",D80=""),"",IF(COUNTIFS($B:$B,$B80,$A:$A,$K80,D:D,"&gt;=0")=0,"",D80-SUMIFS(D:D,$B:$B,$B80,$A:$A,$K80)))</f>
@@ -6223,7 +6219,7 @@
     </row>
     <row r="81">
       <c r="A81" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
@@ -6255,7 +6251,7 @@
         </is>
       </c>
       <c r="K81" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L81" s="16">
         <f>IF(OR($K81="",D81=""),"",IF(COUNTIFS($B:$B,$B81,$A:$A,$K81,D:D,"&gt;=0")=0,"",D81-SUMIFS(D:D,$B:$B,$B81,$A:$A,$K81)))</f>
@@ -6276,7 +6272,7 @@
     </row>
     <row r="82">
       <c r="A82" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
@@ -6292,10 +6288,12 @@
         <v>150</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>120.99</v>
+        <v>114.99</v>
       </c>
       <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
+      <c r="G82" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="H82" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A82,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A82,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6310,7 +6308,7 @@
         </is>
       </c>
       <c r="K82" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L82" s="16">
         <f>IF(OR($K82="",D82=""),"",IF(COUNTIFS($B:$B,$B82,$A:$A,$K82,D:D,"&gt;=0")=0,"",D82-SUMIFS(D:D,$B:$B,$B82,$A:$A,$K82)))</f>
@@ -6331,7 +6329,7 @@
     </row>
     <row r="83">
       <c r="A83" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
@@ -6365,7 +6363,7 @@
         </is>
       </c>
       <c r="K83" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L83" s="16">
         <f>IF(OR($K83="",D83=""),"",IF(COUNTIFS($B:$B,$B83,$A:$A,$K83,D:D,"&gt;=0")=0,"",D83-SUMIFS(D:D,$B:$B,$B83,$A:$A,$K83)))</f>
@@ -6386,7 +6384,7 @@
     </row>
     <row r="84">
       <c r="A84" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
@@ -6402,7 +6400,7 @@
         <v>435.99</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>399.9</v>
+        <v>394.99</v>
       </c>
       <c r="F84" s="2" t="n"/>
       <c r="G84" s="2" t="n"/>
@@ -6420,7 +6418,7 @@
         </is>
       </c>
       <c r="K84" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L84" s="16">
         <f>IF(OR($K84="",D84=""),"",IF(COUNTIFS($B:$B,$B84,$A:$A,$K84,D:D,"&gt;=0")=0,"",D84-SUMIFS(D:D,$B:$B,$B84,$A:$A,$K84)))</f>
@@ -6441,7 +6439,7 @@
     </row>
     <row r="85">
       <c r="A85" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
@@ -6457,7 +6455,7 @@
         <v>429.97</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>379.99</v>
+        <v>375</v>
       </c>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
@@ -6475,7 +6473,7 @@
         </is>
       </c>
       <c r="K85" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L85" s="16">
         <f>IF(OR($K85="",D85=""),"",IF(COUNTIFS($B:$B,$B85,$A:$A,$K85,D:D,"&gt;=0")=0,"",D85-SUMIFS(D:D,$B:$B,$B85,$A:$A,$K85)))</f>
@@ -6496,7 +6494,7 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
@@ -6512,7 +6510,7 @@
         <v>209.99</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>170</v>
+        <v>164.99</v>
       </c>
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
@@ -6530,7 +6528,7 @@
         </is>
       </c>
       <c r="K86" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L86" s="16">
         <f>IF(OR($K86="",D86=""),"",IF(COUNTIFS($B:$B,$B86,$A:$A,$K86,D:D,"&gt;=0")=0,"",D86-SUMIFS(D:D,$B:$B,$B86,$A:$A,$K86)))</f>
@@ -6551,7 +6549,7 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
@@ -6564,10 +6562,10 @@
         </is>
       </c>
       <c r="D87" s="7" t="n">
-        <v>114.99</v>
+        <v>117.99</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
@@ -6585,7 +6583,7 @@
         </is>
       </c>
       <c r="K87" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L87" s="16">
         <f>IF(OR($K87="",D87=""),"",IF(COUNTIFS($B:$B,$B87,$A:$A,$K87,D:D,"&gt;=0")=0,"",D87-SUMIFS(D:D,$B:$B,$B87,$A:$A,$K87)))</f>
@@ -6606,7 +6604,7 @@
     </row>
     <row r="88">
       <c r="A88" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
@@ -6640,7 +6638,7 @@
         </is>
       </c>
       <c r="K88" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L88" s="16">
         <f>IF(OR($K88="",D88=""),"",IF(COUNTIFS($B:$B,$B88,$A:$A,$K88,D:D,"&gt;=0")=0,"",D88-SUMIFS(D:D,$B:$B,$B88,$A:$A,$K88)))</f>
@@ -6661,7 +6659,7 @@
     </row>
     <row r="89">
       <c r="A89" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
@@ -6677,14 +6675,10 @@
         <v>329</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="F89" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G89" s="8" t="n">
-        <v>5350</v>
-      </c>
+        <v>275.99</v>
+      </c>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
       <c r="H89" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A89,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A89,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6699,7 +6693,7 @@
         </is>
       </c>
       <c r="K89" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L89" s="16">
         <f>IF(OR($K89="",D89=""),"",IF(COUNTIFS($B:$B,$B89,$A:$A,$K89,D:D,"&gt;=0")=0,"",D89-SUMIFS(D:D,$B:$B,$B89,$A:$A,$K89)))</f>
@@ -6720,7 +6714,7 @@
     </row>
     <row r="90">
       <c r="A90" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
@@ -6734,7 +6728,7 @@
       </c>
       <c r="D90" s="2" t="n"/>
       <c r="E90" s="7" t="n">
-        <v>299.99</v>
+        <v>295</v>
       </c>
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
@@ -6752,7 +6746,7 @@
         </is>
       </c>
       <c r="K90" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L90" s="16">
         <f>IF(OR($K90="",D90=""),"",IF(COUNTIFS($B:$B,$B90,$A:$A,$K90,D:D,"&gt;=0")=0,"",D90-SUMIFS(D:D,$B:$B,$B90,$A:$A,$K90)))</f>
@@ -6773,7 +6767,7 @@
     </row>
     <row r="91">
       <c r="A91" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
@@ -6786,10 +6780,10 @@
         </is>
       </c>
       <c r="D91" s="7" t="n">
-        <v>143.24</v>
+        <v>142.24</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>122.99</v>
+        <v>121.99</v>
       </c>
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="n"/>
@@ -6807,7 +6801,7 @@
         </is>
       </c>
       <c r="K91" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L91" s="16">
         <f>IF(OR($K91="",D91=""),"",IF(COUNTIFS($B:$B,$B91,$A:$A,$K91,D:D,"&gt;=0")=0,"",D91-SUMIFS(D:D,$B:$B,$B91,$A:$A,$K91)))</f>
@@ -6828,7 +6822,7 @@
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
@@ -6844,7 +6838,7 @@
         <v>138.9</v>
       </c>
       <c r="E92" s="7" t="n">
-        <v>135</v>
+        <v>129.99</v>
       </c>
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
@@ -6862,7 +6856,7 @@
         </is>
       </c>
       <c r="K92" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L92" s="16">
         <f>IF(OR($K92="",D92=""),"",IF(COUNTIFS($B:$B,$B92,$A:$A,$K92,D:D,"&gt;=0")=0,"",D92-SUMIFS(D:D,$B:$B,$B92,$A:$A,$K92)))</f>
@@ -6883,7 +6877,7 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
@@ -6896,10 +6890,10 @@
         </is>
       </c>
       <c r="D93" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>65</v>
       </c>
       <c r="F93" s="2" t="n"/>
       <c r="G93" s="2" t="n"/>
@@ -6917,7 +6911,7 @@
         </is>
       </c>
       <c r="K93" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L93" s="16">
         <f>IF(OR($K93="",D93=""),"",IF(COUNTIFS($B:$B,$B93,$A:$A,$K93,D:D,"&gt;=0")=0,"",D93-SUMIFS(D:D,$B:$B,$B93,$A:$A,$K93)))</f>
@@ -6938,7 +6932,7 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
@@ -6957,9 +6951,7 @@
         <v>134</v>
       </c>
       <c r="F94" s="2" t="n"/>
-      <c r="G94" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G94" s="2" t="n"/>
       <c r="H94" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A94,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A94,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6974,7 +6966,7 @@
         </is>
       </c>
       <c r="K94" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L94" s="16">
         <f>IF(OR($K94="",D94=""),"",IF(COUNTIFS($B:$B,$B94,$A:$A,$K94,D:D,"&gt;=0")=0,"",D94-SUMIFS(D:D,$B:$B,$B94,$A:$A,$K94)))</f>
@@ -6995,7 +6987,7 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
@@ -7027,7 +7019,7 @@
         </is>
       </c>
       <c r="K95" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L95" s="16">
         <f>IF(OR($K95="",D95=""),"",IF(COUNTIFS($B:$B,$B95,$A:$A,$K95,D:D,"&gt;=0")=0,"",D95-SUMIFS(D:D,$B:$B,$B95,$A:$A,$K95)))</f>
@@ -7048,7 +7040,7 @@
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
@@ -7064,7 +7056,7 @@
         <v>150</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>99</v>
+        <v>120.99</v>
       </c>
       <c r="F96" s="2" t="n"/>
       <c r="G96" s="2" t="n"/>
@@ -7082,7 +7074,7 @@
         </is>
       </c>
       <c r="K96" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L96" s="16">
         <f>IF(OR($K96="",D96=""),"",IF(COUNTIFS($B:$B,$B96,$A:$A,$K96,D:D,"&gt;=0")=0,"",D96-SUMIFS(D:D,$B:$B,$B96,$A:$A,$K96)))</f>
@@ -7103,7 +7095,7 @@
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
@@ -7119,7 +7111,7 @@
         <v>234.99</v>
       </c>
       <c r="E97" s="7" t="n">
-        <v>209.99</v>
+        <v>229</v>
       </c>
       <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="n"/>
@@ -7137,7 +7129,7 @@
         </is>
       </c>
       <c r="K97" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L97" s="16">
         <f>IF(OR($K97="",D97=""),"",IF(COUNTIFS($B:$B,$B97,$A:$A,$K97,D:D,"&gt;=0")=0,"",D97-SUMIFS(D:D,$B:$B,$B97,$A:$A,$K97)))</f>
@@ -7158,7 +7150,7 @@
     </row>
     <row r="98">
       <c r="A98" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
@@ -7192,7 +7184,7 @@
         </is>
       </c>
       <c r="K98" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L98" s="16">
         <f>IF(OR($K98="",D98=""),"",IF(COUNTIFS($B:$B,$B98,$A:$A,$K98,D:D,"&gt;=0")=0,"",D98-SUMIFS(D:D,$B:$B,$B98,$A:$A,$K98)))</f>
@@ -7213,7 +7205,7 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
@@ -7226,10 +7218,10 @@
         </is>
       </c>
       <c r="D99" s="7" t="n">
-        <v>493</v>
+        <v>429.97</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>383.99</v>
+        <v>379.99</v>
       </c>
       <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
@@ -7247,7 +7239,7 @@
         </is>
       </c>
       <c r="K99" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L99" s="16">
         <f>IF(OR($K99="",D99=""),"",IF(COUNTIFS($B:$B,$B99,$A:$A,$K99,D:D,"&gt;=0")=0,"",D99-SUMIFS(D:D,$B:$B,$B99,$A:$A,$K99)))</f>
@@ -7268,7 +7260,7 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
@@ -7284,12 +7276,10 @@
         <v>209.99</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>179.99</v>
+        <v>170</v>
       </c>
       <c r="F100" s="2" t="n"/>
-      <c r="G100" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G100" s="2" t="n"/>
       <c r="H100" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A100,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A100,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7304,7 +7294,7 @@
         </is>
       </c>
       <c r="K100" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L100" s="16">
         <f>IF(OR($K100="",D100=""),"",IF(COUNTIFS($B:$B,$B100,$A:$A,$K100,D:D,"&gt;=0")=0,"",D100-SUMIFS(D:D,$B:$B,$B100,$A:$A,$K100)))</f>
@@ -7325,7 +7315,7 @@
     </row>
     <row r="101">
       <c r="A101" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
@@ -7344,9 +7334,7 @@
         <v>99.98999999999999</v>
       </c>
       <c r="F101" s="2" t="n"/>
-      <c r="G101" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G101" s="2" t="n"/>
       <c r="H101" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A101,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A101,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7361,7 +7349,7 @@
         </is>
       </c>
       <c r="K101" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L101" s="16">
         <f>IF(OR($K101="",D101=""),"",IF(COUNTIFS($B:$B,$B101,$A:$A,$K101,D:D,"&gt;=0")=0,"",D101-SUMIFS(D:D,$B:$B,$B101,$A:$A,$K101)))</f>
@@ -7382,7 +7370,7 @@
     </row>
     <row r="102">
       <c r="A102" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
@@ -7401,9 +7389,7 @@
         <v>454.99</v>
       </c>
       <c r="F102" s="2" t="n"/>
-      <c r="G102" s="8" t="n">
-        <v>6140</v>
-      </c>
+      <c r="G102" s="2" t="n"/>
       <c r="H102" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A102,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A102,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7418,7 +7404,7 @@
         </is>
       </c>
       <c r="K102" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L102" s="16">
         <f>IF(OR($K102="",D102=""),"",IF(COUNTIFS($B:$B,$B102,$A:$A,$K102,D:D,"&gt;=0")=0,"",D102-SUMIFS(D:D,$B:$B,$B102,$A:$A,$K102)))</f>
@@ -7439,7 +7425,7 @@
     </row>
     <row r="103">
       <c r="A103" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
@@ -7457,9 +7443,11 @@
       <c r="E103" s="7" t="n">
         <v>283.99</v>
       </c>
-      <c r="F103" s="2" t="n"/>
+      <c r="F103" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="G103" s="8" t="n">
-        <v>4760</v>
+        <v>5350</v>
       </c>
       <c r="H103" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A103,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A103,Dólar!$A:$A,0))),"")</f>
@@ -7475,7 +7463,7 @@
         </is>
       </c>
       <c r="K103" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L103" s="16">
         <f>IF(OR($K103="",D103=""),"",IF(COUNTIFS($B:$B,$B103,$A:$A,$K103,D:D,"&gt;=0")=0,"",D103-SUMIFS(D:D,$B:$B,$B103,$A:$A,$K103)))</f>
@@ -7496,7 +7484,7 @@
     </row>
     <row r="104">
       <c r="A104" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
@@ -7510,7 +7498,7 @@
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" s="7" t="n">
-        <v>305</v>
+        <v>299.99</v>
       </c>
       <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="n"/>
@@ -7527,7 +7515,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K104" s="5" t="n"/>
+      <c r="K104" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L104" s="16">
         <f>IF(OR($K104="",D104=""),"",IF(COUNTIFS($B:$B,$B104,$A:$A,$K104,D:D,"&gt;=0")=0,"",D104-SUMIFS(D:D,$B:$B,$B104,$A:$A,$K104)))</f>
         <v/>
@@ -7547,7 +7537,7 @@
     </row>
     <row r="105">
       <c r="A105" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
@@ -7560,15 +7550,13 @@
         </is>
       </c>
       <c r="D105" s="7" t="n">
-        <v>144.25</v>
+        <v>143.24</v>
       </c>
       <c r="E105" s="7" t="n">
         <v>122.99</v>
       </c>
       <c r="F105" s="2" t="n"/>
-      <c r="G105" s="8" t="n">
-        <v>2860</v>
-      </c>
+      <c r="G105" s="2" t="n"/>
       <c r="H105" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A105,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A105,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7583,7 +7571,7 @@
         </is>
       </c>
       <c r="K105" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L105" s="16">
         <f>IF(OR($K105="",D105=""),"",IF(COUNTIFS($B:$B,$B105,$A:$A,$K105,D:D,"&gt;=0")=0,"",D105-SUMIFS(D:D,$B:$B,$B105,$A:$A,$K105)))</f>
@@ -7604,7 +7592,7 @@
     </row>
     <row r="106">
       <c r="A106" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
@@ -7637,7 +7625,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K106" s="5" t="n"/>
+      <c r="K106" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L106" s="16">
         <f>IF(OR($K106="",D106=""),"",IF(COUNTIFS($B:$B,$B106,$A:$A,$K106,D:D,"&gt;=0")=0,"",D106-SUMIFS(D:D,$B:$B,$B106,$A:$A,$K106)))</f>
         <v/>
@@ -7657,7 +7647,7 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
@@ -7670,15 +7660,13 @@
         </is>
       </c>
       <c r="D107" s="7" t="n">
-        <v>75</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>59.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F107" s="2" t="n"/>
-      <c r="G107" s="8" t="n">
-        <v>2150</v>
-      </c>
+      <c r="G107" s="2" t="n"/>
       <c r="H107" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A107,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A107,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7693,7 +7681,7 @@
         </is>
       </c>
       <c r="K107" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L107" s="16">
         <f>IF(OR($K107="",D107=""),"",IF(COUNTIFS($B:$B,$B107,$A:$A,$K107,D:D,"&gt;=0")=0,"",D107-SUMIFS(D:D,$B:$B,$B107,$A:$A,$K107)))</f>
@@ -7714,7 +7702,7 @@
     </row>
     <row r="108">
       <c r="A108" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
@@ -7730,11 +7718,11 @@
         <v>164.49</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>136.99</v>
+        <v>134</v>
       </c>
       <c r="F108" s="2" t="n"/>
       <c r="G108" s="8" t="n">
-        <v>2520</v>
+        <v>2460</v>
       </c>
       <c r="H108" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A108,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A108,Dólar!$A:$A,0))),"")</f>
@@ -7750,7 +7738,7 @@
         </is>
       </c>
       <c r="K108" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L108" s="16">
         <f>IF(OR($K108="",D108=""),"",IF(COUNTIFS($B:$B,$B108,$A:$A,$K108,D:D,"&gt;=0")=0,"",D108-SUMIFS(D:D,$B:$B,$B108,$A:$A,$K108)))</f>
@@ -7771,7 +7759,7 @@
     </row>
     <row r="109">
       <c r="A109" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
@@ -7783,9 +7771,7 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D109" s="7" t="n">
-        <v>259.78</v>
-      </c>
+      <c r="D109" s="2" t="n"/>
       <c r="E109" s="7" t="n">
         <v>149.99</v>
       </c>
@@ -7805,7 +7791,7 @@
         </is>
       </c>
       <c r="K109" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L109" s="16">
         <f>IF(OR($K109="",D109=""),"",IF(COUNTIFS($B:$B,$B109,$A:$A,$K109,D:D,"&gt;=0")=0,"",D109-SUMIFS(D:D,$B:$B,$B109,$A:$A,$K109)))</f>
@@ -7826,7 +7812,7 @@
     </row>
     <row r="110">
       <c r="A110" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
@@ -7842,12 +7828,10 @@
         <v>150</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>119.95</v>
+        <v>99</v>
       </c>
       <c r="F110" s="2" t="n"/>
-      <c r="G110" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G110" s="2" t="n"/>
       <c r="H110" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A110,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A110,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7861,7 +7845,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K110" s="5" t="n"/>
+      <c r="K110" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L110" s="16">
         <f>IF(OR($K110="",D110=""),"",IF(COUNTIFS($B:$B,$B110,$A:$A,$K110,D:D,"&gt;=0")=0,"",D110-SUMIFS(D:D,$B:$B,$B110,$A:$A,$K110)))</f>
         <v/>
@@ -7881,7 +7867,7 @@
     </row>
     <row r="111">
       <c r="A111" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
@@ -7894,15 +7880,13 @@
         </is>
       </c>
       <c r="D111" s="7" t="n">
-        <v>244.87</v>
+        <v>234.99</v>
       </c>
       <c r="E111" s="7" t="n">
         <v>209.99</v>
       </c>
       <c r="F111" s="2" t="n"/>
-      <c r="G111" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G111" s="2" t="n"/>
       <c r="H111" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A111,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A111,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7917,7 +7901,7 @@
         </is>
       </c>
       <c r="K111" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L111" s="16">
         <f>IF(OR($K111="",D111=""),"",IF(COUNTIFS($B:$B,$B111,$A:$A,$K111,D:D,"&gt;=0")=0,"",D111-SUMIFS(D:D,$B:$B,$B111,$A:$A,$K111)))</f>
@@ -7938,7 +7922,7 @@
     </row>
     <row r="112">
       <c r="A112" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
@@ -7972,7 +7956,7 @@
         </is>
       </c>
       <c r="K112" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L112" s="16">
         <f>IF(OR($K112="",D112=""),"",IF(COUNTIFS($B:$B,$B112,$A:$A,$K112,D:D,"&gt;=0")=0,"",D112-SUMIFS(D:D,$B:$B,$B112,$A:$A,$K112)))</f>
@@ -7993,7 +7977,7 @@
     </row>
     <row r="113">
       <c r="A113" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
@@ -8009,11 +7993,9 @@
         <v>493</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F113" s="8" t="n">
-        <v>4500</v>
-      </c>
+        <v>383.99</v>
+      </c>
+      <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
       <c r="H113" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A113,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A113,Dólar!$A:$A,0))),"")</f>
@@ -8028,7 +8010,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K113" s="5" t="n"/>
+      <c r="K113" s="15" t="n">
+        <v>46307</v>
+      </c>
       <c r="L113" s="16">
         <f>IF(OR($K113="",D113=""),"",IF(COUNTIFS($B:$B,$B113,$A:$A,$K113,D:D,"&gt;=0")=0,"",D113-SUMIFS(D:D,$B:$B,$B113,$A:$A,$K113)))</f>
         <v/>
@@ -8048,7 +8032,7 @@
     </row>
     <row r="114">
       <c r="A114" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
@@ -8060,10 +8044,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
+      <c r="D114" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>179.99</v>
+      </c>
       <c r="F114" s="2" t="n"/>
-      <c r="G114" s="2" t="n"/>
+      <c r="G114" s="8" t="n">
+        <v>4060</v>
+      </c>
       <c r="H114" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A114,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A114,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8072,8 +8062,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A114,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J114" s="2" t="n"/>
-      <c r="K114" s="5" t="n"/>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K114" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L114" s="16">
         <f>IF(OR($K114="",D114=""),"",IF(COUNTIFS($B:$B,$B114,$A:$A,$K114,D:D,"&gt;=0")=0,"",D114-SUMIFS(D:D,$B:$B,$B114,$A:$A,$K114)))</f>
         <v/>
@@ -8093,7 +8089,7 @@
     </row>
     <row r="115">
       <c r="A115" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
@@ -8105,12 +8101,16 @@
           <t>SSD</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n"/>
-      <c r="E115" s="2" t="n"/>
-      <c r="F115" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="G115" s="2" t="n"/>
+      <c r="D115" s="7" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="E115" s="7" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F115" s="2" t="n"/>
+      <c r="G115" s="8" t="n">
+        <v>1860</v>
+      </c>
       <c r="H115" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A115,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A115,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8124,7 +8124,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K115" s="5" t="n"/>
+      <c r="K115" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L115" s="16">
         <f>IF(OR($K115="",D115=""),"",IF(COUNTIFS($B:$B,$B115,$A:$A,$K115,D:D,"&gt;=0")=0,"",D115-SUMIFS(D:D,$B:$B,$B115,$A:$A,$K115)))</f>
         <v/>
@@ -8144,7 +8146,7 @@
     </row>
     <row r="116">
       <c r="A116" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
@@ -8156,11 +8158,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
+      <c r="D116" s="7" t="n">
+        <v>499.99</v>
+      </c>
+      <c r="E116" s="7" t="n">
+        <v>454.99</v>
+      </c>
       <c r="F116" s="2" t="n"/>
       <c r="G116" s="8" t="n">
-        <v>5580</v>
+        <v>6140</v>
       </c>
       <c r="H116" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A116,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A116,Dólar!$A:$A,0))),"")</f>
@@ -8175,7 +8181,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K116" s="5" t="n"/>
+      <c r="K116" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L116" s="16">
         <f>IF(OR($K116="",D116=""),"",IF(COUNTIFS($B:$B,$B116,$A:$A,$K116,D:D,"&gt;=0")=0,"",D116-SUMIFS(D:D,$B:$B,$B116,$A:$A,$K116)))</f>
         <v/>
@@ -8195,7 +8203,7 @@
     </row>
     <row r="117">
       <c r="A117" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
@@ -8207,12 +8215,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D117" s="2" t="n"/>
-      <c r="E117" s="2" t="n"/>
-      <c r="F117" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G117" s="2" t="n"/>
+      <c r="D117" s="7" t="n">
+        <v>329</v>
+      </c>
+      <c r="E117" s="7" t="n">
+        <v>283.99</v>
+      </c>
+      <c r="F117" s="2" t="n"/>
+      <c r="G117" s="8" t="n">
+        <v>4760</v>
+      </c>
       <c r="H117" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A117,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A117,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8226,7 +8238,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K117" s="5" t="n"/>
+      <c r="K117" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L117" s="16">
         <f>IF(OR($K117="",D117=""),"",IF(COUNTIFS($B:$B,$B117,$A:$A,$K117,D:D,"&gt;=0")=0,"",D117-SUMIFS(D:D,$B:$B,$B117,$A:$A,$K117)))</f>
         <v/>
@@ -8246,11 +8260,11 @@
     </row>
     <row r="118">
       <c r="A118" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -8259,7 +8273,9 @@
         </is>
       </c>
       <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
+      <c r="E118" s="7" t="n">
+        <v>305</v>
+      </c>
       <c r="F118" s="2" t="n"/>
       <c r="G118" s="2" t="n"/>
       <c r="H118" s="9">
@@ -8270,7 +8286,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A118,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J118" s="2" t="n"/>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K118" s="5" t="n"/>
       <c r="L118" s="16">
         <f>IF(OR($K118="",D118=""),"",IF(COUNTIFS($B:$B,$B118,$A:$A,$K118,D:D,"&gt;=0")=0,"",D118-SUMIFS(D:D,$B:$B,$B118,$A:$A,$K118)))</f>
@@ -8291,24 +8311,28 @@
     </row>
     <row r="119">
       <c r="A119" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="n"/>
-      <c r="E119" s="2" t="n"/>
-      <c r="F119" s="8" t="n">
-        <v>900</v>
-      </c>
-      <c r="G119" s="2" t="n"/>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>144.25</v>
+      </c>
+      <c r="E119" s="7" t="n">
+        <v>122.99</v>
+      </c>
+      <c r="F119" s="2" t="n"/>
+      <c r="G119" s="8" t="n">
+        <v>2860</v>
+      </c>
       <c r="H119" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A119,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A119,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8322,7 +8346,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K119" s="5" t="n"/>
+      <c r="K119" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L119" s="16">
         <f>IF(OR($K119="",D119=""),"",IF(COUNTIFS($B:$B,$B119,$A:$A,$K119,D:D,"&gt;=0")=0,"",D119-SUMIFS(D:D,$B:$B,$B119,$A:$A,$K119)))</f>
         <v/>
@@ -8342,11 +8368,11 @@
     </row>
     <row r="120">
       <c r="A120" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -8354,8 +8380,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
+      <c r="D120" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E120" s="7" t="n">
+        <v>135</v>
+      </c>
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
       <c r="H120" s="9">
@@ -8366,7 +8396,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A120,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J120" s="2" t="n"/>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K120" s="5" t="n"/>
       <c r="L120" s="16">
         <f>IF(OR($K120="",D120=""),"",IF(COUNTIFS($B:$B,$B120,$A:$A,$K120,D:D,"&gt;=0")=0,"",D120-SUMIFS(D:D,$B:$B,$B120,$A:$A,$K120)))</f>
@@ -8387,23 +8421,27 @@
     </row>
     <row r="121">
       <c r="A121" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n"/>
-      <c r="E121" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E121" s="7" t="n">
+        <v>59.99</v>
+      </c>
       <c r="F121" s="2" t="n"/>
       <c r="G121" s="8" t="n">
-        <v>2300</v>
+        <v>2150</v>
       </c>
       <c r="H121" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A121,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A121,Dólar!$A:$A,0))),"")</f>
@@ -8418,7 +8456,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K121" s="5" t="n"/>
+      <c r="K121" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L121" s="16">
         <f>IF(OR($K121="",D121=""),"",IF(COUNTIFS($B:$B,$B121,$A:$A,$K121,D:D,"&gt;=0")=0,"",D121-SUMIFS(D:D,$B:$B,$B121,$A:$A,$K121)))</f>
         <v/>
@@ -8438,11 +8478,11 @@
     </row>
     <row r="122">
       <c r="A122" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -8450,11 +8490,15 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D122" s="2" t="n"/>
-      <c r="E122" s="2" t="n"/>
+      <c r="D122" s="7" t="n">
+        <v>164.49</v>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>136.99</v>
+      </c>
       <c r="F122" s="2" t="n"/>
       <c r="G122" s="8" t="n">
-        <v>3950</v>
+        <v>2520</v>
       </c>
       <c r="H122" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A122,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A122,Dólar!$A:$A,0))),"")</f>
@@ -8469,7 +8513,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K122" s="5" t="n"/>
+      <c r="K122" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L122" s="16">
         <f>IF(OR($K122="",D122=""),"",IF(COUNTIFS($B:$B,$B122,$A:$A,$K122,D:D,"&gt;=0")=0,"",D122-SUMIFS(D:D,$B:$B,$B122,$A:$A,$K122)))</f>
         <v/>
@@ -8489,23 +8535,25 @@
     </row>
     <row r="123">
       <c r="A123" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="n"/>
-      <c r="E123" s="2" t="n"/>
-      <c r="F123" s="8" t="n">
-        <v>6200</v>
-      </c>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>259.78</v>
+      </c>
+      <c r="E123" s="7" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="F123" s="2" t="n"/>
       <c r="G123" s="2" t="n"/>
       <c r="H123" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A123,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A123,Dólar!$A:$A,0))),"")</f>
@@ -8520,7 +8568,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K123" s="5" t="n"/>
+      <c r="K123" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L123" s="16">
         <f>IF(OR($K123="",D123=""),"",IF(COUNTIFS($B:$B,$B123,$A:$A,$K123,D:D,"&gt;=0")=0,"",D123-SUMIFS(D:D,$B:$B,$B123,$A:$A,$K123)))</f>
         <v/>
@@ -8538,8 +8588,722 @@
         <v/>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-12400F</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>119.95</v>
+      </c>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="8" t="n">
+        <v>2460</v>
+      </c>
+      <c r="H124" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A124,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A124,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I124" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A124,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n"/>
+      <c r="L124" s="16">
+        <f>IF(OR($K124="",D124=""),"",IF(COUNTIFS($B:$B,$B124,$A:$A,$K124,D:D,"&gt;=0")=0,"",D124-SUMIFS(D:D,$B:$B,$B124,$A:$A,$K124)))</f>
+        <v/>
+      </c>
+      <c r="M124" s="16">
+        <f>IF(OR($K124="",E124=""),"",IF(COUNTIFS($B:$B,$B124,$A:$A,$K124,E:E,"&gt;=0")=0,"",E124-SUMIFS(E:E,$B:$B,$B124,$A:$A,$K124)))</f>
+        <v/>
+      </c>
+      <c r="N124" s="16">
+        <f>IF(OR($K124="",F124=""),"",IF(COUNTIFS($B:$B,$B124,$A:$A,$K124,F:F,"&gt;=0")=0,"",F124-SUMIFS(F:F,$B:$B,$B124,$A:$A,$K124)))</f>
+        <v/>
+      </c>
+      <c r="O124" s="16">
+        <f>IF(OR($K124="",G124=""),"",IF(COUNTIFS($B:$B,$B124,$A:$A,$K124,G:G,"&gt;=0")=0,"",G124-SUMIFS(G:G,$B:$B,$B124,$A:$A,$K124)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>244.87</v>
+      </c>
+      <c r="E125" s="7" t="n">
+        <v>209.99</v>
+      </c>
+      <c r="F125" s="2" t="n"/>
+      <c r="G125" s="8" t="n">
+        <v>4290</v>
+      </c>
+      <c r="H125" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A125,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A125,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I125" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A125,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K125" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L125" s="16">
+        <f>IF(OR($K125="",D125=""),"",IF(COUNTIFS($B:$B,$B125,$A:$A,$K125,D:D,"&gt;=0")=0,"",D125-SUMIFS(D:D,$B:$B,$B125,$A:$A,$K125)))</f>
+        <v/>
+      </c>
+      <c r="M125" s="16">
+        <f>IF(OR($K125="",E125=""),"",IF(COUNTIFS($B:$B,$B125,$A:$A,$K125,E:E,"&gt;=0")=0,"",E125-SUMIFS(E:E,$B:$B,$B125,$A:$A,$K125)))</f>
+        <v/>
+      </c>
+      <c r="N125" s="16">
+        <f>IF(OR($K125="",F125=""),"",IF(COUNTIFS($B:$B,$B125,$A:$A,$K125,F:F,"&gt;=0")=0,"",F125-SUMIFS(F:F,$B:$B,$B125,$A:$A,$K125)))</f>
+        <v/>
+      </c>
+      <c r="O125" s="16">
+        <f>IF(OR($K125="",G125=""),"",IF(COUNTIFS($B:$B,$B125,$A:$A,$K125,G:G,"&gt;=0")=0,"",G125-SUMIFS(G:G,$B:$B,$B125,$A:$A,$K125)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>399.9</v>
+      </c>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A126,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A126,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I126" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A126,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K126" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="L126" s="16">
+        <f>IF(OR($K126="",D126=""),"",IF(COUNTIFS($B:$B,$B126,$A:$A,$K126,D:D,"&gt;=0")=0,"",D126-SUMIFS(D:D,$B:$B,$B126,$A:$A,$K126)))</f>
+        <v/>
+      </c>
+      <c r="M126" s="16">
+        <f>IF(OR($K126="",E126=""),"",IF(COUNTIFS($B:$B,$B126,$A:$A,$K126,E:E,"&gt;=0")=0,"",E126-SUMIFS(E:E,$B:$B,$B126,$A:$A,$K126)))</f>
+        <v/>
+      </c>
+      <c r="N126" s="16">
+        <f>IF(OR($K126="",F126=""),"",IF(COUNTIFS($B:$B,$B126,$A:$A,$K126,F:F,"&gt;=0")=0,"",F126-SUMIFS(F:F,$B:$B,$B126,$A:$A,$K126)))</f>
+        <v/>
+      </c>
+      <c r="O126" s="16">
+        <f>IF(OR($K126="",G126=""),"",IF(COUNTIFS($B:$B,$B126,$A:$A,$K126,G:G,"&gt;=0")=0,"",G126-SUMIFS(G:G,$B:$B,$B126,$A:$A,$K126)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E127" s="7" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="F127" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G127" s="2" t="n"/>
+      <c r="H127" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A127,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A127,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I127" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A127,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n"/>
+      <c r="L127" s="16">
+        <f>IF(OR($K127="",D127=""),"",IF(COUNTIFS($B:$B,$B127,$A:$A,$K127,D:D,"&gt;=0")=0,"",D127-SUMIFS(D:D,$B:$B,$B127,$A:$A,$K127)))</f>
+        <v/>
+      </c>
+      <c r="M127" s="16">
+        <f>IF(OR($K127="",E127=""),"",IF(COUNTIFS($B:$B,$B127,$A:$A,$K127,E:E,"&gt;=0")=0,"",E127-SUMIFS(E:E,$B:$B,$B127,$A:$A,$K127)))</f>
+        <v/>
+      </c>
+      <c r="N127" s="16">
+        <f>IF(OR($K127="",F127=""),"",IF(COUNTIFS($B:$B,$B127,$A:$A,$K127,F:F,"&gt;=0")=0,"",F127-SUMIFS(F:F,$B:$B,$B127,$A:$A,$K127)))</f>
+        <v/>
+      </c>
+      <c r="O127" s="16">
+        <f>IF(OR($K127="",G127=""),"",IF(COUNTIFS($B:$B,$B127,$A:$A,$K127,G:G,"&gt;=0")=0,"",G127-SUMIFS(G:G,$B:$B,$B127,$A:$A,$K127)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="n"/>
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A128,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A128,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I128" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A128,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J128" s="2" t="n"/>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="16">
+        <f>IF(OR($K128="",D128=""),"",IF(COUNTIFS($B:$B,$B128,$A:$A,$K128,D:D,"&gt;=0")=0,"",D128-SUMIFS(D:D,$B:$B,$B128,$A:$A,$K128)))</f>
+        <v/>
+      </c>
+      <c r="M128" s="16">
+        <f>IF(OR($K128="",E128=""),"",IF(COUNTIFS($B:$B,$B128,$A:$A,$K128,E:E,"&gt;=0")=0,"",E128-SUMIFS(E:E,$B:$B,$B128,$A:$A,$K128)))</f>
+        <v/>
+      </c>
+      <c r="N128" s="16">
+        <f>IF(OR($K128="",F128=""),"",IF(COUNTIFS($B:$B,$B128,$A:$A,$K128,F:F,"&gt;=0")=0,"",F128-SUMIFS(F:F,$B:$B,$B128,$A:$A,$K128)))</f>
+        <v/>
+      </c>
+      <c r="O128" s="16">
+        <f>IF(OR($K128="",G128=""),"",IF(COUNTIFS($B:$B,$B128,$A:$A,$K128,G:G,"&gt;=0")=0,"",G128-SUMIFS(G:G,$B:$B,$B128,$A:$A,$K128)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>SSD</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
+      <c r="F129" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="G129" s="2" t="n"/>
+      <c r="H129" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A129,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A129,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I129" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A129,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n"/>
+      <c r="L129" s="16">
+        <f>IF(OR($K129="",D129=""),"",IF(COUNTIFS($B:$B,$B129,$A:$A,$K129,D:D,"&gt;=0")=0,"",D129-SUMIFS(D:D,$B:$B,$B129,$A:$A,$K129)))</f>
+        <v/>
+      </c>
+      <c r="M129" s="16">
+        <f>IF(OR($K129="",E129=""),"",IF(COUNTIFS($B:$B,$B129,$A:$A,$K129,E:E,"&gt;=0")=0,"",E129-SUMIFS(E:E,$B:$B,$B129,$A:$A,$K129)))</f>
+        <v/>
+      </c>
+      <c r="N129" s="16">
+        <f>IF(OR($K129="",F129=""),"",IF(COUNTIFS($B:$B,$B129,$A:$A,$K129,F:F,"&gt;=0")=0,"",F129-SUMIFS(F:F,$B:$B,$B129,$A:$A,$K129)))</f>
+        <v/>
+      </c>
+      <c r="O129" s="16">
+        <f>IF(OR($K129="",G129=""),"",IF(COUNTIFS($B:$B,$B129,$A:$A,$K129,G:G,"&gt;=0")=0,"",G129-SUMIFS(G:G,$B:$B,$B129,$A:$A,$K129)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 9 9950X</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="8" t="n">
+        <v>5580</v>
+      </c>
+      <c r="H130" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A130,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A130,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I130" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A130,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n"/>
+      <c r="L130" s="16">
+        <f>IF(OR($K130="",D130=""),"",IF(COUNTIFS($B:$B,$B130,$A:$A,$K130,D:D,"&gt;=0")=0,"",D130-SUMIFS(D:D,$B:$B,$B130,$A:$A,$K130)))</f>
+        <v/>
+      </c>
+      <c r="M130" s="16">
+        <f>IF(OR($K130="",E130=""),"",IF(COUNTIFS($B:$B,$B130,$A:$A,$K130,E:E,"&gt;=0")=0,"",E130-SUMIFS(E:E,$B:$B,$B130,$A:$A,$K130)))</f>
+        <v/>
+      </c>
+      <c r="N130" s="16">
+        <f>IF(OR($K130="",F130=""),"",IF(COUNTIFS($B:$B,$B130,$A:$A,$K130,F:F,"&gt;=0")=0,"",F130-SUMIFS(F:F,$B:$B,$B130,$A:$A,$K130)))</f>
+        <v/>
+      </c>
+      <c r="O130" s="16">
+        <f>IF(OR($K130="",G130=""),"",IF(COUNTIFS($B:$B,$B130,$A:$A,$K130,G:G,"&gt;=0")=0,"",G130-SUMIFS(G:G,$B:$B,$B130,$A:$A,$K130)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
+      <c r="F131" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G131" s="2" t="n"/>
+      <c r="H131" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A131,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A131,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I131" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A131,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n"/>
+      <c r="L131" s="16">
+        <f>IF(OR($K131="",D131=""),"",IF(COUNTIFS($B:$B,$B131,$A:$A,$K131,D:D,"&gt;=0")=0,"",D131-SUMIFS(D:D,$B:$B,$B131,$A:$A,$K131)))</f>
+        <v/>
+      </c>
+      <c r="M131" s="16">
+        <f>IF(OR($K131="",E131=""),"",IF(COUNTIFS($B:$B,$B131,$A:$A,$K131,E:E,"&gt;=0")=0,"",E131-SUMIFS(E:E,$B:$B,$B131,$A:$A,$K131)))</f>
+        <v/>
+      </c>
+      <c r="N131" s="16">
+        <f>IF(OR($K131="",F131=""),"",IF(COUNTIFS($B:$B,$B131,$A:$A,$K131,F:F,"&gt;=0")=0,"",F131-SUMIFS(F:F,$B:$B,$B131,$A:$A,$K131)))</f>
+        <v/>
+      </c>
+      <c r="O131" s="16">
+        <f>IF(OR($K131="",G131=""),"",IF(COUNTIFS($B:$B,$B131,$A:$A,$K131,G:G,"&gt;=0")=0,"",G131-SUMIFS(G:G,$B:$B,$B131,$A:$A,$K131)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="n"/>
+      <c r="H132" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A132,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A132,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I132" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A132,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J132" s="2" t="n"/>
+      <c r="K132" s="5" t="n"/>
+      <c r="L132" s="16">
+        <f>IF(OR($K132="",D132=""),"",IF(COUNTIFS($B:$B,$B132,$A:$A,$K132,D:D,"&gt;=0")=0,"",D132-SUMIFS(D:D,$B:$B,$B132,$A:$A,$K132)))</f>
+        <v/>
+      </c>
+      <c r="M132" s="16">
+        <f>IF(OR($K132="",E132=""),"",IF(COUNTIFS($B:$B,$B132,$A:$A,$K132,E:E,"&gt;=0")=0,"",E132-SUMIFS(E:E,$B:$B,$B132,$A:$A,$K132)))</f>
+        <v/>
+      </c>
+      <c r="N132" s="16">
+        <f>IF(OR($K132="",F132=""),"",IF(COUNTIFS($B:$B,$B132,$A:$A,$K132,F:F,"&gt;=0")=0,"",F132-SUMIFS(F:F,$B:$B,$B132,$A:$A,$K132)))</f>
+        <v/>
+      </c>
+      <c r="O132" s="16">
+        <f>IF(OR($K132="",G132=""),"",IF(COUNTIFS($B:$B,$B132,$A:$A,$K132,G:G,"&gt;=0")=0,"",G132-SUMIFS(G:G,$B:$B,$B132,$A:$A,$K132)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A133,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A133,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I133" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A133,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n"/>
+      <c r="L133" s="16">
+        <f>IF(OR($K133="",D133=""),"",IF(COUNTIFS($B:$B,$B133,$A:$A,$K133,D:D,"&gt;=0")=0,"",D133-SUMIFS(D:D,$B:$B,$B133,$A:$A,$K133)))</f>
+        <v/>
+      </c>
+      <c r="M133" s="16">
+        <f>IF(OR($K133="",E133=""),"",IF(COUNTIFS($B:$B,$B133,$A:$A,$K133,E:E,"&gt;=0")=0,"",E133-SUMIFS(E:E,$B:$B,$B133,$A:$A,$K133)))</f>
+        <v/>
+      </c>
+      <c r="N133" s="16">
+        <f>IF(OR($K133="",F133=""),"",IF(COUNTIFS($B:$B,$B133,$A:$A,$K133,F:F,"&gt;=0")=0,"",F133-SUMIFS(F:F,$B:$B,$B133,$A:$A,$K133)))</f>
+        <v/>
+      </c>
+      <c r="O133" s="16">
+        <f>IF(OR($K133="",G133=""),"",IF(COUNTIFS($B:$B,$B133,$A:$A,$K133,G:G,"&gt;=0")=0,"",G133-SUMIFS(G:G,$B:$B,$B133,$A:$A,$K133)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="n"/>
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A134,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A134,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I134" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A134,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J134" s="2" t="n"/>
+      <c r="K134" s="5" t="n"/>
+      <c r="L134" s="16">
+        <f>IF(OR($K134="",D134=""),"",IF(COUNTIFS($B:$B,$B134,$A:$A,$K134,D:D,"&gt;=0")=0,"",D134-SUMIFS(D:D,$B:$B,$B134,$A:$A,$K134)))</f>
+        <v/>
+      </c>
+      <c r="M134" s="16">
+        <f>IF(OR($K134="",E134=""),"",IF(COUNTIFS($B:$B,$B134,$A:$A,$K134,E:E,"&gt;=0")=0,"",E134-SUMIFS(E:E,$B:$B,$B134,$A:$A,$K134)))</f>
+        <v/>
+      </c>
+      <c r="N134" s="16">
+        <f>IF(OR($K134="",F134=""),"",IF(COUNTIFS($B:$B,$B134,$A:$A,$K134,F:F,"&gt;=0")=0,"",F134-SUMIFS(F:F,$B:$B,$B134,$A:$A,$K134)))</f>
+        <v/>
+      </c>
+      <c r="O134" s="16">
+        <f>IF(OR($K134="",G134=""),"",IF(COUNTIFS($B:$B,$B134,$A:$A,$K134,G:G,"&gt;=0")=0,"",G134-SUMIFS(G:G,$B:$B,$B134,$A:$A,$K134)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+      <c r="F135" s="2" t="n"/>
+      <c r="G135" s="8" t="n">
+        <v>2300</v>
+      </c>
+      <c r="H135" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A135,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A135,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I135" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A135,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n"/>
+      <c r="L135" s="16">
+        <f>IF(OR($K135="",D135=""),"",IF(COUNTIFS($B:$B,$B135,$A:$A,$K135,D:D,"&gt;=0")=0,"",D135-SUMIFS(D:D,$B:$B,$B135,$A:$A,$K135)))</f>
+        <v/>
+      </c>
+      <c r="M135" s="16">
+        <f>IF(OR($K135="",E135=""),"",IF(COUNTIFS($B:$B,$B135,$A:$A,$K135,E:E,"&gt;=0")=0,"",E135-SUMIFS(E:E,$B:$B,$B135,$A:$A,$K135)))</f>
+        <v/>
+      </c>
+      <c r="N135" s="16">
+        <f>IF(OR($K135="",F135=""),"",IF(COUNTIFS($B:$B,$B135,$A:$A,$K135,F:F,"&gt;=0")=0,"",F135-SUMIFS(F:F,$B:$B,$B135,$A:$A,$K135)))</f>
+        <v/>
+      </c>
+      <c r="O135" s="16">
+        <f>IF(OR($K135="",G135=""),"",IF(COUNTIFS($B:$B,$B135,$A:$A,$K135,G:G,"&gt;=0")=0,"",G135-SUMIFS(G:G,$B:$B,$B135,$A:$A,$K135)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="n"/>
+      <c r="F136" s="2" t="n"/>
+      <c r="G136" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H136" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A136,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A136,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I136" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A136,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n"/>
+      <c r="L136" s="16">
+        <f>IF(OR($K136="",D136=""),"",IF(COUNTIFS($B:$B,$B136,$A:$A,$K136,D:D,"&gt;=0")=0,"",D136-SUMIFS(D:D,$B:$B,$B136,$A:$A,$K136)))</f>
+        <v/>
+      </c>
+      <c r="M136" s="16">
+        <f>IF(OR($K136="",E136=""),"",IF(COUNTIFS($B:$B,$B136,$A:$A,$K136,E:E,"&gt;=0")=0,"",E136-SUMIFS(E:E,$B:$B,$B136,$A:$A,$K136)))</f>
+        <v/>
+      </c>
+      <c r="N136" s="16">
+        <f>IF(OR($K136="",F136=""),"",IF(COUNTIFS($B:$B,$B136,$A:$A,$K136,F:F,"&gt;=0")=0,"",F136-SUMIFS(F:F,$B:$B,$B136,$A:$A,$K136)))</f>
+        <v/>
+      </c>
+      <c r="O136" s="16">
+        <f>IF(OR($K136="",G136=""),"",IF(COUNTIFS($B:$B,$B136,$A:$A,$K136,G:G,"&gt;=0")=0,"",G136-SUMIFS(G:G,$B:$B,$B136,$A:$A,$K136)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G137" s="2" t="n"/>
+      <c r="H137" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A137,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A137,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I137" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A137,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n"/>
+      <c r="L137" s="16">
+        <f>IF(OR($K137="",D137=""),"",IF(COUNTIFS($B:$B,$B137,$A:$A,$K137,D:D,"&gt;=0")=0,"",D137-SUMIFS(D:D,$B:$B,$B137,$A:$A,$K137)))</f>
+        <v/>
+      </c>
+      <c r="M137" s="16">
+        <f>IF(OR($K137="",E137=""),"",IF(COUNTIFS($B:$B,$B137,$A:$A,$K137,E:E,"&gt;=0")=0,"",E137-SUMIFS(E:E,$B:$B,$B137,$A:$A,$K137)))</f>
+        <v/>
+      </c>
+      <c r="N137" s="16">
+        <f>IF(OR($K137="",F137=""),"",IF(COUNTIFS($B:$B,$B137,$A:$A,$K137,F:F,"&gt;=0")=0,"",F137-SUMIFS(F:F,$B:$B,$B137,$A:$A,$K137)))</f>
+        <v/>
+      </c>
+      <c r="O137" s="16">
+        <f>IF(OR($K137="",G137=""),"",IF(COUNTIFS($B:$B,$B137,$A:$A,$K137,G:G,"&gt;=0")=0,"",G137-SUMIFS(G:G,$B:$B,$B137,$A:$A,$K137)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M123">
+  <conditionalFormatting sqref="L2:M137">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -8547,7 +9311,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O123">
+  <conditionalFormatting sqref="N2:O137">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -8668,17 +9432,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId133"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId120"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId134"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8843,7 +9621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9146,6 +9924,32 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>11.84</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="E12" s="10">
+        <f>IF(COUNT(C12:D12)=2,AVERAGE(C12:D12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>BCB oficial 11.70 (bcb.gob.bo); paralelo dolarbolivia.net 20/10 07:55 (compra 11.84 / venta 11.82); usado = promedio del paralelo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9157,7 +9961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H326"/>
+  <dimension ref="A1:H351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -18144,34 +18948,34 @@
     </row>
     <row r="237">
       <c r="A237" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E237" s="11" t="n">
-        <v>5580</v>
+        <v>138.9</v>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G237" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor 3c_wholesaler 99.1%; (New) AMD Ryzen 5 5600 Vermeer Zen3 6-Core 12-Thread AM4 CPU</t>
         </is>
       </c>
       <c r="H237" s="6" t="inlineStr">
@@ -18182,34 +18986,34 @@
     </row>
     <row r="238">
       <c r="A238" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E238" s="11" t="n">
-        <v>2300</v>
+        <v>213.95</v>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G238" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor bra_dewaa 99.7%; AMD Ryzen 5 7600 6-Core 12-Thread Unlocked Desktop Processor</t>
         </is>
       </c>
       <c r="H238" s="6" t="inlineStr">
@@ -18220,34 +19024,34 @@
     </row>
     <row r="239">
       <c r="A239" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C239" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
-        <v>3950</v>
+        <v>324.99</v>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G239" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay API; vendedor geoelectronics7 99.4%; AMD Ryzen 7 7800X3D 100-00000910 - Processor No Cooler</t>
         </is>
       </c>
       <c r="H239" s="6" t="inlineStr">
@@ -18258,34 +19062,34 @@
     </row>
     <row r="240">
       <c r="A240" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C240" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E240" s="11" t="n">
-        <v>4800</v>
+        <v>549.99</v>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G240" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay API; vendedor newegg 99.6%; AMD Ryzen 9 9950X - Ryzen 9 9000 Series Granite Ridge (Zen 5</t>
         </is>
       </c>
       <c r="H240" s="6" t="inlineStr">
@@ -18296,34 +19100,34 @@
     </row>
     <row r="241">
       <c r="A241" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C241" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
-        <v>5190</v>
+        <v>150</v>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G241" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor algonz1137 100.0%; INTEL CPU Core i5-12400F / 6/12 / 2.5GHz / 6xxChipset / BX80; envío no indicado</t>
         </is>
       </c>
       <c r="H241" s="6" t="inlineStr">
@@ -18334,34 +19138,34 @@
     </row>
     <row r="242">
       <c r="A242" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C242" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E242" s="11" t="n">
-        <v>5390</v>
+        <v>164.49</v>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G242" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t xml:space="preserve">eBay API; vendedor newegg 99.6%; Intel Core i5-14400F - Core i5 14th Gen Raptor Lake 10-Core </t>
         </is>
       </c>
       <c r="H242" s="6" t="inlineStr">
@@ -18372,34 +19176,34 @@
     </row>
     <row r="243">
       <c r="A243" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C243" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E243" s="11" t="n">
-        <v>2000</v>
+        <v>244.88</v>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G243" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor astomore 100.0%; Intel Core Ultra 7 Processor 265K with 20 Cores and Up to 5.</t>
         </is>
       </c>
       <c r="H243" s="6" t="inlineStr">
@@ -18410,34 +19214,34 @@
     </row>
     <row r="244">
       <c r="A244" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C244" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E244" s="11" t="n">
-        <v>2650</v>
+        <v>479.99</v>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G244" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>eBay API; vendedor 2012roms 100.0%; Corsair Vengeance 32GB (2x16GB) DDR5 5600MHz CL36 Desktop RA; envío no indicado</t>
         </is>
       </c>
       <c r="H244" s="6" t="inlineStr">
@@ -18448,34 +19252,34 @@
     </row>
     <row r="245">
       <c r="A245" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C245" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E245" s="11" t="n">
-        <v>2700</v>
+        <v>444.99</v>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G245" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>eBay API; vendedor monksflips 99.8%; Corsair Vengeance RGB 32GB (2x16GB) RAM DDR5 6000MHz Z30K</t>
         </is>
       </c>
       <c r="H245" s="6" t="inlineStr">
@@ -18486,34 +19290,34 @@
     </row>
     <row r="246">
       <c r="A246" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C246" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E246" s="11" t="n">
-        <v>6200</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G246" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t>eBay API; vendedor supnahllc 99.8%; XPG 16GB 2X8GB 3200MHz DDR4 Kit-NEW; envío no indicado</t>
         </is>
       </c>
       <c r="H246" s="6" t="inlineStr">
@@ -18524,34 +19328,34 @@
     </row>
     <row r="247">
       <c r="A247" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C247" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
-        <v>540</v>
+        <v>114.99</v>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G247" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>eBay API; vendedor gadgetworld03 98.9%; Derlar DN-850Q 1TB M.2 NVME PCIe 4.0 SSD - New</t>
         </is>
       </c>
       <c r="H247" s="6" t="inlineStr">
@@ -18562,34 +19366,34 @@
     </row>
     <row r="248">
       <c r="A248" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C248" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E248" s="11" t="n">
-        <v>900</v>
+        <v>163.11</v>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G248" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>eBay API; vendedor tratg 99.3%; SSD Internal Solid State Drive 2TB M.2 NVMe SSD 2280 - Up To</t>
         </is>
       </c>
       <c r="H248" s="6" t="inlineStr">
@@ -18600,34 +19404,34 @@
     </row>
     <row r="249">
       <c r="A249" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C249" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
-        <v>1500</v>
+        <v>129.99</v>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G249" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>eBay API; vendedor paymore_cary 99.7%; AMD Ryzen 5 5600 3.50GHz 6 Core 100-000000927 12 Thread AM4</t>
         </is>
       </c>
       <c r="H249" s="6" t="inlineStr">
@@ -18638,34 +19442,34 @@
     </row>
     <row r="250">
       <c r="A250" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C250" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E250" s="11" t="n">
-        <v>1500</v>
+        <v>336</v>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G250" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>eBay API; vendedor jariah_tomko 100.0%; AMD Ryzen 7 5700X3D 8-Core 16-Thread AM4 CPU | 96MB 3D V-Cac; envío no indicado</t>
         </is>
       </c>
       <c r="H250" s="6" t="inlineStr">
@@ -18676,34 +19480,34 @@
     </row>
     <row r="251">
       <c r="A251" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C251" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
-        <v>1850</v>
+        <v>120</v>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G251" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>eBay API; vendedor shenidss9ckq 99.1%; AMD Ryzen 5 7600 3.80GHz 6 Core 100-000001015 12 Thread AM5</t>
         </is>
       </c>
       <c r="H251" s="6" t="inlineStr">
@@ -18714,34 +19518,34 @@
     </row>
     <row r="252">
       <c r="A252" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C252" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E252" s="11" t="n">
-        <v>2000</v>
+        <v>289.99</v>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G252" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>eBay API; vendedor cole_x 100.0%; AMD Ryzen 7 7800X3D Processor/ CPU (8-Core 4.2GHz - 104MB - ; envío no indicado</t>
         </is>
       </c>
       <c r="H252" s="6" t="inlineStr">
@@ -18752,34 +19556,34 @@
     </row>
     <row r="253">
       <c r="A253" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C253" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
-        <v>1800</v>
+        <v>454.99</v>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G253" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>eBay API; vendedor goodios_direct 99.6%; **  AMD Ryzen 9 9950X Processor - USED  **</t>
         </is>
       </c>
       <c r="H253" s="6" t="inlineStr">
@@ -18790,34 +19594,34 @@
     </row>
     <row r="254">
       <c r="A254" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C254" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E254" s="11" t="n">
-        <v>3550</v>
+        <v>124.99</v>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G254" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>eBay API; vendedor silencedpp7 100.0%; Intel Core i5-12400F 2.50GHz 6 Core SRL4W 12 Thread LGA 1700; envío no indicado</t>
         </is>
       </c>
       <c r="H254" s="6" t="inlineStr">
@@ -18828,34 +19632,34 @@
     </row>
     <row r="255">
       <c r="A255" s="15" t="n">
-        <v>46307</v>
+        <v>46315</v>
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C255" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E255" s="11" t="n">
-        <v>5664</v>
+        <v>150</v>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G255" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>eBay API; vendedor bargdeals65 99.7%; Intel Core i5-13400 SRMBP 2.5GHz 10-Cores 16 Threads 20MB Ca; envío no indicado</t>
         </is>
       </c>
       <c r="H255" s="6" t="inlineStr">
@@ -18866,11 +19670,11 @@
     </row>
     <row r="256">
       <c r="A256" s="15" t="n">
-        <v>46307</v>
+        <v>46315</v>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C256" s="5" t="inlineStr">
@@ -18880,20 +19684,20 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E256" s="11" t="n">
-        <v>2537</v>
+        <v>134.99</v>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G256" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>eBay API; vendedor paymore_pooler 99.7%; Intel Core i5-14400F 2.50GHz 10 Core SRN3R 16 Thread LGA 170</t>
         </is>
       </c>
       <c r="H256" s="6" t="inlineStr">
@@ -18904,34 +19708,34 @@
     </row>
     <row r="257">
       <c r="A257" s="15" t="n">
-        <v>46307</v>
+        <v>46315</v>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C257" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E257" s="11" t="n">
-        <v>3127</v>
+        <v>379.99</v>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G257" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t>eBay API; vendedor nn-red 100.0%; Corsair Vengeance RGB Pro 32GB (2x16GB) RAM DDR5 5600MHz CMH; envío no indicado</t>
         </is>
       </c>
       <c r="H257" s="6" t="inlineStr">
@@ -18942,34 +19746,34 @@
     </row>
     <row r="258">
       <c r="A258" s="15" t="n">
-        <v>46307</v>
+        <v>46315</v>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C258" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E258" s="11" t="n">
-        <v>2150</v>
+        <v>399.99</v>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G258" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t xml:space="preserve">eBay API; vendedor allnighter1994 99.7%; Corsair Vengeance 32GB (2x16GB) DDR5 6000MHz CL36 WHITE RAM </t>
         </is>
       </c>
       <c r="H258" s="6" t="inlineStr">
@@ -18980,34 +19784,34 @@
     </row>
     <row r="259">
       <c r="A259" s="15" t="n">
-        <v>46307</v>
+        <v>46315</v>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C259" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E259" s="11" t="n">
-        <v>6140</v>
+        <v>69.95</v>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G259" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t>eBay API; vendedor custompc2005 99.4%; OLOy Warhawk RGB Sync 16GB (2 x 8GB) DDR4 3200MHz CL16 Deskt</t>
         </is>
       </c>
       <c r="H259" s="6" t="inlineStr">
@@ -19018,34 +19822,34 @@
     </row>
     <row r="260">
       <c r="A260" s="15" t="n">
-        <v>46307</v>
+        <v>46315</v>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C260" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E260" s="11" t="n">
-        <v>4760</v>
+        <v>90</v>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G260" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>eBay API; vendedor fabulouscomputers 98.3%; 1tb ssd nvme; envío no indicado</t>
         </is>
       </c>
       <c r="H260" s="6" t="inlineStr">
@@ -19056,34 +19860,34 @@
     </row>
     <row r="261">
       <c r="A261" s="15" t="n">
-        <v>46307</v>
+        <v>46315</v>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C261" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E261" s="11" t="n">
-        <v>6800</v>
+        <v>184.99</v>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G261" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay API; vendedor mmm-electronics 100.0%; Crucial P2 2TB NVMe M.2 2280 PCIe 3.0 SSD CT2000P2SSD8 - Tes; envío no indicado</t>
         </is>
       </c>
       <c r="H261" s="6" t="inlineStr">
@@ -19094,7 +19898,7 @@
     </row>
     <row r="262">
       <c r="A262" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
@@ -19103,16 +19907,16 @@
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E262" s="11" t="n">
-        <v>2100</v>
+        <v>5580</v>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
@@ -19121,7 +19925,7 @@
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H262" s="6" t="inlineStr">
@@ -19132,7 +19936,7 @@
     </row>
     <row r="263">
       <c r="A263" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
@@ -19141,16 +19945,16 @@
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
-        <v>1800</v>
+        <v>2300</v>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
@@ -19159,7 +19963,7 @@
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H263" s="6" t="inlineStr">
@@ -19170,25 +19974,25 @@
     </row>
     <row r="264">
       <c r="A264" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E264" s="11" t="n">
-        <v>4500</v>
+        <v>3950</v>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
@@ -19197,7 +20001,7 @@
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H264" s="6" t="inlineStr">
@@ -19208,25 +20012,25 @@
     </row>
     <row r="265">
       <c r="A265" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E265" s="11" t="n">
-        <v>6700</v>
+        <v>4800</v>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
@@ -19235,7 +20039,7 @@
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H265" s="6" t="inlineStr">
@@ -19246,25 +20050,25 @@
     </row>
     <row r="266">
       <c r="A266" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E266" s="11" t="n">
-        <v>2520</v>
+        <v>5190</v>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
@@ -19273,7 +20077,7 @@
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H266" s="6" t="inlineStr">
@@ -19284,25 +20088,25 @@
     </row>
     <row r="267">
       <c r="A267" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E267" s="11" t="n">
-        <v>4290</v>
+        <v>5390</v>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
@@ -19311,7 +20115,7 @@
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H267" s="6" t="inlineStr">
@@ -19322,11 +20126,11 @@
     </row>
     <row r="268">
       <c r="A268" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
@@ -19336,11 +20140,11 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E268" s="11" t="n">
-        <v>2860</v>
+        <v>2000</v>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
@@ -19349,7 +20153,7 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H268" s="6" t="inlineStr">
@@ -19360,25 +20164,25 @@
     </row>
     <row r="269">
       <c r="A269" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E269" s="11" t="n">
-        <v>2460</v>
+        <v>2650</v>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
@@ -19387,7 +20191,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H269" s="6" t="inlineStr">
@@ -19398,25 +20202,25 @@
     </row>
     <row r="270">
       <c r="A270" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E270" s="11" t="n">
-        <v>5360</v>
+        <v>2700</v>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
@@ -19425,7 +20229,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H270" s="6" t="inlineStr">
@@ -19436,25 +20240,25 @@
     </row>
     <row r="271">
       <c r="A271" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E271" s="11" t="n">
-        <v>1710</v>
+        <v>6200</v>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
@@ -19463,7 +20267,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H271" s="6" t="inlineStr">
@@ -19474,25 +20278,25 @@
     </row>
     <row r="272">
       <c r="A272" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E272" s="11" t="n">
-        <v>2310</v>
+        <v>540</v>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
@@ -19501,7 +20305,7 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H272" s="6" t="inlineStr">
@@ -19512,11 +20316,11 @@
     </row>
     <row r="273">
       <c r="A273" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C273" s="5" t="inlineStr">
@@ -19526,11 +20330,11 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E273" s="11" t="n">
-        <v>2160</v>
+        <v>900</v>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
@@ -19539,7 +20343,7 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H273" s="6" t="inlineStr">
@@ -19550,25 +20354,25 @@
     </row>
     <row r="274">
       <c r="A274" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E274" s="11" t="n">
-        <v>5360</v>
+        <v>1500</v>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
@@ -19577,7 +20381,7 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H274" s="6" t="inlineStr">
@@ -19588,25 +20392,25 @@
     </row>
     <row r="275">
       <c r="A275" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E275" s="11" t="n">
-        <v>5660</v>
+        <v>1500</v>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
@@ -19615,7 +20419,7 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H275" s="6" t="inlineStr">
@@ -19626,25 +20430,25 @@
     </row>
     <row r="276">
       <c r="A276" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E276" s="11" t="n">
-        <v>5860</v>
+        <v>1850</v>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
@@ -19653,7 +20457,7 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H276" s="6" t="inlineStr">
@@ -19664,11 +20468,11 @@
     </row>
     <row r="277">
       <c r="A277" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C277" s="5" t="inlineStr">
@@ -19678,11 +20482,11 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E277" s="11" t="n">
-        <v>1860</v>
+        <v>2000</v>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
@@ -19691,7 +20495,7 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H277" s="6" t="inlineStr">
@@ -19702,11 +20506,11 @@
     </row>
     <row r="278">
       <c r="A278" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C278" s="5" t="inlineStr">
@@ -19716,11 +20520,11 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E278" s="11" t="n">
-        <v>2060</v>
+        <v>1800</v>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
@@ -19729,7 +20533,7 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H278" s="6" t="inlineStr">
@@ -19740,25 +20544,25 @@
     </row>
     <row r="279">
       <c r="A279" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E279" s="11" t="n">
-        <v>2152</v>
+        <v>3550</v>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
@@ -19767,7 +20571,7 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H279" s="6" t="inlineStr">
@@ -19787,16 +20591,16 @@
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E280" s="11" t="n">
-        <v>4060</v>
+        <v>5664</v>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
@@ -19805,7 +20609,7 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H280" s="6" t="inlineStr">
@@ -19825,16 +20629,16 @@
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E281" s="11" t="n">
-        <v>4560</v>
+        <v>2537</v>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
@@ -19843,7 +20647,7 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H281" s="6" t="inlineStr">
@@ -19863,16 +20667,16 @@
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E282" s="11" t="n">
-        <v>5500</v>
+        <v>3127</v>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
@@ -19881,7 +20685,7 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H282" s="6" t="inlineStr">
@@ -19901,16 +20705,16 @@
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Compucenter (WhatsApp)</t>
         </is>
       </c>
       <c r="E283" s="11" t="n">
-        <v>2500</v>
+        <v>2150</v>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
@@ -19919,7 +20723,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
         </is>
       </c>
       <c r="H283" s="6" t="inlineStr">
@@ -19939,16 +20743,16 @@
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E284" s="11" t="n">
-        <v>5200</v>
+        <v>6140</v>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
@@ -19957,7 +20761,7 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+          <t>nuevo OEM (garantía 6 meses)</t>
         </is>
       </c>
       <c r="H284" s="6" t="inlineStr">
@@ -19968,7 +20772,7 @@
     </row>
     <row r="285">
       <c r="A285" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
@@ -19982,11 +20786,11 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E285" s="11" t="n">
-        <v>5500</v>
+        <v>4760</v>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
@@ -19995,14 +20799,18 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
-        </is>
-      </c>
-      <c r="H285" s="2" t="n"/>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+        </is>
+      </c>
+      <c r="H285" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
@@ -20011,16 +20819,16 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E286" s="11" t="n">
-        <v>2460</v>
+        <v>6800</v>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
@@ -20029,14 +20837,18 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H286" s="2" t="n"/>
+          <t>no indicado</t>
+        </is>
+      </c>
+      <c r="H286" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
@@ -20045,16 +20857,16 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E287" s="11" t="n">
-        <v>2500</v>
+        <v>2100</v>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
@@ -20063,14 +20875,18 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H287" s="2" t="n"/>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H287" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
@@ -20079,16 +20895,16 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E288" s="11" t="n">
-        <v>6840</v>
+        <v>1800</v>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
@@ -20097,14 +20913,18 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
-        </is>
-      </c>
-      <c r="H288" s="2" t="n"/>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H288" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
@@ -20113,16 +20933,16 @@
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E289" s="11" t="n">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
@@ -20131,7 +20951,7 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
         </is>
       </c>
       <c r="H289" s="6" t="inlineStr">
@@ -20142,7 +20962,7 @@
     </row>
     <row r="290">
       <c r="A290" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
@@ -20151,16 +20971,16 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E290" s="11" t="n">
-        <v>5350</v>
+        <v>6700</v>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
@@ -20169,32 +20989,36 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
-        </is>
-      </c>
-      <c r="H290" s="2" t="n"/>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+        </is>
+      </c>
+      <c r="H290" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E291" s="11" t="n">
-        <v>7400</v>
+        <v>2520</v>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
@@ -20203,7 +21027,7 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+          <t>disponible (web)</t>
         </is>
       </c>
       <c r="H291" s="6" t="inlineStr">
@@ -20214,7 +21038,7 @@
     </row>
     <row r="292">
       <c r="A292" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
@@ -20223,16 +21047,16 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (web)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E292" s="11" t="n">
-        <v>2953</v>
+        <v>4290</v>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
@@ -20241,7 +21065,7 @@
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
         </is>
       </c>
       <c r="H292" s="6" t="inlineStr">
@@ -20252,7 +21076,7 @@
     </row>
     <row r="293">
       <c r="A293" s="15" t="n">
-        <v>46309</v>
+        <v>46307</v>
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
@@ -20261,16 +21085,16 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900K</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Crazy Store (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E293" s="11" t="n">
-        <v>6013</v>
+        <v>2860</v>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
@@ -20279,14 +21103,18 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H293" s="2" t="n"/>
+          <t>stock bajo (web)</t>
+        </is>
+      </c>
+      <c r="H293" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
@@ -20295,16 +21123,16 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E294" s="11" t="n">
-        <v>5890</v>
+        <v>2460</v>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
@@ -20313,14 +21141,18 @@
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
-        </is>
-      </c>
-      <c r="H294" s="2" t="n"/>
+          <t>disponible (web)</t>
+        </is>
+      </c>
+      <c r="H294" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
@@ -20329,16 +21161,16 @@
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E295" s="11" t="n">
-        <v>3080</v>
+        <v>5360</v>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
@@ -20347,14 +21179,18 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
-        </is>
-      </c>
-      <c r="H295" s="2" t="n"/>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H295" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
@@ -20363,16 +21199,16 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E296" s="11" t="n">
-        <v>3650</v>
+        <v>1710</v>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
@@ -20381,14 +21217,18 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H296" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H296" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
@@ -20397,16 +21237,16 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>PC Factor (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E297" s="11" t="n">
-        <v>3792</v>
+        <v>2310</v>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
@@ -20415,14 +21255,18 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H297" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H297" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B298" s="5" t="inlineStr">
         <is>
@@ -20431,16 +21275,16 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E298" s="11" t="n">
-        <v>2800</v>
+        <v>2160</v>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
@@ -20449,14 +21293,18 @@
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="H298" s="2" t="n"/>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+        </is>
+      </c>
+      <c r="H298" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
@@ -20465,16 +21313,16 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E299" s="11" t="n">
-        <v>2260</v>
+        <v>5360</v>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
@@ -20483,14 +21331,18 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H299" s="2" t="n"/>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H299" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
@@ -20499,16 +21351,16 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E300" s="11" t="n">
-        <v>2750</v>
+        <v>5660</v>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
@@ -20517,14 +21369,18 @@
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
-        </is>
-      </c>
-      <c r="H300" s="2" t="n"/>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H300" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
@@ -20533,16 +21389,16 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7700X</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E301" s="11" t="n">
-        <v>3480</v>
+        <v>5860</v>
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
@@ -20551,14 +21407,18 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>sin confirmar si es sellado (se preguntó)</t>
-        </is>
-      </c>
-      <c r="H301" s="2" t="n"/>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H301" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
@@ -20567,16 +21427,16 @@
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E302" s="11" t="n">
-        <v>2900</v>
+        <v>1860</v>
       </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
@@ -20585,14 +21445,18 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
-        </is>
-      </c>
-      <c r="H302" s="2" t="n"/>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H302" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
@@ -20606,11 +21470,11 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E303" s="11" t="n">
-        <v>1754</v>
+        <v>2060</v>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
@@ -20619,14 +21483,18 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
-        </is>
-      </c>
-      <c r="H303" s="2" t="n"/>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H303" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
@@ -20635,16 +21503,16 @@
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E304" s="11" t="n">
-        <v>2785</v>
+        <v>2152</v>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
@@ -20653,14 +21521,18 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H304" s="2" t="n"/>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H304" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
@@ -20669,16 +21541,16 @@
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E305" s="11" t="n">
-        <v>1778</v>
+        <v>4060</v>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
@@ -20687,14 +21559,18 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H305" s="2" t="n"/>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H305" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="15" t="n">
-        <v>46310</v>
+        <v>46307</v>
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
@@ -20703,16 +21579,16 @@
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E306" s="11" t="n">
-        <v>1600</v>
+        <v>4560</v>
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
@@ -20721,14 +21597,18 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H306" s="2" t="n"/>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H306" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
@@ -20737,16 +21617,16 @@
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E307" s="11" t="n">
-        <v>2500</v>
+        <v>5500</v>
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
@@ -20755,32 +21635,36 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
-        </is>
-      </c>
-      <c r="H307" s="2" t="n"/>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H307" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E308" s="11" t="n">
-        <v>1730</v>
+        <v>2500</v>
       </c>
       <c r="F308" s="5" t="inlineStr">
         <is>
@@ -20789,7 +21673,7 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H308" s="6" t="inlineStr">
@@ -20800,7 +21684,7 @@
     </row>
     <row r="309">
       <c r="A309" s="15" t="n">
-        <v>46311</v>
+        <v>46307</v>
       </c>
       <c r="B309" s="5" t="inlineStr">
         <is>
@@ -20809,16 +21693,16 @@
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E309" s="11" t="n">
-        <v>2384</v>
+        <v>5200</v>
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
@@ -20827,7 +21711,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H309" s="6" t="inlineStr">
@@ -20838,7 +21722,7 @@
     </row>
     <row r="310">
       <c r="A310" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B310" s="5" t="inlineStr">
         <is>
@@ -20852,11 +21736,11 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E310" s="11" t="n">
-        <v>5664</v>
+        <v>5500</v>
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
@@ -20865,18 +21749,14 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>nuevo BOX (web: USD 480 a 11,80)</t>
-        </is>
-      </c>
-      <c r="H310" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B311" s="5" t="inlineStr">
         <is>
@@ -20885,16 +21765,16 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E311" s="11" t="n">
-        <v>2218</v>
+        <v>2460</v>
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
@@ -20903,18 +21783,14 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H311" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B312" s="5" t="inlineStr">
         <is>
@@ -20923,16 +21799,16 @@
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico (WhatsApp)</t>
+          <t>Soft Computers (WhatsApp)</t>
         </is>
       </c>
       <c r="E312" s="11" t="n">
-        <v>2850</v>
+        <v>2500</v>
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
@@ -20941,14 +21817,14 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
+          <t>nuevo OEM</t>
         </is>
       </c>
       <c r="H312" s="2" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B313" s="5" t="inlineStr">
         <is>
@@ -20962,11 +21838,11 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico (WhatsApp)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E313" s="11" t="n">
-        <v>5960</v>
+        <v>6840</v>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
@@ -20975,32 +21851,32 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
         </is>
       </c>
       <c r="H313" s="2" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="15" t="n">
-        <v>46311</v>
+        <v>46308</v>
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Gamer Store Cbba (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
         </is>
       </c>
       <c r="E314" s="11" t="n">
-        <v>2067</v>
+        <v>4800</v>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
@@ -21009,32 +21885,36 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H314" s="2" t="n"/>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+        </is>
+      </c>
+      <c r="H314" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="15" t="n">
-        <v>46312</v>
+        <v>46308</v>
       </c>
       <c r="B315" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E315" s="11" t="n">
-        <v>1230</v>
+        <v>5350</v>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
@@ -21043,18 +21923,14 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
-        </is>
-      </c>
-      <c r="H315" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="15" t="n">
-        <v>46312</v>
+        <v>46309</v>
       </c>
       <c r="B316" s="5" t="inlineStr">
         <is>
@@ -21063,16 +21939,16 @@
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E316" s="11" t="n">
-        <v>1500</v>
+        <v>7400</v>
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
@@ -21081,7 +21957,7 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>sin dato de estado ni marca (recién publicado)</t>
+          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H316" s="6" t="inlineStr">
@@ -21092,25 +21968,25 @@
     </row>
     <row r="317">
       <c r="A317" s="15" t="n">
-        <v>46312</v>
+        <v>46309</v>
       </c>
       <c r="B317" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C317" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Geek Store Bolivia (web)</t>
         </is>
       </c>
       <c r="E317" s="11" t="n">
-        <v>1850</v>
+        <v>2953</v>
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
@@ -21119,7 +21995,7 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>Kingston NV3 1TB (estado sin dato)</t>
+          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H317" s="6" t="inlineStr">
@@ -21130,7 +22006,7 @@
     </row>
     <row r="318">
       <c r="A318" s="15" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B318" s="5" t="inlineStr">
         <is>
@@ -21139,16 +22015,16 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Intel Core i9-14900K</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Crazy Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E318" s="11" t="n">
-        <v>2726</v>
+        <v>6013</v>
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
@@ -21157,32 +22033,32 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: otro modelo (Crucial BX500 2TB es SATA, no NVMe; nuevo; lista mayorista USD 230 × 11,85 del 12/10, sin factura; 35 en stock; garantía solo de prueba; solo referencia)</t>
+          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B319" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>SMART CUBE (WhatsApp)</t>
         </is>
       </c>
       <c r="E319" s="11" t="n">
-        <v>1800</v>
+        <v>5890</v>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
@@ -21191,36 +22067,32 @@
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: otro modelo (es 5600X, solo procesador, recién publicado)</t>
-        </is>
-      </c>
-      <c r="H319" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B320" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>SMART CUBE (WhatsApp)</t>
         </is>
       </c>
       <c r="E320" s="11" t="n">
-        <v>1800</v>
+        <v>3080</v>
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
@@ -21229,36 +22101,32 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: otro modelo (i5-13400F, precio fijo)</t>
-        </is>
-      </c>
-      <c r="H320" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B321" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>SMART CUBE (WhatsApp)</t>
         </is>
       </c>
       <c r="E321" s="11" t="n">
-        <v>2600</v>
+        <v>3650</v>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
@@ -21267,36 +22135,32 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: otro modelo (i5-14400 sin F)</t>
-        </is>
-      </c>
-      <c r="H321" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>RAM DDR5 16GB</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>PC Factor (WhatsApp)</t>
         </is>
       </c>
       <c r="E322" s="11" t="n">
-        <v>5800</v>
+        <v>3792</v>
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
@@ -21305,36 +22169,32 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB 2x16 6000 MHz (estado sin dato)</t>
-        </is>
-      </c>
-      <c r="H322" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E323" s="11" t="n">
-        <v>2500</v>
+        <v>2800</v>
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
@@ -21343,36 +22203,32 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>Lexar NM790 1TB con disipador (estado sin dato)</t>
-        </is>
-      </c>
-      <c r="H323" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>OEM</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B324" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
         </is>
       </c>
       <c r="E324" s="11" t="n">
-        <v>2050</v>
+        <v>2260</v>
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
@@ -21381,18 +22237,14 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>WD Green SN3000 1TB (estado sin dato)</t>
-        </is>
-      </c>
-      <c r="H324" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B325" s="5" t="inlineStr">
         <is>
@@ -21401,16 +22253,16 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
         </is>
       </c>
       <c r="E325" s="11" t="n">
-        <v>2800</v>
+        <v>2750</v>
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
@@ -21419,44 +22271,946 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (reconfirmado 16:09)</t>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
         </is>
       </c>
       <c r="H325" s="2" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B326" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C326" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7700X</t>
+        </is>
+      </c>
+      <c r="D326" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E326" s="11" t="n">
+        <v>3480</v>
+      </c>
+      <c r="F326" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G326" s="5" t="inlineStr">
+        <is>
+          <t>sin confirmar si es sellado (se preguntó)</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B327" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C327" s="5" t="inlineStr">
+        <is>
+          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+        </is>
+      </c>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>Geek Store Bolivia (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E327" s="11" t="n">
+        <v>2900</v>
+      </c>
+      <c r="F327" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G327" s="5" t="inlineStr">
+        <is>
+          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B328" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C328" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D328" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E328" s="11" t="n">
+        <v>1754</v>
+      </c>
+      <c r="F328" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G328" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B329" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C329" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D329" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E329" s="11" t="n">
+        <v>2785</v>
+      </c>
+      <c r="F329" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G329" s="5" t="inlineStr">
+        <is>
+          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B330" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C330" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D330" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E330" s="11" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F330" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G330" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B331" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C331" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D331" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E331" s="11" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F331" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G331" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B332" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C332" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D332" s="5" t="inlineStr">
+        <is>
+          <t>Soft Computers (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E332" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F332" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G332" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B333" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C333" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D333" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba</t>
+        </is>
+      </c>
+      <c r="E333" s="11" t="n">
+        <v>1730</v>
+      </c>
+      <c r="F333" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G333" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+        </is>
+      </c>
+      <c r="H333" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B334" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C334" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D334" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E334" s="11" t="n">
+        <v>2384</v>
+      </c>
+      <c r="F334" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G334" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
+        </is>
+      </c>
+      <c r="H334" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B335" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C335" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D335" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E335" s="11" t="n">
+        <v>5664</v>
+      </c>
+      <c r="F335" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G335" s="5" t="inlineStr">
+        <is>
+          <t>nuevo BOX (web: USD 480 a 11,80)</t>
+        </is>
+      </c>
+      <c r="H335" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B336" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C336" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D336" s="5" t="inlineStr">
+        <is>
+          <t>Cyrex Store (web)</t>
+        </is>
+      </c>
+      <c r="E336" s="11" t="n">
+        <v>2218</v>
+      </c>
+      <c r="F336" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G336" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H336" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B337" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C337" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D337" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E337" s="11" t="n">
+        <v>2850</v>
+      </c>
+      <c r="F337" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G337" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B338" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C338" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D338" s="5" t="inlineStr">
+        <is>
+          <t>Punto Tecnológico (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E338" s="11" t="n">
+        <v>5960</v>
+      </c>
+      <c r="F338" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G338" s="5" t="inlineStr">
+        <is>
+          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="15" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B339" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C339" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D339" s="5" t="inlineStr">
+        <is>
+          <t>Gamer Store Cbba (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E339" s="11" t="n">
+        <v>2067</v>
+      </c>
+      <c r="F339" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G339" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B340" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C340" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D340" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E340" s="11" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F340" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G340" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
+        </is>
+      </c>
+      <c r="H340" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B341" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D341" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E341" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F341" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G341" s="5" t="inlineStr">
+        <is>
+          <t>sin dato de estado ni marca (recién publicado)</t>
+        </is>
+      </c>
+      <c r="H341" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="15" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B342" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C342" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D342" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E342" s="11" t="n">
+        <v>1850</v>
+      </c>
+      <c r="F342" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G342" s="5" t="inlineStr">
+        <is>
+          <t>Kingston NV3 1TB (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H342" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="15" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B343" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C343" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 2TB</t>
+        </is>
+      </c>
+      <c r="D343" s="5" t="inlineStr">
+        <is>
+          <t>Shopping PC (catálogo PDF)</t>
+        </is>
+      </c>
+      <c r="E343" s="11" t="n">
+        <v>2726</v>
+      </c>
+      <c r="F343" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G343" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otro modelo (Crucial BX500 2TB es SATA, no NVMe; nuevo; lista mayorista USD 230 × 11,85 del 12/10, sin factura; 35 en stock; garantía solo de prueba; solo referencia)</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="15" t="n">
         <v>46314</v>
       </c>
-      <c r="B326" s="5" t="inlineStr">
+      <c r="B344" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C344" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 5600</t>
+        </is>
+      </c>
+      <c r="D344" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E344" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F344" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G344" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otro modelo (es 5600X, solo procesador, recién publicado)</t>
+        </is>
+      </c>
+      <c r="H344" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B345" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C345" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-13400</t>
+        </is>
+      </c>
+      <c r="D345" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E345" s="11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F345" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G345" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otro modelo (i5-13400F, precio fijo)</t>
+        </is>
+      </c>
+      <c r="H345" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B346" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C346" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core i5-14400F</t>
+        </is>
+      </c>
+      <c r="D346" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E346" s="11" t="n">
+        <v>2600</v>
+      </c>
+      <c r="F346" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G346" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otro modelo (i5-14400 sin F)</t>
+        </is>
+      </c>
+      <c r="H346" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B347" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C347" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="D347" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E347" s="11" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F347" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G347" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB 2x16 6000 MHz (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H347" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B348" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D348" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E348" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F348" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G348" s="5" t="inlineStr">
+        <is>
+          <t>Lexar NM790 1TB con disipador (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H348" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B349" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C349" s="5" t="inlineStr">
+        <is>
+          <t>SSD NVMe 1TB</t>
+        </is>
+      </c>
+      <c r="D349" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E349" s="11" t="n">
+        <v>2050</v>
+      </c>
+      <c r="F349" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G349" s="5" t="inlineStr">
+        <is>
+          <t>WD Green SN3000 1TB (estado sin dato)</t>
+        </is>
+      </c>
+      <c r="H349" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B350" s="5" t="inlineStr">
         <is>
           <t>Tienda</t>
         </is>
       </c>
-      <c r="C326" s="5" t="inlineStr">
+      <c r="C350" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 5 7600</t>
+        </is>
+      </c>
+      <c r="D350" s="5" t="inlineStr">
+        <is>
+          <t>OverCity (WhatsApp)</t>
+        </is>
+      </c>
+      <c r="E350" s="11" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F350" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G350" s="5" t="inlineStr">
+        <is>
+          <t>nuevo OEM (reconfirmado 16:09)</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="15" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B351" s="5" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="C351" s="5" t="inlineStr">
         <is>
           <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
-      <c r="D326" s="5" t="inlineStr">
+      <c r="D351" s="5" t="inlineStr">
         <is>
           <t>OverCity (WhatsApp)</t>
         </is>
       </c>
-      <c r="E326" s="11" t="n">
+      <c r="E351" s="11" t="n">
         <v>4100</v>
       </c>
-      <c r="F326" s="5" t="inlineStr">
+      <c r="F351" s="5" t="inlineStr">
         <is>
           <t>Bs</t>
         </is>
       </c>
-      <c r="G326" s="5" t="inlineStr">
+      <c r="G351" s="5" t="inlineStr">
         <is>
           <t>nuevo OEM</t>
         </is>
       </c>
-      <c r="H326" s="2" t="n"/>
+      <c r="H351" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21743,26 +23497,51 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId281"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId324"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId300"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId325"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H351" headerRowCount="1">
-  <autoFilter ref="A1:H351"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H355" headerRowCount="1">
+  <autoFilter ref="A1:H355"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -2055,7 +2055,9 @@
       <c r="E5" s="7" t="n">
         <v>289.99</v>
       </c>
-      <c r="F5" s="2" t="n"/>
+      <c r="F5" s="8" t="n">
+        <v>5390</v>
+      </c>
       <c r="G5" s="2" t="n"/>
       <c r="H5" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A5,Dólar!$A:$A,0))),"")</f>
@@ -2273,7 +2275,9 @@
       <c r="E9" s="7" t="n">
         <v>69.95</v>
       </c>
-      <c r="F9" s="2" t="n"/>
+      <c r="F9" s="8" t="n">
+        <v>1400</v>
+      </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A9,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A9,Dólar!$A:$A,0))),"")</f>
@@ -9961,7 +9965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H351"/>
+  <dimension ref="A1:H355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -23211,6 +23215,150 @@
         </is>
       </c>
       <c r="H351" s="2" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B352" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C352" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D352" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E352" s="11" t="n">
+        <v>5190</v>
+      </c>
+      <c r="F352" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G352" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: anuncio viejo (nuevo; publicado hace 13 semanas)</t>
+        </is>
+      </c>
+      <c r="H352" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B353" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C353" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 7800X3D</t>
+        </is>
+      </c>
+      <c r="D353" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E353" s="11" t="n">
+        <v>5390</v>
+      </c>
+      <c r="F353" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G353" s="5" t="inlineStr">
+        <is>
+          <t>nuevo (anuncio 'El mejor para Gaming'; disponible)</t>
+        </is>
+      </c>
+      <c r="H353" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B354" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C354" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="D354" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace La Paz (particular)</t>
+        </is>
+      </c>
+      <c r="E354" s="11" t="n">
+        <v>3950</v>
+      </c>
+      <c r="F354" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G354" s="5" t="inlineStr">
+        <is>
+          <t>no cuenta: otra ciudad (La Paz; nuevo)</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B355" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace</t>
+        </is>
+      </c>
+      <c r="C355" s="5" t="inlineStr">
+        <is>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
+        </is>
+      </c>
+      <c r="D355" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace Cochabamba (particular)</t>
+        </is>
+      </c>
+      <c r="E355" s="11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F355" s="5" t="inlineStr">
+        <is>
+          <t>Bs</t>
+        </is>
+      </c>
+      <c r="G355" s="5" t="inlineStr">
+        <is>
+          <t>2x8 = 16GB (marca y frecuencia sin dato; antes Bs 1.600; vuelve a aparecer)</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23538,10 +23686,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId322"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId323"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId326"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId325"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId327"/>
   </tableParts>
 </worksheet>
 </file>
--- a/importacion-cochabamba.xlsx
+++ b/importacion-cochabamba.xlsx
@@ -253,8 +253,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Hoy" displayName="Hoy" ref="A4:Q18" headerRowCount="1">
-  <autoFilter ref="A4:Q18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Hoy" displayName="Hoy" ref="A4:Q19" headerRowCount="1">
+  <autoFilter ref="A4:Q19"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Producto"/>
     <tableColumn id="2" name="Tipo"/>
@@ -279,8 +279,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O137" headerRowCount="1">
-  <autoFilter ref="A1:O137"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Historial" displayName="Historial" ref="A1:O139" headerRowCount="1">
+  <autoFilter ref="A1:O139"/>
   <tableColumns count="15">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Producto"/>
@@ -303,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H355" headerRowCount="1">
-  <autoFilter ref="A1:H355"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Movimientos" displayName="Movimientos" ref="A1:H366" headerRowCount="1">
+  <autoFilter ref="A1:H366"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Fecha"/>
     <tableColumn id="2" name="Origen"/>
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -850,7 +850,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -864,17 +864,19 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>244.88</v>
+        <v>199.99</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>239.99</v>
-      </c>
-      <c r="G6" s="2" t="n"/>
+        <v>169.99</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>4000</v>
+      </c>
       <c r="H6" s="8" t="n">
-        <v>3950</v>
+        <v>3480</v>
       </c>
       <c r="I6" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -885,7 +887,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="L6" s="11">
         <f>IF(D6="","",MIN(MAX(Supuestos!$B$5,CEILING((K6*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D6*Supuestos!$B$9))</f>
@@ -915,7 +917,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -929,19 +931,17 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>324.99</v>
+        <v>244.88</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>289.99</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>4800</v>
-      </c>
+        <v>239.99</v>
+      </c>
+      <c r="G7" s="2" t="n"/>
       <c r="H7" s="8" t="n">
-        <v>4760</v>
+        <v>3950</v>
       </c>
       <c r="I7" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -952,7 +952,7 @@
         <v/>
       </c>
       <c r="K7" s="8" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="L7" s="11">
         <f>IF(D7="","",MIN(MAX(Supuestos!$B$5,CEILING((K7*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D7*Supuestos!$B$9))</f>
@@ -982,7 +982,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -996,17 +996,19 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>150</v>
+        <v>324.99</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>124.99</v>
-      </c>
-      <c r="G8" s="2" t="n"/>
+        <v>289.99</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>4800</v>
+      </c>
       <c r="H8" s="8" t="n">
-        <v>2260</v>
+        <v>4760</v>
       </c>
       <c r="I8" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1017,7 +1019,7 @@
         <v/>
       </c>
       <c r="K8" s="8" t="n">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="L8" s="11">
         <f>IF(D8="","",MIN(MAX(Supuestos!$B$5,CEILING((K8*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D8*Supuestos!$B$9))</f>
@@ -1047,7 +1049,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1061,17 +1063,17 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>164.49</v>
+        <v>150</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>134.99</v>
+        <v>124.99</v>
       </c>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="8" t="n">
-        <v>2384</v>
+        <v>2260</v>
       </c>
       <c r="I9" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1112,12 +1114,12 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -1126,18 +1128,18 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>444.99</v>
+        <v>164.49</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="H10" s="2" t="n"/>
+        <v>134.99</v>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="8" t="n">
+        <v>2384</v>
+      </c>
       <c r="I10" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1147,7 +1149,7 @@
         <v/>
       </c>
       <c r="K10" s="8" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="L10" s="11">
         <f>IF(D10="","",MIN(MAX(Supuestos!$B$5,CEILING((K10*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D10*Supuestos!$B$9))</f>
@@ -1177,12 +1179,12 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1191,18 +1193,18 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>213.95</v>
+        <v>444.99</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="8" t="n">
-        <v>2800</v>
-      </c>
+        <v>399.99</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="H11" s="2" t="n"/>
       <c r="I11" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1212,7 +1214,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="n">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="L11" s="11">
         <f>IF(D11="","",MIN(MAX(Supuestos!$B$5,CEILING((K11*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D11*Supuestos!$B$9))</f>
@@ -1242,7 +1244,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1256,17 +1258,17 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>549.99</v>
+        <v>213.95</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>454.99</v>
+        <v>120</v>
       </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="8" t="n">
-        <v>5580</v>
+        <v>2800</v>
       </c>
       <c r="I12" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1307,12 +1309,12 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1321,19 +1323,17 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>77.98999999999999</v>
+        <v>549.99</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>69.95</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>900</v>
-      </c>
+        <v>454.99</v>
+      </c>
+      <c r="G13" s="2" t="n"/>
       <c r="H13" s="8" t="n">
-        <v>2150</v>
+        <v>5580</v>
       </c>
       <c r="I13" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1344,7 +1344,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="L13" s="11">
         <f>IF(D13="","",MIN(MAX(Supuestos!$B$5,CEILING((K13*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D13*Supuestos!$B$9))</f>
@@ -1374,12 +1374,12 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1388,19 +1388,19 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>114.99</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>90</v>
+        <v>69.95</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>1230</v>
+        <v>900</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>1754</v>
+        <v>2150</v>
       </c>
       <c r="I14" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
@@ -1411,7 +1411,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="L14" s="11">
         <f>IF(D14="","",MIN(MAX(Supuestos!$B$5,CEILING((K14*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D14*Supuestos!$B$9))</f>
@@ -1441,12 +1441,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1455,18 +1455,20 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>479.99</v>
+        <v>114.99</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>379.99</v>
+        <v>90</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H15" s="2" t="n"/>
+        <v>1230</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="I15" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1476,7 +1478,7 @@
         <v/>
       </c>
       <c r="K15" s="8" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="L15" s="11">
         <f>IF(D15="","",MIN(MAX(Supuestos!$B$5,CEILING((K15*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D15*Supuestos!$B$9))</f>
@@ -1506,12 +1508,12 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1520,18 +1522,18 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>259.78</v>
+        <v>479.99</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>150</v>
-      </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="8" t="n">
-        <v>2300</v>
-      </c>
+        <v>379.99</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>4500</v>
+      </c>
+      <c r="H16" s="2" t="n"/>
       <c r="I16" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1541,7 +1543,7 @@
         <v/>
       </c>
       <c r="K16" s="8" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="L16" s="11">
         <f>IF(D16="","",MIN(MAX(Supuestos!$B$5,CEILING((K16*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D16*Supuestos!$B$9))</f>
@@ -1571,7 +1573,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1585,16 +1587,18 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>138.9</v>
+        <v>259.78</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>129.99</v>
+        <v>150</v>
       </c>
       <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="H17" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="I17" s="9">
         <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
         <v/>
@@ -1604,7 +1608,7 @@
         <v/>
       </c>
       <c r="K17" s="8" t="n">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="L17" s="11">
         <f>IF(D17="","",MIN(MAX(Supuestos!$B$5,CEILING((K17*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D17*Supuestos!$B$9))</f>
@@ -1634,7 +1638,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1647,10 +1651,14 @@
           <t>ver en eBay</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
+      <c r="D18" s="7" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="F18" s="7" t="n">
-        <v>336</v>
+        <v>129.99</v>
       </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
@@ -1691,30 +1699,66 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Ryzen 7 5700X3D</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ver en eBay</t>
+        </is>
+      </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
+      <c r="F19" s="7" t="n">
+        <v>336</v>
+      </c>
       <c r="G19" s="2" t="n"/>
       <c r="H19" s="2" t="n"/>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n"/>
+      <c r="I19" s="9">
+        <f>INDEX(Dólar!$B:$B,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="J19" s="10">
+        <f>INDEX(Dólar!$E:$E,MATCH(MAX(Dólar!$A:$A),Dólar!$A:$A,0))</f>
+        <v/>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="L19" s="11">
+        <f>IF(D19="","",MIN(MAX(Supuestos!$B$5,CEILING((K19*Supuestos!$B$3+Supuestos!$B$7)/1000,Supuestos!$B$6))*Supuestos!$B$4/Supuestos!$B$3,Supuestos!$B$8+D19*Supuestos!$B$9))</f>
+        <v/>
+      </c>
+      <c r="M19" s="12">
+        <f>IF(D19="","",(D19+E19+L19+(D19+E19)*Supuestos!$B$10)*Supuestos!$B$11)</f>
+        <v/>
+      </c>
+      <c r="N19" s="12">
+        <f>IF(COUNT(G19:H19)=0,"",MIN(G19:H19))</f>
+        <v/>
+      </c>
+      <c r="O19" s="13">
+        <f>IF(OR(M19="",N19=""),"",N19-M19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="14">
+        <f>IF(O19="","",O19/N19)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="5">
+        <f>IF(P19="",IF(AND(D19="",N19=""),"Sin datos",IF(D19="","Sin precio eBay","Sin precio local")),IF(P19&gt;=Supuestos!$B$12,"Conviene",IF(P19&gt;=Supuestos!$B$13,"Justo","No conviene")))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Azul: datos de eBay, Marketplace y tiendas (de los CSV del repo). Negro: fórmulas. Para probar otros supuestos (unidades, aduana, dólar) cambia la hoja Supuestos.</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
       <c r="D20" s="2" t="n"/>
@@ -1732,8 +1776,31 @@
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Azul: datos de eBay, Marketplace y tiendas (de los CSV del repo). Negro: fórmulas. Para probar otros supuestos (unidades, aduana, dólar) cambia la hoja Supuestos.</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="Q5:Q18">
+  <conditionalFormatting sqref="Q5:Q19">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Conviene"</formula>
     </cfRule>
@@ -1759,10 +1826,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1773,7 +1841,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O137"/>
+  <dimension ref="A1:O139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2098,7 +2166,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -2106,12 +2174,18 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n"/>
+      <c r="D6" s="7" t="n">
+        <v>199.99</v>
+      </c>
       <c r="E6" s="7" t="n">
-        <v>336</v>
-      </c>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
+        <v>169.99</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>3667</v>
+      </c>
       <c r="H6" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A6,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A6,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2126,7 +2200,7 @@
         </is>
       </c>
       <c r="K6" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="L6" s="16">
         <f>IF(OR($K6="",D6=""),"",IF(COUNTIFS($B:$B,$B6,$A:$A,$K6,D:D,"&gt;=0")=0,"",D6-SUMIFS(D:D,$B:$B,$B6,$A:$A,$K6)))</f>
@@ -2151,7 +2225,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2159,11 +2233,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>213.95</v>
-      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="7" t="n">
-        <v>120</v>
+        <v>336</v>
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
@@ -2206,7 +2278,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2215,10 +2287,10 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>138.9</v>
+        <v>213.95</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>129.99</v>
+        <v>120</v>
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
@@ -2261,23 +2333,21 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>77.98999999999999</v>
+        <v>138.9</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>69.95</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>1400</v>
-      </c>
+        <v>129.99</v>
+      </c>
+      <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A9,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A9,Dólar!$A:$A,0))),"")</f>
@@ -2318,21 +2388,23 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>164.49</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>134.99</v>
-      </c>
-      <c r="F10" s="2" t="n"/>
+        <v>69.95</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>1400</v>
+      </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A10,Dólar!$A:$A,0))),"")</f>
@@ -2373,7 +2445,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2381,9 +2453,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="D11" s="7" t="n">
+        <v>164.49</v>
+      </c>
       <c r="E11" s="7" t="n">
-        <v>150</v>
+        <v>134.99</v>
       </c>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
@@ -2426,7 +2500,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -2434,11 +2508,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="7" t="n">
         <v>150</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>124.99</v>
       </c>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
@@ -2481,7 +2553,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2490,9 +2562,11 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>244.88</v>
-      </c>
-      <c r="E13" s="2" t="n"/>
+        <v>150</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>124.99</v>
+      </c>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="9">
@@ -2534,20 +2608,18 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>444.99</v>
-      </c>
-      <c r="E14" s="7" t="n">
-        <v>399.99</v>
-      </c>
+        <v>244.88</v>
+      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n"/>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="9">
@@ -2589,7 +2661,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2598,10 +2670,10 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>479.99</v>
+        <v>444.99</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>379.99</v>
+        <v>399.99</v>
       </c>
       <c r="F15" s="2" t="n"/>
       <c r="G15" s="2" t="n"/>
@@ -2640,23 +2712,23 @@
     </row>
     <row r="16">
       <c r="A16" s="15" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>209.99</v>
+        <v>479.99</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>154.99</v>
+        <v>379.99</v>
       </c>
       <c r="F16" s="2" t="n"/>
       <c r="G16" s="2" t="n"/>
@@ -2674,7 +2746,7 @@
         </is>
       </c>
       <c r="K16" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="L16" s="16">
         <f>IF(OR($K16="",D16=""),"",IF(COUNTIFS($B:$B,$B16,$A:$A,$K16,D:D,"&gt;=0")=0,"",D16-SUMIFS(D:D,$B:$B,$B16,$A:$A,$K16)))</f>
@@ -2699,7 +2771,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2708,14 +2780,12 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>117.94</v>
+        <v>209.99</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>2050</v>
-      </c>
+        <v>154.99</v>
+      </c>
+      <c r="F17" s="2" t="n"/>
       <c r="G17" s="2" t="n"/>
       <c r="H17" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A17,Dólar!$A:$A,0))),"")</f>
@@ -2756,21 +2826,23 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>549.99</v>
+        <v>117.94</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="F18" s="2" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>2050</v>
+      </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A18,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A18,Dólar!$A:$A,0))),"")</f>
@@ -2811,7 +2883,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2820,10 +2892,10 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>324.99</v>
+        <v>549.99</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>285</v>
+        <v>454.99</v>
       </c>
       <c r="F19" s="2" t="n"/>
       <c r="G19" s="2" t="n"/>
@@ -2866,7 +2938,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2874,9 +2946,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="D20" s="7" t="n">
+        <v>324.99</v>
+      </c>
       <c r="E20" s="7" t="n">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
@@ -2919,7 +2993,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2927,16 +3001,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
-        <v>140.26</v>
-      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" s="7" t="n">
-        <v>120</v>
+        <v>336</v>
       </c>
       <c r="F21" s="2" t="n"/>
-      <c r="G21" s="8" t="n">
-        <v>2800</v>
-      </c>
+      <c r="G21" s="2" t="n"/>
       <c r="H21" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A21,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -2976,7 +3046,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2985,13 +3055,15 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>138.9</v>
+        <v>140.26</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>107.99</v>
+        <v>120</v>
       </c>
       <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
+      <c r="G22" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H22" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A22,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A22,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3031,19 +3103,19 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>118.96</v>
+        <v>138.9</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>69.98999999999999</v>
+        <v>107.99</v>
       </c>
       <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="n"/>
@@ -3086,19 +3158,19 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>164.49</v>
+        <v>118.96</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>139.99</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F24" s="2" t="n"/>
       <c r="G24" s="2" t="n"/>
@@ -3141,7 +3213,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3149,9 +3221,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D25" s="2" t="n"/>
+      <c r="D25" s="7" t="n">
+        <v>164.49</v>
+      </c>
       <c r="E25" s="7" t="n">
-        <v>149.99</v>
+        <v>139.99</v>
       </c>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="2" t="n"/>
@@ -3194,7 +3268,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -3202,11 +3276,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D26" s="7" t="n">
-        <v>150</v>
-      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="7" t="n">
-        <v>124.99</v>
+        <v>149.99</v>
       </c>
       <c r="F26" s="2" t="n"/>
       <c r="G26" s="2" t="n"/>
@@ -3249,7 +3321,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3258,15 +3330,13 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>235.27</v>
+        <v>150</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>239.99</v>
+        <v>124.99</v>
       </c>
       <c r="F27" s="2" t="n"/>
-      <c r="G27" s="8" t="n">
-        <v>4100</v>
-      </c>
+      <c r="G27" s="2" t="n"/>
       <c r="H27" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A27,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A27,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3306,24 +3376,24 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>450</v>
+        <v>235.27</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>419.99</v>
-      </c>
-      <c r="F28" s="8" t="n">
-        <v>5800</v>
-      </c>
-      <c r="G28" s="2" t="n"/>
+        <v>239.99</v>
+      </c>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="8" t="n">
+        <v>4100</v>
+      </c>
       <c r="H28" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A28,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A28,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -3363,7 +3433,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3372,12 +3442,14 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>429.97</v>
+        <v>450</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>379.99</v>
-      </c>
-      <c r="F29" s="2" t="n"/>
+        <v>419.99</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>5800</v>
+      </c>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A29,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A29,Dólar!$A:$A,0))),"")</f>
@@ -3414,23 +3486,23 @@
     </row>
     <row r="30">
       <c r="A30" s="15" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>209.99</v>
+        <v>429.97</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>160</v>
+        <v>379.99</v>
       </c>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
@@ -3448,7 +3520,7 @@
         </is>
       </c>
       <c r="K30" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="L30" s="16">
         <f>IF(OR($K30="",D30=""),"",IF(COUNTIFS($B:$B,$B30,$A:$A,$K30,D:D,"&gt;=0")=0,"",D30-SUMIFS(D:D,$B:$B,$B30,$A:$A,$K30)))</f>
@@ -3473,7 +3545,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3482,10 +3554,10 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>93.5</v>
+        <v>209.99</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>96.94</v>
+        <v>160</v>
       </c>
       <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
@@ -3528,19 +3600,19 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>549.99</v>
+        <v>93.5</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>454.99</v>
+        <v>96.94</v>
       </c>
       <c r="F32" s="2" t="n"/>
       <c r="G32" s="2" t="n"/>
@@ -3583,7 +3655,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -3592,10 +3664,10 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>324.99</v>
+        <v>549.99</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>289.99</v>
+        <v>454.99</v>
       </c>
       <c r="F33" s="2" t="n"/>
       <c r="G33" s="2" t="n"/>
@@ -3638,7 +3710,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -3646,9 +3718,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="D34" s="7" t="n">
+        <v>324.99</v>
+      </c>
       <c r="E34" s="7" t="n">
-        <v>315</v>
+        <v>289.99</v>
       </c>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
@@ -3691,7 +3765,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -3699,11 +3773,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D35" s="7" t="n">
-        <v>213.95</v>
-      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" s="7" t="n">
-        <v>120</v>
+        <v>315</v>
       </c>
       <c r="F35" s="2" t="n"/>
       <c r="G35" s="2" t="n"/>
@@ -3746,7 +3818,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -3755,10 +3827,10 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>138.9</v>
+        <v>213.95</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>129.99</v>
+        <v>120</v>
       </c>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
@@ -3801,19 +3873,19 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>118.96</v>
+        <v>138.9</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>72.95</v>
+        <v>129.99</v>
       </c>
       <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="n"/>
@@ -3856,19 +3928,19 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>164.49</v>
+        <v>118.96</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>139.99</v>
+        <v>72.95</v>
       </c>
       <c r="F38" s="2" t="n"/>
       <c r="G38" s="2" t="n"/>
@@ -3911,7 +3983,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -3919,9 +3991,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="D39" s="7" t="n">
+        <v>164.49</v>
+      </c>
       <c r="E39" s="7" t="n">
-        <v>125</v>
+        <v>139.99</v>
       </c>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
@@ -3964,7 +4038,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -3972,11 +4046,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D40" s="7" t="n">
-        <v>150</v>
-      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" s="7" t="n">
-        <v>124.99</v>
+        <v>125</v>
       </c>
       <c r="F40" s="2" t="n"/>
       <c r="G40" s="2" t="n"/>
@@ -4019,7 +4091,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -4028,10 +4100,10 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>235.27</v>
+        <v>150</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>209.68</v>
+        <v>124.99</v>
       </c>
       <c r="F41" s="2" t="n"/>
       <c r="G41" s="2" t="n"/>
@@ -4074,19 +4146,19 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>450</v>
+        <v>235.27</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>419.99</v>
+        <v>209.68</v>
       </c>
       <c r="F42" s="2" t="n"/>
       <c r="G42" s="2" t="n"/>
@@ -4129,7 +4201,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -4138,10 +4210,10 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>429.97</v>
+        <v>450</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>379.99</v>
+        <v>419.99</v>
       </c>
       <c r="F43" s="2" t="n"/>
       <c r="G43" s="2" t="n"/>
@@ -4180,23 +4252,23 @@
     </row>
     <row r="44">
       <c r="A44" s="15" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>209.99</v>
+        <v>429.97</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>160</v>
+        <v>379.99</v>
       </c>
       <c r="F44" s="2" t="n"/>
       <c r="G44" s="2" t="n"/>
@@ -4214,7 +4286,7 @@
         </is>
       </c>
       <c r="K44" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="L44" s="16">
         <f>IF(OR($K44="",D44=""),"",IF(COUNTIFS($B:$B,$B44,$A:$A,$K44,D:D,"&gt;=0")=0,"",D44-SUMIFS(D:D,$B:$B,$B44,$A:$A,$K44)))</f>
@@ -4239,7 +4311,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -4248,14 +4320,12 @@
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>128.99</v>
+        <v>209.99</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>98.59</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>1230</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="n"/>
       <c r="H45" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A45,Dólar!$A:$A,0))),"")</f>
@@ -4296,21 +4366,23 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D46" s="7" t="n">
-        <v>549.99</v>
+        <v>128.99</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="F46" s="2" t="n"/>
+        <v>98.59</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>1230</v>
+      </c>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A46,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A46,Dólar!$A:$A,0))),"")</f>
@@ -4351,7 +4423,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -4360,10 +4432,10 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>324.99</v>
+        <v>549.99</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>275</v>
+        <v>454.99</v>
       </c>
       <c r="F47" s="2" t="n"/>
       <c r="G47" s="2" t="n"/>
@@ -4406,7 +4478,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -4414,9 +4486,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="D48" s="7" t="n">
+        <v>324.99</v>
+      </c>
       <c r="E48" s="7" t="n">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="F48" s="2" t="n"/>
       <c r="G48" s="2" t="n"/>
@@ -4459,7 +4533,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -4467,11 +4541,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D49" s="7" t="n">
-        <v>140.26</v>
-      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" s="7" t="n">
-        <v>120</v>
+        <v>315</v>
       </c>
       <c r="F49" s="2" t="n"/>
       <c r="G49" s="2" t="n"/>
@@ -4514,7 +4586,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -4523,10 +4595,10 @@
         </is>
       </c>
       <c r="D50" s="7" t="n">
-        <v>138.9</v>
+        <v>140.26</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>129.99</v>
+        <v>120</v>
       </c>
       <c r="F50" s="2" t="n"/>
       <c r="G50" s="2" t="n"/>
@@ -4569,19 +4641,19 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D51" s="7" t="n">
-        <v>118.96</v>
+        <v>138.9</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>71.95</v>
+        <v>129.99</v>
       </c>
       <c r="F51" s="2" t="n"/>
       <c r="G51" s="2" t="n"/>
@@ -4624,19 +4696,19 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D52" s="7" t="n">
-        <v>164.49</v>
+        <v>118.96</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>139.99</v>
+        <v>71.95</v>
       </c>
       <c r="F52" s="2" t="n"/>
       <c r="G52" s="2" t="n"/>
@@ -4679,7 +4751,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -4687,9 +4759,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="D53" s="7" t="n">
+        <v>164.49</v>
+      </c>
       <c r="E53" s="7" t="n">
-        <v>125</v>
+        <v>139.99</v>
       </c>
       <c r="F53" s="2" t="n"/>
       <c r="G53" s="2" t="n"/>
@@ -4732,7 +4806,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -4740,11 +4814,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D54" s="7" t="n">
-        <v>150</v>
-      </c>
+      <c r="D54" s="2" t="n"/>
       <c r="E54" s="7" t="n">
-        <v>120.99</v>
+        <v>125</v>
       </c>
       <c r="F54" s="2" t="n"/>
       <c r="G54" s="2" t="n"/>
@@ -4787,7 +4859,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -4796,10 +4868,10 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>235.27</v>
+        <v>150</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>229</v>
+        <v>120.99</v>
       </c>
       <c r="F55" s="2" t="n"/>
       <c r="G55" s="2" t="n"/>
@@ -4842,19 +4914,19 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>474.49</v>
+        <v>235.27</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>399.99</v>
+        <v>229</v>
       </c>
       <c r="F56" s="2" t="n"/>
       <c r="G56" s="2" t="n"/>
@@ -4897,7 +4969,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -4906,10 +4978,10 @@
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>429.97</v>
+        <v>474.49</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>375</v>
+        <v>399.99</v>
       </c>
       <c r="F57" s="2" t="n"/>
       <c r="G57" s="2" t="n"/>
@@ -4948,23 +5020,23 @@
     </row>
     <row r="58">
       <c r="A58" s="15" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D58" s="7" t="n">
-        <v>209.99</v>
+        <v>429.97</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>161.99</v>
+        <v>375</v>
       </c>
       <c r="F58" s="2" t="n"/>
       <c r="G58" s="2" t="n"/>
@@ -4982,7 +5054,7 @@
         </is>
       </c>
       <c r="K58" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="L58" s="16">
         <f>IF(OR($K58="",D58=""),"",IF(COUNTIFS($B:$B,$B58,$A:$A,$K58,D:D,"&gt;=0")=0,"",D58-SUMIFS(D:D,$B:$B,$B58,$A:$A,$K58)))</f>
@@ -5007,7 +5079,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -5016,14 +5088,12 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>110</v>
+        <v>209.99</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="F59" s="8" t="n">
-        <v>1730</v>
-      </c>
+        <v>161.99</v>
+      </c>
+      <c r="F59" s="2" t="n"/>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A59,Dólar!$A:$A,0))),"")</f>
@@ -5064,21 +5134,23 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>549.99</v>
+        <v>110</v>
       </c>
       <c r="E60" s="7" t="n">
-        <v>454.99</v>
-      </c>
-      <c r="F60" s="2" t="n"/>
+        <v>80</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>1730</v>
+      </c>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A60,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A60,Dólar!$A:$A,0))),"")</f>
@@ -5119,7 +5191,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -5128,15 +5200,13 @@
         </is>
       </c>
       <c r="D61" s="7" t="n">
-        <v>320</v>
+        <v>549.99</v>
       </c>
       <c r="E61" s="7" t="n">
-        <v>279.99</v>
+        <v>454.99</v>
       </c>
       <c r="F61" s="2" t="n"/>
-      <c r="G61" s="8" t="n">
-        <v>5664</v>
-      </c>
+      <c r="G61" s="2" t="n"/>
       <c r="H61" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A61,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5176,7 +5246,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -5184,12 +5254,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="D62" s="7" t="n">
+        <v>320</v>
+      </c>
       <c r="E62" s="7" t="n">
-        <v>298.01</v>
+        <v>279.99</v>
       </c>
       <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
+      <c r="G62" s="8" t="n">
+        <v>5664</v>
+      </c>
       <c r="H62" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A62,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A62,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5229,7 +5303,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -5237,16 +5311,12 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D63" s="7" t="n">
-        <v>141.24</v>
-      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" s="7" t="n">
-        <v>120</v>
+        <v>298.01</v>
       </c>
       <c r="F63" s="2" t="n"/>
-      <c r="G63" s="8" t="n">
-        <v>2850</v>
-      </c>
+      <c r="G63" s="2" t="n"/>
       <c r="H63" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A63,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5286,7 +5356,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -5295,13 +5365,15 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>138.9</v>
+        <v>141.24</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>129.99</v>
+        <v>120</v>
       </c>
       <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
+      <c r="G64" s="8" t="n">
+        <v>2850</v>
+      </c>
       <c r="H64" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A64,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A64,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5341,19 +5413,19 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D65" s="7" t="n">
-        <v>118.96</v>
+        <v>138.9</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>73.95</v>
+        <v>129.99</v>
       </c>
       <c r="F65" s="2" t="n"/>
       <c r="G65" s="2" t="n"/>
@@ -5396,24 +5468,22 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D66" s="7" t="n">
-        <v>164.49</v>
+        <v>118.96</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>139.99</v>
+        <v>73.95</v>
       </c>
       <c r="F66" s="2" t="n"/>
-      <c r="G66" s="8" t="n">
-        <v>2384</v>
-      </c>
+      <c r="G66" s="2" t="n"/>
       <c r="H66" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A66,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5453,7 +5523,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -5461,12 +5531,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D67" s="2" t="n"/>
+      <c r="D67" s="7" t="n">
+        <v>164.49</v>
+      </c>
       <c r="E67" s="7" t="n">
-        <v>149.99</v>
+        <v>139.99</v>
       </c>
       <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
+      <c r="G67" s="8" t="n">
+        <v>2384</v>
+      </c>
       <c r="H67" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A67,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A67,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5506,7 +5580,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -5514,11 +5588,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D68" s="7" t="n">
-        <v>150</v>
-      </c>
+      <c r="D68" s="2" t="n"/>
       <c r="E68" s="7" t="n">
-        <v>120.99</v>
+        <v>149.99</v>
       </c>
       <c r="F68" s="2" t="n"/>
       <c r="G68" s="2" t="n"/>
@@ -5561,7 +5633,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -5570,10 +5642,10 @@
         </is>
       </c>
       <c r="D69" s="7" t="n">
-        <v>234.99</v>
+        <v>150</v>
       </c>
       <c r="E69" s="7" t="n">
-        <v>229</v>
+        <v>120.99</v>
       </c>
       <c r="F69" s="2" t="n"/>
       <c r="G69" s="2" t="n"/>
@@ -5616,19 +5688,19 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D70" s="7" t="n">
-        <v>474.49</v>
+        <v>234.99</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>389.99</v>
+        <v>229</v>
       </c>
       <c r="F70" s="2" t="n"/>
       <c r="G70" s="2" t="n"/>
@@ -5671,7 +5743,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -5680,10 +5752,10 @@
         </is>
       </c>
       <c r="D71" s="7" t="n">
-        <v>429.97</v>
+        <v>474.49</v>
       </c>
       <c r="E71" s="7" t="n">
-        <v>379.99</v>
+        <v>389.99</v>
       </c>
       <c r="F71" s="2" t="n"/>
       <c r="G71" s="2" t="n"/>
@@ -5722,23 +5794,23 @@
     </row>
     <row r="72">
       <c r="A72" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D72" s="7" t="n">
-        <v>209.99</v>
+        <v>429.97</v>
       </c>
       <c r="E72" s="7" t="n">
-        <v>175</v>
+        <v>379.99</v>
       </c>
       <c r="F72" s="2" t="n"/>
       <c r="G72" s="2" t="n"/>
@@ -5756,7 +5828,7 @@
         </is>
       </c>
       <c r="K72" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="L72" s="16">
         <f>IF(OR($K72="",D72=""),"",IF(COUNTIFS($B:$B,$B72,$A:$A,$K72,D:D,"&gt;=0")=0,"",D72-SUMIFS(D:D,$B:$B,$B72,$A:$A,$K72)))</f>
@@ -5781,7 +5853,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -5790,15 +5862,13 @@
         </is>
       </c>
       <c r="D73" s="7" t="n">
-        <v>128.99</v>
+        <v>209.99</v>
       </c>
       <c r="E73" s="7" t="n">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="F73" s="2" t="n"/>
-      <c r="G73" s="8" t="n">
-        <v>1754</v>
-      </c>
+      <c r="G73" s="2" t="n"/>
       <c r="H73" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A73,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5838,22 +5908,24 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D74" s="7" t="n">
-        <v>689.34</v>
+        <v>128.99</v>
       </c>
       <c r="E74" s="7" t="n">
-        <v>375</v>
+        <v>80</v>
       </c>
       <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
+      <c r="G74" s="8" t="n">
+        <v>1754</v>
+      </c>
       <c r="H74" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A74,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A74,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5893,7 +5965,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -5902,15 +5974,13 @@
         </is>
       </c>
       <c r="D75" s="7" t="n">
-        <v>320</v>
+        <v>689.34</v>
       </c>
       <c r="E75" s="7" t="n">
-        <v>279.99</v>
+        <v>375</v>
       </c>
       <c r="F75" s="2" t="n"/>
-      <c r="G75" s="8" t="n">
-        <v>5890</v>
-      </c>
+      <c r="G75" s="2" t="n"/>
       <c r="H75" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A75,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -5950,7 +6020,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -5958,12 +6028,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D76" s="2" t="n"/>
+      <c r="D76" s="7" t="n">
+        <v>320</v>
+      </c>
       <c r="E76" s="7" t="n">
-        <v>295</v>
+        <v>279.99</v>
       </c>
       <c r="F76" s="2" t="n"/>
-      <c r="G76" s="2" t="n"/>
+      <c r="G76" s="8" t="n">
+        <v>5890</v>
+      </c>
       <c r="H76" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A76,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A76,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6003,7 +6077,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -6011,15 +6085,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D77" s="7" t="n">
-        <v>142.24</v>
-      </c>
-      <c r="E77" s="7" t="n">
-        <v>120</v>
-      </c>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="n"/>
       <c r="G77" s="8" t="n">
-        <v>2800</v>
+        <v>3480</v>
       </c>
       <c r="H77" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A77,Dólar!$A:$A,0))),"")</f>
@@ -6029,14 +6099,8 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A77,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>ver anuncio</t>
-        </is>
-      </c>
-      <c r="K77" s="15" t="n">
-        <v>46309</v>
-      </c>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="5" t="n"/>
       <c r="L77" s="16">
         <f>IF(OR($K77="",D77=""),"",IF(COUNTIFS($B:$B,$B77,$A:$A,$K77,D:D,"&gt;=0")=0,"",D77-SUMIFS(D:D,$B:$B,$B77,$A:$A,$K77)))</f>
         <v/>
@@ -6060,7 +6124,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -6068,11 +6132,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D78" s="7" t="n">
-        <v>138.9</v>
-      </c>
+      <c r="D78" s="2" t="n"/>
       <c r="E78" s="7" t="n">
-        <v>135</v>
+        <v>295</v>
       </c>
       <c r="F78" s="2" t="n"/>
       <c r="G78" s="2" t="n"/>
@@ -6115,22 +6177,24 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D79" s="7" t="n">
-        <v>75</v>
+        <v>142.24</v>
       </c>
       <c r="E79" s="7" t="n">
-        <v>73.95</v>
+        <v>120</v>
       </c>
       <c r="F79" s="2" t="n"/>
-      <c r="G79" s="2" t="n"/>
+      <c r="G79" s="8" t="n">
+        <v>2800</v>
+      </c>
       <c r="H79" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A79,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A79,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6170,7 +6234,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -6179,15 +6243,13 @@
         </is>
       </c>
       <c r="D80" s="7" t="n">
-        <v>164.49</v>
+        <v>138.9</v>
       </c>
       <c r="E80" s="7" t="n">
-        <v>134.99</v>
+        <v>135</v>
       </c>
       <c r="F80" s="2" t="n"/>
-      <c r="G80" s="8" t="n">
-        <v>2750</v>
-      </c>
+      <c r="G80" s="2" t="n"/>
       <c r="H80" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A80,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6227,17 +6289,19 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>75</v>
+      </c>
       <c r="E81" s="7" t="n">
-        <v>149.99</v>
+        <v>73.95</v>
       </c>
       <c r="F81" s="2" t="n"/>
       <c r="G81" s="2" t="n"/>
@@ -6280,7 +6344,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -6289,14 +6353,14 @@
         </is>
       </c>
       <c r="D82" s="7" t="n">
-        <v>150</v>
+        <v>164.49</v>
       </c>
       <c r="E82" s="7" t="n">
-        <v>114.99</v>
+        <v>134.99</v>
       </c>
       <c r="F82" s="2" t="n"/>
       <c r="G82" s="8" t="n">
-        <v>2260</v>
+        <v>2750</v>
       </c>
       <c r="H82" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A82,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A82,Dólar!$A:$A,0))),"")</f>
@@ -6337,7 +6401,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -6345,11 +6409,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D83" s="7" t="n">
-        <v>234.99</v>
-      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" s="7" t="n">
-        <v>229</v>
+        <v>149.99</v>
       </c>
       <c r="F83" s="2" t="n"/>
       <c r="G83" s="2" t="n"/>
@@ -6392,22 +6454,24 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D84" s="7" t="n">
-        <v>435.99</v>
+        <v>150</v>
       </c>
       <c r="E84" s="7" t="n">
-        <v>394.99</v>
+        <v>114.99</v>
       </c>
       <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
+      <c r="G84" s="8" t="n">
+        <v>2260</v>
+      </c>
       <c r="H84" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A84,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A84,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -6447,19 +6511,19 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D85" s="7" t="n">
-        <v>429.97</v>
+        <v>234.99</v>
       </c>
       <c r="E85" s="7" t="n">
-        <v>375</v>
+        <v>229</v>
       </c>
       <c r="F85" s="2" t="n"/>
       <c r="G85" s="2" t="n"/>
@@ -6498,23 +6562,23 @@
     </row>
     <row r="86">
       <c r="A86" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D86" s="7" t="n">
-        <v>209.99</v>
+        <v>435.99</v>
       </c>
       <c r="E86" s="7" t="n">
-        <v>164.99</v>
+        <v>394.99</v>
       </c>
       <c r="F86" s="2" t="n"/>
       <c r="G86" s="2" t="n"/>
@@ -6532,7 +6596,7 @@
         </is>
       </c>
       <c r="K86" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L86" s="16">
         <f>IF(OR($K86="",D86=""),"",IF(COUNTIFS($B:$B,$B86,$A:$A,$K86,D:D,"&gt;=0")=0,"",D86-SUMIFS(D:D,$B:$B,$B86,$A:$A,$K86)))</f>
@@ -6553,23 +6617,23 @@
     </row>
     <row r="87">
       <c r="A87" s="15" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D87" s="7" t="n">
-        <v>117.99</v>
+        <v>429.97</v>
       </c>
       <c r="E87" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>375</v>
       </c>
       <c r="F87" s="2" t="n"/>
       <c r="G87" s="2" t="n"/>
@@ -6587,7 +6651,7 @@
         </is>
       </c>
       <c r="K87" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="L87" s="16">
         <f>IF(OR($K87="",D87=""),"",IF(COUNTIFS($B:$B,$B87,$A:$A,$K87,D:D,"&gt;=0")=0,"",D87-SUMIFS(D:D,$B:$B,$B87,$A:$A,$K87)))</f>
@@ -6612,19 +6676,19 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D88" s="7" t="n">
-        <v>499.99</v>
+        <v>209.99</v>
       </c>
       <c r="E88" s="7" t="n">
-        <v>454.99</v>
+        <v>164.99</v>
       </c>
       <c r="F88" s="2" t="n"/>
       <c r="G88" s="2" t="n"/>
@@ -6667,19 +6731,19 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D89" s="7" t="n">
-        <v>329</v>
+        <v>117.99</v>
       </c>
       <c r="E89" s="7" t="n">
-        <v>275.99</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="F89" s="2" t="n"/>
       <c r="G89" s="2" t="n"/>
@@ -6722,7 +6786,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -6730,9 +6794,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="D90" s="7" t="n">
+        <v>499.99</v>
+      </c>
       <c r="E90" s="7" t="n">
-        <v>295</v>
+        <v>454.99</v>
       </c>
       <c r="F90" s="2" t="n"/>
       <c r="G90" s="2" t="n"/>
@@ -6775,7 +6841,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -6784,10 +6850,10 @@
         </is>
       </c>
       <c r="D91" s="7" t="n">
-        <v>142.24</v>
+        <v>329</v>
       </c>
       <c r="E91" s="7" t="n">
-        <v>121.99</v>
+        <v>275.99</v>
       </c>
       <c r="F91" s="2" t="n"/>
       <c r="G91" s="2" t="n"/>
@@ -6830,7 +6896,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -6838,11 +6904,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D92" s="7" t="n">
-        <v>138.9</v>
-      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" s="7" t="n">
-        <v>129.99</v>
+        <v>295</v>
       </c>
       <c r="F92" s="2" t="n"/>
       <c r="G92" s="2" t="n"/>
@@ -6885,19 +6949,19 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D93" s="7" t="n">
-        <v>72.98999999999999</v>
+        <v>142.24</v>
       </c>
       <c r="E93" s="7" t="n">
-        <v>65</v>
+        <v>121.99</v>
       </c>
       <c r="F93" s="2" t="n"/>
       <c r="G93" s="2" t="n"/>
@@ -6940,7 +7004,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -6949,10 +7013,10 @@
         </is>
       </c>
       <c r="D94" s="7" t="n">
-        <v>164.49</v>
+        <v>138.9</v>
       </c>
       <c r="E94" s="7" t="n">
-        <v>134</v>
+        <v>129.99</v>
       </c>
       <c r="F94" s="2" t="n"/>
       <c r="G94" s="2" t="n"/>
@@ -6995,17 +7059,19 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>72.98999999999999</v>
+      </c>
       <c r="E95" s="7" t="n">
-        <v>149.99</v>
+        <v>65</v>
       </c>
       <c r="F95" s="2" t="n"/>
       <c r="G95" s="2" t="n"/>
@@ -7048,7 +7114,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -7057,10 +7123,10 @@
         </is>
       </c>
       <c r="D96" s="7" t="n">
-        <v>150</v>
+        <v>164.49</v>
       </c>
       <c r="E96" s="7" t="n">
-        <v>120.99</v>
+        <v>134</v>
       </c>
       <c r="F96" s="2" t="n"/>
       <c r="G96" s="2" t="n"/>
@@ -7103,7 +7169,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -7111,11 +7177,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D97" s="7" t="n">
-        <v>234.99</v>
-      </c>
+      <c r="D97" s="2" t="n"/>
       <c r="E97" s="7" t="n">
-        <v>229</v>
+        <v>149.99</v>
       </c>
       <c r="F97" s="2" t="n"/>
       <c r="G97" s="2" t="n"/>
@@ -7158,19 +7222,19 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D98" s="7" t="n">
-        <v>435.99</v>
+        <v>150</v>
       </c>
       <c r="E98" s="7" t="n">
-        <v>399.9</v>
+        <v>120.99</v>
       </c>
       <c r="F98" s="2" t="n"/>
       <c r="G98" s="2" t="n"/>
@@ -7213,19 +7277,19 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D99" s="7" t="n">
-        <v>429.97</v>
+        <v>234.99</v>
       </c>
       <c r="E99" s="7" t="n">
-        <v>379.99</v>
+        <v>229</v>
       </c>
       <c r="F99" s="2" t="n"/>
       <c r="G99" s="2" t="n"/>
@@ -7264,23 +7328,23 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D100" s="7" t="n">
-        <v>209.99</v>
+        <v>435.99</v>
       </c>
       <c r="E100" s="7" t="n">
-        <v>170</v>
+        <v>399.9</v>
       </c>
       <c r="F100" s="2" t="n"/>
       <c r="G100" s="2" t="n"/>
@@ -7298,7 +7362,7 @@
         </is>
       </c>
       <c r="K100" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L100" s="16">
         <f>IF(OR($K100="",D100=""),"",IF(COUNTIFS($B:$B,$B100,$A:$A,$K100,D:D,"&gt;=0")=0,"",D100-SUMIFS(D:D,$B:$B,$B100,$A:$A,$K100)))</f>
@@ -7319,23 +7383,23 @@
     </row>
     <row r="101">
       <c r="A101" s="15" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D101" s="7" t="n">
-        <v>114.99</v>
+        <v>429.97</v>
       </c>
       <c r="E101" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>379.99</v>
       </c>
       <c r="F101" s="2" t="n"/>
       <c r="G101" s="2" t="n"/>
@@ -7353,7 +7417,7 @@
         </is>
       </c>
       <c r="K101" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L101" s="16">
         <f>IF(OR($K101="",D101=""),"",IF(COUNTIFS($B:$B,$B101,$A:$A,$K101,D:D,"&gt;=0")=0,"",D101-SUMIFS(D:D,$B:$B,$B101,$A:$A,$K101)))</f>
@@ -7378,19 +7442,19 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D102" s="7" t="n">
-        <v>499.99</v>
+        <v>209.99</v>
       </c>
       <c r="E102" s="7" t="n">
-        <v>454.99</v>
+        <v>170</v>
       </c>
       <c r="F102" s="2" t="n"/>
       <c r="G102" s="2" t="n"/>
@@ -7433,26 +7497,22 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D103" s="7" t="n">
-        <v>329</v>
+        <v>114.99</v>
       </c>
       <c r="E103" s="7" t="n">
-        <v>283.99</v>
-      </c>
-      <c r="F103" s="8" t="n">
-        <v>4800</v>
-      </c>
-      <c r="G103" s="8" t="n">
-        <v>5350</v>
-      </c>
+        <v>99.98999999999999</v>
+      </c>
+      <c r="F103" s="2" t="n"/>
+      <c r="G103" s="2" t="n"/>
       <c r="H103" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A103,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A103,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7492,7 +7552,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -7500,9 +7560,11 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="D104" s="7" t="n">
+        <v>499.99</v>
+      </c>
       <c r="E104" s="7" t="n">
-        <v>299.99</v>
+        <v>454.99</v>
       </c>
       <c r="F104" s="2" t="n"/>
       <c r="G104" s="2" t="n"/>
@@ -7545,7 +7607,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -7554,13 +7616,17 @@
         </is>
       </c>
       <c r="D105" s="7" t="n">
-        <v>143.24</v>
+        <v>329</v>
       </c>
       <c r="E105" s="7" t="n">
-        <v>122.99</v>
-      </c>
-      <c r="F105" s="2" t="n"/>
-      <c r="G105" s="2" t="n"/>
+        <v>283.99</v>
+      </c>
+      <c r="F105" s="8" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G105" s="8" t="n">
+        <v>5350</v>
+      </c>
       <c r="H105" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A105,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A105,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7600,7 +7666,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -7608,11 +7674,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D106" s="7" t="n">
-        <v>138.9</v>
-      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" s="7" t="n">
-        <v>135</v>
+        <v>299.99</v>
       </c>
       <c r="F106" s="2" t="n"/>
       <c r="G106" s="2" t="n"/>
@@ -7655,19 +7719,19 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D107" s="7" t="n">
-        <v>92.98999999999999</v>
+        <v>143.24</v>
       </c>
       <c r="E107" s="7" t="n">
-        <v>64.98999999999999</v>
+        <v>122.99</v>
       </c>
       <c r="F107" s="2" t="n"/>
       <c r="G107" s="2" t="n"/>
@@ -7710,7 +7774,7 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
@@ -7719,15 +7783,13 @@
         </is>
       </c>
       <c r="D108" s="7" t="n">
-        <v>164.49</v>
+        <v>138.9</v>
       </c>
       <c r="E108" s="7" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F108" s="2" t="n"/>
-      <c r="G108" s="8" t="n">
-        <v>2460</v>
-      </c>
+      <c r="G108" s="2" t="n"/>
       <c r="H108" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A108,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A108,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7767,17 +7829,19 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>92.98999999999999</v>
+      </c>
       <c r="E109" s="7" t="n">
-        <v>149.99</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F109" s="2" t="n"/>
       <c r="G109" s="2" t="n"/>
@@ -7820,7 +7884,7 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
@@ -7829,13 +7893,15 @@
         </is>
       </c>
       <c r="D110" s="7" t="n">
-        <v>150</v>
+        <v>164.49</v>
       </c>
       <c r="E110" s="7" t="n">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="n"/>
+      <c r="G110" s="8" t="n">
+        <v>2460</v>
+      </c>
       <c r="H110" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A110,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A110,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -7875,7 +7941,7 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
@@ -7883,11 +7949,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D111" s="7" t="n">
-        <v>234.99</v>
-      </c>
+      <c r="D111" s="2" t="n"/>
       <c r="E111" s="7" t="n">
-        <v>209.99</v>
+        <v>149.99</v>
       </c>
       <c r="F111" s="2" t="n"/>
       <c r="G111" s="2" t="n"/>
@@ -7930,19 +7994,19 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D112" s="7" t="n">
-        <v>435.99</v>
+        <v>150</v>
       </c>
       <c r="E112" s="7" t="n">
-        <v>399.9</v>
+        <v>99</v>
       </c>
       <c r="F112" s="2" t="n"/>
       <c r="G112" s="2" t="n"/>
@@ -7985,19 +8049,19 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D113" s="7" t="n">
-        <v>493</v>
+        <v>234.99</v>
       </c>
       <c r="E113" s="7" t="n">
-        <v>383.99</v>
+        <v>209.99</v>
       </c>
       <c r="F113" s="2" t="n"/>
       <c r="G113" s="2" t="n"/>
@@ -8036,28 +8100,26 @@
     </row>
     <row r="114">
       <c r="A114" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D114" s="7" t="n">
-        <v>209.99</v>
+        <v>435.99</v>
       </c>
       <c r="E114" s="7" t="n">
-        <v>179.99</v>
+        <v>399.9</v>
       </c>
       <c r="F114" s="2" t="n"/>
-      <c r="G114" s="8" t="n">
-        <v>4060</v>
-      </c>
+      <c r="G114" s="2" t="n"/>
       <c r="H114" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A114,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A114,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8072,7 +8134,7 @@
         </is>
       </c>
       <c r="K114" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L114" s="16">
         <f>IF(OR($K114="",D114=""),"",IF(COUNTIFS($B:$B,$B114,$A:$A,$K114,D:D,"&gt;=0")=0,"",D114-SUMIFS(D:D,$B:$B,$B114,$A:$A,$K114)))</f>
@@ -8093,28 +8155,26 @@
     </row>
     <row r="115">
       <c r="A115" s="15" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D115" s="7" t="n">
-        <v>114.99</v>
+        <v>493</v>
       </c>
       <c r="E115" s="7" t="n">
-        <v>99.98999999999999</v>
+        <v>383.99</v>
       </c>
       <c r="F115" s="2" t="n"/>
-      <c r="G115" s="8" t="n">
-        <v>1860</v>
-      </c>
+      <c r="G115" s="2" t="n"/>
       <c r="H115" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A115,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A115,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8129,7 +8189,7 @@
         </is>
       </c>
       <c r="K115" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L115" s="16">
         <f>IF(OR($K115="",D115=""),"",IF(COUNTIFS($B:$B,$B115,$A:$A,$K115,D:D,"&gt;=0")=0,"",D115-SUMIFS(D:D,$B:$B,$B115,$A:$A,$K115)))</f>
@@ -8154,23 +8214,23 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D116" s="7" t="n">
-        <v>499.99</v>
+        <v>209.99</v>
       </c>
       <c r="E116" s="7" t="n">
-        <v>454.99</v>
+        <v>179.99</v>
       </c>
       <c r="F116" s="2" t="n"/>
       <c r="G116" s="8" t="n">
-        <v>6140</v>
+        <v>4060</v>
       </c>
       <c r="H116" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A116,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A116,Dólar!$A:$A,0))),"")</f>
@@ -8211,23 +8271,23 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D117" s="7" t="n">
-        <v>329</v>
+        <v>114.99</v>
       </c>
       <c r="E117" s="7" t="n">
-        <v>283.99</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="F117" s="2" t="n"/>
       <c r="G117" s="8" t="n">
-        <v>4760</v>
+        <v>1860</v>
       </c>
       <c r="H117" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A117,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A117,Dólar!$A:$A,0))),"")</f>
@@ -8268,7 +8328,7 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 5700X3D</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
@@ -8276,12 +8336,16 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="D118" s="7" t="n">
+        <v>499.99</v>
+      </c>
       <c r="E118" s="7" t="n">
-        <v>305</v>
+        <v>454.99</v>
       </c>
       <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
+      <c r="G118" s="8" t="n">
+        <v>6140</v>
+      </c>
       <c r="H118" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A118,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A118,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8295,7 +8359,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K118" s="5" t="n"/>
+      <c r="K118" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L118" s="16">
         <f>IF(OR($K118="",D118=""),"",IF(COUNTIFS($B:$B,$B118,$A:$A,$K118,D:D,"&gt;=0")=0,"",D118-SUMIFS(D:D,$B:$B,$B118,$A:$A,$K118)))</f>
         <v/>
@@ -8319,7 +8385,7 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
@@ -8328,14 +8394,14 @@
         </is>
       </c>
       <c r="D119" s="7" t="n">
-        <v>144.25</v>
+        <v>329</v>
       </c>
       <c r="E119" s="7" t="n">
-        <v>122.99</v>
+        <v>283.99</v>
       </c>
       <c r="F119" s="2" t="n"/>
       <c r="G119" s="8" t="n">
-        <v>2860</v>
+        <v>4760</v>
       </c>
       <c r="H119" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A119,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A119,Dólar!$A:$A,0))),"")</f>
@@ -8376,7 +8442,7 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Ryzen 7 5700X3D</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
@@ -8384,11 +8450,9 @@
           <t>CPU</t>
         </is>
       </c>
-      <c r="D120" s="7" t="n">
-        <v>138.9</v>
-      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" s="7" t="n">
-        <v>135</v>
+        <v>305</v>
       </c>
       <c r="F120" s="2" t="n"/>
       <c r="G120" s="2" t="n"/>
@@ -8429,23 +8493,23 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D121" s="7" t="n">
-        <v>75</v>
+        <v>144.25</v>
       </c>
       <c r="E121" s="7" t="n">
-        <v>59.99</v>
+        <v>122.99</v>
       </c>
       <c r="F121" s="2" t="n"/>
       <c r="G121" s="8" t="n">
-        <v>2150</v>
+        <v>2860</v>
       </c>
       <c r="H121" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A121,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A121,Dólar!$A:$A,0))),"")</f>
@@ -8486,7 +8550,7 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
@@ -8495,15 +8559,13 @@
         </is>
       </c>
       <c r="D122" s="7" t="n">
-        <v>164.49</v>
+        <v>138.9</v>
       </c>
       <c r="E122" s="7" t="n">
-        <v>136.99</v>
+        <v>135</v>
       </c>
       <c r="F122" s="2" t="n"/>
-      <c r="G122" s="8" t="n">
-        <v>2520</v>
-      </c>
+      <c r="G122" s="2" t="n"/>
       <c r="H122" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A122,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A122,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8517,9 +8579,7 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K122" s="15" t="n">
-        <v>46306</v>
-      </c>
+      <c r="K122" s="5" t="n"/>
       <c r="L122" s="16">
         <f>IF(OR($K122="",D122=""),"",IF(COUNTIFS($B:$B,$B122,$A:$A,$K122,D:D,"&gt;=0")=0,"",D122-SUMIFS(D:D,$B:$B,$B122,$A:$A,$K122)))</f>
         <v/>
@@ -8543,22 +8603,24 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D123" s="7" t="n">
-        <v>259.78</v>
+        <v>75</v>
       </c>
       <c r="E123" s="7" t="n">
-        <v>149.99</v>
+        <v>59.99</v>
       </c>
       <c r="F123" s="2" t="n"/>
-      <c r="G123" s="2" t="n"/>
+      <c r="G123" s="8" t="n">
+        <v>2150</v>
+      </c>
       <c r="H123" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A123,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A123,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8598,7 +8660,7 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
@@ -8607,14 +8669,14 @@
         </is>
       </c>
       <c r="D124" s="7" t="n">
-        <v>150</v>
+        <v>164.49</v>
       </c>
       <c r="E124" s="7" t="n">
-        <v>119.95</v>
+        <v>136.99</v>
       </c>
       <c r="F124" s="2" t="n"/>
       <c r="G124" s="8" t="n">
-        <v>2460</v>
+        <v>2520</v>
       </c>
       <c r="H124" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A124,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A124,Dólar!$A:$A,0))),"")</f>
@@ -8629,7 +8691,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K124" s="5" t="n"/>
+      <c r="K124" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L124" s="16">
         <f>IF(OR($K124="",D124=""),"",IF(COUNTIFS($B:$B,$B124,$A:$A,$K124,D:D,"&gt;=0")=0,"",D124-SUMIFS(D:D,$B:$B,$B124,$A:$A,$K124)))</f>
         <v/>
@@ -8653,7 +8717,7 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
@@ -8662,15 +8726,13 @@
         </is>
       </c>
       <c r="D125" s="7" t="n">
-        <v>244.87</v>
+        <v>259.78</v>
       </c>
       <c r="E125" s="7" t="n">
-        <v>209.99</v>
+        <v>149.99</v>
       </c>
       <c r="F125" s="2" t="n"/>
-      <c r="G125" s="8" t="n">
-        <v>4290</v>
-      </c>
+      <c r="G125" s="2" t="n"/>
       <c r="H125" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A125,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A125,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8710,22 +8772,24 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D126" s="7" t="n">
-        <v>435.99</v>
+        <v>150</v>
       </c>
       <c r="E126" s="7" t="n">
-        <v>399.9</v>
+        <v>119.95</v>
       </c>
       <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
+      <c r="G126" s="8" t="n">
+        <v>2460</v>
+      </c>
       <c r="H126" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A126,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A126,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8739,9 +8803,7 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K126" s="15" t="n">
-        <v>46306</v>
-      </c>
+      <c r="K126" s="5" t="n"/>
       <c r="L126" s="16">
         <f>IF(OR($K126="",D126=""),"",IF(COUNTIFS($B:$B,$B126,$A:$A,$K126,D:D,"&gt;=0")=0,"",D126-SUMIFS(D:D,$B:$B,$B126,$A:$A,$K126)))</f>
         <v/>
@@ -8765,24 +8827,24 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D127" s="7" t="n">
-        <v>493</v>
+        <v>244.87</v>
       </c>
       <c r="E127" s="7" t="n">
-        <v>399.99</v>
-      </c>
-      <c r="F127" s="8" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G127" s="2" t="n"/>
+        <v>209.99</v>
+      </c>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="8" t="n">
+        <v>4290</v>
+      </c>
       <c r="H127" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A127,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A127,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8796,7 +8858,9 @@
           <t>ver anuncio</t>
         </is>
       </c>
-      <c r="K127" s="5" t="n"/>
+      <c r="K127" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L127" s="16">
         <f>IF(OR($K127="",D127=""),"",IF(COUNTIFS($B:$B,$B127,$A:$A,$K127,D:D,"&gt;=0")=0,"",D127-SUMIFS(D:D,$B:$B,$B127,$A:$A,$K127)))</f>
         <v/>
@@ -8816,20 +8880,24 @@
     </row>
     <row r="128">
       <c r="A128" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>435.99</v>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>399.9</v>
+      </c>
       <c r="F128" s="2" t="n"/>
       <c r="G128" s="2" t="n"/>
       <c r="H128" s="9">
@@ -8840,8 +8908,14 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A128,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J128" s="2" t="n"/>
-      <c r="K128" s="5" t="n"/>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K128" s="15" t="n">
+        <v>46306</v>
+      </c>
       <c r="L128" s="16">
         <f>IF(OR($K128="",D128=""),"",IF(COUNTIFS($B:$B,$B128,$A:$A,$K128,D:D,"&gt;=0")=0,"",D128-SUMIFS(D:D,$B:$B,$B128,$A:$A,$K128)))</f>
         <v/>
@@ -8861,22 +8935,26 @@
     </row>
     <row r="129">
       <c r="A129" s="15" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>SSD</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="n"/>
-      <c r="E129" s="2" t="n"/>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>493</v>
+      </c>
+      <c r="E129" s="7" t="n">
+        <v>399.99</v>
+      </c>
       <c r="F129" s="8" t="n">
-        <v>1800</v>
+        <v>4500</v>
       </c>
       <c r="G129" s="2" t="n"/>
       <c r="H129" s="9">
@@ -8916,20 +8994,18 @@
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D130" s="2" t="n"/>
       <c r="E130" s="2" t="n"/>
       <c r="F130" s="2" t="n"/>
-      <c r="G130" s="8" t="n">
-        <v>5580</v>
-      </c>
+      <c r="G130" s="2" t="n"/>
       <c r="H130" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A130,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A130,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -8938,11 +9014,7 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A130,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J130" s="6" t="inlineStr">
-        <is>
-          <t>ver anuncio</t>
-        </is>
-      </c>
+      <c r="J130" s="2" t="n"/>
       <c r="K130" s="5" t="n"/>
       <c r="L130" s="16">
         <f>IF(OR($K130="",D130=""),"",IF(COUNTIFS($B:$B,$B130,$A:$A,$K130,D:D,"&gt;=0")=0,"",D130-SUMIFS(D:D,$B:$B,$B130,$A:$A,$K130)))</f>
@@ -8967,18 +9039,18 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="D131" s="2" t="n"/>
       <c r="E131" s="2" t="n"/>
       <c r="F131" s="8" t="n">
-        <v>4800</v>
+        <v>1800</v>
       </c>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="9">
@@ -9018,7 +9090,7 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
@@ -9029,7 +9101,9 @@
       <c r="D132" s="2" t="n"/>
       <c r="E132" s="2" t="n"/>
       <c r="F132" s="2" t="n"/>
-      <c r="G132" s="2" t="n"/>
+      <c r="G132" s="8" t="n">
+        <v>5580</v>
+      </c>
       <c r="H132" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A132,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A132,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -9038,7 +9112,11 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A132,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J132" s="2" t="n"/>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
       <c r="K132" s="5" t="n"/>
       <c r="L132" s="16">
         <f>IF(OR($K132="",D132=""),"",IF(COUNTIFS($B:$B,$B132,$A:$A,$K132,D:D,"&gt;=0")=0,"",D132-SUMIFS(D:D,$B:$B,$B132,$A:$A,$K132)))</f>
@@ -9063,18 +9141,18 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D133" s="2" t="n"/>
       <c r="E133" s="2" t="n"/>
       <c r="F133" s="8" t="n">
-        <v>900</v>
+        <v>4800</v>
       </c>
       <c r="G133" s="2" t="n"/>
       <c r="H133" s="9">
@@ -9114,7 +9192,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
@@ -9159,20 +9237,20 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>CPU</t>
+          <t>RAM</t>
         </is>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" s="2" t="n"/>
-      <c r="F135" s="2" t="n"/>
-      <c r="G135" s="8" t="n">
-        <v>2300</v>
-      </c>
+      <c r="F135" s="8" t="n">
+        <v>900</v>
+      </c>
+      <c r="G135" s="2" t="n"/>
       <c r="H135" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A135,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A135,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -9210,7 +9288,7 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
@@ -9221,9 +9299,7 @@
       <c r="D136" s="2" t="n"/>
       <c r="E136" s="2" t="n"/>
       <c r="F136" s="2" t="n"/>
-      <c r="G136" s="8" t="n">
-        <v>3950</v>
-      </c>
+      <c r="G136" s="2" t="n"/>
       <c r="H136" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A136,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A136,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -9232,11 +9308,7 @@
         <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A136,Dólar!$A:$A,0)),"")</f>
         <v/>
       </c>
-      <c r="J136" s="6" t="inlineStr">
-        <is>
-          <t>ver anuncio</t>
-        </is>
-      </c>
+      <c r="J136" s="2" t="n"/>
       <c r="K136" s="5" t="n"/>
       <c r="L136" s="16">
         <f>IF(OR($K136="",D136=""),"",IF(COUNTIFS($B:$B,$B136,$A:$A,$K136,D:D,"&gt;=0")=0,"",D136-SUMIFS(D:D,$B:$B,$B136,$A:$A,$K136)))</f>
@@ -9261,20 +9333,20 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>RAM</t>
+          <t>CPU</t>
         </is>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" s="2" t="n"/>
-      <c r="F137" s="8" t="n">
-        <v>6200</v>
-      </c>
-      <c r="G137" s="2" t="n"/>
+      <c r="F137" s="2" t="n"/>
+      <c r="G137" s="8" t="n">
+        <v>2300</v>
+      </c>
       <c r="H137" s="9">
         <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A137,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A137,Dólar!$A:$A,0))),"")</f>
         <v/>
@@ -9306,8 +9378,110 @@
         <v/>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>Intel Core Ultra 7 265K</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="8" t="n">
+        <v>3950</v>
+      </c>
+      <c r="H138" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A138,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A138,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I138" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A138,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J138" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n"/>
+      <c r="L138" s="16">
+        <f>IF(OR($K138="",D138=""),"",IF(COUNTIFS($B:$B,$B138,$A:$A,$K138,D:D,"&gt;=0")=0,"",D138-SUMIFS(D:D,$B:$B,$B138,$A:$A,$K138)))</f>
+        <v/>
+      </c>
+      <c r="M138" s="16">
+        <f>IF(OR($K138="",E138=""),"",IF(COUNTIFS($B:$B,$B138,$A:$A,$K138,E:E,"&gt;=0")=0,"",E138-SUMIFS(E:E,$B:$B,$B138,$A:$A,$K138)))</f>
+        <v/>
+      </c>
+      <c r="N138" s="16">
+        <f>IF(OR($K138="",F138=""),"",IF(COUNTIFS($B:$B,$B138,$A:$A,$K138,F:F,"&gt;=0")=0,"",F138-SUMIFS(F:F,$B:$B,$B138,$A:$A,$K138)))</f>
+        <v/>
+      </c>
+      <c r="O138" s="16">
+        <f>IF(OR($K138="",G138=""),"",IF(COUNTIFS($B:$B,$B138,$A:$A,$K138,G:G,"&gt;=0")=0,"",G138-SUMIFS(G:G,$B:$B,$B138,$A:$A,$K138)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="8" t="n">
+        <v>6200</v>
+      </c>
+      <c r="G139" s="2" t="n"/>
+      <c r="H139" s="9">
+        <f>IFERROR(IF(INDEX(Dólar!$B:$B,MATCH(A139,Dólar!$A:$A,0))="","",INDEX(Dólar!$B:$B,MATCH(A139,Dólar!$A:$A,0))),"")</f>
+        <v/>
+      </c>
+      <c r="I139" s="10">
+        <f>IFERROR(INDEX(Dólar!$E:$E,MATCH(A139,Dólar!$A:$A,0)),"")</f>
+        <v/>
+      </c>
+      <c r="J139" s="6" t="inlineStr">
+        <is>
+          <t>ver anuncio</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n"/>
+      <c r="L139" s="16">
+        <f>IF(OR($K139="",D139=""),"",IF(COUNTIFS($B:$B,$B139,$A:$A,$K139,D:D,"&gt;=0")=0,"",D139-SUMIFS(D:D,$B:$B,$B139,$A:$A,$K139)))</f>
+        <v/>
+      </c>
+      <c r="M139" s="16">
+        <f>IF(OR($K139="",E139=""),"",IF(COUNTIFS($B:$B,$B139,$A:$A,$K139,E:E,"&gt;=0")=0,"",E139-SUMIFS(E:E,$B:$B,$B139,$A:$A,$K139)))</f>
+        <v/>
+      </c>
+      <c r="N139" s="16">
+        <f>IF(OR($K139="",F139=""),"",IF(COUNTIFS($B:$B,$B139,$A:$A,$K139,F:F,"&gt;=0")=0,"",F139-SUMIFS(F:F,$B:$B,$B139,$A:$A,$K139)))</f>
+        <v/>
+      </c>
+      <c r="O139" s="16">
+        <f>IF(OR($K139="",G139=""),"",IF(COUNTIFS($B:$B,$B139,$A:$A,$K139,G:G,"&gt;=0")=0,"",G139-SUMIFS(G:G,$B:$B,$B139,$A:$A,$K139)))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="L2:M137">
+  <conditionalFormatting sqref="L2:M139">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="2">
       <formula>0</formula>
     </cfRule>
@@ -9315,7 +9489,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:O137">
+  <conditionalFormatting sqref="N2:O139">
     <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -9399,68 +9573,69 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId73"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J76" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J77" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J78" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J79" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J80" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J81" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J82" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J83" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J84" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J85" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J86" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J87" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J88" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J89" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J110" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J112" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J113" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J114" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J115" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J117" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J118" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J119" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J120" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J121" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J122" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J123" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J124" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J125" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J126" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J136" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId134"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId134"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId135"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9965,7 +10140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H355"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -19902,34 +20077,34 @@
     </row>
     <row r="262">
       <c r="A262" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C262" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E262" s="11" t="n">
-        <v>5580</v>
+        <v>219</v>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G262" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay (Chrome, API sin claves); kn32451 99,9 %; nuevo, Buy It Now, envio gratis</t>
         </is>
       </c>
       <c r="H262" s="6" t="inlineStr">
@@ -19940,34 +20115,34 @@
     </row>
     <row r="263">
       <c r="A263" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C263" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
-        <v>2300</v>
+        <v>212</v>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G263" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay (Chrome, API sin claves); irepaircellphone 99,6 %; nuevo, Buy It Now, envio gratis</t>
         </is>
       </c>
       <c r="H263" s="6" t="inlineStr">
@@ -19978,34 +20153,34 @@
     </row>
     <row r="264">
       <c r="A264" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C264" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>MSR Computers (web; fecha de actualización desconocida)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="E264" s="11" t="n">
-        <v>3950</v>
+        <v>199.99</v>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G264" s="5" t="inlineStr">
         <is>
-          <t>nuevo</t>
+          <t>eBay (Chrome, API sin claves); paymore_cary 99,7 %; nuevo, Buy It Now, envio gratis</t>
         </is>
       </c>
       <c r="H264" s="6" t="inlineStr">
@@ -20016,34 +20191,34 @@
     </row>
     <row r="265">
       <c r="A265" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C265" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor)</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E265" s="11" t="n">
-        <v>4800</v>
+        <v>173.05</v>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G265" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado (según anuncio)</t>
+          <t>eBay (Chrome, API sin claves); schneller0391 98,1 %; usado, Buy It Now, envio 5,80</t>
         </is>
       </c>
       <c r="H265" s="6" t="inlineStr">
@@ -20054,34 +20229,34 @@
     </row>
     <row r="266">
       <c r="A266" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C266" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E266" s="11" t="n">
-        <v>5190</v>
+        <v>169.99</v>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G266" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay (Chrome, API sin claves); paymore_spring 99,5 %; usado, Buy It Now, envio gratis</t>
         </is>
       </c>
       <c r="H266" s="6" t="inlineStr">
@@ -20092,34 +20267,34 @@
     </row>
     <row r="267">
       <c r="A267" s="15" t="n">
-        <v>46306</v>
+        <v>46315</v>
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C267" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>usado</t>
         </is>
       </c>
       <c r="E267" s="11" t="n">
-        <v>5390</v>
+        <v>169.99</v>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
-          <t>Bs</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G267" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>eBay (Chrome, API sin claves); paymore_fort_thomas 99,5 %; usado, Buy It Now, envio gratis</t>
         </is>
       </c>
       <c r="H267" s="6" t="inlineStr">
@@ -20134,21 +20309,21 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C268" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E268" s="11" t="n">
-        <v>2000</v>
+        <v>5580</v>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
@@ -20157,7 +20332,7 @@
       </c>
       <c r="G268" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H268" s="6" t="inlineStr">
@@ -20172,21 +20347,21 @@
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C269" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Marketplace La Paz</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E269" s="11" t="n">
-        <v>2650</v>
+        <v>2300</v>
       </c>
       <c r="F269" s="5" t="inlineStr">
         <is>
@@ -20195,7 +20370,7 @@
       </c>
       <c r="G269" s="5" t="inlineStr">
         <is>
-          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H269" s="6" t="inlineStr">
@@ -20210,21 +20385,21 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C270" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>MSR Computers (web; fecha de actualización desconocida)</t>
         </is>
       </c>
       <c r="E270" s="11" t="n">
-        <v>2700</v>
+        <v>3950</v>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
@@ -20233,7 +20408,7 @@
       </c>
       <c r="G270" s="5" t="inlineStr">
         <is>
-          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
+          <t>nuevo</t>
         </is>
       </c>
       <c r="H270" s="6" t="inlineStr">
@@ -20253,16 +20428,16 @@
       </c>
       <c r="C271" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Marketplace Cochabamba (particular/vendedor)</t>
         </is>
       </c>
       <c r="E271" s="11" t="n">
-        <v>6200</v>
+        <v>4800</v>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
@@ -20271,7 +20446,7 @@
       </c>
       <c r="G271" s="5" t="inlineStr">
         <is>
-          <t>no indicado (modelo RS)</t>
+          <t>nuevo sellado (según anuncio)</t>
         </is>
       </c>
       <c r="H271" s="6" t="inlineStr">
@@ -20291,7 +20466,7 @@
       </c>
       <c r="C272" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D272" s="5" t="inlineStr">
@@ -20300,7 +20475,7 @@
         </is>
       </c>
       <c r="E272" s="11" t="n">
-        <v>540</v>
+        <v>5190</v>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
@@ -20309,7 +20484,7 @@
       </c>
       <c r="G272" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H272" s="6" t="inlineStr">
@@ -20329,7 +20504,7 @@
       </c>
       <c r="C273" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D273" s="5" t="inlineStr">
@@ -20338,7 +20513,7 @@
         </is>
       </c>
       <c r="E273" s="11" t="n">
-        <v>900</v>
+        <v>5390</v>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
@@ -20347,7 +20522,7 @@
       </c>
       <c r="G273" s="5" t="inlineStr">
         <is>
-          <t>no indicado (16GB 3200; configuración no indicada)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H273" s="6" t="inlineStr">
@@ -20367,16 +20542,16 @@
       </c>
       <c r="C274" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E274" s="11" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
@@ -20385,7 +20560,7 @@
       </c>
       <c r="G274" s="5" t="inlineStr">
         <is>
-          <t>no indicado (2x8 3200; Sacaba)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H274" s="6" t="inlineStr">
@@ -20405,16 +20580,16 @@
       </c>
       <c r="C275" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Marketplace La Paz</t>
         </is>
       </c>
       <c r="E275" s="11" t="n">
-        <v>1500</v>
+        <v>2650</v>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
@@ -20423,7 +20598,7 @@
       </c>
       <c r="G275" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
+          <t>no indicado (es 7600X; está en La Paz: solo referencia)</t>
         </is>
       </c>
       <c r="H275" s="6" t="inlineStr">
@@ -20443,7 +20618,7 @@
       </c>
       <c r="C276" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D276" s="5" t="inlineStr">
@@ -20452,7 +20627,7 @@
         </is>
       </c>
       <c r="E276" s="11" t="n">
-        <v>1850</v>
+        <v>2700</v>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
@@ -20461,7 +20636,7 @@
       </c>
       <c r="G276" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 1TB)</t>
+          <t>confirmado por Messenger el 12/10: es el i5-14400 con gráficos (no el F), nuevo en blíster, precio final Bs 2.700; no cuenta</t>
         </is>
       </c>
       <c r="H276" s="6" t="inlineStr">
@@ -20481,7 +20656,7 @@
       </c>
       <c r="C277" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D277" s="5" t="inlineStr">
@@ -20490,7 +20665,7 @@
         </is>
       </c>
       <c r="E277" s="11" t="n">
-        <v>2000</v>
+        <v>6200</v>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
@@ -20499,7 +20674,7 @@
       </c>
       <c r="G277" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Crucial P310 1TB)</t>
+          <t>no indicado (modelo RS)</t>
         </is>
       </c>
       <c r="H277" s="6" t="inlineStr">
@@ -20519,7 +20694,7 @@
       </c>
       <c r="C278" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D278" s="5" t="inlineStr">
@@ -20528,7 +20703,7 @@
         </is>
       </c>
       <c r="E278" s="11" t="n">
-        <v>1800</v>
+        <v>540</v>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
@@ -20537,7 +20712,7 @@
       </c>
       <c r="G278" s="5" t="inlineStr">
         <is>
-          <t>no indicado (M.2 1TB; marca no indicada)</t>
+          <t>no indicado (Kingston Fury Beast RGB 16GB 3200; probablemente 1x16; no cuenta)</t>
         </is>
       </c>
       <c r="H278" s="6" t="inlineStr">
@@ -20557,7 +20732,7 @@
       </c>
       <c r="C279" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D279" s="5" t="inlineStr">
@@ -20566,7 +20741,7 @@
         </is>
       </c>
       <c r="E279" s="11" t="n">
-        <v>3550</v>
+        <v>900</v>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
@@ -20575,7 +20750,7 @@
       </c>
       <c r="G279" s="5" t="inlineStr">
         <is>
-          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
+          <t>no indicado (16GB 3200; configuración no indicada)</t>
         </is>
       </c>
       <c r="H279" s="6" t="inlineStr">
@@ -20586,25 +20761,25 @@
     </row>
     <row r="280">
       <c r="A280" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C280" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E280" s="11" t="n">
-        <v>5664</v>
+        <v>1500</v>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
@@ -20613,7 +20788,7 @@
       </c>
       <c r="G280" s="5" t="inlineStr">
         <is>
-          <t>BOX (según foto de su web; USD 480)</t>
+          <t>no indicado (2x8 3200; Sacaba)</t>
         </is>
       </c>
       <c r="H280" s="6" t="inlineStr">
@@ -20624,25 +20799,25 @@
     </row>
     <row r="281">
       <c r="A281" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C281" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E281" s="11" t="n">
-        <v>2537</v>
+        <v>1500</v>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
@@ -20651,7 +20826,7 @@
       </c>
       <c r="G281" s="5" t="inlineStr">
         <is>
-          <t>OEM (sin caja; según foto de su web; USD 215)</t>
+          <t>no indicado (Corsair Vengeance 2x8; Sacaba; rebajado de 1600)</t>
         </is>
       </c>
       <c r="H281" s="6" t="inlineStr">
@@ -20662,25 +20837,25 @@
     </row>
     <row r="282">
       <c r="A282" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C282" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB (1x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (WhatsApp)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E282" s="11" t="n">
-        <v>3127</v>
+        <v>1850</v>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
@@ -20689,7 +20864,7 @@
       </c>
       <c r="G282" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
+          <t>no indicado (Kingston NV3 1TB)</t>
         </is>
       </c>
       <c r="H282" s="6" t="inlineStr">
@@ -20700,25 +20875,25 @@
     </row>
     <row r="283">
       <c r="A283" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C283" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Compucenter (WhatsApp)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E283" s="11" t="n">
-        <v>2150</v>
+        <v>2000</v>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
@@ -20727,7 +20902,7 @@
       </c>
       <c r="G283" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
+          <t>no indicado (Crucial P310 1TB)</t>
         </is>
       </c>
       <c r="H283" s="6" t="inlineStr">
@@ -20738,25 +20913,25 @@
     </row>
     <row r="284">
       <c r="A284" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C284" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 9 9950X</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E284" s="11" t="n">
-        <v>6140</v>
+        <v>1800</v>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
@@ -20765,7 +20940,7 @@
       </c>
       <c r="G284" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (garantía 6 meses)</t>
+          <t>no indicado (M.2 1TB; marca no indicada)</t>
         </is>
       </c>
       <c r="H284" s="6" t="inlineStr">
@@ -20776,25 +20951,25 @@
     </row>
     <row r="285">
       <c r="A285" s="15" t="n">
-        <v>46307</v>
+        <v>46306</v>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C285" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Tienda Supermall (WhatsApp)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E285" s="11" t="n">
-        <v>4760</v>
+        <v>3550</v>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
@@ -20803,7 +20978,7 @@
       </c>
       <c r="G285" s="5" t="inlineStr">
         <is>
-          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
+          <t>revisado el 12/10: es un SSD externo portátil SanDisk 2TB (1050 MB/s, USB con cable, IP65), no un NVMe interno; no cuenta</t>
         </is>
       </c>
       <c r="H285" s="6" t="inlineStr">
@@ -20823,16 +20998,16 @@
       </c>
       <c r="C286" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E286" s="11" t="n">
-        <v>6800</v>
+        <v>5664</v>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
@@ -20841,7 +21016,7 @@
       </c>
       <c r="G286" s="5" t="inlineStr">
         <is>
-          <t>no indicado</t>
+          <t>BOX (según foto de su web; USD 480)</t>
         </is>
       </c>
       <c r="H286" s="6" t="inlineStr">
@@ -20861,16 +21036,16 @@
       </c>
       <c r="C287" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E287" s="11" t="n">
-        <v>2100</v>
+        <v>2537</v>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
@@ -20879,7 +21054,7 @@
       </c>
       <c r="G287" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>OEM (sin caja; según foto de su web; USD 215)</t>
         </is>
       </c>
       <c r="H287" s="6" t="inlineStr">
@@ -20899,16 +21074,16 @@
       </c>
       <c r="C288" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>RAM DDR5 16GB (1x16) 6000</t>
         </is>
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>Cyrex Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E288" s="11" t="n">
-        <v>1800</v>
+        <v>3127</v>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
@@ -20917,7 +21092,7 @@
       </c>
       <c r="G288" s="5" t="inlineStr">
         <is>
-          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
+          <t>no indicado (Patriot Viper Venom RGB 1x16 CL30; USD 265; no es el kit Corsair 2x16: solo referencia)</t>
         </is>
       </c>
       <c r="H288" s="6" t="inlineStr">
@@ -20932,21 +21107,21 @@
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C289" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Compucenter (WhatsApp)</t>
         </is>
       </c>
       <c r="E289" s="11" t="n">
-        <v>4500</v>
+        <v>2150</v>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
@@ -20955,7 +21130,7 @@
       </c>
       <c r="G289" s="5" t="inlineStr">
         <is>
-          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
+          <t>nuevo (Corsair Vengeance RGB DDR4 16GB 3600; no dice si es 2x8; Bs 2.560 con factura)</t>
         </is>
       </c>
       <c r="H289" s="6" t="inlineStr">
@@ -20975,16 +21150,16 @@
       </c>
       <c r="C290" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Ryzen 9 9950X</t>
         </is>
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E290" s="11" t="n">
-        <v>6700</v>
+        <v>6140</v>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
@@ -20993,7 +21168,7 @@
       </c>
       <c r="G290" s="5" t="inlineStr">
         <is>
-          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
+          <t>nuevo OEM (garantía 6 meses)</t>
         </is>
       </c>
       <c r="H290" s="6" t="inlineStr">
@@ -21013,16 +21188,16 @@
       </c>
       <c r="C291" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Tienda Supermall (WhatsApp)</t>
         </is>
       </c>
       <c r="E291" s="11" t="n">
-        <v>2520</v>
+        <v>4760</v>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
@@ -21031,7 +21206,7 @@
       </c>
       <c r="G291" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (la tienda lo ofrece como "7700x3d"; foto de caja 7800X3D; stock bajo; garantía 6 meses; confirmar modelo)</t>
         </is>
       </c>
       <c r="H291" s="6" t="inlineStr">
@@ -21051,16 +21226,16 @@
       </c>
       <c r="C292" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E292" s="11" t="n">
-        <v>4290</v>
+        <v>6800</v>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
@@ -21069,7 +21244,7 @@
       </c>
       <c r="G292" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
+          <t>no indicado</t>
         </is>
       </c>
       <c r="H292" s="6" t="inlineStr">
@@ -21089,16 +21264,16 @@
       </c>
       <c r="C293" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E293" s="11" t="n">
-        <v>2860</v>
+        <v>2100</v>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
@@ -21107,7 +21282,7 @@
       </c>
       <c r="G293" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web)</t>
+          <t>no indicado (Kingston NV3 PCIe 4.0; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H293" s="6" t="inlineStr">
@@ -21127,16 +21302,16 @@
       </c>
       <c r="C294" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E294" s="11" t="n">
-        <v>2460</v>
+        <v>1800</v>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
@@ -21145,7 +21320,7 @@
       </c>
       <c r="G294" s="5" t="inlineStr">
         <is>
-          <t>disponible (web)</t>
+          <t>no indicado (marca "ediloca" PCIe 4.0; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H294" s="6" t="inlineStr">
@@ -21160,21 +21335,21 @@
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C295" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E295" s="11" t="n">
-        <v>5360</v>
+        <v>4500</v>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
@@ -21183,7 +21358,7 @@
       </c>
       <c r="G295" s="5" t="inlineStr">
         <is>
-          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
+          <t>usado como nuevo (4 meses de uso; publicado hace 7 semanas)</t>
         </is>
       </c>
       <c r="H295" s="6" t="inlineStr">
@@ -21203,16 +21378,16 @@
       </c>
       <c r="C296" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico · Supermall (web)</t>
+          <t>PC Components Bolivia (WhatsApp; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="E296" s="11" t="n">
-        <v>1710</v>
+        <v>6700</v>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
@@ -21221,7 +21396,7 @@
       </c>
       <c r="G296" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>no indicado (precio c/u llevando 2; Santa Cruz: referencia)</t>
         </is>
       </c>
       <c r="H296" s="6" t="inlineStr">
@@ -21241,7 +21416,7 @@
       </c>
       <c r="C297" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D297" s="5" t="inlineStr">
@@ -21250,7 +21425,7 @@
         </is>
       </c>
       <c r="E297" s="11" t="n">
-        <v>2310</v>
+        <v>2520</v>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
@@ -21259,7 +21434,7 @@
       </c>
       <c r="G297" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>disponible (web)</t>
         </is>
       </c>
       <c r="H297" s="6" t="inlineStr">
@@ -21279,7 +21454,7 @@
       </c>
       <c r="C298" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D298" s="5" t="inlineStr">
@@ -21288,7 +21463,7 @@
         </is>
       </c>
       <c r="E298" s="11" t="n">
-        <v>2160</v>
+        <v>4290</v>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
@@ -21297,7 +21472,7 @@
       </c>
       <c r="G298" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
+          <t>stock bajo (web; por WhatsApp dijeron que el 265K solo está en Santa Cruz)</t>
         </is>
       </c>
       <c r="H298" s="6" t="inlineStr">
@@ -21317,7 +21492,7 @@
       </c>
       <c r="C299" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D299" s="5" t="inlineStr">
@@ -21326,7 +21501,7 @@
         </is>
       </c>
       <c r="E299" s="11" t="n">
-        <v>5360</v>
+        <v>2860</v>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
@@ -21335,7 +21510,7 @@
       </c>
       <c r="G299" s="5" t="inlineStr">
         <is>
-          <t>agotado (web; precio de referencia; no cuenta)</t>
+          <t>stock bajo (web)</t>
         </is>
       </c>
       <c r="H299" s="6" t="inlineStr">
@@ -21355,7 +21530,7 @@
       </c>
       <c r="C300" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D300" s="5" t="inlineStr">
@@ -21364,7 +21539,7 @@
         </is>
       </c>
       <c r="E300" s="11" t="n">
-        <v>5660</v>
+        <v>2460</v>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
@@ -21373,7 +21548,7 @@
       </c>
       <c r="G300" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
+          <t>disponible (web)</t>
         </is>
       </c>
       <c r="H300" s="6" t="inlineStr">
@@ -21393,7 +21568,7 @@
       </c>
       <c r="C301" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D301" s="5" t="inlineStr">
@@ -21402,7 +21577,7 @@
         </is>
       </c>
       <c r="E301" s="11" t="n">
-        <v>5860</v>
+        <v>5360</v>
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
@@ -21411,7 +21586,7 @@
       </c>
       <c r="G301" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
+          <t>agotado (web, "Ryzen 7 7800x3d Chip"; precio de referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H301" s="6" t="inlineStr">
@@ -21431,7 +21606,7 @@
       </c>
       <c r="C302" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D302" s="5" t="inlineStr">
@@ -21440,7 +21615,7 @@
         </is>
       </c>
       <c r="E302" s="11" t="n">
-        <v>1860</v>
+        <v>1710</v>
       </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
@@ -21449,7 +21624,7 @@
       </c>
       <c r="G302" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H302" s="6" t="inlineStr">
@@ -21469,7 +21644,7 @@
       </c>
       <c r="C303" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
@@ -21478,7 +21653,7 @@
         </is>
       </c>
       <c r="E303" s="11" t="n">
-        <v>2060</v>
+        <v>2310</v>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
@@ -21487,7 +21662,7 @@
       </c>
       <c r="G303" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; WD SN3000 M.2 1TB)</t>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H303" s="6" t="inlineStr">
@@ -21507,7 +21682,7 @@
       </c>
       <c r="C304" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
@@ -21516,7 +21691,7 @@
         </is>
       </c>
       <c r="E304" s="11" t="n">
-        <v>2152</v>
+        <v>2160</v>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
@@ -21525,7 +21700,7 @@
       </c>
       <c r="G304" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+          <t>disponible (web; Corsair Vengeance RGB Pro TUF Gaming 2x8 3200)</t>
         </is>
       </c>
       <c r="H304" s="6" t="inlineStr">
@@ -21545,7 +21720,7 @@
       </c>
       <c r="C305" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
@@ -21554,7 +21729,7 @@
         </is>
       </c>
       <c r="E305" s="11" t="n">
-        <v>4060</v>
+        <v>5360</v>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
@@ -21563,7 +21738,7 @@
       </c>
       <c r="G305" s="5" t="inlineStr">
         <is>
-          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+          <t>agotado (web; precio de referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H305" s="6" t="inlineStr">
@@ -21583,7 +21758,7 @@
       </c>
       <c r="C306" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D306" s="5" t="inlineStr">
@@ -21592,7 +21767,7 @@
         </is>
       </c>
       <c r="E306" s="11" t="n">
-        <v>4560</v>
+        <v>5660</v>
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
@@ -21601,7 +21776,7 @@
       </c>
       <c r="G306" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+          <t>disponible (web; Patriot Viper 32GB 6000 RGB: otra marca; no cuenta)</t>
         </is>
       </c>
       <c r="H306" s="6" t="inlineStr">
@@ -21621,16 +21796,16 @@
       </c>
       <c r="C307" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E307" s="11" t="n">
-        <v>5500</v>
+        <v>5860</v>
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
@@ -21639,7 +21814,7 @@
       </c>
       <c r="G307" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
+          <t>disponible (web; Kingston Fury 32GB 2x16 5200/5600: otra marca; no cuenta)</t>
         </is>
       </c>
       <c r="H307" s="6" t="inlineStr">
@@ -21659,16 +21834,16 @@
       </c>
       <c r="C308" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E308" s="11" t="n">
-        <v>2500</v>
+        <v>1860</v>
       </c>
       <c r="F308" s="5" t="inlineStr">
         <is>
@@ -21677,7 +21852,7 @@
       </c>
       <c r="G308" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
+          <t>stock bajo (web; Hiksemi Wave M.2 1TB)</t>
         </is>
       </c>
       <c r="H308" s="6" t="inlineStr">
@@ -21697,16 +21872,16 @@
       </c>
       <c r="C309" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Viadata Computadoras (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E309" s="11" t="n">
-        <v>5200</v>
+        <v>2060</v>
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
@@ -21715,7 +21890,7 @@
       </c>
       <c r="G309" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+          <t>disponible (web; WD SN3000 M.2 1TB)</t>
         </is>
       </c>
       <c r="H309" s="6" t="inlineStr">
@@ -21726,7 +21901,7 @@
     </row>
     <row r="310">
       <c r="A310" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B310" s="5" t="inlineStr">
         <is>
@@ -21735,16 +21910,16 @@
       </c>
       <c r="C310" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E310" s="11" t="n">
-        <v>5500</v>
+        <v>2152</v>
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
@@ -21753,14 +21928,18 @@
       </c>
       <c r="G310" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (solo el chip)</t>
-        </is>
-      </c>
-      <c r="H310" s="2" t="n"/>
+          <t>disponible (web; Kingston NV3 M.2 1TB)</t>
+        </is>
+      </c>
+      <c r="H310" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B311" s="5" t="inlineStr">
         <is>
@@ -21769,16 +21948,16 @@
       </c>
       <c r="C311" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E311" s="11" t="n">
-        <v>2460</v>
+        <v>4060</v>
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
@@ -21787,14 +21966,18 @@
       </c>
       <c r="G311" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H311" s="2" t="n"/>
+          <t>stock bajo (web; Apacer M.2 2TB 7400 MB/s)</t>
+        </is>
+      </c>
+      <c r="H311" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B312" s="5" t="inlineStr">
         <is>
@@ -21803,16 +21986,16 @@
       </c>
       <c r="C312" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>Punto Tecnológico · Supermall (web)</t>
         </is>
       </c>
       <c r="E312" s="11" t="n">
-        <v>2500</v>
+        <v>4560</v>
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
@@ -21821,14 +22004,18 @@
       </c>
       <c r="G312" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H312" s="2" t="n"/>
+          <t>disponible (web; Hiksemi Futurex M.2 2TB)</t>
+        </is>
+      </c>
+      <c r="H312" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B313" s="5" t="inlineStr">
         <is>
@@ -21837,16 +22024,16 @@
       </c>
       <c r="C313" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E313" s="11" t="n">
-        <v>6840</v>
+        <v>5500</v>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
@@ -21855,32 +22042,36 @@
       </c>
       <c r="G313" s="5" t="inlineStr">
         <is>
-          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
-        </is>
-      </c>
-      <c r="H313" s="2" t="n"/>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H313" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C314" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E314" s="11" t="n">
-        <v>4800</v>
+        <v>2500</v>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
@@ -21889,7 +22080,7 @@
       </c>
       <c r="G314" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+          <t>nuevo OEM (es el 5600X, no el 5600; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H314" s="6" t="inlineStr">
@@ -21900,7 +22091,7 @@
     </row>
     <row r="315">
       <c r="A315" s="15" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="B315" s="5" t="inlineStr">
         <is>
@@ -21909,16 +22100,16 @@
       </c>
       <c r="C315" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core Ultra 7 265K</t>
         </is>
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Viadata Computadoras (WhatsApp)</t>
         </is>
       </c>
       <c r="E315" s="11" t="n">
-        <v>5350</v>
+        <v>5200</v>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
@@ -21927,32 +22118,36 @@
       </c>
       <c r="G315" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
-        </is>
-      </c>
-      <c r="H315" s="2" t="n"/>
+          <t>nuevo en caja (es el 265KF, sin gráficos integrados; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H315" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="15" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B316" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C316" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E316" s="11" t="n">
-        <v>7400</v>
+        <v>5500</v>
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
@@ -21961,18 +22156,14 @@
       </c>
       <c r="G316" s="5" t="inlineStr">
         <is>
-          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H316" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo OEM (solo el chip)</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="15" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B317" s="5" t="inlineStr">
         <is>
@@ -21986,11 +22177,11 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (web)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E317" s="11" t="n">
-        <v>2953</v>
+        <v>2460</v>
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
@@ -21999,18 +22190,14 @@
       </c>
       <c r="G317" s="5" t="inlineStr">
         <is>
-          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H317" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo OEM</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="15" t="n">
-        <v>46309</v>
+        <v>46308</v>
       </c>
       <c r="B318" s="5" t="inlineStr">
         <is>
@@ -22019,16 +22206,16 @@
       </c>
       <c r="C318" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i9-14900K</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Crazy Store (WhatsApp)</t>
+          <t>Soft Computers (WhatsApp)</t>
         </is>
       </c>
       <c r="E318" s="11" t="n">
-        <v>6013</v>
+        <v>2500</v>
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
@@ -22037,14 +22224,14 @@
       </c>
       <c r="G318" s="5" t="inlineStr">
         <is>
-          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
+          <t>nuevo OEM</t>
         </is>
       </c>
       <c r="H318" s="2" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="15" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="B319" s="5" t="inlineStr">
         <is>
@@ -22053,16 +22240,16 @@
       </c>
       <c r="C319" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E319" s="11" t="n">
-        <v>5890</v>
+        <v>6840</v>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
@@ -22071,32 +22258,32 @@
       </c>
       <c r="G319" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
+          <t>nuevo (XPG Lancer RGB 32GB 2x16 6000 CL30: otra marca; no cuenta; Corsair agotada; garantía 3 meses)</t>
         </is>
       </c>
       <c r="H319" s="2" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="15" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="B320" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C320" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular/vendedor; Messenger)</t>
         </is>
       </c>
       <c r="E320" s="11" t="n">
-        <v>3080</v>
+        <v>4800</v>
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
@@ -22105,14 +22292,18 @@
       </c>
       <c r="G320" s="5" t="inlineStr">
         <is>
-          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
-        </is>
-      </c>
-      <c r="H320" s="2" t="n"/>
+          <t>nuevo sellado de fábrica, confirmado por el vendedor (último en stock; precio ya rebajado)</t>
+        </is>
+      </c>
+      <c r="H320" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="15" t="n">
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="B321" s="5" t="inlineStr">
         <is>
@@ -22121,16 +22312,16 @@
       </c>
       <c r="C321" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>SMART CUBE (WhatsApp)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E321" s="11" t="n">
-        <v>3650</v>
+        <v>5350</v>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
@@ -22139,32 +22330,32 @@
       </c>
       <c r="G321" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
+          <t>nuevo en caja sellada (box; el OEM está a Bs 5.500; el i5-14400F Bs 2.460 es su precio mínimo)</t>
         </is>
       </c>
       <c r="H321" s="2" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="15" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C322" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR5 16GB</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 5600</t>
         </is>
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>PC Factor (WhatsApp)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E322" s="11" t="n">
-        <v>3792</v>
+        <v>7400</v>
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
@@ -22173,14 +22364,18 @@
       </c>
       <c r="G322" s="5" t="inlineStr">
         <is>
-          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H322" s="2" t="n"/>
+          <t>no indicado (Kingston Fury Beast DDR5 32GB 5600: otra marca; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H322" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="15" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
@@ -22189,16 +22384,16 @@
       </c>
       <c r="C323" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Geek Store Bolivia (web)</t>
         </is>
       </c>
       <c r="E323" s="11" t="n">
-        <v>2800</v>
+        <v>2953</v>
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
@@ -22207,14 +22402,18 @@
       </c>
       <c r="G323" s="5" t="inlineStr">
         <is>
-          <t>OEM</t>
-        </is>
-      </c>
-      <c r="H323" s="2" t="n"/>
+          <t>disponible (web; es el i5-14400 con gráficos, no el F; precio USD 249 en la web, a Bs 11,86; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H323" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="15" t="n">
-        <v>46310</v>
+        <v>46309</v>
       </c>
       <c r="B324" s="5" t="inlineStr">
         <is>
@@ -22223,16 +22422,16 @@
       </c>
       <c r="C324" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-12400F</t>
+          <t>Intel Core i9-14900K</t>
         </is>
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>Crazy Store (WhatsApp)</t>
         </is>
       </c>
       <c r="E324" s="11" t="n">
-        <v>2260</v>
+        <v>6013</v>
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
@@ -22241,7 +22440,7 @@
       </c>
       <c r="G324" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+          <t>nuevo (no está en vigilar.csv; USD 499 o Bs 6.013, rebaja ofrecida hasta Bs 5.700; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H324" s="2" t="n"/>
@@ -22257,16 +22456,16 @@
       </c>
       <c r="C325" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
+          <t>SMART CUBE (WhatsApp)</t>
         </is>
       </c>
       <c r="E325" s="11" t="n">
-        <v>2750</v>
+        <v>5890</v>
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
@@ -22275,7 +22474,7 @@
       </c>
       <c r="G325" s="5" t="inlineStr">
         <is>
-          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
+          <t>nuevo sellado, facturado; llevando 2 rebajan Bs 50 c/u (Bs 5.840)</t>
         </is>
       </c>
       <c r="H325" s="2" t="n"/>
@@ -22291,16 +22490,16 @@
       </c>
       <c r="C326" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7700X</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>SMART CUBE (WhatsApp)</t>
         </is>
       </c>
       <c r="E326" s="11" t="n">
-        <v>3480</v>
+        <v>3080</v>
       </c>
       <c r="F326" s="5" t="inlineStr">
         <is>
@@ -22309,7 +22508,7 @@
       </c>
       <c r="G326" s="5" t="inlineStr">
         <is>
-          <t>sin confirmar si es sellado (se preguntó)</t>
+          <t>nuevo sellado; llevando 2 rebajan Bs 50 c/u (Bs 3.030)</t>
         </is>
       </c>
       <c r="H326" s="2" t="n"/>
@@ -22325,16 +22524,16 @@
       </c>
       <c r="C327" s="5" t="inlineStr">
         <is>
-          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
+          <t>RAM DDR5 16GB 6000 (Apacer NOX)</t>
         </is>
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>Geek Store Bolivia (WhatsApp)</t>
+          <t>SMART CUBE (WhatsApp)</t>
         </is>
       </c>
       <c r="E327" s="11" t="n">
-        <v>2900</v>
+        <v>3650</v>
       </c>
       <c r="F327" s="5" t="inlineStr">
         <is>
@@ -22343,7 +22542,7 @@
       </c>
       <c r="G327" s="5" t="inlineStr">
         <is>
-          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
+          <t>nuevo (Apacer NOX DDR5 16GB 6000: otra marca y capacidad; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H327" s="2" t="n"/>
@@ -22359,16 +22558,16 @@
       </c>
       <c r="C328" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>RAM DDR5 16GB</t>
         </is>
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>PC Factor (WhatsApp)</t>
         </is>
       </c>
       <c r="E328" s="11" t="n">
-        <v>1754</v>
+        <v>3792</v>
       </c>
       <c r="F328" s="5" t="inlineStr">
         <is>
@@ -22377,7 +22576,7 @@
       </c>
       <c r="G328" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
+          <t>nuevo (USD 320 c/u a Bs 11,85; marca y velocidad por confirmar; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H328" s="2" t="n"/>
@@ -22393,16 +22592,16 @@
       </c>
       <c r="C329" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>OverCity (WhatsApp)</t>
         </is>
       </c>
       <c r="E329" s="11" t="n">
-        <v>2785</v>
+        <v>2800</v>
       </c>
       <c r="F329" s="5" t="inlineStr">
         <is>
@@ -22411,7 +22610,7 @@
       </c>
       <c r="G329" s="5" t="inlineStr">
         <is>
-          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
+          <t>OEM</t>
         </is>
       </c>
       <c r="H329" s="2" t="n"/>
@@ -22427,16 +22626,16 @@
       </c>
       <c r="C330" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Intel Core i5-12400F</t>
         </is>
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
         </is>
       </c>
       <c r="E330" s="11" t="n">
-        <v>1778</v>
+        <v>2260</v>
       </c>
       <c r="F330" s="5" t="inlineStr">
         <is>
@@ -22445,7 +22644,7 @@
       </c>
       <c r="G330" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
         </is>
       </c>
       <c r="H330" s="2" t="n"/>
@@ -22461,16 +22660,16 @@
       </c>
       <c r="C331" s="5" t="inlineStr">
         <is>
-          <t>RAM DDR4 16GB (2x8) 3200</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>T&amp;T Todo en Tecnología (WhatsApp)</t>
         </is>
       </c>
       <c r="E331" s="11" t="n">
-        <v>1600</v>
+        <v>2750</v>
       </c>
       <c r="F331" s="5" t="inlineStr">
         <is>
@@ -22479,14 +22678,14 @@
       </c>
       <c r="G331" s="5" t="inlineStr">
         <is>
-          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
+          <t>OEM con cooler Intel; Bs 20 menos c/u llevando 2</t>
         </is>
       </c>
       <c r="H331" s="2" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="15" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B332" s="5" t="inlineStr">
         <is>
@@ -22495,16 +22694,16 @@
       </c>
       <c r="C332" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>Ryzen 7 7700X</t>
         </is>
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Soft Computers (WhatsApp)</t>
+          <t>Geek Store Bolivia (WhatsApp)</t>
         </is>
       </c>
       <c r="E332" s="11" t="n">
-        <v>2500</v>
+        <v>3480</v>
       </c>
       <c r="F332" s="5" t="inlineStr">
         <is>
@@ -22513,32 +22712,32 @@
       </c>
       <c r="G332" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
+          <t>sin confirmar si es sellado (se preguntó)</t>
         </is>
       </c>
       <c r="H332" s="2" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="15" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B333" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C333" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Kingston Fury DDR5 16GB (1 módulo)</t>
         </is>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba</t>
+          <t>Geek Store Bolivia (WhatsApp)</t>
         </is>
       </c>
       <c r="E333" s="11" t="n">
-        <v>1730</v>
+        <v>2900</v>
       </c>
       <c r="F333" s="5" t="inlineStr">
         <is>
@@ -22547,18 +22746,14 @@
       </c>
       <c r="G333" s="5" t="inlineStr">
         <is>
-          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
-        </is>
-      </c>
-      <c r="H333" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>otra marca; velocidad por confirmar (no es la Corsair 32GB 2x16)</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="15" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B334" s="5" t="inlineStr">
         <is>
@@ -22567,16 +22762,16 @@
       </c>
       <c r="C334" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Shopping PC (catálogo PDF)</t>
         </is>
       </c>
       <c r="E334" s="11" t="n">
-        <v>2384</v>
+        <v>1754</v>
       </c>
       <c r="F334" s="5" t="inlineStr">
         <is>
@@ -22585,18 +22780,14 @@
       </c>
       <c r="G334" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
-        </is>
-      </c>
-      <c r="H334" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo (Kingston NV3 1TB; lista mayorista USD 148 del 12/10, sin factura; 146 en stock)</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="15" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B335" s="5" t="inlineStr">
         <is>
@@ -22605,16 +22796,16 @@
       </c>
       <c r="C335" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Shopping PC (catálogo PDF)</t>
         </is>
       </c>
       <c r="E335" s="11" t="n">
-        <v>5664</v>
+        <v>2785</v>
       </c>
       <c r="F335" s="5" t="inlineStr">
         <is>
@@ -22623,18 +22814,14 @@
       </c>
       <c r="G335" s="5" t="inlineStr">
         <is>
-          <t>nuevo BOX (web: USD 480 a 11,80)</t>
-        </is>
-      </c>
-      <c r="H335" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo en caja (es el i5-14400 BOX con gráficos, no el F; lista mayorista USD 235, sin factura; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="15" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B336" s="5" t="inlineStr">
         <is>
@@ -22643,16 +22830,16 @@
       </c>
       <c r="C336" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>Cyrex Store (web)</t>
+          <t>Shopping PC (catálogo PDF)</t>
         </is>
       </c>
       <c r="E336" s="11" t="n">
-        <v>2218</v>
+        <v>1778</v>
       </c>
       <c r="F336" s="5" t="inlineStr">
         <is>
@@ -22661,18 +22848,14 @@
       </c>
       <c r="G336" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H336" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo (Kingston 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 150; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="15" t="n">
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
@@ -22681,16 +22864,16 @@
       </c>
       <c r="C337" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>RAM DDR4 16GB (2x8) 3200</t>
         </is>
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico (WhatsApp)</t>
+          <t>Shopping PC (catálogo PDF)</t>
         </is>
       </c>
       <c r="E337" s="11" t="n">
-        <v>2850</v>
+        <v>1600</v>
       </c>
       <c r="F337" s="5" t="inlineStr">
         <is>
@@ -22699,7 +22882,7 @@
       </c>
       <c r="G337" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
+          <t>nuevo (Musking Redline 16GB DDR4 3200, un módulo, no kit 2x8; lista mayorista USD 135; no cuenta)</t>
         </is>
       </c>
       <c r="H337" s="2" t="n"/>
@@ -22715,16 +22898,16 @@
       </c>
       <c r="C338" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>Punto Tecnológico (WhatsApp)</t>
+          <t>Soft Computers (WhatsApp)</t>
         </is>
       </c>
       <c r="E338" s="11" t="n">
-        <v>5960</v>
+        <v>2500</v>
       </c>
       <c r="F338" s="5" t="inlineStr">
         <is>
@@ -22733,7 +22916,7 @@
       </c>
       <c r="G338" s="5" t="inlineStr">
         <is>
-          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+          <t>nuevo OEM; mismo precio por unidad llevando 2</t>
         </is>
       </c>
       <c r="H338" s="2" t="n"/>
@@ -22744,21 +22927,21 @@
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C339" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Gamer Store Cbba (WhatsApp)</t>
+          <t>Marketplace Cochabamba</t>
         </is>
       </c>
       <c r="E339" s="11" t="n">
-        <v>2067</v>
+        <v>1730</v>
       </c>
       <c r="F339" s="5" t="inlineStr">
         <is>
@@ -22767,32 +22950,36 @@
       </c>
       <c r="G339" s="5" t="inlineStr">
         <is>
-          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
-        </is>
-      </c>
-      <c r="H339" s="2" t="n"/>
+          <t>nuevo (M.2 1TB, marca no indicada; publicado hace 2 días)</t>
+        </is>
+      </c>
+      <c r="H339" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="15" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B340" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C340" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Cyrex Store (web)</t>
         </is>
       </c>
       <c r="E340" s="11" t="n">
-        <v>1230</v>
+        <v>2384</v>
       </c>
       <c r="F340" s="5" t="inlineStr">
         <is>
@@ -22801,7 +22988,7 @@
       </c>
       <c r="G340" s="5" t="inlineStr">
         <is>
-          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
+          <t>nuevo OEM (web: USD 202 a la tasa de la tienda, 11,80; hay otra publicación del mismo a USD 215)</t>
         </is>
       </c>
       <c r="H340" s="6" t="inlineStr">
@@ -22812,25 +22999,25 @@
     </row>
     <row r="341">
       <c r="A341" s="15" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C341" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Ryzen 7 7800X3D</t>
         </is>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Cyrex Store (web)</t>
         </is>
       </c>
       <c r="E341" s="11" t="n">
-        <v>1500</v>
+        <v>5664</v>
       </c>
       <c r="F341" s="5" t="inlineStr">
         <is>
@@ -22839,7 +23026,7 @@
       </c>
       <c r="G341" s="5" t="inlineStr">
         <is>
-          <t>sin dato de estado ni marca (recién publicado)</t>
+          <t>nuevo BOX (web: USD 480 a 11,80)</t>
         </is>
       </c>
       <c r="H341" s="6" t="inlineStr">
@@ -22850,25 +23037,25 @@
     </row>
     <row r="342">
       <c r="A342" s="15" t="n">
-        <v>46312</v>
+        <v>46311</v>
       </c>
       <c r="B342" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C342" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Cyrex Store (web)</t>
         </is>
       </c>
       <c r="E342" s="11" t="n">
-        <v>1850</v>
+        <v>2218</v>
       </c>
       <c r="F342" s="5" t="inlineStr">
         <is>
@@ -22877,7 +23064,7 @@
       </c>
       <c r="G342" s="5" t="inlineStr">
         <is>
-          <t>Kingston NV3 1TB (estado sin dato)</t>
+          <t>nuevo OEM (web: es el i5-13400F, sin gráficos; USD 188 a 11,80; solo referencia; no cuenta)</t>
         </is>
       </c>
       <c r="H342" s="6" t="inlineStr">
@@ -22888,7 +23075,7 @@
     </row>
     <row r="343">
       <c r="A343" s="15" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
@@ -22897,16 +23084,16 @@
       </c>
       <c r="C343" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 2TB</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>Shopping PC (catálogo PDF)</t>
+          <t>Punto Tecnológico (WhatsApp)</t>
         </is>
       </c>
       <c r="E343" s="11" t="n">
-        <v>2726</v>
+        <v>2850</v>
       </c>
       <c r="F343" s="5" t="inlineStr">
         <is>
@@ -22915,32 +23102,32 @@
       </c>
       <c r="G343" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: otro modelo (Crucial BX500 2TB es SATA, no NVMe; nuevo; lista mayorista USD 230 × 11,85 del 12/10, sin factura; 35 en stock; garantía solo de prueba; solo referencia)</t>
+          <t>nuevo OEM, garantía 6 meses (cotización por WhatsApp)</t>
         </is>
       </c>
       <c r="H343" s="2" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="15" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B344" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C344" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 5600</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Punto Tecnológico (WhatsApp)</t>
         </is>
       </c>
       <c r="E344" s="11" t="n">
-        <v>1800</v>
+        <v>5960</v>
       </c>
       <c r="F344" s="5" t="inlineStr">
         <is>
@@ -22949,36 +23136,32 @@
       </c>
       <c r="G344" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: otro modelo (es 5600X, solo procesador, recién publicado)</t>
-        </is>
-      </c>
-      <c r="H344" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>otra marca (Nox Tuf 32GB 2x16, velocidad sin dato); solo referencia; no cuenta</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="15" t="n">
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="B345" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C345" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-13400</t>
+          <t>Ryzen 5 7600</t>
         </is>
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Gamer Store Cbba (WhatsApp)</t>
         </is>
       </c>
       <c r="E345" s="11" t="n">
-        <v>1800</v>
+        <v>2067</v>
       </c>
       <c r="F345" s="5" t="inlineStr">
         <is>
@@ -22987,18 +23170,14 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: otro modelo (i5-13400F, precio fijo)</t>
-        </is>
-      </c>
-      <c r="H345" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>nuevo (es el 7600X; USD 175 a 11,81; solo referencia; no cuenta)</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="15" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B346" s="5" t="inlineStr">
         <is>
@@ -23007,7 +23186,7 @@
       </c>
       <c r="C346" s="5" t="inlineStr">
         <is>
-          <t>Intel Core i5-14400F</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
@@ -23016,7 +23195,7 @@
         </is>
       </c>
       <c r="E346" s="11" t="n">
-        <v>2600</v>
+        <v>1230</v>
       </c>
       <c r="F346" s="5" t="inlineStr">
         <is>
@@ -23025,7 +23204,7 @@
       </c>
       <c r="G346" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: otro modelo (i5-14400 sin F)</t>
+          <t>nuevo (antes Bs 1.730; marca sin dato)</t>
         </is>
       </c>
       <c r="H346" s="6" t="inlineStr">
@@ -23036,7 +23215,7 @@
     </row>
     <row r="347">
       <c r="A347" s="15" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B347" s="5" t="inlineStr">
         <is>
@@ -23045,7 +23224,7 @@
       </c>
       <c r="C347" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
+          <t>SSD NVMe 1TB</t>
         </is>
       </c>
       <c r="D347" s="5" t="inlineStr">
@@ -23054,7 +23233,7 @@
         </is>
       </c>
       <c r="E347" s="11" t="n">
-        <v>5800</v>
+        <v>1500</v>
       </c>
       <c r="F347" s="5" t="inlineStr">
         <is>
@@ -23063,7 +23242,7 @@
       </c>
       <c r="G347" s="5" t="inlineStr">
         <is>
-          <t>Corsair Vengeance RGB 2x16 6000 MHz (estado sin dato)</t>
+          <t>sin dato de estado ni marca (recién publicado)</t>
         </is>
       </c>
       <c r="H347" s="6" t="inlineStr">
@@ -23074,7 +23253,7 @@
     </row>
     <row r="348">
       <c r="A348" s="15" t="n">
-        <v>46314</v>
+        <v>46312</v>
       </c>
       <c r="B348" s="5" t="inlineStr">
         <is>
@@ -23092,7 +23271,7 @@
         </is>
       </c>
       <c r="E348" s="11" t="n">
-        <v>2500</v>
+        <v>1850</v>
       </c>
       <c r="F348" s="5" t="inlineStr">
         <is>
@@ -23101,7 +23280,7 @@
       </c>
       <c r="G348" s="5" t="inlineStr">
         <is>
-          <t>Lexar NM790 1TB con disipador (estado sin dato)</t>
+          <t>Kingston NV3 1TB (estado sin dato)</t>
         </is>
       </c>
       <c r="H348" s="6" t="inlineStr">
@@ -23112,25 +23291,25 @@
     </row>
     <row r="349">
       <c r="A349" s="15" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="B349" s="5" t="inlineStr">
         <is>
-          <t>Marketplace</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="C349" s="5" t="inlineStr">
         <is>
-          <t>SSD NVMe 1TB</t>
+          <t>SSD NVMe 2TB</t>
         </is>
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>Marketplace Cochabamba (particular)</t>
+          <t>Shopping PC (catálogo PDF)</t>
         </is>
       </c>
       <c r="E349" s="11" t="n">
-        <v>2050</v>
+        <v>2726</v>
       </c>
       <c r="F349" s="5" t="inlineStr">
         <is>
@@ -23139,14 +23318,10 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>WD Green SN3000 1TB (estado sin dato)</t>
-        </is>
-      </c>
-      <c r="H349" s="6" t="inlineStr">
-        <is>
-          <t>ver</t>
-        </is>
-      </c>
+          <t>no cuenta: otro modelo (Crucial BX500 2TB es SATA, no NVMe; nuevo; lista mayorista USD 230 × 11,85 del 12/10, sin factura; 35 en stock; garantía solo de prueba; solo referencia)</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="15" t="n">
@@ -23154,21 +23329,21 @@
       </c>
       <c r="B350" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C350" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 5 7600</t>
+          <t>Ryzen 5 5600</t>
         </is>
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E350" s="11" t="n">
-        <v>2800</v>
+        <v>1800</v>
       </c>
       <c r="F350" s="5" t="inlineStr">
         <is>
@@ -23177,10 +23352,14 @@
       </c>
       <c r="G350" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM (reconfirmado 16:09)</t>
-        </is>
-      </c>
-      <c r="H350" s="2" t="n"/>
+          <t>no cuenta: otro modelo (es 5600X, solo procesador, recién publicado)</t>
+        </is>
+      </c>
+      <c r="H350" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="15" t="n">
@@ -23188,21 +23367,21 @@
       </c>
       <c r="B351" s="5" t="inlineStr">
         <is>
-          <t>Tienda</t>
+          <t>Marketplace</t>
         </is>
       </c>
       <c r="C351" s="5" t="inlineStr">
         <is>
-          <t>Intel Core Ultra 7 265K</t>
+          <t>Intel Core i5-13400</t>
         </is>
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>OverCity (WhatsApp)</t>
+          <t>Marketplace Cochabamba (particular)</t>
         </is>
       </c>
       <c r="E351" s="11" t="n">
-        <v>4100</v>
+        <v>1800</v>
       </c>
       <c r="F351" s="5" t="inlineStr">
         <is>
@@ -23211,14 +23390,18 @@
       </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
-          <t>nuevo OEM</t>
-        </is>
-      </c>
-      <c r="H351" s="2" t="n"/>
+          <t>no cuenta: otro modelo (i5-13400F, precio fijo)</t>
+        </is>
+      </c>
+      <c r="H351" s="6" t="inlineStr">
+        <is>
+          <t>ver</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="15" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B352" s="5" t="inlineStr">
         <is>
@@ -23227,7 +23410,7 @@
       </c>
       <c r="C352" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Intel Core i5-14400F</t>
         </is>
       </c>
       <c r="D352" s="5" t="inlineStr">
@@ -23236,7 +23419,7 @@
         </is>
       </c>
       <c r="E352" s="11" t="n">
-        <v>5190</v>
+        <v>2600</v>
       </c>
       <c r="F352" s="5" t="inlineStr">
         <is>
@@ -23245,7 +23428,7 @@
       </c>
       <c r="G352" s="5" t="inlineStr">
         <is>
-          <t>no cuenta: anuncio viejo (nuevo; publicado hace 13 semanas)</t>
+          <t>no cuenta: otro modelo (i5-14400 sin F)</t>
         </is>
       </c>
       <c r="H352" s="6" t="inlineStr">
@@ -23256,7 +23439,7 @@
     </row>
     <row r="353">
       <c r="A353" s="15" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
@@ -23265,7 +23448,7 @@
       </c>
       <c r="C353" s="5" t="inlineStr">
         <is>
-          <t>Ryzen 7 7800X3D</t>
+          <t>Corsair Vengeance RGB DDR5 32GB (2x16) 6000</t>
         </is>
       </c>
       <c r="D353" s="5" t="inlineStr">
@@ -23274,7 +23457,7 @@
         </is>
       </c>
       <c r="E353" s="11" t="n">
-        <v>5390</v>
+        <v>5800</v>
       </c>
       <c r="F353" s="5" t="inlineStr">
         <is>
@@ -23283,7 +23466,7 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>nuevo (anuncio 'El mejor para Gaming'; disponible)</t>
+          <t>Corsair Vengeance RGB 2x16 6000 MHz (estado sin dato)</t>
         </is>
       </c>
       <c r="H353" s="6" t="inlineStr">
@@ -23294,7 +23477,7 @@
     </row>
     <row r="354">
       <c r="A354" s="15" t="n">
-        <v>46315</v>
+        <v>46314</v>
       </c>
       <c r="B354" s="5" t="inlineStr">
         <is>
@@ -23303,16 +23486,16 @@
       </c>
       <c r="C354" s="5" t="inlineStr">
         <is>
-     